--- a/jogos_2025-08-03.xlsx
+++ b/jogos_2025-08-03.xlsx
@@ -262,39 +262,39 @@
     <t>Russia Russian Premier League</t>
   </si>
   <si>
+    <t>China Chinese Super League</t>
+  </si>
+  <si>
     <t>China China League One</t>
   </si>
   <si>
     <t>Belarus Vysheyshaya Liga</t>
   </si>
   <si>
-    <t>China Chinese Super League</t>
-  </si>
-  <si>
     <t>England EFL League One</t>
   </si>
   <si>
+    <t>Germany 2. Bundesliga</t>
+  </si>
+  <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
-    <t>Germany 2. Bundesliga</t>
-  </si>
-  <si>
     <t>Germany 3. Liga</t>
   </si>
   <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
+    <t>Switzerland Challenge League</t>
+  </si>
+  <si>
     <t>Denmark Superliga</t>
   </si>
   <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
     <t>Switzerland Super League</t>
   </si>
   <si>
-    <t>Switzerland Challenge League</t>
-  </si>
-  <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
@@ -307,69 +307,69 @@
     <t>Finland Veikkausliiga</t>
   </si>
   <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
+    <t>Czech Republic First League</t>
+  </si>
+  <si>
     <t>Scotland Premiership</t>
   </si>
   <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
-    <t>Czech Republic First League</t>
-  </si>
-  <si>
     <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
+    <t>Luxembourg National Division</t>
+  </si>
+  <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
-    <t>Luxembourg National Division</t>
+    <t>Uzbekistan Uzbekistan Super League</t>
   </si>
   <si>
     <t>Montenegro Montenegrin First League</t>
   </si>
   <si>
+    <t>Austria Bundesliga</t>
+  </si>
+  <si>
     <t>Slovakia Super Liga</t>
   </si>
   <si>
-    <t>Uzbekistan Uzbekistan Super League</t>
-  </si>
-  <si>
-    <t>Austria Bundesliga</t>
+    <t>Romania Liga I</t>
+  </si>
+  <si>
+    <t>Hungary NB II</t>
   </si>
   <si>
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
-    <t>Hungary NB II</t>
-  </si>
-  <si>
-    <t>Romania Liga I</t>
-  </si>
-  <si>
     <t>Hungary NB I</t>
   </si>
   <si>
+    <t>Chile Primera División</t>
+  </si>
+  <si>
     <t>USA NWSL</t>
   </si>
   <si>
-    <t>Chile Primera División</t>
-  </si>
-  <si>
     <t>Serbia SuperLiga</t>
   </si>
   <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
+    <t>Brazil Serie B</t>
+  </si>
+  <si>
     <t>Brazil Serie A</t>
   </si>
   <si>
-    <t>Brazil Serie B</t>
-  </si>
-  <si>
     <t>Canada Canadian Premier League</t>
   </si>
   <si>
@@ -382,24 +382,24 @@
     <t>Wollongong Wolves</t>
   </si>
   <si>
+    <t>Central Coast II</t>
+  </si>
+  <si>
+    <t>Sydney United</t>
+  </si>
+  <si>
     <t>Blacktown City</t>
   </si>
   <si>
-    <t>Central Coast II</t>
-  </si>
-  <si>
-    <t>Sydney United</t>
-  </si>
-  <si>
     <t>SKA Khabarovsk</t>
   </si>
   <si>
+    <t>Viktoria Žižkov</t>
+  </si>
+  <si>
     <t>Slavia Praha II</t>
   </si>
   <si>
-    <t>Viktoria Žižkov</t>
-  </si>
-  <si>
     <t>WSPG Wels</t>
   </si>
   <si>
@@ -412,363 +412,363 @@
     <t>Akron</t>
   </si>
   <si>
+    <t>Dalian Zhixing</t>
+  </si>
+  <si>
     <t>Suzhou Dongwu</t>
   </si>
   <si>
     <t>Molodechno-DYuSSh 4</t>
   </si>
   <si>
-    <t>Dalian Zhixing</t>
-  </si>
-  <si>
     <t>Stockport County</t>
   </si>
   <si>
+    <t>Dongguan United</t>
+  </si>
+  <si>
+    <t>Greuther Fürth</t>
+  </si>
+  <si>
     <t>KRC Genk</t>
   </si>
   <si>
     <t>Magdeburg</t>
   </si>
   <si>
-    <t>Dongguan United</t>
+    <t>Hannover 96</t>
+  </si>
+  <si>
+    <t>Qingdao Red Lions</t>
   </si>
   <si>
     <t>Erzgebirge Aue</t>
   </si>
   <si>
-    <t>Greuther Fürth</t>
-  </si>
-  <si>
-    <t>Hannover 96</t>
-  </si>
-  <si>
-    <t>Qingdao Red Lions</t>
+    <t>Beijing Guoan</t>
   </si>
   <si>
     <t>Wuhan Three Towns</t>
   </si>
   <si>
-    <t>Beijing Guoan</t>
+    <t>Spartak Kostroma</t>
+  </si>
+  <si>
+    <t>Djurgården</t>
+  </si>
+  <si>
+    <t>Yverdon Sport</t>
+  </si>
+  <si>
+    <t>Häcken</t>
+  </si>
+  <si>
+    <t>SønderjyskE</t>
   </si>
   <si>
     <t>Sichuan Jiuniu</t>
   </si>
   <si>
-    <t>Spartak Kostroma</t>
-  </si>
-  <si>
-    <t>SønderjyskE</t>
-  </si>
-  <si>
-    <t>Djurgården</t>
+    <t>Randers</t>
   </si>
   <si>
     <t>Thun</t>
   </si>
   <si>
-    <t>Randers</t>
-  </si>
-  <si>
-    <t>Häcken</t>
-  </si>
-  <si>
-    <t>Yverdon Sport</t>
-  </si>
-  <si>
     <t>Baník Ostrava II</t>
   </si>
   <si>
     <t>HamKam</t>
   </si>
   <si>
+    <t>Epitsentr Dunayivtsi</t>
+  </si>
+  <si>
     <t>Śląsk Wrocław</t>
   </si>
   <si>
-    <t>Epitsentr Dunayivtsi</t>
+    <t>Baltika</t>
   </si>
   <si>
     <t>Cracovia Kraków</t>
   </si>
   <si>
-    <t>Baltika</t>
-  </si>
-  <si>
     <t>SJK</t>
   </si>
   <si>
+    <t>Sogndal</t>
+  </si>
+  <si>
+    <t>Slovácko</t>
+  </si>
+  <si>
     <t>Falkirk</t>
   </si>
   <si>
-    <t>Sogndal</t>
-  </si>
-  <si>
     <t>Landskrona</t>
   </si>
   <si>
-    <t>Slovácko</t>
-  </si>
-  <si>
     <t>Suduroy</t>
   </si>
   <si>
+    <t>Swift Hesperange</t>
+  </si>
+  <si>
+    <t>F91 Dudelange</t>
+  </si>
+  <si>
+    <t>Rodange</t>
+  </si>
+  <si>
+    <t>Jeunesse Canach</t>
+  </si>
+  <si>
+    <t>Mondorf-les-Bains</t>
+  </si>
+  <si>
+    <t>Differdange 03</t>
+  </si>
+  <si>
+    <t>Hostert</t>
+  </si>
+  <si>
     <t>Harju Jalgpallikool</t>
   </si>
   <si>
-    <t>Rodange</t>
-  </si>
-  <si>
     <t>Dundee</t>
   </si>
   <si>
+    <t>Jeunesse d'Esch</t>
+  </si>
+  <si>
+    <t>AGF</t>
+  </si>
+  <si>
     <t>Cercle Brugge</t>
   </si>
   <si>
-    <t>F91 Dudelange</t>
-  </si>
-  <si>
-    <t>Swift Hesperange</t>
-  </si>
-  <si>
-    <t>Jeunesse d'Esch</t>
-  </si>
-  <si>
-    <t>AGF</t>
-  </si>
-  <si>
-    <t>Differdange 03</t>
-  </si>
-  <si>
     <t>EB - Streymur</t>
   </si>
   <si>
-    <t>Hostert</t>
-  </si>
-  <si>
-    <t>Jeunesse Canach</t>
-  </si>
-  <si>
-    <t>Mondorf-les-Bains</t>
-  </si>
-  <si>
     <t>Luzern</t>
   </si>
   <si>
     <t>Viktoria Köln</t>
   </si>
   <si>
+    <t>Sirius</t>
+  </si>
+  <si>
     <t>Étoile Carouge</t>
   </si>
   <si>
-    <t>Sirius</t>
+    <t>Vålerenga</t>
+  </si>
+  <si>
+    <t>Dukla Praha</t>
+  </si>
+  <si>
+    <t>Zenit</t>
+  </si>
+  <si>
+    <t>Shortan</t>
+  </si>
+  <si>
+    <t>Rubin Kazan</t>
+  </si>
+  <si>
+    <t>Karpaty</t>
+  </si>
+  <si>
+    <t>Vlašim</t>
+  </si>
+  <si>
+    <t>Torpedo BelAZ</t>
+  </si>
+  <si>
+    <t>Dečić</t>
+  </si>
+  <si>
+    <t>Grazer AK</t>
+  </si>
+  <si>
+    <t>Pogoń Siedlce</t>
+  </si>
+  <si>
+    <t>FK Jezero Plav</t>
   </si>
   <si>
     <t>Arsenal Tivat</t>
   </si>
   <si>
-    <t>Vålerenga</t>
+    <t>Rapid Wien</t>
+  </si>
+  <si>
+    <t>Molde</t>
+  </si>
+  <si>
+    <t>Strømsgodset</t>
+  </si>
+  <si>
+    <t>Sutjeska</t>
+  </si>
+  <si>
+    <t>Trenčín</t>
   </si>
   <si>
     <t>KFUM</t>
   </si>
   <si>
-    <t>Trenčín</t>
-  </si>
-  <si>
-    <t>Molde</t>
-  </si>
-  <si>
     <t>Petrovac</t>
   </si>
   <si>
-    <t>Sutjeska</t>
-  </si>
-  <si>
-    <t>Dečić</t>
-  </si>
-  <si>
-    <t>FK Jezero Plav</t>
-  </si>
-  <si>
-    <t>Strømsgodset</t>
-  </si>
-  <si>
-    <t>Shortan</t>
-  </si>
-  <si>
-    <t>Dukla Praha</t>
-  </si>
-  <si>
-    <t>Karpaty</t>
-  </si>
-  <si>
-    <t>Torpedo BelAZ</t>
-  </si>
-  <si>
-    <t>Rubin Kazan</t>
-  </si>
-  <si>
-    <t>Vlašim</t>
-  </si>
-  <si>
-    <t>Pogoń Siedlce</t>
-  </si>
-  <si>
-    <t>Grazer AK</t>
-  </si>
-  <si>
-    <t>Rapid Wien</t>
-  </si>
-  <si>
-    <t>Zenit</t>
+    <t>Radomiak Radom</t>
+  </si>
+  <si>
+    <t>Hermannstadt</t>
   </si>
   <si>
     <t>Motor Lublin</t>
   </si>
   <si>
+    <t>Celtic</t>
+  </si>
+  <si>
+    <t>Karcag SE</t>
+  </si>
+  <si>
     <t>Maribor</t>
   </si>
   <si>
-    <t>Radomiak Radom</t>
-  </si>
-  <si>
     <t>Szentlőrinc SE</t>
   </si>
   <si>
-    <t>Hermannstadt</t>
-  </si>
-  <si>
-    <t>Karcag SE</t>
-  </si>
-  <si>
-    <t>Celtic</t>
+    <t>Várda SE</t>
   </si>
   <si>
     <t>Puskás</t>
   </si>
   <si>
-    <t>Várda SE</t>
-  </si>
-  <si>
     <t>Brøndby</t>
   </si>
   <si>
+    <t>FK Chernomorets Novorossiysk</t>
+  </si>
+  <si>
+    <t>Fakel</t>
+  </si>
+  <si>
     <t>Tammeka</t>
   </si>
   <si>
-    <t>FK Chernomorets Novorossiysk</t>
-  </si>
-  <si>
-    <t>Fakel</t>
-  </si>
-  <si>
     <t>Vysočina Jihlava</t>
   </si>
   <si>
     <t>B68</t>
   </si>
   <si>
+    <t>O'Higgins</t>
+  </si>
+  <si>
+    <t>Washington Spirit</t>
+  </si>
+  <si>
     <t>Union Saint-Gilloise</t>
   </si>
   <si>
-    <t>Washington Spirit</t>
-  </si>
-  <si>
-    <t>O'Higgins</t>
+    <t>Železničar Pančevo</t>
+  </si>
+  <si>
+    <t>MKK-Dnepr</t>
   </si>
   <si>
     <t>Žilina</t>
   </si>
   <si>
-    <t>Železničar Pančevo</t>
-  </si>
-  <si>
-    <t>MKK-Dnepr</t>
-  </si>
-  <si>
     <t>Békéscsaba</t>
   </si>
   <si>
+    <t>Honvéd W</t>
+  </si>
+  <si>
+    <t>Csákvári TK</t>
+  </si>
+  <si>
+    <t>Tiszakécske</t>
+  </si>
+  <si>
     <t>Ajka</t>
   </si>
   <si>
     <t>Sporting KC II</t>
   </si>
   <si>
-    <t>Csákvári TK</t>
-  </si>
-  <si>
-    <t>Honvéd W</t>
-  </si>
-  <si>
-    <t>Tiszakécske</t>
-  </si>
-  <si>
     <t>Sporting Charleroi</t>
   </si>
   <si>
+    <t>Makhachkala</t>
+  </si>
+  <si>
     <t>Górnik Łęczna</t>
   </si>
   <si>
     <t>Wehen Wiesbaden</t>
   </si>
   <si>
-    <t>Makhachkala</t>
+    <t>Győri ETO</t>
   </si>
   <si>
     <t>Pardubice</t>
   </si>
   <si>
-    <t>Győri ETO</t>
-  </si>
-  <si>
     <t>Chicago Fire II</t>
   </si>
   <si>
+    <t>Olimpija</t>
+  </si>
+  <si>
     <t>Legia Warszawa</t>
   </si>
   <si>
-    <t>Olimpija</t>
-  </si>
-  <si>
     <t>CFR Cluj</t>
   </si>
   <si>
+    <t>Chapecoense</t>
+  </si>
+  <si>
+    <t>Botafogo</t>
+  </si>
+  <si>
     <t>Partizan</t>
   </si>
   <si>
+    <t>Colo-Colo</t>
+  </si>
+  <si>
     <t>Corinthians</t>
   </si>
   <si>
-    <t>Botafogo</t>
-  </si>
-  <si>
-    <t>Colo-Colo</t>
-  </si>
-  <si>
-    <t>Chapecoense</t>
-  </si>
-  <si>
     <t>Atlético Ottawa</t>
   </si>
   <si>
+    <t>Ceará</t>
+  </si>
+  <si>
+    <t>Atlético PR</t>
+  </si>
+  <si>
     <t>Ñublense</t>
   </si>
   <si>
-    <t>Atlético PR</t>
-  </si>
-  <si>
     <t>Atlético Mineiro</t>
   </si>
   <si>
-    <t>Ceará</t>
+    <t>Orlando Pride</t>
   </si>
   <si>
     <t>Philadelphia Union II</t>
   </si>
   <si>
-    <t>Orlando Pride</t>
-  </si>
-  <si>
     <t>Vitória</t>
   </si>
   <si>
@@ -787,24 +787,24 @@
     <t>Sydney II</t>
   </si>
   <si>
+    <t>Marconi Stallions</t>
+  </si>
+  <si>
+    <t>St. George Saints</t>
+  </si>
+  <si>
     <t>Mt Druitt Town</t>
   </si>
   <si>
-    <t>Marconi Stallions</t>
-  </si>
-  <si>
-    <t>St. George Saints</t>
-  </si>
-  <si>
     <t>Torpedo Moskva</t>
   </si>
   <si>
+    <t>Prostějov</t>
+  </si>
+  <si>
     <t>České Budějovice</t>
   </si>
   <si>
-    <t>Prostějov</t>
-  </si>
-  <si>
     <t>Floridsdorfer AC</t>
   </si>
   <si>
@@ -817,361 +817,361 @@
     <t>Spartak Moskva</t>
   </si>
   <si>
+    <t>Qingdao Jonoon</t>
+  </si>
+  <si>
     <t>Dalian Huayi</t>
   </si>
   <si>
     <t>Neman Grodno</t>
   </si>
   <si>
-    <t>Qingdao Jonoon</t>
-  </si>
-  <si>
     <t>Bolton Wanderers</t>
   </si>
   <si>
+    <t>Nantong Zhiyun</t>
+  </si>
+  <si>
+    <t>Dynamo Dresden</t>
+  </si>
+  <si>
     <t>Royal Antwerp FC</t>
   </si>
   <si>
     <t>Eintracht Braunschweig</t>
   </si>
   <si>
-    <t>Nantong Zhiyun</t>
+    <t>Kaiserslautern</t>
+  </si>
+  <si>
+    <t>Heilongjiang Lava Spring</t>
   </si>
   <si>
     <t>Hansa Rostock</t>
   </si>
   <si>
-    <t>Dynamo Dresden</t>
-  </si>
-  <si>
-    <t>Kaiserslautern</t>
-  </si>
-  <si>
-    <t>Heilongjiang Lava Spring</t>
+    <t>Tianjin Teda</t>
   </si>
   <si>
     <t>Changchun Yatai</t>
   </si>
   <si>
-    <t>Tianjin Teda</t>
+    <t>Neftekhimik</t>
+  </si>
+  <si>
+    <t>Halmstad</t>
+  </si>
+  <si>
+    <t>Stade Lausanne-Ouchy</t>
+  </si>
+  <si>
+    <t>Elfsborg</t>
+  </si>
+  <si>
+    <t>Nordsjælland</t>
   </si>
   <si>
     <t>Zhejiang FC</t>
   </si>
   <si>
-    <t>Neftekhimik</t>
-  </si>
-  <si>
-    <t>Nordsjælland</t>
-  </si>
-  <si>
-    <t>Halmstad</t>
+    <t>Silkeborg</t>
   </si>
   <si>
     <t>Lausanne Sport</t>
   </si>
   <si>
-    <t>Silkeborg</t>
-  </si>
-  <si>
-    <t>Elfsborg</t>
-  </si>
-  <si>
-    <t>Stade Lausanne-Ouchy</t>
-  </si>
-  <si>
     <t>Líšeň</t>
   </si>
   <si>
     <t>FK Bodo - Glimt</t>
   </si>
   <si>
+    <t>Shakhtar Donetsk</t>
+  </si>
+  <si>
     <t>Ruch Chorzów</t>
   </si>
   <si>
-    <t>Shakhtar Donetsk</t>
+    <t>Orenburg</t>
   </si>
   <si>
     <t>Lechia Gdańsk</t>
   </si>
   <si>
-    <t>Orenburg</t>
-  </si>
-  <si>
     <t>KTP</t>
   </si>
   <si>
+    <t>Skeid</t>
+  </si>
+  <si>
+    <t>Slavia Praha</t>
+  </si>
+  <si>
     <t>Dundee United</t>
   </si>
   <si>
-    <t>Skeid</t>
-  </si>
-  <si>
     <t>Västerås SK</t>
   </si>
   <si>
-    <t>Slavia Praha</t>
-  </si>
-  <si>
     <t>HB</t>
   </si>
   <si>
+    <t>UT Pétange</t>
+  </si>
+  <si>
+    <t>Progrès Niederkorn</t>
+  </si>
+  <si>
+    <t>Racing</t>
+  </si>
+  <si>
+    <t>Mamer</t>
+  </si>
+  <si>
+    <t>UNA Strassen</t>
+  </si>
+  <si>
+    <t>Atert Bissen</t>
+  </si>
+  <si>
+    <t>Victoria Rosport</t>
+  </si>
+  <si>
     <t>Paide</t>
   </si>
   <si>
-    <t>Racing</t>
-  </si>
-  <si>
     <t>Hibernian</t>
   </si>
   <si>
+    <t>UN Käerjéng</t>
+  </si>
+  <si>
+    <t>Midtjylland</t>
+  </si>
+  <si>
     <t>RSC Anderlecht</t>
   </si>
   <si>
-    <t>Progrès Niederkorn</t>
-  </si>
-  <si>
-    <t>UT Pétange</t>
-  </si>
-  <si>
-    <t>UN Käerjéng</t>
-  </si>
-  <si>
-    <t>Midtjylland</t>
-  </si>
-  <si>
-    <t>Atert Bissen</t>
-  </si>
-  <si>
     <t>KÍ</t>
   </si>
   <si>
-    <t>Victoria Rosport</t>
-  </si>
-  <si>
-    <t>Mamer</t>
-  </si>
-  <si>
-    <t>UNA Strassen</t>
-  </si>
-  <si>
     <t>Zürich</t>
   </si>
   <si>
     <t>Schweinfurt</t>
   </si>
   <si>
+    <t>Öster</t>
+  </si>
+  <si>
     <t>Vaduz</t>
   </si>
   <si>
-    <t>Öster</t>
+    <t>Sandefjord</t>
+  </si>
+  <si>
+    <t>Baník Ostrava</t>
+  </si>
+  <si>
+    <t>CSKA Moskva</t>
+  </si>
+  <si>
+    <t>Xorazm</t>
+  </si>
+  <si>
+    <t>FK Sochi</t>
+  </si>
+  <si>
+    <t>Polessya</t>
+  </si>
+  <si>
+    <t>Hanácká</t>
+  </si>
+  <si>
+    <t>Gomel</t>
+  </si>
+  <si>
+    <t>Mladost DG</t>
+  </si>
+  <si>
+    <t>Austria Wien</t>
+  </si>
+  <si>
+    <t>Odra Opole</t>
+  </si>
+  <si>
+    <t>Budućnost</t>
   </si>
   <si>
     <t>Jedinstvo</t>
   </si>
   <si>
-    <t>Sandefjord</t>
+    <t>Blau-Weiß Linz</t>
+  </si>
+  <si>
+    <t>Bryne</t>
+  </si>
+  <si>
+    <t>Haugesund</t>
+  </si>
+  <si>
+    <t>Mornar</t>
+  </si>
+  <si>
+    <t>Spartak Trnava</t>
   </si>
   <si>
     <t>Rosenborg</t>
   </si>
   <si>
-    <t>Spartak Trnava</t>
-  </si>
-  <si>
-    <t>Bryne</t>
-  </si>
-  <si>
     <t>Bokelj</t>
   </si>
   <si>
-    <t>Mornar</t>
-  </si>
-  <si>
-    <t>Mladost DG</t>
-  </si>
-  <si>
-    <t>Budućnost</t>
-  </si>
-  <si>
-    <t>Haugesund</t>
-  </si>
-  <si>
-    <t>Xorazm</t>
-  </si>
-  <si>
-    <t>Baník Ostrava</t>
-  </si>
-  <si>
-    <t>Polessya</t>
-  </si>
-  <si>
-    <t>Gomel</t>
-  </si>
-  <si>
-    <t>FK Sochi</t>
-  </si>
-  <si>
-    <t>Hanácká</t>
-  </si>
-  <si>
-    <t>Odra Opole</t>
-  </si>
-  <si>
-    <t>Austria Wien</t>
-  </si>
-  <si>
-    <t>Blau-Weiß Linz</t>
-  </si>
-  <si>
-    <t>CSKA Moskva</t>
+    <t>Raków Częstochowa</t>
+  </si>
+  <si>
+    <t>Universitatea Cluj</t>
   </si>
   <si>
     <t>Jagiellonia Białystok</t>
   </si>
   <si>
+    <t>St. Mirren</t>
+  </si>
+  <si>
+    <t>Soroksár SC</t>
+  </si>
+  <si>
     <t>Koper</t>
   </si>
   <si>
-    <t>Raków Częstochowa</t>
-  </si>
-  <si>
     <t>Kozármisleny</t>
   </si>
   <si>
-    <t>Universitatea Cluj</t>
-  </si>
-  <si>
-    <t>Soroksár SC</t>
-  </si>
-  <si>
-    <t>St. Mirren</t>
+    <t>Paksi SE</t>
   </si>
   <si>
     <t>Nyíregyháza Spartacus</t>
   </si>
   <si>
-    <t>Paksi SE</t>
-  </si>
-  <si>
     <t>Viborg</t>
   </si>
   <si>
+    <t>Arsenal Tula</t>
+  </si>
+  <si>
+    <t>Sokol Saratov</t>
+  </si>
+  <si>
     <t>Nõmme Kalju</t>
   </si>
   <si>
-    <t>Arsenal Tula</t>
-  </si>
-  <si>
-    <t>Sokol Saratov</t>
-  </si>
-  <si>
     <t>Vyškov</t>
   </si>
   <si>
     <t>NSÍ</t>
   </si>
   <si>
+    <t>Unión La Calera</t>
+  </si>
+  <si>
+    <t>Portland Thorns</t>
+  </si>
+  <si>
     <t>OH Leuven</t>
   </si>
   <si>
-    <t>Portland Thorns</t>
-  </si>
-  <si>
-    <t>Unión La Calera</t>
+    <t>Napredak</t>
+  </si>
+  <si>
+    <t>Slutsk</t>
   </si>
   <si>
     <t>Tatran Prešov</t>
   </si>
   <si>
-    <t>Napredak</t>
-  </si>
-  <si>
-    <t>Slutsk</t>
-  </si>
-  <si>
     <t>Szeged 2011</t>
   </si>
   <si>
+    <t>Budafoki MTE</t>
+  </si>
+  <si>
+    <t>BVSC</t>
+  </si>
+  <si>
+    <t>Mezőkövesd-Zsóry</t>
+  </si>
+  <si>
     <t>Videoton</t>
   </si>
   <si>
     <t>Austin II</t>
   </si>
   <si>
-    <t>BVSC</t>
-  </si>
-  <si>
-    <t>Budafoki MTE</t>
-  </si>
-  <si>
-    <t>Mezőkövesd-Zsóry</t>
-  </si>
-  <si>
     <t>Sint-Truiden</t>
   </si>
   <si>
+    <t>Akhmat Grozny</t>
+  </si>
+  <si>
     <t>Puszcza Niepołomice</t>
   </si>
   <si>
     <t>Ulm</t>
   </si>
   <si>
-    <t>Akhmat Grozny</t>
+    <t>Újpest</t>
   </si>
   <si>
     <t>Sparta Praha</t>
   </si>
   <si>
-    <t>Újpest</t>
-  </si>
-  <si>
     <t>Columbus Crew II</t>
   </si>
   <si>
+    <t>Celje</t>
+  </si>
+  <si>
     <t>Arka Gdynia</t>
   </si>
   <si>
-    <t>Celje</t>
-  </si>
-  <si>
     <t>CS U Craiova</t>
   </si>
   <si>
+    <t>CRB</t>
+  </si>
+  <si>
+    <t>Cruzeiro</t>
+  </si>
+  <si>
     <t>Radnički Kragujevac</t>
   </si>
   <si>
+    <t>Huachipato</t>
+  </si>
+  <si>
     <t>Fortaleza</t>
   </si>
   <si>
-    <t>Cruzeiro</t>
-  </si>
-  <si>
-    <t>Huachipato</t>
-  </si>
-  <si>
-    <t>CRB</t>
-  </si>
-  <si>
     <t>York9 FC</t>
   </si>
   <si>
+    <t>Flamengo</t>
+  </si>
+  <si>
+    <t>Paysandu</t>
+  </si>
+  <si>
     <t>Everton</t>
   </si>
   <si>
-    <t>Paysandu</t>
-  </si>
-  <si>
     <t>Bragantino</t>
   </si>
   <si>
-    <t>Flamengo</t>
+    <t>Utah Royals</t>
   </si>
   <si>
     <t>FC Cincinnati II</t>
-  </si>
-  <si>
-    <t>Utah Royals</t>
   </si>
   <si>
     <t>Palmeiras</t>
@@ -3423,10 +3423,10 @@
         <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E17" t="s">
         <v>136</v>
@@ -3539,7 +3539,7 @@
         <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D18" t="s">
         <v>120</v>
@@ -3566,13 +3566,13 @@
         <v>391</v>
       </c>
       <c r="L18">
-        <v>1.65</v>
+        <v>2.26</v>
       </c>
       <c r="M18">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N18">
-        <v>4.8</v>
+        <v>2.95</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -3614,16 +3614,16 @@
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC18">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF18">
         <v>0</v>
@@ -3655,10 +3655,10 @@
         <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D19" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E19" t="s">
         <v>138</v>
@@ -3771,7 +3771,7 @@
         <v>45</v>
       </c>
       <c r="C20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D20" t="s">
         <v>120</v>
@@ -3798,13 +3798,13 @@
         <v>391</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -3846,10 +3846,10 @@
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD20">
         <v>0</v>
@@ -3887,7 +3887,7 @@
         <v>45</v>
       </c>
       <c r="C21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D21" t="s">
         <v>120</v>
@@ -3914,13 +3914,13 @@
         <v>391</v>
       </c>
       <c r="L21">
-        <v>2.26</v>
+        <v>1.71</v>
       </c>
       <c r="M21">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="N21">
-        <v>2.95</v>
+        <v>4.6</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -3962,16 +3962,16 @@
         <v>0</v>
       </c>
       <c r="AB21">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC21">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AD21">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE21">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF21">
         <v>0</v>
@@ -4003,10 +4003,10 @@
         <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E22" t="s">
         <v>141</v>
@@ -4030,13 +4030,13 @@
         <v>391</v>
       </c>
       <c r="L22">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M22">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N22">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -4078,10 +4078,10 @@
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC22">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD22">
         <v>0</v>
@@ -4119,10 +4119,10 @@
         <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D23" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E23" t="s">
         <v>142</v>
@@ -4235,7 +4235,7 @@
         <v>46</v>
       </c>
       <c r="C24" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D24" t="s">
         <v>119</v>
@@ -4351,7 +4351,7 @@
         <v>46</v>
       </c>
       <c r="C25" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D25" t="s">
         <v>119</v>
@@ -4467,10 +4467,10 @@
         <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D26" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E26" t="s">
         <v>145</v>
@@ -4583,10 +4583,10 @@
         <v>47</v>
       </c>
       <c r="C27" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="D27" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E27" t="s">
         <v>146</v>
@@ -4699,7 +4699,7 @@
         <v>47</v>
       </c>
       <c r="C28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D28" t="s">
         <v>120</v>
@@ -4815,7 +4815,7 @@
         <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D29" t="s">
         <v>119</v>
@@ -4958,13 +4958,13 @@
         <v>391</v>
       </c>
       <c r="L30">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M30">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N30">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O30">
         <v>0</v>
@@ -5006,10 +5006,10 @@
         <v>0</v>
       </c>
       <c r="AB30">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC30">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD30">
         <v>0</v>
@@ -5047,10 +5047,10 @@
         <v>47</v>
       </c>
       <c r="C31" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D31" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E31" t="s">
         <v>150</v>
@@ -5163,10 +5163,10 @@
         <v>47</v>
       </c>
       <c r="C32" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D32" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E32" t="s">
         <v>151</v>
@@ -5306,13 +5306,13 @@
         <v>391</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -5354,10 +5354,10 @@
         <v>0</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD33">
         <v>0</v>
@@ -5627,7 +5627,7 @@
         <v>48</v>
       </c>
       <c r="C36" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="D36" t="s">
         <v>120</v>
@@ -5654,13 +5654,13 @@
         <v>391</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="O36">
         <v>0</v>
@@ -5708,10 +5708,10 @@
         <v>0</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF36">
         <v>0</v>
@@ -5743,7 +5743,7 @@
         <v>48</v>
       </c>
       <c r="C37" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="D37" t="s">
         <v>120</v>
@@ -5770,13 +5770,13 @@
         <v>391</v>
       </c>
       <c r="L37">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M37">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="N37">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="O37">
         <v>0</v>
@@ -5824,10 +5824,10 @@
         <v>0</v>
       </c>
       <c r="AD37">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE37">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AF37">
         <v>0</v>
@@ -5859,7 +5859,7 @@
         <v>49</v>
       </c>
       <c r="C38" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="D38" t="s">
         <v>120</v>
@@ -5886,13 +5886,13 @@
         <v>391</v>
       </c>
       <c r="L38">
-        <v>1.94</v>
+        <v>2.09</v>
       </c>
       <c r="M38">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="N38">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="O38">
         <v>0</v>
@@ -5934,10 +5934,10 @@
         <v>0</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD38">
         <v>0</v>
@@ -5975,7 +5975,7 @@
         <v>49</v>
       </c>
       <c r="C39" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="D39" t="s">
         <v>120</v>
@@ -6002,13 +6002,13 @@
         <v>391</v>
       </c>
       <c r="L39">
-        <v>2.09</v>
+        <v>1.94</v>
       </c>
       <c r="M39">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="N39">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="O39">
         <v>0</v>
@@ -6050,10 +6050,10 @@
         <v>0</v>
       </c>
       <c r="AB39">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC39">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD39">
         <v>0</v>
@@ -6210,7 +6210,7 @@
         <v>97</v>
       </c>
       <c r="D41" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E41" t="s">
         <v>160</v>
@@ -6234,13 +6234,13 @@
         <v>391</v>
       </c>
       <c r="L41">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M41">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N41">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O41">
         <v>0</v>
@@ -6282,10 +6282,10 @@
         <v>0</v>
       </c>
       <c r="AB41">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC41">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD41">
         <v>0</v>
@@ -6326,7 +6326,7 @@
         <v>98</v>
       </c>
       <c r="D42" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E42" t="s">
         <v>161</v>
@@ -6442,7 +6442,7 @@
         <v>99</v>
       </c>
       <c r="D43" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E43" t="s">
         <v>162</v>
@@ -6466,13 +6466,13 @@
         <v>391</v>
       </c>
       <c r="L43">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M43">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O43">
         <v>0</v>
@@ -6514,10 +6514,10 @@
         <v>0</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD43">
         <v>0</v>
@@ -6558,7 +6558,7 @@
         <v>100</v>
       </c>
       <c r="D44" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E44" t="s">
         <v>163</v>
@@ -6790,7 +6790,7 @@
         <v>102</v>
       </c>
       <c r="D46" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E46" t="s">
         <v>165</v>
@@ -6814,13 +6814,13 @@
         <v>391</v>
       </c>
       <c r="L46">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M46">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N46">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="O46">
         <v>0</v>
@@ -6903,7 +6903,7 @@
         <v>52</v>
       </c>
       <c r="C47" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D47" t="s">
         <v>120</v>
@@ -7019,7 +7019,7 @@
         <v>52</v>
       </c>
       <c r="C48" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D48" t="s">
         <v>120</v>
@@ -7046,13 +7046,13 @@
         <v>391</v>
       </c>
       <c r="L48">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M48">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N48">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O48">
         <v>0</v>
@@ -7094,10 +7094,10 @@
         <v>0</v>
       </c>
       <c r="AB48">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC48">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD48">
         <v>0</v>
@@ -7135,7 +7135,7 @@
         <v>52</v>
       </c>
       <c r="C49" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="D49" t="s">
         <v>120</v>
@@ -7251,7 +7251,7 @@
         <v>52</v>
       </c>
       <c r="C50" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D50" t="s">
         <v>120</v>
@@ -7367,7 +7367,7 @@
         <v>52</v>
       </c>
       <c r="C51" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D51" t="s">
         <v>120</v>
@@ -7483,7 +7483,7 @@
         <v>52</v>
       </c>
       <c r="C52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D52" t="s">
         <v>120</v>
@@ -7599,10 +7599,10 @@
         <v>52</v>
       </c>
       <c r="C53" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="D53" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E53" t="s">
         <v>172</v>
@@ -7626,13 +7626,13 @@
         <v>391</v>
       </c>
       <c r="L53">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M53">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="O53">
         <v>0</v>
@@ -7715,7 +7715,7 @@
         <v>52</v>
       </c>
       <c r="C54" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D54" t="s">
         <v>120</v>
@@ -7742,13 +7742,13 @@
         <v>391</v>
       </c>
       <c r="L54">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M54">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O54">
         <v>0</v>
@@ -7790,10 +7790,10 @@
         <v>0</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD54">
         <v>0</v>
@@ -7831,10 +7831,10 @@
         <v>52</v>
       </c>
       <c r="C55" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D55" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E55" t="s">
         <v>174</v>
@@ -7947,7 +7947,7 @@
         <v>52</v>
       </c>
       <c r="C56" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="D56" t="s">
         <v>120</v>
@@ -8063,7 +8063,7 @@
         <v>52</v>
       </c>
       <c r="C57" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="D57" t="s">
         <v>120</v>
@@ -8179,10 +8179,10 @@
         <v>52</v>
       </c>
       <c r="C58" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D58" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E58" t="s">
         <v>177</v>
@@ -8295,7 +8295,7 @@
         <v>53</v>
       </c>
       <c r="C59" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D59" t="s">
         <v>120</v>
@@ -8527,10 +8527,10 @@
         <v>53</v>
       </c>
       <c r="C61" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D61" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E61" t="s">
         <v>180</v>
@@ -8646,7 +8646,7 @@
         <v>90</v>
       </c>
       <c r="D62" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E62" t="s">
         <v>181</v>
@@ -8759,10 +8759,10 @@
         <v>54</v>
       </c>
       <c r="C63" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="D63" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E63" t="s">
         <v>182</v>
@@ -8875,10 +8875,10 @@
         <v>54</v>
       </c>
       <c r="C64" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D64" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E64" t="s">
         <v>183</v>
@@ -8991,10 +8991,10 @@
         <v>54</v>
       </c>
       <c r="C65" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D65" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E65" t="s">
         <v>184</v>
@@ -9018,13 +9018,13 @@
         <v>391</v>
       </c>
       <c r="L65">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M65">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O65">
         <v>0</v>
@@ -9066,10 +9066,10 @@
         <v>0</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD65">
         <v>0</v>
@@ -9107,10 +9107,10 @@
         <v>54</v>
       </c>
       <c r="C66" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D66" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E66" t="s">
         <v>185</v>
@@ -9223,10 +9223,10 @@
         <v>54</v>
       </c>
       <c r="C67" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D67" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E67" t="s">
         <v>186</v>
@@ -9339,7 +9339,7 @@
         <v>54</v>
       </c>
       <c r="C68" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="D68" t="s">
         <v>120</v>
@@ -9366,13 +9366,13 @@
         <v>391</v>
       </c>
       <c r="L68">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M68">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O68">
         <v>0</v>
@@ -9414,10 +9414,10 @@
         <v>0</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD68">
         <v>0</v>
@@ -9455,7 +9455,7 @@
         <v>54</v>
       </c>
       <c r="C69" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="D69" t="s">
         <v>120</v>
@@ -9571,10 +9571,10 @@
         <v>54</v>
       </c>
       <c r="C70" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="D70" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E70" t="s">
         <v>189</v>
@@ -9687,7 +9687,7 @@
         <v>54</v>
       </c>
       <c r="C71" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D71" t="s">
         <v>120</v>
@@ -9803,10 +9803,10 @@
         <v>54</v>
       </c>
       <c r="C72" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="D72" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E72" t="s">
         <v>191</v>
@@ -9830,13 +9830,13 @@
         <v>391</v>
       </c>
       <c r="L72">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M72">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -9878,10 +9878,10 @@
         <v>0</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC72">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD72">
         <v>0</v>
@@ -9919,10 +9919,10 @@
         <v>54</v>
       </c>
       <c r="C73" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="D73" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E73" t="s">
         <v>192</v>
@@ -10035,7 +10035,7 @@
         <v>54</v>
       </c>
       <c r="C74" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D74" t="s">
         <v>120</v>
@@ -10151,7 +10151,7 @@
         <v>54</v>
       </c>
       <c r="C75" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="D75" t="s">
         <v>120</v>
@@ -10178,13 +10178,13 @@
         <v>391</v>
       </c>
       <c r="L75">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M75">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N75">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O75">
         <v>0</v>
@@ -10226,10 +10226,10 @@
         <v>0</v>
       </c>
       <c r="AB75">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC75">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD75">
         <v>0</v>
@@ -10267,10 +10267,10 @@
         <v>54</v>
       </c>
       <c r="C76" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="D76" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E76" t="s">
         <v>195</v>
@@ -10294,13 +10294,13 @@
         <v>391</v>
       </c>
       <c r="L76">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M76">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O76">
         <v>0</v>
@@ -10342,10 +10342,10 @@
         <v>0</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD76">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>54</v>
       </c>
       <c r="C77" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="D77" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E77" t="s">
         <v>196</v>
@@ -10499,10 +10499,10 @@
         <v>54</v>
       </c>
       <c r="C78" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="D78" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E78" t="s">
         <v>197</v>
@@ -10615,7 +10615,7 @@
         <v>54</v>
       </c>
       <c r="C79" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="D79" t="s">
         <v>120</v>
@@ -10758,13 +10758,13 @@
         <v>391</v>
       </c>
       <c r="L80">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M80">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N80">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O80">
         <v>0</v>
@@ -10806,10 +10806,10 @@
         <v>0</v>
       </c>
       <c r="AB80">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC80">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD80">
         <v>0</v>
@@ -10847,10 +10847,10 @@
         <v>54</v>
       </c>
       <c r="C81" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="D81" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E81" t="s">
         <v>200</v>
@@ -10874,13 +10874,13 @@
         <v>391</v>
       </c>
       <c r="L81">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M81">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N81">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O81">
         <v>0</v>
@@ -10922,10 +10922,10 @@
         <v>0</v>
       </c>
       <c r="AB81">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC81">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD81">
         <v>0</v>
@@ -10963,7 +10963,7 @@
         <v>54</v>
       </c>
       <c r="C82" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="D82" t="s">
         <v>120</v>
@@ -10990,13 +10990,13 @@
         <v>391</v>
       </c>
       <c r="L82">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M82">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N82">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O82">
         <v>0</v>
@@ -11038,10 +11038,10 @@
         <v>0</v>
       </c>
       <c r="AB82">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC82">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD82">
         <v>0</v>
@@ -11106,13 +11106,13 @@
         <v>391</v>
       </c>
       <c r="L83">
-        <v>2.65</v>
+        <v>3.15</v>
       </c>
       <c r="M83">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N83">
-        <v>2.41</v>
+        <v>2.17</v>
       </c>
       <c r="O83">
         <v>0</v>
@@ -11222,13 +11222,13 @@
         <v>391</v>
       </c>
       <c r="L84">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M84">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O84">
         <v>0</v>
@@ -11270,10 +11270,10 @@
         <v>0</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD84">
         <v>0</v>
@@ -11338,13 +11338,13 @@
         <v>391</v>
       </c>
       <c r="L85">
-        <v>3.15</v>
+        <v>2.65</v>
       </c>
       <c r="M85">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N85">
-        <v>2.17</v>
+        <v>2.41</v>
       </c>
       <c r="O85">
         <v>0</v>
@@ -11427,7 +11427,7 @@
         <v>55</v>
       </c>
       <c r="C86" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="D86" t="s">
         <v>120</v>
@@ -11454,13 +11454,13 @@
         <v>391</v>
       </c>
       <c r="L86">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="M86">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O86">
         <v>0</v>
@@ -11502,16 +11502,16 @@
         <v>0</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF86">
         <v>0</v>
@@ -11543,7 +11543,7 @@
         <v>55</v>
       </c>
       <c r="C87" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D87" t="s">
         <v>120</v>
@@ -11570,13 +11570,13 @@
         <v>391</v>
       </c>
       <c r="L87">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M87">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N87">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O87">
         <v>0</v>
@@ -11618,10 +11618,10 @@
         <v>0</v>
       </c>
       <c r="AB87">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC87">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD87">
         <v>0</v>
@@ -11659,7 +11659,7 @@
         <v>55</v>
       </c>
       <c r="C88" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D88" t="s">
         <v>120</v>
@@ -11775,7 +11775,7 @@
         <v>55</v>
       </c>
       <c r="C89" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="D89" t="s">
         <v>120</v>
@@ -11802,13 +11802,13 @@
         <v>391</v>
       </c>
       <c r="L89">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="M89">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N89">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O89">
         <v>0</v>
@@ -11850,16 +11850,16 @@
         <v>0</v>
       </c>
       <c r="AB89">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC89">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD89">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE89">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF89">
         <v>0</v>
@@ -12123,7 +12123,7 @@
         <v>57</v>
       </c>
       <c r="C92" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D92" t="s">
         <v>120</v>
@@ -12239,10 +12239,10 @@
         <v>57</v>
       </c>
       <c r="C93" t="s">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="D93" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E93" t="s">
         <v>212</v>
@@ -12266,13 +12266,13 @@
         <v>391</v>
       </c>
       <c r="L93">
-        <v>6.27</v>
+        <v>0</v>
       </c>
       <c r="M93">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N93">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O93">
         <v>0</v>
@@ -12320,10 +12320,10 @@
         <v>0</v>
       </c>
       <c r="AD93">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE93">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF93">
         <v>0</v>
@@ -12471,10 +12471,10 @@
         <v>57</v>
       </c>
       <c r="C95" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="D95" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E95" t="s">
         <v>214</v>
@@ -12498,13 +12498,13 @@
         <v>391</v>
       </c>
       <c r="L95">
-        <v>0</v>
+        <v>6.27</v>
       </c>
       <c r="M95">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O95">
         <v>0</v>
@@ -12552,10 +12552,10 @@
         <v>0</v>
       </c>
       <c r="AD95">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE95">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF95">
         <v>0</v>
@@ -12819,10 +12819,10 @@
         <v>59</v>
       </c>
       <c r="C98" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="D98" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E98" t="s">
         <v>217</v>
@@ -12935,7 +12935,7 @@
         <v>59</v>
       </c>
       <c r="C99" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D99" t="s">
         <v>119</v>
@@ -13051,10 +13051,10 @@
         <v>59</v>
       </c>
       <c r="C100" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="D100" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E100" t="s">
         <v>219</v>
@@ -13167,7 +13167,7 @@
         <v>60</v>
       </c>
       <c r="C101" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="D101" t="s">
         <v>120</v>
@@ -13283,10 +13283,10 @@
         <v>60</v>
       </c>
       <c r="C102" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="D102" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E102" t="s">
         <v>221</v>
@@ -13399,10 +13399,10 @@
         <v>60</v>
       </c>
       <c r="C103" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="D103" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E103" t="s">
         <v>222</v>
@@ -13747,10 +13747,10 @@
         <v>60</v>
       </c>
       <c r="C106" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D106" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E106" t="s">
         <v>225</v>
@@ -14095,10 +14095,10 @@
         <v>60</v>
       </c>
       <c r="C109" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D109" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E109" t="s">
         <v>228</v>
@@ -14211,7 +14211,7 @@
         <v>61</v>
       </c>
       <c r="C110" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D110" t="s">
         <v>120</v>
@@ -14327,7 +14327,7 @@
         <v>62</v>
       </c>
       <c r="C111" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="D111" t="s">
         <v>120</v>
@@ -14354,13 +14354,13 @@
         <v>391</v>
       </c>
       <c r="L111">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M111">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="O111">
         <v>0</v>
@@ -14396,10 +14396,10 @@
         <v>0</v>
       </c>
       <c r="Z111">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA111">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB111">
         <v>0</v>
@@ -14443,7 +14443,7 @@
         <v>62</v>
       </c>
       <c r="C112" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D112" t="s">
         <v>120</v>
@@ -14559,7 +14559,7 @@
         <v>62</v>
       </c>
       <c r="C113" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="D113" t="s">
         <v>120</v>
@@ -14586,13 +14586,13 @@
         <v>391</v>
       </c>
       <c r="L113">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M113">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N113">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="O113">
         <v>0</v>
@@ -14628,10 +14628,10 @@
         <v>0</v>
       </c>
       <c r="Z113">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA113">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB113">
         <v>0</v>
@@ -14675,7 +14675,7 @@
         <v>63</v>
       </c>
       <c r="C114" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="D114" t="s">
         <v>120</v>
@@ -14791,7 +14791,7 @@
         <v>63</v>
       </c>
       <c r="C115" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="D115" t="s">
         <v>120</v>
@@ -15023,7 +15023,7 @@
         <v>64</v>
       </c>
       <c r="C117" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="D117" t="s">
         <v>120</v>
@@ -15050,13 +15050,13 @@
         <v>391</v>
       </c>
       <c r="L117">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M117">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N117">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O117">
         <v>0</v>
@@ -15139,7 +15139,7 @@
         <v>64</v>
       </c>
       <c r="C118" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="D118" t="s">
         <v>120</v>
@@ -15166,13 +15166,13 @@
         <v>391</v>
       </c>
       <c r="L118">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M118">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O118">
         <v>0</v>
@@ -15255,7 +15255,7 @@
         <v>65</v>
       </c>
       <c r="C119" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D119" t="s">
         <v>120</v>
@@ -15371,10 +15371,10 @@
         <v>66</v>
       </c>
       <c r="C120" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D120" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E120" t="s">
         <v>239</v>
@@ -15487,7 +15487,7 @@
         <v>66</v>
       </c>
       <c r="C121" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D121" t="s">
         <v>119</v>
@@ -15514,13 +15514,13 @@
         <v>391</v>
       </c>
       <c r="L121">
-        <v>1.83</v>
+        <v>2.28</v>
       </c>
       <c r="M121">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N121">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="O121">
         <v>0</v>
@@ -15556,16 +15556,16 @@
         <v>0</v>
       </c>
       <c r="Z121">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA121">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB121">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AC121">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AD121">
         <v>0</v>
@@ -15603,10 +15603,10 @@
         <v>66</v>
       </c>
       <c r="C122" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D122" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E122" t="s">
         <v>241</v>
@@ -15630,13 +15630,13 @@
         <v>391</v>
       </c>
       <c r="L122">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M122">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N122">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O122">
         <v>0</v>
@@ -15672,16 +15672,16 @@
         <v>0</v>
       </c>
       <c r="Z122">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA122">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB122">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC122">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD122">
         <v>0</v>
@@ -15719,7 +15719,7 @@
         <v>66</v>
       </c>
       <c r="C123" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D123" t="s">
         <v>119</v>
@@ -15862,13 +15862,13 @@
         <v>391</v>
       </c>
       <c r="L124">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M124">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N124">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O124">
         <v>0</v>
@@ -15910,10 +15910,10 @@
         <v>0</v>
       </c>
       <c r="AB124">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC124">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD124">
         <v>0</v>
@@ -16067,7 +16067,7 @@
         <v>68</v>
       </c>
       <c r="C126" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D126" t="s">
         <v>119</v>
@@ -16094,13 +16094,13 @@
         <v>391</v>
       </c>
       <c r="L126">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M126">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O126">
         <v>0</v>
@@ -16142,10 +16142,10 @@
         <v>0</v>
       </c>
       <c r="AB126">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC126">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD126">
         <v>0</v>
@@ -16183,7 +16183,7 @@
         <v>68</v>
       </c>
       <c r="C127" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D127" t="s">
         <v>119</v>
@@ -16299,7 +16299,7 @@
         <v>68</v>
       </c>
       <c r="C128" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D128" t="s">
         <v>119</v>
@@ -16326,13 +16326,13 @@
         <v>391</v>
       </c>
       <c r="L128">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M128">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N128">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O128">
         <v>0</v>
@@ -16374,10 +16374,10 @@
         <v>0</v>
       </c>
       <c r="AB128">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC128">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD128">
         <v>0</v>
@@ -16415,7 +16415,7 @@
         <v>68</v>
       </c>
       <c r="C129" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D129" t="s">
         <v>119</v>
@@ -16442,13 +16442,13 @@
         <v>391</v>
       </c>
       <c r="L129">
-        <v>3.8</v>
+        <v>2.09</v>
       </c>
       <c r="M129">
         <v>3.15</v>
       </c>
       <c r="N129">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="O129">
         <v>0</v>
@@ -16490,7 +16490,7 @@
         <v>0</v>
       </c>
       <c r="AB129">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC129">
         <v>1.57</v>
@@ -16531,7 +16531,7 @@
         <v>69</v>
       </c>
       <c r="C130" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D130" t="s">
         <v>119</v>
@@ -16647,7 +16647,7 @@
         <v>69</v>
       </c>
       <c r="C131" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D131" t="s">
         <v>119</v>
@@ -16763,7 +16763,7 @@
         <v>70</v>
       </c>
       <c r="C132" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D132" t="s">
         <v>119</v>
@@ -16995,7 +16995,7 @@
         <v>72</v>
       </c>
       <c r="C134" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D134" t="s">
         <v>119</v>

--- a/jogos_2025-08-03.xlsx
+++ b/jogos_2025-08-03.xlsx
@@ -253,48 +253,48 @@
     <t>Austria 2. Liga</t>
   </si>
   <si>
+    <t>Japan J2 League</t>
+  </si>
+  <si>
     <t>Ukraine Ukrainian Premier League</t>
   </si>
   <si>
-    <t>Japan J2 League</t>
-  </si>
-  <si>
     <t>Russia Russian Premier League</t>
   </si>
   <si>
+    <t>England EFL League One</t>
+  </si>
+  <si>
+    <t>China China League One</t>
+  </si>
+  <si>
+    <t>Belarus Vysheyshaya Liga</t>
+  </si>
+  <si>
     <t>China Chinese Super League</t>
   </si>
   <si>
-    <t>China China League One</t>
-  </si>
-  <si>
-    <t>Belarus Vysheyshaya Liga</t>
-  </si>
-  <si>
-    <t>England EFL League One</t>
-  </si>
-  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
+    <t>Germany 3. Liga</t>
+  </si>
+  <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
-    <t>Germany 3. Liga</t>
+    <t>Switzerland Super League</t>
+  </si>
+  <si>
+    <t>Switzerland Challenge League</t>
   </si>
   <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
-    <t>Switzerland Challenge League</t>
-  </si>
-  <si>
     <t>Denmark Superliga</t>
   </si>
   <si>
-    <t>Switzerland Super League</t>
-  </si>
-  <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
@@ -304,21 +304,21 @@
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
+    <t>Czech Republic First League</t>
+  </si>
+  <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
+    <t>Scotland Premiership</t>
+  </si>
+  <si>
     <t>Finland Veikkausliiga</t>
   </si>
   <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
-    <t>Czech Republic First League</t>
-  </si>
-  <si>
-    <t>Scotland Premiership</t>
-  </si>
-  <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
     <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
@@ -328,24 +328,24 @@
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
+    <t>Montenegro Montenegrin First League</t>
+  </si>
+  <si>
+    <t>Slovakia Super Liga</t>
+  </si>
+  <si>
     <t>Uzbekistan Uzbekistan Super League</t>
   </si>
   <si>
-    <t>Montenegro Montenegrin First League</t>
-  </si>
-  <si>
     <t>Austria Bundesliga</t>
   </si>
   <si>
-    <t>Slovakia Super Liga</t>
+    <t>Hungary NB II</t>
   </si>
   <si>
     <t>Romania Liga I</t>
   </si>
   <si>
-    <t>Hungary NB II</t>
-  </si>
-  <si>
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
@@ -382,15 +382,15 @@
     <t>Wollongong Wolves</t>
   </si>
   <si>
+    <t>Sydney United</t>
+  </si>
+  <si>
+    <t>Blacktown City</t>
+  </si>
+  <si>
     <t>Central Coast II</t>
   </si>
   <si>
-    <t>Sydney United</t>
-  </si>
-  <si>
-    <t>Blacktown City</t>
-  </si>
-  <si>
     <t>SKA Khabarovsk</t>
   </si>
   <si>
@@ -403,25 +403,28 @@
     <t>WSPG Wels</t>
   </si>
   <si>
+    <t>Roasso Kumamoto</t>
+  </si>
+  <si>
     <t>Kudrivka</t>
   </si>
   <si>
-    <t>Roasso Kumamoto</t>
-  </si>
-  <si>
     <t>Akron</t>
   </si>
   <si>
+    <t>Stockport County</t>
+  </si>
+  <si>
+    <t>Suzhou Dongwu</t>
+  </si>
+  <si>
+    <t>Molodechno-DYuSSh 4</t>
+  </si>
+  <si>
     <t>Dalian Zhixing</t>
   </si>
   <si>
-    <t>Suzhou Dongwu</t>
-  </si>
-  <si>
-    <t>Molodechno-DYuSSh 4</t>
-  </si>
-  <si>
-    <t>Stockport County</t>
+    <t>Qingdao Red Lions</t>
   </si>
   <si>
     <t>Dongguan United</t>
@@ -430,60 +433,57 @@
     <t>Greuther Fürth</t>
   </si>
   <si>
+    <t>Hannover 96</t>
+  </si>
+  <si>
+    <t>Magdeburg</t>
+  </si>
+  <si>
+    <t>Erzgebirge Aue</t>
+  </si>
+  <si>
     <t>KRC Genk</t>
   </si>
   <si>
-    <t>Magdeburg</t>
-  </si>
-  <si>
-    <t>Hannover 96</t>
-  </si>
-  <si>
-    <t>Qingdao Red Lions</t>
-  </si>
-  <si>
-    <t>Erzgebirge Aue</t>
-  </si>
-  <si>
     <t>Beijing Guoan</t>
   </si>
   <si>
     <t>Wuhan Three Towns</t>
   </si>
   <si>
+    <t>Thun</t>
+  </si>
+  <si>
+    <t>Yverdon Sport</t>
+  </si>
+  <si>
+    <t>Häcken</t>
+  </si>
+  <si>
+    <t>Djurgården</t>
+  </si>
+  <si>
+    <t>Sichuan Jiuniu</t>
+  </si>
+  <si>
+    <t>Randers</t>
+  </si>
+  <si>
+    <t>SønderjyskE</t>
+  </si>
+  <si>
     <t>Spartak Kostroma</t>
   </si>
   <si>
-    <t>Djurgården</t>
-  </si>
-  <si>
-    <t>Yverdon Sport</t>
-  </si>
-  <si>
-    <t>Häcken</t>
-  </si>
-  <si>
-    <t>SønderjyskE</t>
-  </si>
-  <si>
-    <t>Sichuan Jiuniu</t>
-  </si>
-  <si>
-    <t>Randers</t>
-  </si>
-  <si>
-    <t>Thun</t>
+    <t>HamKam</t>
+  </si>
+  <si>
+    <t>Epitsentr Dunayivtsi</t>
   </si>
   <si>
     <t>Baník Ostrava II</t>
   </si>
   <si>
-    <t>HamKam</t>
-  </si>
-  <si>
-    <t>Epitsentr Dunayivtsi</t>
-  </si>
-  <si>
     <t>Śląsk Wrocław</t>
   </si>
   <si>
@@ -493,63 +493,63 @@
     <t>Cracovia Kraków</t>
   </si>
   <si>
+    <t>Landskrona</t>
+  </si>
+  <si>
+    <t>Slovácko</t>
+  </si>
+  <si>
+    <t>Sogndal</t>
+  </si>
+  <si>
+    <t>Falkirk</t>
+  </si>
+  <si>
     <t>SJK</t>
   </si>
   <si>
-    <t>Sogndal</t>
-  </si>
-  <si>
-    <t>Slovácko</t>
-  </si>
-  <si>
-    <t>Falkirk</t>
-  </si>
-  <si>
-    <t>Landskrona</t>
-  </si>
-  <si>
     <t>Suduroy</t>
   </si>
   <si>
+    <t>AGF</t>
+  </si>
+  <si>
+    <t>Jeunesse Canach</t>
+  </si>
+  <si>
+    <t>Harju Jalgpallikool</t>
+  </si>
+  <si>
     <t>Swift Hesperange</t>
   </si>
   <si>
+    <t>Hostert</t>
+  </si>
+  <si>
+    <t>Cercle Brugge</t>
+  </si>
+  <si>
     <t>F91 Dudelange</t>
   </si>
   <si>
+    <t>Dundee</t>
+  </si>
+  <si>
+    <t>Differdange 03</t>
+  </si>
+  <si>
     <t>Rodange</t>
   </si>
   <si>
-    <t>Jeunesse Canach</t>
+    <t>EB - Streymur</t>
   </si>
   <si>
     <t>Mondorf-les-Bains</t>
   </si>
   <si>
-    <t>Differdange 03</t>
-  </si>
-  <si>
-    <t>Hostert</t>
-  </si>
-  <si>
-    <t>Harju Jalgpallikool</t>
-  </si>
-  <si>
-    <t>Dundee</t>
-  </si>
-  <si>
     <t>Jeunesse d'Esch</t>
   </si>
   <si>
-    <t>AGF</t>
-  </si>
-  <si>
-    <t>Cercle Brugge</t>
-  </si>
-  <si>
-    <t>EB - Streymur</t>
-  </si>
-  <si>
     <t>Luzern</t>
   </si>
   <si>
@@ -562,102 +562,102 @@
     <t>Étoile Carouge</t>
   </si>
   <si>
+    <t>Zenit</t>
+  </si>
+  <si>
+    <t>Sutjeska</t>
+  </si>
+  <si>
+    <t>Dečić</t>
+  </si>
+  <si>
+    <t>Trenčín</t>
+  </si>
+  <si>
+    <t>Molde</t>
+  </si>
+  <si>
+    <t>KFUM</t>
+  </si>
+  <si>
+    <t>Petrovac</t>
+  </si>
+  <si>
+    <t>Arsenal Tivat</t>
+  </si>
+  <si>
+    <t>Rubin Kazan</t>
+  </si>
+  <si>
+    <t>FK Jezero Plav</t>
+  </si>
+  <si>
+    <t>Shortan</t>
+  </si>
+  <si>
+    <t>Strømsgodset</t>
+  </si>
+  <si>
+    <t>Rapid Wien</t>
+  </si>
+  <si>
     <t>Vålerenga</t>
   </si>
   <si>
+    <t>Vlašim</t>
+  </si>
+  <si>
+    <t>Karpaty</t>
+  </si>
+  <si>
+    <t>Grazer AK</t>
+  </si>
+  <si>
+    <t>Pogoń Siedlce</t>
+  </si>
+  <si>
     <t>Dukla Praha</t>
   </si>
   <si>
-    <t>Zenit</t>
-  </si>
-  <si>
-    <t>Shortan</t>
-  </si>
-  <si>
-    <t>Rubin Kazan</t>
-  </si>
-  <si>
-    <t>Karpaty</t>
-  </si>
-  <si>
-    <t>Vlašim</t>
-  </si>
-  <si>
     <t>Torpedo BelAZ</t>
   </si>
   <si>
-    <t>Dečić</t>
-  </si>
-  <si>
-    <t>Grazer AK</t>
-  </si>
-  <si>
-    <t>Pogoń Siedlce</t>
-  </si>
-  <si>
-    <t>FK Jezero Plav</t>
-  </si>
-  <si>
-    <t>Arsenal Tivat</t>
-  </si>
-  <si>
-    <t>Rapid Wien</t>
-  </si>
-  <si>
-    <t>Molde</t>
-  </si>
-  <si>
-    <t>Strømsgodset</t>
-  </si>
-  <si>
-    <t>Sutjeska</t>
-  </si>
-  <si>
-    <t>Trenčín</t>
-  </si>
-  <si>
-    <t>KFUM</t>
-  </si>
-  <si>
-    <t>Petrovac</t>
-  </si>
-  <si>
     <t>Radomiak Radom</t>
   </si>
   <si>
+    <t>Szentlőrinc SE</t>
+  </si>
+  <si>
     <t>Hermannstadt</t>
   </si>
   <si>
+    <t>Celtic</t>
+  </si>
+  <si>
     <t>Motor Lublin</t>
   </si>
   <si>
-    <t>Celtic</t>
-  </si>
-  <si>
     <t>Karcag SE</t>
   </si>
   <si>
     <t>Maribor</t>
   </si>
   <si>
-    <t>Szentlőrinc SE</t>
+    <t>Puskás</t>
   </si>
   <si>
     <t>Várda SE</t>
   </si>
   <si>
-    <t>Puskás</t>
+    <t>Fakel</t>
+  </si>
+  <si>
+    <t>FK Chernomorets Novorossiysk</t>
   </si>
   <si>
     <t>Brøndby</t>
   </si>
   <si>
-    <t>FK Chernomorets Novorossiysk</t>
-  </si>
-  <si>
-    <t>Fakel</t>
-  </si>
-  <si>
     <t>Tammeka</t>
   </si>
   <si>
@@ -676,99 +676,99 @@
     <t>Union Saint-Gilloise</t>
   </si>
   <si>
+    <t>Honvéd W</t>
+  </si>
+  <si>
+    <t>Békéscsaba</t>
+  </si>
+  <si>
+    <t>MKK-Dnepr</t>
+  </si>
+  <si>
     <t>Železničar Pančevo</t>
   </si>
   <si>
-    <t>MKK-Dnepr</t>
+    <t>Ajka</t>
+  </si>
+  <si>
+    <t>Sporting KC II</t>
+  </si>
+  <si>
+    <t>Tiszakécske</t>
   </si>
   <si>
     <t>Žilina</t>
   </si>
   <si>
-    <t>Békéscsaba</t>
-  </si>
-  <si>
-    <t>Honvéd W</t>
-  </si>
-  <si>
     <t>Csákvári TK</t>
   </si>
   <si>
-    <t>Tiszakécske</t>
-  </si>
-  <si>
-    <t>Ajka</t>
-  </si>
-  <si>
-    <t>Sporting KC II</t>
-  </si>
-  <si>
     <t>Sporting Charleroi</t>
   </si>
   <si>
+    <t>Wehen Wiesbaden</t>
+  </si>
+  <si>
+    <t>Górnik Łęczna</t>
+  </si>
+  <si>
     <t>Makhachkala</t>
   </si>
   <si>
-    <t>Górnik Łęczna</t>
-  </si>
-  <si>
-    <t>Wehen Wiesbaden</t>
+    <t>Pardubice</t>
   </si>
   <si>
     <t>Győri ETO</t>
   </si>
   <si>
-    <t>Pardubice</t>
-  </si>
-  <si>
     <t>Chicago Fire II</t>
   </si>
   <si>
+    <t>Legia Warszawa</t>
+  </si>
+  <si>
     <t>Olimpija</t>
   </si>
   <si>
-    <t>Legia Warszawa</t>
-  </si>
-  <si>
     <t>CFR Cluj</t>
   </si>
   <si>
+    <t>Partizan</t>
+  </si>
+  <si>
     <t>Chapecoense</t>
   </si>
   <si>
+    <t>Colo-Colo</t>
+  </si>
+  <si>
     <t>Botafogo</t>
   </si>
   <si>
-    <t>Partizan</t>
-  </si>
-  <si>
-    <t>Colo-Colo</t>
-  </si>
-  <si>
     <t>Corinthians</t>
   </si>
   <si>
     <t>Atlético Ottawa</t>
   </si>
   <si>
+    <t>Ñublense</t>
+  </si>
+  <si>
+    <t>Atlético Mineiro</t>
+  </si>
+  <si>
     <t>Ceará</t>
   </si>
   <si>
     <t>Atlético PR</t>
   </si>
   <si>
-    <t>Ñublense</t>
-  </si>
-  <si>
-    <t>Atlético Mineiro</t>
+    <t>Philadelphia Union II</t>
   </si>
   <si>
     <t>Orlando Pride</t>
   </si>
   <si>
-    <t>Philadelphia Union II</t>
-  </si>
-  <si>
     <t>Vitória</t>
   </si>
   <si>
@@ -787,15 +787,15 @@
     <t>Sydney II</t>
   </si>
   <si>
+    <t>St. George Saints</t>
+  </si>
+  <si>
+    <t>Mt Druitt Town</t>
+  </si>
+  <si>
     <t>Marconi Stallions</t>
   </si>
   <si>
-    <t>St. George Saints</t>
-  </si>
-  <si>
-    <t>Mt Druitt Town</t>
-  </si>
-  <si>
     <t>Torpedo Moskva</t>
   </si>
   <si>
@@ -808,25 +808,28 @@
     <t>Floridsdorfer AC</t>
   </si>
   <si>
+    <t>Mito Hollyhock</t>
+  </si>
+  <si>
     <t>Oleksandria</t>
   </si>
   <si>
-    <t>Mito Hollyhock</t>
-  </si>
-  <si>
     <t>Spartak Moskva</t>
   </si>
   <si>
+    <t>Bolton Wanderers</t>
+  </si>
+  <si>
+    <t>Dalian Huayi</t>
+  </si>
+  <si>
+    <t>Neman Grodno</t>
+  </si>
+  <si>
     <t>Qingdao Jonoon</t>
   </si>
   <si>
-    <t>Dalian Huayi</t>
-  </si>
-  <si>
-    <t>Neman Grodno</t>
-  </si>
-  <si>
-    <t>Bolton Wanderers</t>
+    <t>Heilongjiang Lava Spring</t>
   </si>
   <si>
     <t>Nantong Zhiyun</t>
@@ -835,60 +838,57 @@
     <t>Dynamo Dresden</t>
   </si>
   <si>
+    <t>Kaiserslautern</t>
+  </si>
+  <si>
+    <t>Eintracht Braunschweig</t>
+  </si>
+  <si>
+    <t>Hansa Rostock</t>
+  </si>
+  <si>
     <t>Royal Antwerp FC</t>
   </si>
   <si>
-    <t>Eintracht Braunschweig</t>
-  </si>
-  <si>
-    <t>Kaiserslautern</t>
-  </si>
-  <si>
-    <t>Heilongjiang Lava Spring</t>
-  </si>
-  <si>
-    <t>Hansa Rostock</t>
-  </si>
-  <si>
     <t>Tianjin Teda</t>
   </si>
   <si>
     <t>Changchun Yatai</t>
   </si>
   <si>
+    <t>Lausanne Sport</t>
+  </si>
+  <si>
+    <t>Stade Lausanne-Ouchy</t>
+  </si>
+  <si>
+    <t>Elfsborg</t>
+  </si>
+  <si>
+    <t>Halmstad</t>
+  </si>
+  <si>
+    <t>Zhejiang FC</t>
+  </si>
+  <si>
+    <t>Silkeborg</t>
+  </si>
+  <si>
+    <t>Nordsjælland</t>
+  </si>
+  <si>
     <t>Neftekhimik</t>
   </si>
   <si>
-    <t>Halmstad</t>
-  </si>
-  <si>
-    <t>Stade Lausanne-Ouchy</t>
-  </si>
-  <si>
-    <t>Elfsborg</t>
-  </si>
-  <si>
-    <t>Nordsjælland</t>
-  </si>
-  <si>
-    <t>Zhejiang FC</t>
-  </si>
-  <si>
-    <t>Silkeborg</t>
-  </si>
-  <si>
-    <t>Lausanne Sport</t>
+    <t>FK Bodo - Glimt</t>
+  </si>
+  <si>
+    <t>Shakhtar Donetsk</t>
   </si>
   <si>
     <t>Líšeň</t>
   </si>
   <si>
-    <t>FK Bodo - Glimt</t>
-  </si>
-  <si>
-    <t>Shakhtar Donetsk</t>
-  </si>
-  <si>
     <t>Ruch Chorzów</t>
   </si>
   <si>
@@ -898,63 +898,63 @@
     <t>Lechia Gdańsk</t>
   </si>
   <si>
+    <t>Västerås SK</t>
+  </si>
+  <si>
+    <t>Slavia Praha</t>
+  </si>
+  <si>
+    <t>Skeid</t>
+  </si>
+  <si>
+    <t>Dundee United</t>
+  </si>
+  <si>
     <t>KTP</t>
   </si>
   <si>
-    <t>Skeid</t>
-  </si>
-  <si>
-    <t>Slavia Praha</t>
-  </si>
-  <si>
-    <t>Dundee United</t>
-  </si>
-  <si>
-    <t>Västerås SK</t>
-  </si>
-  <si>
     <t>HB</t>
   </si>
   <si>
+    <t>Midtjylland</t>
+  </si>
+  <si>
+    <t>Mamer</t>
+  </si>
+  <si>
+    <t>Paide</t>
+  </si>
+  <si>
     <t>UT Pétange</t>
   </si>
   <si>
+    <t>Victoria Rosport</t>
+  </si>
+  <si>
+    <t>RSC Anderlecht</t>
+  </si>
+  <si>
     <t>Progrès Niederkorn</t>
   </si>
   <si>
+    <t>Hibernian</t>
+  </si>
+  <si>
+    <t>Atert Bissen</t>
+  </si>
+  <si>
     <t>Racing</t>
   </si>
   <si>
-    <t>Mamer</t>
+    <t>KÍ</t>
   </si>
   <si>
     <t>UNA Strassen</t>
   </si>
   <si>
-    <t>Atert Bissen</t>
-  </si>
-  <si>
-    <t>Victoria Rosport</t>
-  </si>
-  <si>
-    <t>Paide</t>
-  </si>
-  <si>
-    <t>Hibernian</t>
-  </si>
-  <si>
     <t>UN Käerjéng</t>
   </si>
   <si>
-    <t>Midtjylland</t>
-  </si>
-  <si>
-    <t>RSC Anderlecht</t>
-  </si>
-  <si>
-    <t>KÍ</t>
-  </si>
-  <si>
     <t>Zürich</t>
   </si>
   <si>
@@ -967,102 +967,102 @@
     <t>Vaduz</t>
   </si>
   <si>
+    <t>CSKA Moskva</t>
+  </si>
+  <si>
+    <t>Mornar</t>
+  </si>
+  <si>
+    <t>Mladost DG</t>
+  </si>
+  <si>
+    <t>Spartak Trnava</t>
+  </si>
+  <si>
+    <t>Bryne</t>
+  </si>
+  <si>
+    <t>Rosenborg</t>
+  </si>
+  <si>
+    <t>Bokelj</t>
+  </si>
+  <si>
+    <t>Jedinstvo</t>
+  </si>
+  <si>
+    <t>FK Sochi</t>
+  </si>
+  <si>
+    <t>Budućnost</t>
+  </si>
+  <si>
+    <t>Xorazm</t>
+  </si>
+  <si>
+    <t>Haugesund</t>
+  </si>
+  <si>
+    <t>Blau-Weiß Linz</t>
+  </si>
+  <si>
     <t>Sandefjord</t>
   </si>
   <si>
+    <t>Hanácká</t>
+  </si>
+  <si>
+    <t>Polessya</t>
+  </si>
+  <si>
+    <t>Austria Wien</t>
+  </si>
+  <si>
+    <t>Odra Opole</t>
+  </si>
+  <si>
     <t>Baník Ostrava</t>
   </si>
   <si>
-    <t>CSKA Moskva</t>
-  </si>
-  <si>
-    <t>Xorazm</t>
-  </si>
-  <si>
-    <t>FK Sochi</t>
-  </si>
-  <si>
-    <t>Polessya</t>
-  </si>
-  <si>
-    <t>Hanácká</t>
-  </si>
-  <si>
     <t>Gomel</t>
   </si>
   <si>
-    <t>Mladost DG</t>
-  </si>
-  <si>
-    <t>Austria Wien</t>
-  </si>
-  <si>
-    <t>Odra Opole</t>
-  </si>
-  <si>
-    <t>Budućnost</t>
-  </si>
-  <si>
-    <t>Jedinstvo</t>
-  </si>
-  <si>
-    <t>Blau-Weiß Linz</t>
-  </si>
-  <si>
-    <t>Bryne</t>
-  </si>
-  <si>
-    <t>Haugesund</t>
-  </si>
-  <si>
-    <t>Mornar</t>
-  </si>
-  <si>
-    <t>Spartak Trnava</t>
-  </si>
-  <si>
-    <t>Rosenborg</t>
-  </si>
-  <si>
-    <t>Bokelj</t>
-  </si>
-  <si>
     <t>Raków Częstochowa</t>
   </si>
   <si>
+    <t>Kozármisleny</t>
+  </si>
+  <si>
     <t>Universitatea Cluj</t>
   </si>
   <si>
+    <t>St. Mirren</t>
+  </si>
+  <si>
     <t>Jagiellonia Białystok</t>
   </si>
   <si>
-    <t>St. Mirren</t>
-  </si>
-  <si>
     <t>Soroksár SC</t>
   </si>
   <si>
     <t>Koper</t>
   </si>
   <si>
-    <t>Kozármisleny</t>
+    <t>Nyíregyháza Spartacus</t>
   </si>
   <si>
     <t>Paksi SE</t>
   </si>
   <si>
-    <t>Nyíregyháza Spartacus</t>
+    <t>Sokol Saratov</t>
+  </si>
+  <si>
+    <t>Arsenal Tula</t>
   </si>
   <si>
     <t>Viborg</t>
   </si>
   <si>
-    <t>Arsenal Tula</t>
-  </si>
-  <si>
-    <t>Sokol Saratov</t>
-  </si>
-  <si>
     <t>Nõmme Kalju</t>
   </si>
   <si>
@@ -1081,97 +1081,97 @@
     <t>OH Leuven</t>
   </si>
   <si>
+    <t>Budafoki MTE</t>
+  </si>
+  <si>
+    <t>Szeged 2011</t>
+  </si>
+  <si>
+    <t>Slutsk</t>
+  </si>
+  <si>
     <t>Napredak</t>
   </si>
   <si>
-    <t>Slutsk</t>
+    <t>Videoton</t>
+  </si>
+  <si>
+    <t>Austin II</t>
+  </si>
+  <si>
+    <t>Mezőkövesd-Zsóry</t>
   </si>
   <si>
     <t>Tatran Prešov</t>
   </si>
   <si>
-    <t>Szeged 2011</t>
-  </si>
-  <si>
-    <t>Budafoki MTE</t>
-  </si>
-  <si>
     <t>BVSC</t>
   </si>
   <si>
-    <t>Mezőkövesd-Zsóry</t>
-  </si>
-  <si>
-    <t>Videoton</t>
-  </si>
-  <si>
-    <t>Austin II</t>
-  </si>
-  <si>
     <t>Sint-Truiden</t>
   </si>
   <si>
+    <t>Ulm</t>
+  </si>
+  <si>
+    <t>Puszcza Niepołomice</t>
+  </si>
+  <si>
     <t>Akhmat Grozny</t>
   </si>
   <si>
-    <t>Puszcza Niepołomice</t>
-  </si>
-  <si>
-    <t>Ulm</t>
+    <t>Sparta Praha</t>
   </si>
   <si>
     <t>Újpest</t>
   </si>
   <si>
-    <t>Sparta Praha</t>
-  </si>
-  <si>
     <t>Columbus Crew II</t>
   </si>
   <si>
+    <t>Arka Gdynia</t>
+  </si>
+  <si>
     <t>Celje</t>
   </si>
   <si>
-    <t>Arka Gdynia</t>
-  </si>
-  <si>
     <t>CS U Craiova</t>
   </si>
   <si>
+    <t>Radnički Kragujevac</t>
+  </si>
+  <si>
     <t>CRB</t>
   </si>
   <si>
+    <t>Huachipato</t>
+  </si>
+  <si>
     <t>Cruzeiro</t>
   </si>
   <si>
-    <t>Radnički Kragujevac</t>
-  </si>
-  <si>
-    <t>Huachipato</t>
-  </si>
-  <si>
     <t>Fortaleza</t>
   </si>
   <si>
     <t>York9 FC</t>
   </si>
   <si>
+    <t>Everton</t>
+  </si>
+  <si>
+    <t>Bragantino</t>
+  </si>
+  <si>
     <t>Flamengo</t>
   </si>
   <si>
     <t>Paysandu</t>
   </si>
   <si>
-    <t>Everton</t>
-  </si>
-  <si>
-    <t>Bragantino</t>
+    <t>FC Cincinnati II</t>
   </si>
   <si>
     <t>Utah Royals</t>
-  </si>
-  <si>
-    <t>FC Cincinnati II</t>
   </si>
   <si>
     <t>Palmeiras</t>
@@ -2614,7 +2614,7 @@
         <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E10" t="s">
         <v>129</v>
@@ -2638,13 +2638,13 @@
         <v>391</v>
       </c>
       <c r="L10">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="M10">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N10">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -2680,10 +2680,10 @@
         <v>0</v>
       </c>
       <c r="Z10">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA10">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB10">
         <v>0</v>
@@ -2730,7 +2730,7 @@
         <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E11" t="s">
         <v>130</v>
@@ -2754,13 +2754,13 @@
         <v>391</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -2796,10 +2796,10 @@
         <v>0</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB11">
         <v>0</v>
@@ -2962,7 +2962,7 @@
         <v>82</v>
       </c>
       <c r="D13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E13" t="s">
         <v>132</v>
@@ -2986,13 +2986,13 @@
         <v>391</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -3034,10 +3034,10 @@
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD13">
         <v>0</v>
@@ -3310,7 +3310,7 @@
         <v>85</v>
       </c>
       <c r="D16" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E16" t="s">
         <v>135</v>
@@ -3334,13 +3334,13 @@
         <v>391</v>
       </c>
       <c r="L16">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M16">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N16">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O16">
         <v>0</v>
@@ -3382,10 +3382,10 @@
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD16">
         <v>0</v>
@@ -3539,10 +3539,10 @@
         <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E18" t="s">
         <v>137</v>
@@ -3566,13 +3566,13 @@
         <v>391</v>
       </c>
       <c r="L18">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M18">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N18">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -3614,16 +3614,16 @@
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC18">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD18">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE18">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF18">
         <v>0</v>
@@ -3655,7 +3655,7 @@
         <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D19" t="s">
         <v>120</v>
@@ -3682,13 +3682,13 @@
         <v>391</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -3730,16 +3730,16 @@
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF19">
         <v>0</v>
@@ -3798,13 +3798,13 @@
         <v>391</v>
       </c>
       <c r="L20">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="M20">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="N20">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>1.6</v>
       </c>
       <c r="AC20">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AD20">
         <v>0</v>
@@ -3914,13 +3914,13 @@
         <v>391</v>
       </c>
       <c r="L21">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="M21">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="N21">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -3965,7 +3965,7 @@
         <v>1.6</v>
       </c>
       <c r="AC21">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AD21">
         <v>0</v>
@@ -4003,10 +4003,10 @@
         <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D22" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E22" t="s">
         <v>141</v>
@@ -4235,7 +4235,7 @@
         <v>46</v>
       </c>
       <c r="C24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D24" t="s">
         <v>119</v>
@@ -4351,7 +4351,7 @@
         <v>46</v>
       </c>
       <c r="C25" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D25" t="s">
         <v>119</v>
@@ -4467,7 +4467,7 @@
         <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="D26" t="s">
         <v>120</v>
@@ -4494,13 +4494,13 @@
         <v>391</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -4542,10 +4542,10 @@
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD26">
         <v>0</v>
@@ -4583,10 +4583,10 @@
         <v>47</v>
       </c>
       <c r="C27" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D27" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E27" t="s">
         <v>146</v>
@@ -4699,10 +4699,10 @@
         <v>47</v>
       </c>
       <c r="C28" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E28" t="s">
         <v>147</v>
@@ -4815,7 +4815,7 @@
         <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D29" t="s">
         <v>119</v>
@@ -4931,10 +4931,10 @@
         <v>47</v>
       </c>
       <c r="C30" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D30" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E30" t="s">
         <v>149</v>
@@ -5047,10 +5047,10 @@
         <v>47</v>
       </c>
       <c r="C31" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="D31" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E31" t="s">
         <v>150</v>
@@ -5163,7 +5163,7 @@
         <v>47</v>
       </c>
       <c r="C32" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D32" t="s">
         <v>120</v>
@@ -5279,7 +5279,7 @@
         <v>47</v>
       </c>
       <c r="C33" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="D33" t="s">
         <v>120</v>
@@ -5306,13 +5306,13 @@
         <v>391</v>
       </c>
       <c r="L33">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M33">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N33">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -5354,10 +5354,10 @@
         <v>0</v>
       </c>
       <c r="AB33">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC33">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD33">
         <v>0</v>
@@ -5395,10 +5395,10 @@
         <v>48</v>
       </c>
       <c r="C34" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="D34" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E34" t="s">
         <v>153</v>
@@ -5511,10 +5511,10 @@
         <v>48</v>
       </c>
       <c r="C35" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="D35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E35" t="s">
         <v>154</v>
@@ -5538,13 +5538,13 @@
         <v>391</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="O35">
         <v>0</v>
@@ -5592,10 +5592,10 @@
         <v>0</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF35">
         <v>0</v>
@@ -5627,7 +5627,7 @@
         <v>48</v>
       </c>
       <c r="C36" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D36" t="s">
         <v>120</v>
@@ -5654,13 +5654,13 @@
         <v>391</v>
       </c>
       <c r="L36">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M36">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="N36">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="O36">
         <v>0</v>
@@ -5708,10 +5708,10 @@
         <v>0</v>
       </c>
       <c r="AD36">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE36">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AF36">
         <v>0</v>
@@ -6210,7 +6210,7 @@
         <v>97</v>
       </c>
       <c r="D41" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E41" t="s">
         <v>160</v>
@@ -6326,7 +6326,7 @@
         <v>98</v>
       </c>
       <c r="D42" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E42" t="s">
         <v>161</v>
@@ -6787,7 +6787,7 @@
         <v>52</v>
       </c>
       <c r="C46" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D46" t="s">
         <v>120</v>
@@ -7019,10 +7019,10 @@
         <v>52</v>
       </c>
       <c r="C48" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D48" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E48" t="s">
         <v>167</v>
@@ -7046,13 +7046,13 @@
         <v>391</v>
       </c>
       <c r="L48">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M48">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="O48">
         <v>0</v>
@@ -7367,7 +7367,7 @@
         <v>52</v>
       </c>
       <c r="C51" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="D51" t="s">
         <v>120</v>
@@ -7599,10 +7599,10 @@
         <v>52</v>
       </c>
       <c r="C53" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D53" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E53" t="s">
         <v>172</v>
@@ -7626,13 +7626,13 @@
         <v>391</v>
       </c>
       <c r="L53">
-        <v>1.26</v>
+        <v>2.6</v>
       </c>
       <c r="M53">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="N53">
-        <v>9.4</v>
+        <v>2.6</v>
       </c>
       <c r="O53">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD53">
         <v>0</v>
@@ -7715,7 +7715,7 @@
         <v>52</v>
       </c>
       <c r="C54" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D54" t="s">
         <v>120</v>
@@ -7742,13 +7742,13 @@
         <v>391</v>
       </c>
       <c r="L54">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M54">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N54">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O54">
         <v>0</v>
@@ -7790,10 +7790,10 @@
         <v>0</v>
       </c>
       <c r="AB54">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC54">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD54">
         <v>0</v>
@@ -7947,10 +7947,10 @@
         <v>52</v>
       </c>
       <c r="C56" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="D56" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E56" t="s">
         <v>175</v>
@@ -8063,7 +8063,7 @@
         <v>52</v>
       </c>
       <c r="C57" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="D57" t="s">
         <v>120</v>
@@ -8179,10 +8179,10 @@
         <v>52</v>
       </c>
       <c r="C58" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D58" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E58" t="s">
         <v>177</v>
@@ -8295,7 +8295,7 @@
         <v>53</v>
       </c>
       <c r="C59" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D59" t="s">
         <v>120</v>
@@ -8411,7 +8411,7 @@
         <v>53</v>
       </c>
       <c r="C60" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D60" t="s">
         <v>120</v>
@@ -8527,7 +8527,7 @@
         <v>53</v>
       </c>
       <c r="C61" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D61" t="s">
         <v>119</v>
@@ -8759,10 +8759,10 @@
         <v>54</v>
       </c>
       <c r="C63" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D63" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E63" t="s">
         <v>182</v>
@@ -8786,13 +8786,13 @@
         <v>391</v>
       </c>
       <c r="L63">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M63">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O63">
         <v>0</v>
@@ -8834,10 +8834,10 @@
         <v>0</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD63">
         <v>0</v>
@@ -8875,7 +8875,7 @@
         <v>54</v>
       </c>
       <c r="C64" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D64" t="s">
         <v>120</v>
@@ -8991,7 +8991,7 @@
         <v>54</v>
       </c>
       <c r="C65" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="D65" t="s">
         <v>120</v>
@@ -9018,13 +9018,13 @@
         <v>391</v>
       </c>
       <c r="L65">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M65">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N65">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O65">
         <v>0</v>
@@ -9066,10 +9066,10 @@
         <v>0</v>
       </c>
       <c r="AB65">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC65">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD65">
         <v>0</v>
@@ -9107,10 +9107,10 @@
         <v>54</v>
       </c>
       <c r="C66" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D66" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E66" t="s">
         <v>185</v>
@@ -9223,10 +9223,10 @@
         <v>54</v>
       </c>
       <c r="C67" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="D67" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E67" t="s">
         <v>186</v>
@@ -9339,10 +9339,10 @@
         <v>54</v>
       </c>
       <c r="C68" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="D68" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E68" t="s">
         <v>187</v>
@@ -9366,13 +9366,13 @@
         <v>391</v>
       </c>
       <c r="L68">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M68">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N68">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O68">
         <v>0</v>
@@ -9414,10 +9414,10 @@
         <v>0</v>
       </c>
       <c r="AB68">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC68">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD68">
         <v>0</v>
@@ -9455,7 +9455,7 @@
         <v>54</v>
       </c>
       <c r="C69" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="D69" t="s">
         <v>120</v>
@@ -9571,10 +9571,10 @@
         <v>54</v>
       </c>
       <c r="C70" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="D70" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E70" t="s">
         <v>189</v>
@@ -9687,7 +9687,7 @@
         <v>54</v>
       </c>
       <c r="C71" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="D71" t="s">
         <v>120</v>
@@ -9803,7 +9803,7 @@
         <v>54</v>
       </c>
       <c r="C72" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D72" t="s">
         <v>120</v>
@@ -9830,13 +9830,13 @@
         <v>391</v>
       </c>
       <c r="L72">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M72">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N72">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -9878,10 +9878,10 @@
         <v>0</v>
       </c>
       <c r="AB72">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC72">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD72">
         <v>0</v>
@@ -9919,10 +9919,10 @@
         <v>54</v>
       </c>
       <c r="C73" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="D73" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E73" t="s">
         <v>192</v>
@@ -10035,10 +10035,10 @@
         <v>54</v>
       </c>
       <c r="C74" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="D74" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E74" t="s">
         <v>193</v>
@@ -10151,7 +10151,7 @@
         <v>54</v>
       </c>
       <c r="C75" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D75" t="s">
         <v>120</v>
@@ -10178,13 +10178,13 @@
         <v>391</v>
       </c>
       <c r="L75">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M75">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O75">
         <v>0</v>
@@ -10226,10 +10226,10 @@
         <v>0</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD75">
         <v>0</v>
@@ -10267,10 +10267,10 @@
         <v>54</v>
       </c>
       <c r="C76" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="D76" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E76" t="s">
         <v>195</v>
@@ -10294,13 +10294,13 @@
         <v>391</v>
       </c>
       <c r="L76">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M76">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N76">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O76">
         <v>0</v>
@@ -10342,10 +10342,10 @@
         <v>0</v>
       </c>
       <c r="AB76">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC76">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD76">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>54</v>
       </c>
       <c r="C77" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="D77" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E77" t="s">
         <v>196</v>
@@ -10499,10 +10499,10 @@
         <v>54</v>
       </c>
       <c r="C78" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="D78" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E78" t="s">
         <v>197</v>
@@ -10526,13 +10526,13 @@
         <v>391</v>
       </c>
       <c r="L78">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M78">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O78">
         <v>0</v>
@@ -10574,10 +10574,10 @@
         <v>0</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD78">
         <v>0</v>
@@ -10615,7 +10615,7 @@
         <v>54</v>
       </c>
       <c r="C79" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D79" t="s">
         <v>120</v>
@@ -10642,13 +10642,13 @@
         <v>391</v>
       </c>
       <c r="L79">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M79">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O79">
         <v>0</v>
@@ -10690,10 +10690,10 @@
         <v>0</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD79">
         <v>0</v>
@@ -10731,7 +10731,7 @@
         <v>54</v>
       </c>
       <c r="C80" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="D80" t="s">
         <v>120</v>
@@ -10847,10 +10847,10 @@
         <v>54</v>
       </c>
       <c r="C81" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D81" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E81" t="s">
         <v>200</v>
@@ -10963,10 +10963,10 @@
         <v>54</v>
       </c>
       <c r="C82" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="D82" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E82" t="s">
         <v>201</v>
@@ -11222,13 +11222,13 @@
         <v>391</v>
       </c>
       <c r="L84">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M84">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N84">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O84">
         <v>0</v>
@@ -11270,10 +11270,10 @@
         <v>0</v>
       </c>
       <c r="AB84">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC84">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD84">
         <v>0</v>
@@ -11311,7 +11311,7 @@
         <v>55</v>
       </c>
       <c r="C85" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="D85" t="s">
         <v>120</v>
@@ -11338,13 +11338,13 @@
         <v>391</v>
       </c>
       <c r="L85">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="M85">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N85">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="O85">
         <v>0</v>
@@ -11386,10 +11386,10 @@
         <v>0</v>
       </c>
       <c r="AB85">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC85">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD85">
         <v>0</v>
@@ -11543,7 +11543,7 @@
         <v>55</v>
       </c>
       <c r="C87" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="D87" t="s">
         <v>120</v>
@@ -11570,13 +11570,13 @@
         <v>391</v>
       </c>
       <c r="L87">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M87">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O87">
         <v>0</v>
@@ -11659,7 +11659,7 @@
         <v>55</v>
       </c>
       <c r="C88" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D88" t="s">
         <v>120</v>
@@ -11775,7 +11775,7 @@
         <v>55</v>
       </c>
       <c r="C89" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D89" t="s">
         <v>120</v>
@@ -12123,7 +12123,7 @@
         <v>57</v>
       </c>
       <c r="C92" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="D92" t="s">
         <v>120</v>
@@ -12355,7 +12355,7 @@
         <v>57</v>
       </c>
       <c r="C94" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="D94" t="s">
         <v>120</v>
@@ -13051,7 +13051,7 @@
         <v>59</v>
       </c>
       <c r="C100" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D100" t="s">
         <v>120</v>
@@ -13167,7 +13167,7 @@
         <v>60</v>
       </c>
       <c r="C101" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D101" t="s">
         <v>120</v>
@@ -13283,10 +13283,10 @@
         <v>60</v>
       </c>
       <c r="C102" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="D102" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E102" t="s">
         <v>221</v>
@@ -13399,10 +13399,10 @@
         <v>60</v>
       </c>
       <c r="C103" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="D103" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E103" t="s">
         <v>222</v>
@@ -13515,7 +13515,7 @@
         <v>60</v>
       </c>
       <c r="C104" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D104" t="s">
         <v>120</v>
@@ -13631,7 +13631,7 @@
         <v>60</v>
       </c>
       <c r="C105" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D105" t="s">
         <v>120</v>
@@ -13747,10 +13747,10 @@
         <v>60</v>
       </c>
       <c r="C106" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D106" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E106" t="s">
         <v>225</v>
@@ -13863,7 +13863,7 @@
         <v>60</v>
       </c>
       <c r="C107" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D107" t="s">
         <v>120</v>
@@ -13979,7 +13979,7 @@
         <v>60</v>
       </c>
       <c r="C108" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D108" t="s">
         <v>120</v>
@@ -14095,10 +14095,10 @@
         <v>60</v>
       </c>
       <c r="C109" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D109" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E109" t="s">
         <v>228</v>
@@ -14211,7 +14211,7 @@
         <v>61</v>
       </c>
       <c r="C110" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D110" t="s">
         <v>120</v>
@@ -14327,7 +14327,7 @@
         <v>62</v>
       </c>
       <c r="C111" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D111" t="s">
         <v>120</v>
@@ -14354,13 +14354,13 @@
         <v>391</v>
       </c>
       <c r="L111">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M111">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N111">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="O111">
         <v>0</v>
@@ -14396,10 +14396,10 @@
         <v>0</v>
       </c>
       <c r="Z111">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA111">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB111">
         <v>0</v>
@@ -14559,7 +14559,7 @@
         <v>62</v>
       </c>
       <c r="C113" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D113" t="s">
         <v>120</v>
@@ -14586,13 +14586,13 @@
         <v>391</v>
       </c>
       <c r="L113">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M113">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="O113">
         <v>0</v>
@@ -14628,10 +14628,10 @@
         <v>0</v>
       </c>
       <c r="Z113">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA113">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB113">
         <v>0</v>
@@ -14675,7 +14675,7 @@
         <v>63</v>
       </c>
       <c r="C114" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="D114" t="s">
         <v>120</v>
@@ -14791,7 +14791,7 @@
         <v>63</v>
       </c>
       <c r="C115" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="D115" t="s">
         <v>120</v>
@@ -15023,7 +15023,7 @@
         <v>64</v>
       </c>
       <c r="C117" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="D117" t="s">
         <v>120</v>
@@ -15050,13 +15050,13 @@
         <v>391</v>
       </c>
       <c r="L117">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M117">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O117">
         <v>0</v>
@@ -15139,7 +15139,7 @@
         <v>64</v>
       </c>
       <c r="C118" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="D118" t="s">
         <v>120</v>
@@ -15166,13 +15166,13 @@
         <v>391</v>
       </c>
       <c r="L118">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M118">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N118">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O118">
         <v>0</v>
@@ -15255,7 +15255,7 @@
         <v>65</v>
       </c>
       <c r="C119" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D119" t="s">
         <v>120</v>
@@ -15371,10 +15371,10 @@
         <v>66</v>
       </c>
       <c r="C120" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D120" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E120" t="s">
         <v>239</v>
@@ -15487,7 +15487,7 @@
         <v>66</v>
       </c>
       <c r="C121" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D121" t="s">
         <v>119</v>
@@ -15514,13 +15514,13 @@
         <v>391</v>
       </c>
       <c r="L121">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M121">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N121">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O121">
         <v>0</v>
@@ -15556,16 +15556,16 @@
         <v>0</v>
       </c>
       <c r="Z121">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA121">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB121">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC121">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD121">
         <v>0</v>
@@ -15603,10 +15603,10 @@
         <v>66</v>
       </c>
       <c r="C122" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D122" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E122" t="s">
         <v>241</v>
@@ -15719,7 +15719,7 @@
         <v>66</v>
       </c>
       <c r="C123" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D123" t="s">
         <v>119</v>
@@ -15746,13 +15746,13 @@
         <v>391</v>
       </c>
       <c r="L123">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M123">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N123">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O123">
         <v>0</v>
@@ -15788,16 +15788,16 @@
         <v>0</v>
       </c>
       <c r="Z123">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA123">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB123">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC123">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD123">
         <v>0</v>
@@ -16067,7 +16067,7 @@
         <v>68</v>
       </c>
       <c r="C126" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D126" t="s">
         <v>119</v>
@@ -16094,13 +16094,13 @@
         <v>391</v>
       </c>
       <c r="L126">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M126">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N126">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O126">
         <v>0</v>
@@ -16142,10 +16142,10 @@
         <v>0</v>
       </c>
       <c r="AB126">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC126">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD126">
         <v>0</v>
@@ -16183,7 +16183,7 @@
         <v>68</v>
       </c>
       <c r="C127" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D127" t="s">
         <v>119</v>
@@ -16210,13 +16210,13 @@
         <v>391</v>
       </c>
       <c r="L127">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M127">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N127">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O127">
         <v>0</v>
@@ -16258,10 +16258,10 @@
         <v>0</v>
       </c>
       <c r="AB127">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC127">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD127">
         <v>0</v>
@@ -16299,7 +16299,7 @@
         <v>68</v>
       </c>
       <c r="C128" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D128" t="s">
         <v>119</v>
@@ -16326,13 +16326,13 @@
         <v>391</v>
       </c>
       <c r="L128">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M128">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N128">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O128">
         <v>0</v>
@@ -16374,10 +16374,10 @@
         <v>0</v>
       </c>
       <c r="AB128">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC128">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD128">
         <v>0</v>
@@ -16415,7 +16415,7 @@
         <v>68</v>
       </c>
       <c r="C129" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D129" t="s">
         <v>119</v>
@@ -16442,13 +16442,13 @@
         <v>391</v>
       </c>
       <c r="L129">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M129">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N129">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O129">
         <v>0</v>
@@ -16490,10 +16490,10 @@
         <v>0</v>
       </c>
       <c r="AB129">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC129">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD129">
         <v>0</v>
@@ -16531,7 +16531,7 @@
         <v>69</v>
       </c>
       <c r="C130" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D130" t="s">
         <v>119</v>
@@ -16647,7 +16647,7 @@
         <v>69</v>
       </c>
       <c r="C131" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D131" t="s">
         <v>119</v>

--- a/jogos_2025-08-03.xlsx
+++ b/jogos_2025-08-03.xlsx
@@ -274,27 +274,27 @@
     <t>China Chinese Super League</t>
   </si>
   <si>
+    <t>Belgium Pro League</t>
+  </si>
+  <si>
+    <t>Germany 3. Liga</t>
+  </si>
+  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
-    <t>Germany 3. Liga</t>
-  </si>
-  <si>
-    <t>Belgium Pro League</t>
+    <t>Switzerland Challenge League</t>
+  </si>
+  <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
+    <t>Denmark Superliga</t>
   </si>
   <si>
     <t>Switzerland Super League</t>
   </si>
   <si>
-    <t>Switzerland Challenge League</t>
-  </si>
-  <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
@@ -304,21 +304,21 @@
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
+    <t>Scotland Premiership</t>
+  </si>
+  <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
+    <t>Finland Veikkausliiga</t>
+  </si>
+  <si>
     <t>Czech Republic First League</t>
   </si>
   <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
-    <t>Scotland Premiership</t>
-  </si>
-  <si>
-    <t>Finland Veikkausliiga</t>
-  </si>
-  <si>
     <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
@@ -331,24 +331,24 @@
     <t>Montenegro Montenegrin First League</t>
   </si>
   <si>
+    <t>Uzbekistan Uzbekistan Super League</t>
+  </si>
+  <si>
+    <t>Austria Bundesliga</t>
+  </si>
+  <si>
     <t>Slovakia Super Liga</t>
   </si>
   <si>
-    <t>Uzbekistan Uzbekistan Super League</t>
-  </si>
-  <si>
-    <t>Austria Bundesliga</t>
-  </si>
-  <si>
     <t>Hungary NB II</t>
   </si>
   <si>
+    <t>Slovenia PrvaLiga</t>
+  </si>
+  <si>
     <t>Romania Liga I</t>
   </si>
   <si>
-    <t>Slovenia PrvaLiga</t>
-  </si>
-  <si>
     <t>Hungary NB I</t>
   </si>
   <si>
@@ -364,12 +364,12 @@
     <t>USA MLS Next Pro</t>
   </si>
   <si>
+    <t>Brazil Serie A</t>
+  </si>
+  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
-    <t>Brazil Serie A</t>
-  </si>
-  <si>
     <t>Canada Canadian Premier League</t>
   </si>
   <si>
@@ -379,15 +379,15 @@
     <t>2025/2026</t>
   </si>
   <si>
+    <t>Blacktown City</t>
+  </si>
+  <si>
+    <t>Sydney United</t>
+  </si>
+  <si>
     <t>Wollongong Wolves</t>
   </si>
   <si>
-    <t>Sydney United</t>
-  </si>
-  <si>
-    <t>Blacktown City</t>
-  </si>
-  <si>
     <t>Central Coast II</t>
   </si>
   <si>
@@ -424,66 +424,66 @@
     <t>Dalian Zhixing</t>
   </si>
   <si>
+    <t>KRC Genk</t>
+  </si>
+  <si>
+    <t>Erzgebirge Aue</t>
+  </si>
+  <si>
+    <t>Magdeburg</t>
+  </si>
+  <si>
     <t>Qingdao Red Lions</t>
   </si>
   <si>
+    <t>Hannover 96</t>
+  </si>
+  <si>
+    <t>Greuther Fürth</t>
+  </si>
+  <si>
     <t>Dongguan United</t>
   </si>
   <si>
-    <t>Greuther Fürth</t>
-  </si>
-  <si>
-    <t>Hannover 96</t>
-  </si>
-  <si>
-    <t>Magdeburg</t>
-  </si>
-  <si>
-    <t>Erzgebirge Aue</t>
-  </si>
-  <si>
-    <t>KRC Genk</t>
+    <t>Wuhan Three Towns</t>
   </si>
   <si>
     <t>Beijing Guoan</t>
   </si>
   <si>
-    <t>Wuhan Three Towns</t>
+    <t>Yverdon Sport</t>
+  </si>
+  <si>
+    <t>Djurgården</t>
+  </si>
+  <si>
+    <t>Häcken</t>
+  </si>
+  <si>
+    <t>Sichuan Jiuniu</t>
+  </si>
+  <si>
+    <t>SønderjyskE</t>
+  </si>
+  <si>
+    <t>Randers</t>
+  </si>
+  <si>
+    <t>Spartak Kostroma</t>
   </si>
   <si>
     <t>Thun</t>
   </si>
   <si>
-    <t>Yverdon Sport</t>
-  </si>
-  <si>
-    <t>Häcken</t>
-  </si>
-  <si>
-    <t>Djurgården</t>
-  </si>
-  <si>
-    <t>Sichuan Jiuniu</t>
-  </si>
-  <si>
-    <t>Randers</t>
-  </si>
-  <si>
-    <t>SønderjyskE</t>
-  </si>
-  <si>
-    <t>Spartak Kostroma</t>
-  </si>
-  <si>
     <t>HamKam</t>
   </si>
   <si>
+    <t>Baník Ostrava II</t>
+  </si>
+  <si>
     <t>Epitsentr Dunayivtsi</t>
   </si>
   <si>
-    <t>Baník Ostrava II</t>
-  </si>
-  <si>
     <t>Śląsk Wrocław</t>
   </si>
   <si>
@@ -493,213 +493,213 @@
     <t>Cracovia Kraków</t>
   </si>
   <si>
+    <t>Falkirk</t>
+  </si>
+  <si>
+    <t>Sogndal</t>
+  </si>
+  <si>
     <t>Landskrona</t>
   </si>
   <si>
+    <t>SJK</t>
+  </si>
+  <si>
     <t>Slovácko</t>
   </si>
   <si>
-    <t>Sogndal</t>
-  </si>
-  <si>
-    <t>Falkirk</t>
-  </si>
-  <si>
-    <t>SJK</t>
-  </si>
-  <si>
     <t>Suduroy</t>
   </si>
   <si>
+    <t>Differdange 03</t>
+  </si>
+  <si>
+    <t>Mondorf-les-Bains</t>
+  </si>
+  <si>
+    <t>EB - Streymur</t>
+  </si>
+  <si>
+    <t>Dundee</t>
+  </si>
+  <si>
     <t>AGF</t>
   </si>
   <si>
+    <t>Rodange</t>
+  </si>
+  <si>
+    <t>Harju Jalgpallikool</t>
+  </si>
+  <si>
+    <t>Jeunesse d'Esch</t>
+  </si>
+  <si>
+    <t>F91 Dudelange</t>
+  </si>
+  <si>
+    <t>Hostert</t>
+  </si>
+  <si>
+    <t>Cercle Brugge</t>
+  </si>
+  <si>
     <t>Jeunesse Canach</t>
   </si>
   <si>
-    <t>Harju Jalgpallikool</t>
-  </si>
-  <si>
     <t>Swift Hesperange</t>
   </si>
   <si>
-    <t>Hostert</t>
-  </si>
-  <si>
-    <t>Cercle Brugge</t>
-  </si>
-  <si>
-    <t>F91 Dudelange</t>
-  </si>
-  <si>
-    <t>Dundee</t>
-  </si>
-  <si>
-    <t>Differdange 03</t>
-  </si>
-  <si>
-    <t>Rodange</t>
-  </si>
-  <si>
-    <t>EB - Streymur</t>
-  </si>
-  <si>
-    <t>Mondorf-les-Bains</t>
-  </si>
-  <si>
-    <t>Jeunesse d'Esch</t>
+    <t>Sirius</t>
   </si>
   <si>
     <t>Luzern</t>
   </si>
   <si>
+    <t>Étoile Carouge</t>
+  </si>
+  <si>
     <t>Viktoria Köln</t>
   </si>
   <si>
-    <t>Sirius</t>
-  </si>
-  <si>
-    <t>Étoile Carouge</t>
+    <t>Arsenal Tivat</t>
   </si>
   <si>
     <t>Zenit</t>
   </si>
   <si>
+    <t>Shortan</t>
+  </si>
+  <si>
+    <t>Dukla Praha</t>
+  </si>
+  <si>
+    <t>Rubin Kazan</t>
+  </si>
+  <si>
+    <t>Torpedo BelAZ</t>
+  </si>
+  <si>
+    <t>Karpaty</t>
+  </si>
+  <si>
+    <t>Vlašim</t>
+  </si>
+  <si>
+    <t>Strømsgodset</t>
+  </si>
+  <si>
+    <t>Grazer AK</t>
+  </si>
+  <si>
+    <t>Trenčín</t>
+  </si>
+  <si>
+    <t>Vålerenga</t>
+  </si>
+  <si>
+    <t>KFUM</t>
+  </si>
+  <si>
+    <t>Molde</t>
+  </si>
+  <si>
     <t>Sutjeska</t>
   </si>
   <si>
+    <t>Pogoń Siedlce</t>
+  </si>
+  <si>
+    <t>FK Jezero Plav</t>
+  </si>
+  <si>
     <t>Dečić</t>
   </si>
   <si>
-    <t>Trenčín</t>
-  </si>
-  <si>
-    <t>Molde</t>
-  </si>
-  <si>
-    <t>KFUM</t>
+    <t>Rapid Wien</t>
   </si>
   <si>
     <t>Petrovac</t>
   </si>
   <si>
-    <t>Arsenal Tivat</t>
-  </si>
-  <si>
-    <t>Rubin Kazan</t>
-  </si>
-  <si>
-    <t>FK Jezero Plav</t>
-  </si>
-  <si>
-    <t>Shortan</t>
-  </si>
-  <si>
-    <t>Strømsgodset</t>
-  </si>
-  <si>
-    <t>Rapid Wien</t>
-  </si>
-  <si>
-    <t>Vålerenga</t>
-  </si>
-  <si>
-    <t>Vlašim</t>
-  </si>
-  <si>
-    <t>Karpaty</t>
-  </si>
-  <si>
-    <t>Grazer AK</t>
-  </si>
-  <si>
-    <t>Pogoń Siedlce</t>
-  </si>
-  <si>
-    <t>Dukla Praha</t>
-  </si>
-  <si>
-    <t>Torpedo BelAZ</t>
+    <t>Karcag SE</t>
+  </si>
+  <si>
+    <t>Celtic</t>
+  </si>
+  <si>
+    <t>Maribor</t>
+  </si>
+  <si>
+    <t>Hermannstadt</t>
+  </si>
+  <si>
+    <t>Szentlőrinc SE</t>
+  </si>
+  <si>
+    <t>Motor Lublin</t>
   </si>
   <si>
     <t>Radomiak Radom</t>
   </si>
   <si>
-    <t>Szentlőrinc SE</t>
-  </si>
-  <si>
-    <t>Hermannstadt</t>
-  </si>
-  <si>
-    <t>Celtic</t>
-  </si>
-  <si>
-    <t>Motor Lublin</t>
-  </si>
-  <si>
-    <t>Karcag SE</t>
-  </si>
-  <si>
-    <t>Maribor</t>
-  </si>
-  <si>
     <t>Puskás</t>
   </si>
   <si>
     <t>Várda SE</t>
   </si>
   <si>
+    <t>Brøndby</t>
+  </si>
+  <si>
+    <t>Tammeka</t>
+  </si>
+  <si>
+    <t>Vysočina Jihlava</t>
+  </si>
+  <si>
+    <t>FK Chernomorets Novorossiysk</t>
+  </si>
+  <si>
     <t>Fakel</t>
   </si>
   <si>
-    <t>FK Chernomorets Novorossiysk</t>
-  </si>
-  <si>
-    <t>Brøndby</t>
-  </si>
-  <si>
-    <t>Tammeka</t>
-  </si>
-  <si>
-    <t>Vysočina Jihlava</t>
-  </si>
-  <si>
     <t>B68</t>
   </si>
   <si>
+    <t>Union Saint-Gilloise</t>
+  </si>
+  <si>
     <t>O'Higgins</t>
   </si>
   <si>
     <t>Washington Spirit</t>
   </si>
   <si>
-    <t>Union Saint-Gilloise</t>
+    <t>Železničar Pančevo</t>
+  </si>
+  <si>
+    <t>Ajka</t>
+  </si>
+  <si>
+    <t>MKK-Dnepr</t>
+  </si>
+  <si>
+    <t>Žilina</t>
+  </si>
+  <si>
+    <t>Tiszakécske</t>
   </si>
   <si>
     <t>Honvéd W</t>
   </si>
   <si>
+    <t>Sporting KC II</t>
+  </si>
+  <si>
     <t>Békéscsaba</t>
   </si>
   <si>
-    <t>MKK-Dnepr</t>
-  </si>
-  <si>
-    <t>Železničar Pančevo</t>
-  </si>
-  <si>
-    <t>Ajka</t>
-  </si>
-  <si>
-    <t>Sporting KC II</t>
-  </si>
-  <si>
-    <t>Tiszakécske</t>
-  </si>
-  <si>
-    <t>Žilina</t>
-  </si>
-  <si>
     <t>Csákvári TK</t>
   </si>
   <si>
@@ -709,45 +709,45 @@
     <t>Wehen Wiesbaden</t>
   </si>
   <si>
+    <t>Makhachkala</t>
+  </si>
+  <si>
     <t>Górnik Łęczna</t>
   </si>
   <si>
-    <t>Makhachkala</t>
+    <t>Győri ETO</t>
   </si>
   <si>
     <t>Pardubice</t>
   </si>
   <si>
-    <t>Győri ETO</t>
-  </si>
-  <si>
     <t>Chicago Fire II</t>
   </si>
   <si>
+    <t>Olimpija</t>
+  </si>
+  <si>
     <t>Legia Warszawa</t>
   </si>
   <si>
-    <t>Olimpija</t>
-  </si>
-  <si>
     <t>CFR Cluj</t>
   </si>
   <si>
     <t>Partizan</t>
   </si>
   <si>
+    <t>Botafogo</t>
+  </si>
+  <si>
+    <t>Corinthians</t>
+  </si>
+  <si>
     <t>Chapecoense</t>
   </si>
   <si>
     <t>Colo-Colo</t>
   </si>
   <si>
-    <t>Botafogo</t>
-  </si>
-  <si>
-    <t>Corinthians</t>
-  </si>
-  <si>
     <t>Atlético Ottawa</t>
   </si>
   <si>
@@ -757,12 +757,12 @@
     <t>Atlético Mineiro</t>
   </si>
   <si>
+    <t>Atlético PR</t>
+  </si>
+  <si>
     <t>Ceará</t>
   </si>
   <si>
-    <t>Atlético PR</t>
-  </si>
-  <si>
     <t>Philadelphia Union II</t>
   </si>
   <si>
@@ -784,15 +784,15 @@
     <t>Los Angeles II</t>
   </si>
   <si>
+    <t>Mt Druitt Town</t>
+  </si>
+  <si>
+    <t>St. George Saints</t>
+  </si>
+  <si>
     <t>Sydney II</t>
   </si>
   <si>
-    <t>St. George Saints</t>
-  </si>
-  <si>
-    <t>Mt Druitt Town</t>
-  </si>
-  <si>
     <t>Marconi Stallions</t>
   </si>
   <si>
@@ -829,66 +829,66 @@
     <t>Qingdao Jonoon</t>
   </si>
   <si>
+    <t>Royal Antwerp FC</t>
+  </si>
+  <si>
+    <t>Hansa Rostock</t>
+  </si>
+  <si>
+    <t>Eintracht Braunschweig</t>
+  </si>
+  <si>
     <t>Heilongjiang Lava Spring</t>
   </si>
   <si>
+    <t>Kaiserslautern</t>
+  </si>
+  <si>
+    <t>Dynamo Dresden</t>
+  </si>
+  <si>
     <t>Nantong Zhiyun</t>
   </si>
   <si>
-    <t>Dynamo Dresden</t>
-  </si>
-  <si>
-    <t>Kaiserslautern</t>
-  </si>
-  <si>
-    <t>Eintracht Braunschweig</t>
-  </si>
-  <si>
-    <t>Hansa Rostock</t>
-  </si>
-  <si>
-    <t>Royal Antwerp FC</t>
+    <t>Changchun Yatai</t>
   </si>
   <si>
     <t>Tianjin Teda</t>
   </si>
   <si>
-    <t>Changchun Yatai</t>
+    <t>Stade Lausanne-Ouchy</t>
+  </si>
+  <si>
+    <t>Halmstad</t>
+  </si>
+  <si>
+    <t>Elfsborg</t>
+  </si>
+  <si>
+    <t>Zhejiang FC</t>
+  </si>
+  <si>
+    <t>Nordsjælland</t>
+  </si>
+  <si>
+    <t>Silkeborg</t>
+  </si>
+  <si>
+    <t>Neftekhimik</t>
   </si>
   <si>
     <t>Lausanne Sport</t>
   </si>
   <si>
-    <t>Stade Lausanne-Ouchy</t>
-  </si>
-  <si>
-    <t>Elfsborg</t>
-  </si>
-  <si>
-    <t>Halmstad</t>
-  </si>
-  <si>
-    <t>Zhejiang FC</t>
-  </si>
-  <si>
-    <t>Silkeborg</t>
-  </si>
-  <si>
-    <t>Nordsjælland</t>
-  </si>
-  <si>
-    <t>Neftekhimik</t>
-  </si>
-  <si>
     <t>FK Bodo - Glimt</t>
   </si>
   <si>
+    <t>Líšeň</t>
+  </si>
+  <si>
     <t>Shakhtar Donetsk</t>
   </si>
   <si>
-    <t>Líšeň</t>
-  </si>
-  <si>
     <t>Ruch Chorzów</t>
   </si>
   <si>
@@ -898,213 +898,213 @@
     <t>Lechia Gdańsk</t>
   </si>
   <si>
+    <t>Dundee United</t>
+  </si>
+  <si>
+    <t>Skeid</t>
+  </si>
+  <si>
     <t>Västerås SK</t>
   </si>
   <si>
+    <t>KTP</t>
+  </si>
+  <si>
     <t>Slavia Praha</t>
   </si>
   <si>
-    <t>Skeid</t>
-  </si>
-  <si>
-    <t>Dundee United</t>
-  </si>
-  <si>
-    <t>KTP</t>
-  </si>
-  <si>
     <t>HB</t>
   </si>
   <si>
+    <t>Atert Bissen</t>
+  </si>
+  <si>
+    <t>UNA Strassen</t>
+  </si>
+  <si>
+    <t>KÍ</t>
+  </si>
+  <si>
+    <t>Hibernian</t>
+  </si>
+  <si>
     <t>Midtjylland</t>
   </si>
   <si>
+    <t>Racing</t>
+  </si>
+  <si>
+    <t>Paide</t>
+  </si>
+  <si>
+    <t>UN Käerjéng</t>
+  </si>
+  <si>
+    <t>Progrès Niederkorn</t>
+  </si>
+  <si>
+    <t>Victoria Rosport</t>
+  </si>
+  <si>
+    <t>RSC Anderlecht</t>
+  </si>
+  <si>
     <t>Mamer</t>
   </si>
   <si>
-    <t>Paide</t>
-  </si>
-  <si>
     <t>UT Pétange</t>
   </si>
   <si>
-    <t>Victoria Rosport</t>
-  </si>
-  <si>
-    <t>RSC Anderlecht</t>
-  </si>
-  <si>
-    <t>Progrès Niederkorn</t>
-  </si>
-  <si>
-    <t>Hibernian</t>
-  </si>
-  <si>
-    <t>Atert Bissen</t>
-  </si>
-  <si>
-    <t>Racing</t>
-  </si>
-  <si>
-    <t>KÍ</t>
-  </si>
-  <si>
-    <t>UNA Strassen</t>
-  </si>
-  <si>
-    <t>UN Käerjéng</t>
+    <t>Öster</t>
   </si>
   <si>
     <t>Zürich</t>
   </si>
   <si>
+    <t>Vaduz</t>
+  </si>
+  <si>
     <t>Schweinfurt</t>
   </si>
   <si>
-    <t>Öster</t>
-  </si>
-  <si>
-    <t>Vaduz</t>
+    <t>Jedinstvo</t>
   </si>
   <si>
     <t>CSKA Moskva</t>
   </si>
   <si>
+    <t>Xorazm</t>
+  </si>
+  <si>
+    <t>Baník Ostrava</t>
+  </si>
+  <si>
+    <t>FK Sochi</t>
+  </si>
+  <si>
+    <t>Gomel</t>
+  </si>
+  <si>
+    <t>Polessya</t>
+  </si>
+  <si>
+    <t>Hanácká</t>
+  </si>
+  <si>
+    <t>Haugesund</t>
+  </si>
+  <si>
+    <t>Austria Wien</t>
+  </si>
+  <si>
+    <t>Spartak Trnava</t>
+  </si>
+  <si>
+    <t>Sandefjord</t>
+  </si>
+  <si>
+    <t>Rosenborg</t>
+  </si>
+  <si>
+    <t>Bryne</t>
+  </si>
+  <si>
     <t>Mornar</t>
   </si>
   <si>
+    <t>Odra Opole</t>
+  </si>
+  <si>
+    <t>Budućnost</t>
+  </si>
+  <si>
     <t>Mladost DG</t>
   </si>
   <si>
-    <t>Spartak Trnava</t>
-  </si>
-  <si>
-    <t>Bryne</t>
-  </si>
-  <si>
-    <t>Rosenborg</t>
+    <t>Blau-Weiß Linz</t>
   </si>
   <si>
     <t>Bokelj</t>
   </si>
   <si>
-    <t>Jedinstvo</t>
-  </si>
-  <si>
-    <t>FK Sochi</t>
-  </si>
-  <si>
-    <t>Budućnost</t>
-  </si>
-  <si>
-    <t>Xorazm</t>
-  </si>
-  <si>
-    <t>Haugesund</t>
-  </si>
-  <si>
-    <t>Blau-Weiß Linz</t>
-  </si>
-  <si>
-    <t>Sandefjord</t>
-  </si>
-  <si>
-    <t>Hanácká</t>
-  </si>
-  <si>
-    <t>Polessya</t>
-  </si>
-  <si>
-    <t>Austria Wien</t>
-  </si>
-  <si>
-    <t>Odra Opole</t>
-  </si>
-  <si>
-    <t>Baník Ostrava</t>
-  </si>
-  <si>
-    <t>Gomel</t>
+    <t>Soroksár SC</t>
+  </si>
+  <si>
+    <t>St. Mirren</t>
+  </si>
+  <si>
+    <t>Koper</t>
+  </si>
+  <si>
+    <t>Universitatea Cluj</t>
+  </si>
+  <si>
+    <t>Kozármisleny</t>
+  </si>
+  <si>
+    <t>Jagiellonia Białystok</t>
   </si>
   <si>
     <t>Raków Częstochowa</t>
   </si>
   <si>
-    <t>Kozármisleny</t>
-  </si>
-  <si>
-    <t>Universitatea Cluj</t>
-  </si>
-  <si>
-    <t>St. Mirren</t>
-  </si>
-  <si>
-    <t>Jagiellonia Białystok</t>
-  </si>
-  <si>
-    <t>Soroksár SC</t>
-  </si>
-  <si>
-    <t>Koper</t>
-  </si>
-  <si>
     <t>Nyíregyháza Spartacus</t>
   </si>
   <si>
     <t>Paksi SE</t>
   </si>
   <si>
+    <t>Viborg</t>
+  </si>
+  <si>
+    <t>Nõmme Kalju</t>
+  </si>
+  <si>
+    <t>Vyškov</t>
+  </si>
+  <si>
+    <t>Arsenal Tula</t>
+  </si>
+  <si>
     <t>Sokol Saratov</t>
   </si>
   <si>
-    <t>Arsenal Tula</t>
-  </si>
-  <si>
-    <t>Viborg</t>
-  </si>
-  <si>
-    <t>Nõmme Kalju</t>
-  </si>
-  <si>
-    <t>Vyškov</t>
-  </si>
-  <si>
     <t>NSÍ</t>
   </si>
   <si>
+    <t>OH Leuven</t>
+  </si>
+  <si>
     <t>Unión La Calera</t>
   </si>
   <si>
     <t>Portland Thorns</t>
   </si>
   <si>
-    <t>OH Leuven</t>
+    <t>Napredak</t>
+  </si>
+  <si>
+    <t>Videoton</t>
+  </si>
+  <si>
+    <t>Slutsk</t>
+  </si>
+  <si>
+    <t>Tatran Prešov</t>
+  </si>
+  <si>
+    <t>Mezőkövesd-Zsóry</t>
   </si>
   <si>
     <t>Budafoki MTE</t>
   </si>
   <si>
+    <t>Austin II</t>
+  </si>
+  <si>
     <t>Szeged 2011</t>
   </si>
   <si>
-    <t>Slutsk</t>
-  </si>
-  <si>
-    <t>Napredak</t>
-  </si>
-  <si>
-    <t>Videoton</t>
-  </si>
-  <si>
-    <t>Austin II</t>
-  </si>
-  <si>
-    <t>Mezőkövesd-Zsóry</t>
-  </si>
-  <si>
-    <t>Tatran Prešov</t>
-  </si>
-  <si>
     <t>BVSC</t>
   </si>
   <si>
@@ -1114,45 +1114,45 @@
     <t>Ulm</t>
   </si>
   <si>
+    <t>Akhmat Grozny</t>
+  </si>
+  <si>
     <t>Puszcza Niepołomice</t>
   </si>
   <si>
-    <t>Akhmat Grozny</t>
+    <t>Újpest</t>
   </si>
   <si>
     <t>Sparta Praha</t>
   </si>
   <si>
-    <t>Újpest</t>
-  </si>
-  <si>
     <t>Columbus Crew II</t>
   </si>
   <si>
+    <t>Celje</t>
+  </si>
+  <si>
     <t>Arka Gdynia</t>
   </si>
   <si>
-    <t>Celje</t>
-  </si>
-  <si>
     <t>CS U Craiova</t>
   </si>
   <si>
     <t>Radnički Kragujevac</t>
   </si>
   <si>
+    <t>Cruzeiro</t>
+  </si>
+  <si>
+    <t>Fortaleza</t>
+  </si>
+  <si>
     <t>CRB</t>
   </si>
   <si>
     <t>Huachipato</t>
   </si>
   <si>
-    <t>Cruzeiro</t>
-  </si>
-  <si>
-    <t>Fortaleza</t>
-  </si>
-  <si>
     <t>York9 FC</t>
   </si>
   <si>
@@ -1162,10 +1162,10 @@
     <t>Bragantino</t>
   </si>
   <si>
+    <t>Paysandu</t>
+  </si>
+  <si>
     <t>Flamengo</t>
-  </si>
-  <si>
-    <t>Paysandu</t>
   </si>
   <si>
     <t>FC Cincinnati II</t>
@@ -2638,13 +2638,13 @@
         <v>391</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -2686,10 +2686,10 @@
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD10">
         <v>0</v>
@@ -3423,10 +3423,10 @@
         <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D17" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E17" t="s">
         <v>136</v>
@@ -3539,10 +3539,10 @@
         <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D18" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E18" t="s">
         <v>137</v>
@@ -3655,7 +3655,7 @@
         <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D19" t="s">
         <v>120</v>
@@ -3682,13 +3682,13 @@
         <v>391</v>
       </c>
       <c r="L19">
-        <v>2.26</v>
+        <v>1.65</v>
       </c>
       <c r="M19">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N19">
-        <v>2.95</v>
+        <v>4.8</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -3730,16 +3730,16 @@
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC19">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD19">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE19">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF19">
         <v>0</v>
@@ -3771,10 +3771,10 @@
         <v>45</v>
       </c>
       <c r="C20" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E20" t="s">
         <v>139</v>
@@ -3798,13 +3798,13 @@
         <v>391</v>
       </c>
       <c r="L20">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M20">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N20">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -3846,10 +3846,10 @@
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC20">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD20">
         <v>0</v>
@@ -3887,7 +3887,7 @@
         <v>45</v>
       </c>
       <c r="C21" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D21" t="s">
         <v>120</v>
@@ -3914,13 +3914,13 @@
         <v>391</v>
       </c>
       <c r="L21">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="M21">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="N21">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -3965,7 +3965,7 @@
         <v>1.6</v>
       </c>
       <c r="AC21">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AD21">
         <v>0</v>
@@ -4003,7 +4003,7 @@
         <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D22" t="s">
         <v>120</v>
@@ -4030,13 +4030,13 @@
         <v>391</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -4078,16 +4078,16 @@
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF22">
         <v>0</v>
@@ -4119,10 +4119,10 @@
         <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E23" t="s">
         <v>142</v>
@@ -4262,13 +4262,13 @@
         <v>391</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O24">
         <v>0</v>
@@ -4378,13 +4378,13 @@
         <v>391</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O25">
         <v>0</v>
@@ -4494,13 +4494,13 @@
         <v>391</v>
       </c>
       <c r="L26">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M26">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N26">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -4542,10 +4542,10 @@
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC26">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD26">
         <v>0</v>
@@ -4586,7 +4586,7 @@
         <v>90</v>
       </c>
       <c r="D27" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E27" t="s">
         <v>146</v>
@@ -4610,13 +4610,13 @@
         <v>391</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -4658,10 +4658,10 @@
         <v>0</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD27">
         <v>0</v>
@@ -4699,7 +4699,7 @@
         <v>47</v>
       </c>
       <c r="C28" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D28" t="s">
         <v>119</v>
@@ -4815,7 +4815,7 @@
         <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D29" t="s">
         <v>119</v>
@@ -4931,10 +4931,10 @@
         <v>47</v>
       </c>
       <c r="C30" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D30" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E30" t="s">
         <v>149</v>
@@ -5047,7 +5047,7 @@
         <v>47</v>
       </c>
       <c r="C31" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D31" t="s">
         <v>120</v>
@@ -5163,7 +5163,7 @@
         <v>47</v>
       </c>
       <c r="C32" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="D32" t="s">
         <v>120</v>
@@ -5279,7 +5279,7 @@
         <v>47</v>
       </c>
       <c r="C33" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="D33" t="s">
         <v>120</v>
@@ -5306,13 +5306,13 @@
         <v>391</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -5354,10 +5354,10 @@
         <v>0</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD33">
         <v>0</v>
@@ -5511,7 +5511,7 @@
         <v>48</v>
       </c>
       <c r="C35" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D35" t="s">
         <v>120</v>
@@ -5538,13 +5538,13 @@
         <v>391</v>
       </c>
       <c r="L35">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M35">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="N35">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="O35">
         <v>0</v>
@@ -5592,10 +5592,10 @@
         <v>0</v>
       </c>
       <c r="AD35">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE35">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AF35">
         <v>0</v>
@@ -5627,7 +5627,7 @@
         <v>48</v>
       </c>
       <c r="C36" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D36" t="s">
         <v>120</v>
@@ -5654,13 +5654,13 @@
         <v>391</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="O36">
         <v>0</v>
@@ -5708,10 +5708,10 @@
         <v>0</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF36">
         <v>0</v>
@@ -6094,7 +6094,7 @@
         <v>96</v>
       </c>
       <c r="D40" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E40" t="s">
         <v>159</v>
@@ -6118,13 +6118,13 @@
         <v>391</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M40">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O40">
         <v>0</v>
@@ -6166,10 +6166,10 @@
         <v>0</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD40">
         <v>0</v>
@@ -6210,7 +6210,7 @@
         <v>97</v>
       </c>
       <c r="D41" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E41" t="s">
         <v>160</v>
@@ -6350,13 +6350,13 @@
         <v>391</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M42">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O42">
         <v>0</v>
@@ -6442,7 +6442,7 @@
         <v>99</v>
       </c>
       <c r="D43" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E43" t="s">
         <v>162</v>
@@ -6466,13 +6466,13 @@
         <v>391</v>
       </c>
       <c r="L43">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M43">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N43">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O43">
         <v>0</v>
@@ -6514,10 +6514,10 @@
         <v>0</v>
       </c>
       <c r="AB43">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC43">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD43">
         <v>0</v>
@@ -6558,7 +6558,7 @@
         <v>100</v>
       </c>
       <c r="D44" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E44" t="s">
         <v>163</v>
@@ -6787,7 +6787,7 @@
         <v>52</v>
       </c>
       <c r="C46" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="D46" t="s">
         <v>120</v>
@@ -7019,7 +7019,7 @@
         <v>52</v>
       </c>
       <c r="C48" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D48" t="s">
         <v>119</v>
@@ -7046,13 +7046,13 @@
         <v>391</v>
       </c>
       <c r="L48">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M48">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N48">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="O48">
         <v>0</v>
@@ -7135,7 +7135,7 @@
         <v>52</v>
       </c>
       <c r="C49" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D49" t="s">
         <v>120</v>
@@ -7162,13 +7162,13 @@
         <v>391</v>
       </c>
       <c r="L49">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M49">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O49">
         <v>0</v>
@@ -7210,10 +7210,10 @@
         <v>0</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD49">
         <v>0</v>
@@ -7251,7 +7251,7 @@
         <v>52</v>
       </c>
       <c r="C50" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="D50" t="s">
         <v>120</v>
@@ -7367,7 +7367,7 @@
         <v>52</v>
       </c>
       <c r="C51" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="D51" t="s">
         <v>120</v>
@@ -7483,10 +7483,10 @@
         <v>52</v>
       </c>
       <c r="C52" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D52" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E52" t="s">
         <v>171</v>
@@ -7510,13 +7510,13 @@
         <v>391</v>
       </c>
       <c r="L52">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M52">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="O52">
         <v>0</v>
@@ -7599,7 +7599,7 @@
         <v>52</v>
       </c>
       <c r="C53" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D53" t="s">
         <v>120</v>
@@ -7626,13 +7626,13 @@
         <v>391</v>
       </c>
       <c r="L53">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M53">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N53">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O53">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="AB53">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC53">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD53">
         <v>0</v>
@@ -7947,10 +7947,10 @@
         <v>52</v>
       </c>
       <c r="C56" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="D56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E56" t="s">
         <v>175</v>
@@ -7974,13 +7974,13 @@
         <v>391</v>
       </c>
       <c r="L56">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M56">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O56">
         <v>0</v>
@@ -8022,10 +8022,10 @@
         <v>0</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD56">
         <v>0</v>
@@ -8295,10 +8295,10 @@
         <v>53</v>
       </c>
       <c r="C59" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D59" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E59" t="s">
         <v>178</v>
@@ -8322,13 +8322,13 @@
         <v>391</v>
       </c>
       <c r="L59">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M59">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N59">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O59">
         <v>0</v>
@@ -8370,10 +8370,10 @@
         <v>0</v>
       </c>
       <c r="AB59">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC59">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AD59">
         <v>0</v>
@@ -8411,7 +8411,7 @@
         <v>53</v>
       </c>
       <c r="C60" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D60" t="s">
         <v>120</v>
@@ -8438,13 +8438,13 @@
         <v>391</v>
       </c>
       <c r="L60">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M60">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O60">
         <v>0</v>
@@ -8486,10 +8486,10 @@
         <v>0</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD60">
         <v>0</v>
@@ -8527,10 +8527,10 @@
         <v>53</v>
       </c>
       <c r="C61" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D61" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E61" t="s">
         <v>180</v>
@@ -8643,7 +8643,7 @@
         <v>53</v>
       </c>
       <c r="C62" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D62" t="s">
         <v>120</v>
@@ -8759,7 +8759,7 @@
         <v>54</v>
       </c>
       <c r="C63" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="D63" t="s">
         <v>120</v>
@@ -8786,13 +8786,13 @@
         <v>391</v>
       </c>
       <c r="L63">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M63">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N63">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O63">
         <v>0</v>
@@ -8834,10 +8834,10 @@
         <v>0</v>
       </c>
       <c r="AB63">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC63">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD63">
         <v>0</v>
@@ -8875,7 +8875,7 @@
         <v>54</v>
       </c>
       <c r="C64" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="D64" t="s">
         <v>120</v>
@@ -8902,13 +8902,13 @@
         <v>391</v>
       </c>
       <c r="L64">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M64">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O64">
         <v>0</v>
@@ -8950,10 +8950,10 @@
         <v>0</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD64">
         <v>0</v>
@@ -8991,10 +8991,10 @@
         <v>54</v>
       </c>
       <c r="C65" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D65" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E65" t="s">
         <v>184</v>
@@ -9107,7 +9107,7 @@
         <v>54</v>
       </c>
       <c r="C66" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D66" t="s">
         <v>120</v>
@@ -9223,10 +9223,10 @@
         <v>54</v>
       </c>
       <c r="C67" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D67" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E67" t="s">
         <v>186</v>
@@ -9339,7 +9339,7 @@
         <v>54</v>
       </c>
       <c r="C68" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="D68" t="s">
         <v>119</v>
@@ -9455,7 +9455,7 @@
         <v>54</v>
       </c>
       <c r="C69" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="D69" t="s">
         <v>120</v>
@@ -9482,13 +9482,13 @@
         <v>391</v>
       </c>
       <c r="L69">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M69">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O69">
         <v>0</v>
@@ -9530,10 +9530,10 @@
         <v>0</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD69">
         <v>0</v>
@@ -9571,7 +9571,7 @@
         <v>54</v>
       </c>
       <c r="C70" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="D70" t="s">
         <v>120</v>
@@ -9687,10 +9687,10 @@
         <v>54</v>
       </c>
       <c r="C71" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="D71" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E71" t="s">
         <v>190</v>
@@ -9803,7 +9803,7 @@
         <v>54</v>
       </c>
       <c r="C72" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D72" t="s">
         <v>120</v>
@@ -9830,13 +9830,13 @@
         <v>391</v>
       </c>
       <c r="L72">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M72">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -9878,10 +9878,10 @@
         <v>0</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC72">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD72">
         <v>0</v>
@@ -9919,10 +9919,10 @@
         <v>54</v>
       </c>
       <c r="C73" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D73" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E73" t="s">
         <v>192</v>
@@ -10062,13 +10062,13 @@
         <v>391</v>
       </c>
       <c r="L74">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M74">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O74">
         <v>0</v>
@@ -10110,10 +10110,10 @@
         <v>0</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD74">
         <v>0</v>
@@ -10151,10 +10151,10 @@
         <v>54</v>
       </c>
       <c r="C75" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="D75" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E75" t="s">
         <v>194</v>
@@ -10178,13 +10178,13 @@
         <v>391</v>
       </c>
       <c r="L75">
-        <v>1.47</v>
+        <v>2.5</v>
       </c>
       <c r="M75">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="N75">
-        <v>6.2</v>
+        <v>2.65</v>
       </c>
       <c r="O75">
         <v>0</v>
@@ -10226,10 +10226,10 @@
         <v>0</v>
       </c>
       <c r="AB75">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="AC75">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AD75">
         <v>0</v>
@@ -10294,13 +10294,13 @@
         <v>391</v>
       </c>
       <c r="L76">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M76">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O76">
         <v>0</v>
@@ -10342,10 +10342,10 @@
         <v>0</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD76">
         <v>0</v>
@@ -10383,7 +10383,7 @@
         <v>54</v>
       </c>
       <c r="C77" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="D77" t="s">
         <v>120</v>
@@ -10499,7 +10499,7 @@
         <v>54</v>
       </c>
       <c r="C78" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="D78" t="s">
         <v>120</v>
@@ -10526,13 +10526,13 @@
         <v>391</v>
       </c>
       <c r="L78">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M78">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N78">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O78">
         <v>0</v>
@@ -10574,10 +10574,10 @@
         <v>0</v>
       </c>
       <c r="AB78">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC78">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD78">
         <v>0</v>
@@ -10615,7 +10615,7 @@
         <v>54</v>
       </c>
       <c r="C79" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D79" t="s">
         <v>120</v>
@@ -10642,13 +10642,13 @@
         <v>391</v>
       </c>
       <c r="L79">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M79">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N79">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O79">
         <v>0</v>
@@ -10690,10 +10690,10 @@
         <v>0</v>
       </c>
       <c r="AB79">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC79">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD79">
         <v>0</v>
@@ -10731,7 +10731,7 @@
         <v>54</v>
       </c>
       <c r="C80" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="D80" t="s">
         <v>120</v>
@@ -10847,7 +10847,7 @@
         <v>54</v>
       </c>
       <c r="C81" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="D81" t="s">
         <v>120</v>
@@ -10874,13 +10874,13 @@
         <v>391</v>
       </c>
       <c r="L81">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M81">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O81">
         <v>0</v>
@@ -10922,10 +10922,10 @@
         <v>0</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD81">
         <v>0</v>
@@ -10963,10 +10963,10 @@
         <v>54</v>
       </c>
       <c r="C82" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="D82" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E82" t="s">
         <v>201</v>
@@ -11079,7 +11079,7 @@
         <v>55</v>
       </c>
       <c r="C83" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D83" t="s">
         <v>120</v>
@@ -11106,13 +11106,13 @@
         <v>391</v>
       </c>
       <c r="L83">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M83">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N83">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O83">
         <v>0</v>
@@ -11195,7 +11195,7 @@
         <v>55</v>
       </c>
       <c r="C84" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="D84" t="s">
         <v>120</v>
@@ -11222,13 +11222,13 @@
         <v>391</v>
       </c>
       <c r="L84">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="M84">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O84">
         <v>0</v>
@@ -11270,16 +11270,16 @@
         <v>0</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF84">
         <v>0</v>
@@ -11338,13 +11338,13 @@
         <v>391</v>
       </c>
       <c r="L85">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M85">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N85">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O85">
         <v>0</v>
@@ -11386,10 +11386,10 @@
         <v>0</v>
       </c>
       <c r="AB85">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC85">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD85">
         <v>0</v>
@@ -11427,7 +11427,7 @@
         <v>55</v>
       </c>
       <c r="C86" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="D86" t="s">
         <v>120</v>
@@ -11454,13 +11454,13 @@
         <v>391</v>
       </c>
       <c r="L86">
-        <v>1.24</v>
+        <v>2.6</v>
       </c>
       <c r="M86">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="N86">
-        <v>12</v>
+        <v>2.6</v>
       </c>
       <c r="O86">
         <v>0</v>
@@ -11502,16 +11502,16 @@
         <v>0</v>
       </c>
       <c r="AB86">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="AC86">
-        <v>2.75</v>
+        <v>1.6</v>
       </c>
       <c r="AD86">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE86">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF86">
         <v>0</v>
@@ -11543,7 +11543,7 @@
         <v>55</v>
       </c>
       <c r="C87" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D87" t="s">
         <v>120</v>
@@ -11570,13 +11570,13 @@
         <v>391</v>
       </c>
       <c r="L87">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M87">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N87">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O87">
         <v>0</v>
@@ -11659,7 +11659,7 @@
         <v>55</v>
       </c>
       <c r="C88" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="D88" t="s">
         <v>120</v>
@@ -11686,13 +11686,13 @@
         <v>391</v>
       </c>
       <c r="L88">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M88">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O88">
         <v>0</v>
@@ -11775,7 +11775,7 @@
         <v>55</v>
       </c>
       <c r="C89" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="D89" t="s">
         <v>120</v>
@@ -11802,13 +11802,13 @@
         <v>391</v>
       </c>
       <c r="L89">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M89">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O89">
         <v>0</v>
@@ -12123,7 +12123,7 @@
         <v>57</v>
       </c>
       <c r="C92" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="D92" t="s">
         <v>120</v>
@@ -12239,10 +12239,10 @@
         <v>57</v>
       </c>
       <c r="C93" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="D93" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E93" t="s">
         <v>212</v>
@@ -12266,13 +12266,13 @@
         <v>391</v>
       </c>
       <c r="L93">
-        <v>0</v>
+        <v>6.27</v>
       </c>
       <c r="M93">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O93">
         <v>0</v>
@@ -12320,10 +12320,10 @@
         <v>0</v>
       </c>
       <c r="AD93">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE93">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF93">
         <v>0</v>
@@ -12355,7 +12355,7 @@
         <v>57</v>
       </c>
       <c r="C94" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="D94" t="s">
         <v>120</v>
@@ -12471,10 +12471,10 @@
         <v>57</v>
       </c>
       <c r="C95" t="s">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="D95" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E95" t="s">
         <v>214</v>
@@ -12498,13 +12498,13 @@
         <v>391</v>
       </c>
       <c r="L95">
-        <v>6.27</v>
+        <v>0</v>
       </c>
       <c r="M95">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N95">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O95">
         <v>0</v>
@@ -12552,10 +12552,10 @@
         <v>0</v>
       </c>
       <c r="AD95">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE95">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF95">
         <v>0</v>
@@ -12587,7 +12587,7 @@
         <v>57</v>
       </c>
       <c r="C96" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D96" t="s">
         <v>120</v>
@@ -12819,10 +12819,10 @@
         <v>59</v>
       </c>
       <c r="C98" t="s">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="D98" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E98" t="s">
         <v>217</v>
@@ -12935,7 +12935,7 @@
         <v>59</v>
       </c>
       <c r="C99" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D99" t="s">
         <v>119</v>
@@ -13051,10 +13051,10 @@
         <v>59</v>
       </c>
       <c r="C100" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="D100" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E100" t="s">
         <v>219</v>
@@ -13167,7 +13167,7 @@
         <v>60</v>
       </c>
       <c r="C101" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D101" t="s">
         <v>120</v>
@@ -13515,7 +13515,7 @@
         <v>60</v>
       </c>
       <c r="C104" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D104" t="s">
         <v>120</v>
@@ -13747,10 +13747,10 @@
         <v>60</v>
       </c>
       <c r="C106" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D106" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E106" t="s">
         <v>225</v>
@@ -13863,10 +13863,10 @@
         <v>60</v>
       </c>
       <c r="C107" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="D107" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E107" t="s">
         <v>226</v>
@@ -13979,7 +13979,7 @@
         <v>60</v>
       </c>
       <c r="C108" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D108" t="s">
         <v>120</v>
@@ -14211,7 +14211,7 @@
         <v>61</v>
       </c>
       <c r="C110" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D110" t="s">
         <v>120</v>
@@ -14443,7 +14443,7 @@
         <v>62</v>
       </c>
       <c r="C112" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="D112" t="s">
         <v>120</v>
@@ -14470,13 +14470,13 @@
         <v>391</v>
       </c>
       <c r="L112">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M112">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="O112">
         <v>0</v>
@@ -14512,10 +14512,10 @@
         <v>0</v>
       </c>
       <c r="Z112">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA112">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB112">
         <v>0</v>
@@ -14559,7 +14559,7 @@
         <v>62</v>
       </c>
       <c r="C113" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="D113" t="s">
         <v>120</v>
@@ -14586,13 +14586,13 @@
         <v>391</v>
       </c>
       <c r="L113">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M113">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N113">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="O113">
         <v>0</v>
@@ -14628,10 +14628,10 @@
         <v>0</v>
       </c>
       <c r="Z113">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA113">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB113">
         <v>0</v>
@@ -14675,7 +14675,7 @@
         <v>63</v>
       </c>
       <c r="C114" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="D114" t="s">
         <v>120</v>
@@ -14791,7 +14791,7 @@
         <v>63</v>
       </c>
       <c r="C115" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="D115" t="s">
         <v>120</v>
@@ -15023,7 +15023,7 @@
         <v>64</v>
       </c>
       <c r="C117" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="D117" t="s">
         <v>120</v>
@@ -15050,13 +15050,13 @@
         <v>391</v>
       </c>
       <c r="L117">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M117">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N117">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O117">
         <v>0</v>
@@ -15139,7 +15139,7 @@
         <v>64</v>
       </c>
       <c r="C118" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="D118" t="s">
         <v>120</v>
@@ -15166,13 +15166,13 @@
         <v>391</v>
       </c>
       <c r="L118">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M118">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O118">
         <v>0</v>
@@ -15255,7 +15255,7 @@
         <v>65</v>
       </c>
       <c r="C119" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D119" t="s">
         <v>120</v>
@@ -15514,13 +15514,13 @@
         <v>391</v>
       </c>
       <c r="L121">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M121">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N121">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O121">
         <v>0</v>
@@ -15556,16 +15556,16 @@
         <v>0</v>
       </c>
       <c r="Z121">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA121">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB121">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC121">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD121">
         <v>0</v>
@@ -15603,7 +15603,7 @@
         <v>66</v>
       </c>
       <c r="C122" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D122" t="s">
         <v>119</v>
@@ -15630,13 +15630,13 @@
         <v>391</v>
       </c>
       <c r="L122">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M122">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N122">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O122">
         <v>0</v>
@@ -15678,10 +15678,10 @@
         <v>0</v>
       </c>
       <c r="AB122">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC122">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD122">
         <v>0</v>
@@ -15746,13 +15746,13 @@
         <v>391</v>
       </c>
       <c r="L123">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M123">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N123">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O123">
         <v>0</v>
@@ -15788,16 +15788,16 @@
         <v>0</v>
       </c>
       <c r="Z123">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA123">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB123">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC123">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD123">
         <v>0</v>
@@ -15835,7 +15835,7 @@
         <v>66</v>
       </c>
       <c r="C124" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D124" t="s">
         <v>119</v>
@@ -15862,13 +15862,13 @@
         <v>391</v>
       </c>
       <c r="L124">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M124">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N124">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O124">
         <v>0</v>
@@ -15910,10 +15910,10 @@
         <v>0</v>
       </c>
       <c r="AB124">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC124">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD124">
         <v>0</v>
@@ -16183,7 +16183,7 @@
         <v>68</v>
       </c>
       <c r="C127" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D127" t="s">
         <v>119</v>
@@ -16326,13 +16326,13 @@
         <v>391</v>
       </c>
       <c r="L128">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M128">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N128">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O128">
         <v>0</v>
@@ -16374,10 +16374,10 @@
         <v>0</v>
       </c>
       <c r="AB128">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC128">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD128">
         <v>0</v>
@@ -16442,13 +16442,13 @@
         <v>391</v>
       </c>
       <c r="L129">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M129">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N129">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O129">
         <v>0</v>
@@ -16490,10 +16490,10 @@
         <v>0</v>
       </c>
       <c r="AB129">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC129">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD129">
         <v>0</v>
@@ -16763,7 +16763,7 @@
         <v>70</v>
       </c>
       <c r="C132" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D132" t="s">
         <v>119</v>
@@ -16995,7 +16995,7 @@
         <v>72</v>
       </c>
       <c r="C134" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D134" t="s">
         <v>119</v>

--- a/jogos_2025-08-03.xlsx
+++ b/jogos_2025-08-03.xlsx
@@ -253,48 +253,48 @@
     <t>Austria 2. Liga</t>
   </si>
   <si>
+    <t>Ukraine Ukrainian Premier League</t>
+  </si>
+  <si>
     <t>Japan J2 League</t>
   </si>
   <si>
-    <t>Ukraine Ukrainian Premier League</t>
-  </si>
-  <si>
     <t>Russia Russian Premier League</t>
   </si>
   <si>
     <t>England EFL League One</t>
   </si>
   <si>
+    <t>Belarus Vysheyshaya Liga</t>
+  </si>
+  <si>
     <t>China China League One</t>
   </si>
   <si>
-    <t>Belarus Vysheyshaya Liga</t>
-  </si>
-  <si>
     <t>China Chinese Super League</t>
   </si>
   <si>
+    <t>Germany 2. Bundesliga</t>
+  </si>
+  <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
     <t>Germany 3. Liga</t>
   </si>
   <si>
-    <t>Germany 2. Bundesliga</t>
+    <t>Switzerland Super League</t>
+  </si>
+  <si>
+    <t>Sweden Allsvenskan</t>
   </si>
   <si>
     <t>Switzerland Challenge League</t>
   </si>
   <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
     <t>Denmark Superliga</t>
   </si>
   <si>
-    <t>Switzerland Super League</t>
-  </si>
-  <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
@@ -304,21 +304,21 @@
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
     <t>Scotland Premiership</t>
   </si>
   <si>
+    <t>Czech Republic First League</t>
+  </si>
+  <si>
+    <t>Finland Veikkausliiga</t>
+  </si>
+  <si>
     <t>Norway First Division</t>
   </si>
   <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
-    <t>Finland Veikkausliiga</t>
-  </si>
-  <si>
-    <t>Czech Republic First League</t>
-  </si>
-  <si>
     <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
@@ -331,12 +331,12 @@
     <t>Montenegro Montenegrin First League</t>
   </si>
   <si>
+    <t>Austria Bundesliga</t>
+  </si>
+  <si>
     <t>Uzbekistan Uzbekistan Super League</t>
   </si>
   <si>
-    <t>Austria Bundesliga</t>
-  </si>
-  <si>
     <t>Slovakia Super Liga</t>
   </si>
   <si>
@@ -358,12 +358,12 @@
     <t>USA NWSL</t>
   </si>
   <si>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
     <t>Serbia SuperLiga</t>
   </si>
   <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
     <t>Brazil Serie A</t>
   </si>
   <si>
@@ -379,15 +379,15 @@
     <t>2025/2026</t>
   </si>
   <si>
+    <t>Wollongong Wolves</t>
+  </si>
+  <si>
     <t>Blacktown City</t>
   </si>
   <si>
     <t>Sydney United</t>
   </si>
   <si>
-    <t>Wollongong Wolves</t>
-  </si>
-  <si>
     <t>Central Coast II</t>
   </si>
   <si>
@@ -403,27 +403,33 @@
     <t>WSPG Wels</t>
   </si>
   <si>
+    <t>Kudrivka</t>
+  </si>
+  <si>
     <t>Roasso Kumamoto</t>
   </si>
   <si>
-    <t>Kudrivka</t>
-  </si>
-  <si>
     <t>Akron</t>
   </si>
   <si>
     <t>Stockport County</t>
   </si>
   <si>
+    <t>Molodechno-DYuSSh 4</t>
+  </si>
+  <si>
     <t>Suzhou Dongwu</t>
   </si>
   <si>
-    <t>Molodechno-DYuSSh 4</t>
-  </si>
-  <si>
     <t>Dalian Zhixing</t>
   </si>
   <si>
+    <t>Hannover 96</t>
+  </si>
+  <si>
+    <t>Dongguan United</t>
+  </si>
+  <si>
     <t>KRC Genk</t>
   </si>
   <si>
@@ -433,48 +439,42 @@
     <t>Magdeburg</t>
   </si>
   <si>
+    <t>Greuther Fürth</t>
+  </si>
+  <si>
     <t>Qingdao Red Lions</t>
   </si>
   <si>
-    <t>Hannover 96</t>
-  </si>
-  <si>
-    <t>Greuther Fürth</t>
-  </si>
-  <si>
-    <t>Dongguan United</t>
+    <t>Beijing Guoan</t>
   </si>
   <si>
     <t>Wuhan Three Towns</t>
   </si>
   <si>
-    <t>Beijing Guoan</t>
+    <t>Thun</t>
+  </si>
+  <si>
+    <t>Sichuan Jiuniu</t>
+  </si>
+  <si>
+    <t>Djurgården</t>
   </si>
   <si>
     <t>Yverdon Sport</t>
   </si>
   <si>
-    <t>Djurgården</t>
+    <t>Randers</t>
   </si>
   <si>
     <t>Häcken</t>
   </si>
   <si>
-    <t>Sichuan Jiuniu</t>
-  </si>
-  <si>
     <t>SønderjyskE</t>
   </si>
   <si>
-    <t>Randers</t>
-  </si>
-  <si>
     <t>Spartak Kostroma</t>
   </si>
   <si>
-    <t>Thun</t>
-  </si>
-  <si>
     <t>HamKam</t>
   </si>
   <si>
@@ -493,138 +493,147 @@
     <t>Cracovia Kraków</t>
   </si>
   <si>
+    <t>Landskrona</t>
+  </si>
+  <si>
     <t>Falkirk</t>
   </si>
   <si>
+    <t>Slovácko</t>
+  </si>
+  <si>
+    <t>SJK</t>
+  </si>
+  <si>
     <t>Sogndal</t>
   </si>
   <si>
-    <t>Landskrona</t>
-  </si>
-  <si>
-    <t>SJK</t>
-  </si>
-  <si>
-    <t>Slovácko</t>
-  </si>
-  <si>
     <t>Suduroy</t>
   </si>
   <si>
+    <t>EB - Streymur</t>
+  </si>
+  <si>
+    <t>Jeunesse d'Esch</t>
+  </si>
+  <si>
+    <t>F91 Dudelange</t>
+  </si>
+  <si>
+    <t>Jeunesse Canach</t>
+  </si>
+  <si>
+    <t>Dundee</t>
+  </si>
+  <si>
     <t>Differdange 03</t>
   </si>
   <si>
+    <t>Hostert</t>
+  </si>
+  <si>
     <t>Mondorf-les-Bains</t>
   </si>
   <si>
-    <t>EB - Streymur</t>
-  </si>
-  <si>
-    <t>Dundee</t>
+    <t>Cercle Brugge</t>
+  </si>
+  <si>
+    <t>Swift Hesperange</t>
   </si>
   <si>
     <t>AGF</t>
   </si>
   <si>
+    <t>Harju Jalgpallikool</t>
+  </si>
+  <si>
     <t>Rodange</t>
   </si>
   <si>
-    <t>Harju Jalgpallikool</t>
-  </si>
-  <si>
-    <t>Jeunesse d'Esch</t>
-  </si>
-  <si>
-    <t>F91 Dudelange</t>
-  </si>
-  <si>
-    <t>Hostert</t>
-  </si>
-  <si>
-    <t>Cercle Brugge</t>
-  </si>
-  <si>
-    <t>Jeunesse Canach</t>
-  </si>
-  <si>
-    <t>Swift Hesperange</t>
+    <t>Étoile Carouge</t>
   </si>
   <si>
     <t>Sirius</t>
   </si>
   <si>
+    <t>Viktoria Köln</t>
+  </si>
+  <si>
     <t>Luzern</t>
   </si>
   <si>
-    <t>Étoile Carouge</t>
-  </si>
-  <si>
-    <t>Viktoria Köln</t>
+    <t>Karpaty</t>
+  </si>
+  <si>
+    <t>Torpedo BelAZ</t>
+  </si>
+  <si>
+    <t>Vålerenga</t>
+  </si>
+  <si>
+    <t>Zenit</t>
+  </si>
+  <si>
+    <t>FK Jezero Plav</t>
+  </si>
+  <si>
+    <t>KFUM</t>
+  </si>
+  <si>
+    <t>Rapid Wien</t>
+  </si>
+  <si>
+    <t>Vlašim</t>
+  </si>
+  <si>
+    <t>Rubin Kazan</t>
+  </si>
+  <si>
+    <t>Grazer AK</t>
+  </si>
+  <si>
+    <t>Pogoń Siedlce</t>
+  </si>
+  <si>
+    <t>Molde</t>
+  </si>
+  <si>
+    <t>Shortan</t>
+  </si>
+  <si>
+    <t>Dukla Praha</t>
+  </si>
+  <si>
+    <t>Dečić</t>
+  </si>
+  <si>
+    <t>Petrovac</t>
+  </si>
+  <si>
+    <t>Trenčín</t>
+  </si>
+  <si>
+    <t>Sutjeska</t>
   </si>
   <si>
     <t>Arsenal Tivat</t>
   </si>
   <si>
-    <t>Zenit</t>
-  </si>
-  <si>
-    <t>Shortan</t>
-  </si>
-  <si>
-    <t>Dukla Praha</t>
-  </si>
-  <si>
-    <t>Rubin Kazan</t>
-  </si>
-  <si>
-    <t>Torpedo BelAZ</t>
-  </si>
-  <si>
-    <t>Karpaty</t>
-  </si>
-  <si>
-    <t>Vlašim</t>
-  </si>
-  <si>
     <t>Strømsgodset</t>
   </si>
   <si>
-    <t>Grazer AK</t>
-  </si>
-  <si>
-    <t>Trenčín</t>
-  </si>
-  <si>
-    <t>Vålerenga</t>
-  </si>
-  <si>
-    <t>KFUM</t>
-  </si>
-  <si>
-    <t>Molde</t>
-  </si>
-  <si>
-    <t>Sutjeska</t>
-  </si>
-  <si>
-    <t>Pogoń Siedlce</t>
-  </si>
-  <si>
-    <t>FK Jezero Plav</t>
-  </si>
-  <si>
-    <t>Dečić</t>
-  </si>
-  <si>
-    <t>Rapid Wien</t>
-  </si>
-  <si>
-    <t>Petrovac</t>
+    <t>Motor Lublin</t>
   </si>
   <si>
     <t>Karcag SE</t>
   </si>
   <si>
+    <t>Radomiak Radom</t>
+  </si>
+  <si>
+    <t>Szentlőrinc SE</t>
+  </si>
+  <si>
     <t>Celtic</t>
   </si>
   <si>
@@ -634,36 +643,27 @@
     <t>Hermannstadt</t>
   </si>
   <si>
-    <t>Szentlőrinc SE</t>
-  </si>
-  <si>
-    <t>Motor Lublin</t>
-  </si>
-  <si>
-    <t>Radomiak Radom</t>
+    <t>Várda SE</t>
   </si>
   <si>
     <t>Puskás</t>
   </si>
   <si>
-    <t>Várda SE</t>
-  </si>
-  <si>
     <t>Brøndby</t>
   </si>
   <si>
     <t>Tammeka</t>
   </si>
   <si>
+    <t>FK Chernomorets Novorossiysk</t>
+  </si>
+  <si>
+    <t>Fakel</t>
+  </si>
+  <si>
     <t>Vysočina Jihlava</t>
   </si>
   <si>
-    <t>FK Chernomorets Novorossiysk</t>
-  </si>
-  <si>
-    <t>Fakel</t>
-  </si>
-  <si>
     <t>B68</t>
   </si>
   <si>
@@ -676,51 +676,51 @@
     <t>Washington Spirit</t>
   </si>
   <si>
+    <t>Békéscsaba</t>
+  </si>
+  <si>
+    <t>Tiszakécske</t>
+  </si>
+  <si>
+    <t>Honvéd W</t>
+  </si>
+  <si>
+    <t>Csákvári TK</t>
+  </si>
+  <si>
+    <t>MKK-Dnepr</t>
+  </si>
+  <si>
+    <t>Žilina</t>
+  </si>
+  <si>
+    <t>Sporting KC II</t>
+  </si>
+  <si>
+    <t>Ajka</t>
+  </si>
+  <si>
     <t>Železničar Pančevo</t>
   </si>
   <si>
-    <t>Ajka</t>
-  </si>
-  <si>
-    <t>MKK-Dnepr</t>
-  </si>
-  <si>
-    <t>Žilina</t>
-  </si>
-  <si>
-    <t>Tiszakécske</t>
-  </si>
-  <si>
-    <t>Honvéd W</t>
-  </si>
-  <si>
-    <t>Sporting KC II</t>
-  </si>
-  <si>
-    <t>Békéscsaba</t>
-  </si>
-  <si>
-    <t>Csákvári TK</t>
-  </si>
-  <si>
     <t>Sporting Charleroi</t>
   </si>
   <si>
+    <t>Górnik Łęczna</t>
+  </si>
+  <si>
+    <t>Makhachkala</t>
+  </si>
+  <si>
     <t>Wehen Wiesbaden</t>
   </si>
   <si>
-    <t>Makhachkala</t>
-  </si>
-  <si>
-    <t>Górnik Łęczna</t>
+    <t>Pardubice</t>
   </si>
   <si>
     <t>Győri ETO</t>
   </si>
   <si>
-    <t>Pardubice</t>
-  </si>
-  <si>
     <t>Chicago Fire II</t>
   </si>
   <si>
@@ -733,36 +733,36 @@
     <t>CFR Cluj</t>
   </si>
   <si>
+    <t>Botafogo</t>
+  </si>
+  <si>
     <t>Partizan</t>
   </si>
   <si>
-    <t>Botafogo</t>
+    <t>Colo-Colo</t>
+  </si>
+  <si>
+    <t>Chapecoense</t>
   </si>
   <si>
     <t>Corinthians</t>
   </si>
   <si>
-    <t>Chapecoense</t>
-  </si>
-  <si>
-    <t>Colo-Colo</t>
-  </si>
-  <si>
     <t>Atlético Ottawa</t>
   </si>
   <si>
+    <t>Atlético Mineiro</t>
+  </si>
+  <si>
+    <t>Ceará</t>
+  </si>
+  <si>
     <t>Ñublense</t>
   </si>
   <si>
-    <t>Atlético Mineiro</t>
-  </si>
-  <si>
     <t>Atlético PR</t>
   </si>
   <si>
-    <t>Ceará</t>
-  </si>
-  <si>
     <t>Philadelphia Union II</t>
   </si>
   <si>
@@ -784,15 +784,15 @@
     <t>Los Angeles II</t>
   </si>
   <si>
+    <t>Sydney II</t>
+  </si>
+  <si>
     <t>Mt Druitt Town</t>
   </si>
   <si>
     <t>St. George Saints</t>
   </si>
   <si>
-    <t>Sydney II</t>
-  </si>
-  <si>
     <t>Marconi Stallions</t>
   </si>
   <si>
@@ -808,27 +808,33 @@
     <t>Floridsdorfer AC</t>
   </si>
   <si>
+    <t>Oleksandria</t>
+  </si>
+  <si>
     <t>Mito Hollyhock</t>
   </si>
   <si>
-    <t>Oleksandria</t>
-  </si>
-  <si>
     <t>Spartak Moskva</t>
   </si>
   <si>
     <t>Bolton Wanderers</t>
   </si>
   <si>
+    <t>Neman Grodno</t>
+  </si>
+  <si>
     <t>Dalian Huayi</t>
   </si>
   <si>
-    <t>Neman Grodno</t>
-  </si>
-  <si>
     <t>Qingdao Jonoon</t>
   </si>
   <si>
+    <t>Kaiserslautern</t>
+  </si>
+  <si>
+    <t>Nantong Zhiyun</t>
+  </si>
+  <si>
     <t>Royal Antwerp FC</t>
   </si>
   <si>
@@ -838,48 +844,42 @@
     <t>Eintracht Braunschweig</t>
   </si>
   <si>
+    <t>Dynamo Dresden</t>
+  </si>
+  <si>
     <t>Heilongjiang Lava Spring</t>
   </si>
   <si>
-    <t>Kaiserslautern</t>
-  </si>
-  <si>
-    <t>Dynamo Dresden</t>
-  </si>
-  <si>
-    <t>Nantong Zhiyun</t>
+    <t>Tianjin Teda</t>
   </si>
   <si>
     <t>Changchun Yatai</t>
   </si>
   <si>
-    <t>Tianjin Teda</t>
+    <t>Lausanne Sport</t>
+  </si>
+  <si>
+    <t>Zhejiang FC</t>
+  </si>
+  <si>
+    <t>Halmstad</t>
   </si>
   <si>
     <t>Stade Lausanne-Ouchy</t>
   </si>
   <si>
-    <t>Halmstad</t>
+    <t>Silkeborg</t>
   </si>
   <si>
     <t>Elfsborg</t>
   </si>
   <si>
-    <t>Zhejiang FC</t>
-  </si>
-  <si>
     <t>Nordsjælland</t>
   </si>
   <si>
-    <t>Silkeborg</t>
-  </si>
-  <si>
     <t>Neftekhimik</t>
   </si>
   <si>
-    <t>Lausanne Sport</t>
-  </si>
-  <si>
     <t>FK Bodo - Glimt</t>
   </si>
   <si>
@@ -898,138 +898,147 @@
     <t>Lechia Gdańsk</t>
   </si>
   <si>
+    <t>Västerås SK</t>
+  </si>
+  <si>
     <t>Dundee United</t>
   </si>
   <si>
+    <t>Slavia Praha</t>
+  </si>
+  <si>
+    <t>KTP</t>
+  </si>
+  <si>
     <t>Skeid</t>
   </si>
   <si>
-    <t>Västerås SK</t>
-  </si>
-  <si>
-    <t>KTP</t>
-  </si>
-  <si>
-    <t>Slavia Praha</t>
-  </si>
-  <si>
     <t>HB</t>
   </si>
   <si>
+    <t>KÍ</t>
+  </si>
+  <si>
+    <t>UN Käerjéng</t>
+  </si>
+  <si>
+    <t>Progrès Niederkorn</t>
+  </si>
+  <si>
+    <t>Mamer</t>
+  </si>
+  <si>
+    <t>Hibernian</t>
+  </si>
+  <si>
     <t>Atert Bissen</t>
   </si>
   <si>
+    <t>Victoria Rosport</t>
+  </si>
+  <si>
     <t>UNA Strassen</t>
   </si>
   <si>
-    <t>KÍ</t>
-  </si>
-  <si>
-    <t>Hibernian</t>
+    <t>RSC Anderlecht</t>
+  </si>
+  <si>
+    <t>UT Pétange</t>
   </si>
   <si>
     <t>Midtjylland</t>
   </si>
   <si>
+    <t>Paide</t>
+  </si>
+  <si>
     <t>Racing</t>
   </si>
   <si>
-    <t>Paide</t>
-  </si>
-  <si>
-    <t>UN Käerjéng</t>
-  </si>
-  <si>
-    <t>Progrès Niederkorn</t>
-  </si>
-  <si>
-    <t>Victoria Rosport</t>
-  </si>
-  <si>
-    <t>RSC Anderlecht</t>
-  </si>
-  <si>
-    <t>Mamer</t>
-  </si>
-  <si>
-    <t>UT Pétange</t>
+    <t>Vaduz</t>
   </si>
   <si>
     <t>Öster</t>
   </si>
   <si>
+    <t>Schweinfurt</t>
+  </si>
+  <si>
     <t>Zürich</t>
   </si>
   <si>
-    <t>Vaduz</t>
-  </si>
-  <si>
-    <t>Schweinfurt</t>
+    <t>Polessya</t>
+  </si>
+  <si>
+    <t>Gomel</t>
+  </si>
+  <si>
+    <t>Sandefjord</t>
+  </si>
+  <si>
+    <t>CSKA Moskva</t>
+  </si>
+  <si>
+    <t>Budućnost</t>
+  </si>
+  <si>
+    <t>Rosenborg</t>
+  </si>
+  <si>
+    <t>Blau-Weiß Linz</t>
+  </si>
+  <si>
+    <t>Hanácká</t>
+  </si>
+  <si>
+    <t>FK Sochi</t>
+  </si>
+  <si>
+    <t>Austria Wien</t>
+  </si>
+  <si>
+    <t>Odra Opole</t>
+  </si>
+  <si>
+    <t>Bryne</t>
+  </si>
+  <si>
+    <t>Xorazm</t>
+  </si>
+  <si>
+    <t>Baník Ostrava</t>
+  </si>
+  <si>
+    <t>Mladost DG</t>
+  </si>
+  <si>
+    <t>Bokelj</t>
+  </si>
+  <si>
+    <t>Spartak Trnava</t>
+  </si>
+  <si>
+    <t>Mornar</t>
   </si>
   <si>
     <t>Jedinstvo</t>
   </si>
   <si>
-    <t>CSKA Moskva</t>
-  </si>
-  <si>
-    <t>Xorazm</t>
-  </si>
-  <si>
-    <t>Baník Ostrava</t>
-  </si>
-  <si>
-    <t>FK Sochi</t>
-  </si>
-  <si>
-    <t>Gomel</t>
-  </si>
-  <si>
-    <t>Polessya</t>
-  </si>
-  <si>
-    <t>Hanácká</t>
-  </si>
-  <si>
     <t>Haugesund</t>
   </si>
   <si>
-    <t>Austria Wien</t>
-  </si>
-  <si>
-    <t>Spartak Trnava</t>
-  </si>
-  <si>
-    <t>Sandefjord</t>
-  </si>
-  <si>
-    <t>Rosenborg</t>
-  </si>
-  <si>
-    <t>Bryne</t>
-  </si>
-  <si>
-    <t>Mornar</t>
-  </si>
-  <si>
-    <t>Odra Opole</t>
-  </si>
-  <si>
-    <t>Budućnost</t>
-  </si>
-  <si>
-    <t>Mladost DG</t>
-  </si>
-  <si>
-    <t>Blau-Weiß Linz</t>
-  </si>
-  <si>
-    <t>Bokelj</t>
+    <t>Jagiellonia Białystok</t>
   </si>
   <si>
     <t>Soroksár SC</t>
   </si>
   <si>
+    <t>Raków Częstochowa</t>
+  </si>
+  <si>
+    <t>Kozármisleny</t>
+  </si>
+  <si>
     <t>St. Mirren</t>
   </si>
   <si>
@@ -1039,36 +1048,27 @@
     <t>Universitatea Cluj</t>
   </si>
   <si>
-    <t>Kozármisleny</t>
-  </si>
-  <si>
-    <t>Jagiellonia Białystok</t>
-  </si>
-  <si>
-    <t>Raków Częstochowa</t>
+    <t>Paksi SE</t>
   </si>
   <si>
     <t>Nyíregyháza Spartacus</t>
   </si>
   <si>
-    <t>Paksi SE</t>
-  </si>
-  <si>
     <t>Viborg</t>
   </si>
   <si>
     <t>Nõmme Kalju</t>
   </si>
   <si>
+    <t>Arsenal Tula</t>
+  </si>
+  <si>
+    <t>Sokol Saratov</t>
+  </si>
+  <si>
     <t>Vyškov</t>
   </si>
   <si>
-    <t>Arsenal Tula</t>
-  </si>
-  <si>
-    <t>Sokol Saratov</t>
-  </si>
-  <si>
     <t>NSÍ</t>
   </si>
   <si>
@@ -1081,51 +1081,51 @@
     <t>Portland Thorns</t>
   </si>
   <si>
+    <t>Szeged 2011</t>
+  </si>
+  <si>
+    <t>Mezőkövesd-Zsóry</t>
+  </si>
+  <si>
+    <t>Budafoki MTE</t>
+  </si>
+  <si>
+    <t>BVSC</t>
+  </si>
+  <si>
+    <t>Slutsk</t>
+  </si>
+  <si>
+    <t>Tatran Prešov</t>
+  </si>
+  <si>
+    <t>Austin II</t>
+  </si>
+  <si>
+    <t>Videoton</t>
+  </si>
+  <si>
     <t>Napredak</t>
   </si>
   <si>
-    <t>Videoton</t>
-  </si>
-  <si>
-    <t>Slutsk</t>
-  </si>
-  <si>
-    <t>Tatran Prešov</t>
-  </si>
-  <si>
-    <t>Mezőkövesd-Zsóry</t>
-  </si>
-  <si>
-    <t>Budafoki MTE</t>
-  </si>
-  <si>
-    <t>Austin II</t>
-  </si>
-  <si>
-    <t>Szeged 2011</t>
-  </si>
-  <si>
-    <t>BVSC</t>
-  </si>
-  <si>
     <t>Sint-Truiden</t>
   </si>
   <si>
+    <t>Puszcza Niepołomice</t>
+  </si>
+  <si>
+    <t>Akhmat Grozny</t>
+  </si>
+  <si>
     <t>Ulm</t>
   </si>
   <si>
-    <t>Akhmat Grozny</t>
-  </si>
-  <si>
-    <t>Puszcza Niepołomice</t>
+    <t>Sparta Praha</t>
   </si>
   <si>
     <t>Újpest</t>
   </si>
   <si>
-    <t>Sparta Praha</t>
-  </si>
-  <si>
     <t>Columbus Crew II</t>
   </si>
   <si>
@@ -1138,34 +1138,34 @@
     <t>CS U Craiova</t>
   </si>
   <si>
+    <t>Cruzeiro</t>
+  </si>
+  <si>
     <t>Radnički Kragujevac</t>
   </si>
   <si>
-    <t>Cruzeiro</t>
+    <t>Huachipato</t>
+  </si>
+  <si>
+    <t>CRB</t>
   </si>
   <si>
     <t>Fortaleza</t>
   </si>
   <si>
-    <t>CRB</t>
-  </si>
-  <si>
-    <t>Huachipato</t>
-  </si>
-  <si>
     <t>York9 FC</t>
   </si>
   <si>
+    <t>Bragantino</t>
+  </si>
+  <si>
+    <t>Flamengo</t>
+  </si>
+  <si>
     <t>Everton</t>
   </si>
   <si>
-    <t>Bragantino</t>
-  </si>
-  <si>
     <t>Paysandu</t>
-  </si>
-  <si>
-    <t>Flamengo</t>
   </si>
   <si>
     <t>FC Cincinnati II</t>
@@ -2614,7 +2614,7 @@
         <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E10" t="s">
         <v>129</v>
@@ -2638,13 +2638,13 @@
         <v>391</v>
       </c>
       <c r="L10">
-        <v>3.15</v>
+        <v>5.4</v>
       </c>
       <c r="M10">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N10">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -2680,16 +2680,16 @@
         <v>0</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB10">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC10">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD10">
         <v>0</v>
@@ -2730,7 +2730,7 @@
         <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E11" t="s">
         <v>130</v>
@@ -2754,13 +2754,13 @@
         <v>391</v>
       </c>
       <c r="L11">
-        <v>5.4</v>
+        <v>3.15</v>
       </c>
       <c r="M11">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N11">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -2796,16 +2796,16 @@
         <v>0</v>
       </c>
       <c r="Z11">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD11">
         <v>0</v>
@@ -3450,13 +3450,13 @@
         <v>391</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O17">
         <v>0</v>
@@ -3498,10 +3498,10 @@
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD17">
         <v>0</v>
@@ -3539,10 +3539,10 @@
         <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E18" t="s">
         <v>137</v>
@@ -3655,7 +3655,7 @@
         <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D19" t="s">
         <v>120</v>
@@ -3682,13 +3682,13 @@
         <v>391</v>
       </c>
       <c r="L19">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M19">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N19">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -3730,10 +3730,10 @@
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC19">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD19">
         <v>0</v>
@@ -3771,10 +3771,10 @@
         <v>45</v>
       </c>
       <c r="C20" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D20" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E20" t="s">
         <v>139</v>
@@ -3887,7 +3887,7 @@
         <v>45</v>
       </c>
       <c r="C21" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D21" t="s">
         <v>120</v>
@@ -3914,13 +3914,13 @@
         <v>391</v>
       </c>
       <c r="L21">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="M21">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="N21">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -3965,7 +3965,7 @@
         <v>1.6</v>
       </c>
       <c r="AC21">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AD21">
         <v>0</v>
@@ -4003,7 +4003,7 @@
         <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D22" t="s">
         <v>120</v>
@@ -4119,7 +4119,7 @@
         <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D23" t="s">
         <v>119</v>
@@ -4262,13 +4262,13 @@
         <v>391</v>
       </c>
       <c r="L24">
-        <v>1.64</v>
+        <v>1.39</v>
       </c>
       <c r="M24">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="N24">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="O24">
         <v>0</v>
@@ -4378,13 +4378,13 @@
         <v>391</v>
       </c>
       <c r="L25">
-        <v>1.39</v>
+        <v>1.64</v>
       </c>
       <c r="M25">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="N25">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="O25">
         <v>0</v>
@@ -4494,13 +4494,13 @@
         <v>391</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -4542,10 +4542,10 @@
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD26">
         <v>0</v>
@@ -4583,7 +4583,7 @@
         <v>47</v>
       </c>
       <c r="C27" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D27" t="s">
         <v>119</v>
@@ -4610,13 +4610,13 @@
         <v>391</v>
       </c>
       <c r="L27">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M27">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N27">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -4658,10 +4658,10 @@
         <v>0</v>
       </c>
       <c r="AB27">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC27">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD27">
         <v>0</v>
@@ -4726,13 +4726,13 @@
         <v>391</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O28">
         <v>0</v>
@@ -4774,10 +4774,10 @@
         <v>0</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD28">
         <v>0</v>
@@ -4815,10 +4815,10 @@
         <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D29" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E29" t="s">
         <v>148</v>
@@ -4931,7 +4931,7 @@
         <v>47</v>
       </c>
       <c r="C30" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D30" t="s">
         <v>120</v>
@@ -5047,10 +5047,10 @@
         <v>47</v>
       </c>
       <c r="C31" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D31" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E31" t="s">
         <v>150</v>
@@ -5163,7 +5163,7 @@
         <v>47</v>
       </c>
       <c r="C32" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="D32" t="s">
         <v>120</v>
@@ -5279,7 +5279,7 @@
         <v>47</v>
       </c>
       <c r="C33" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="D33" t="s">
         <v>120</v>
@@ -5306,13 +5306,13 @@
         <v>391</v>
       </c>
       <c r="L33">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M33">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N33">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -5354,10 +5354,10 @@
         <v>0</v>
       </c>
       <c r="AB33">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC33">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD33">
         <v>0</v>
@@ -5627,7 +5627,7 @@
         <v>48</v>
       </c>
       <c r="C36" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D36" t="s">
         <v>120</v>
@@ -6094,7 +6094,7 @@
         <v>96</v>
       </c>
       <c r="D40" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E40" t="s">
         <v>159</v>
@@ -6118,13 +6118,13 @@
         <v>391</v>
       </c>
       <c r="L40">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="M40">
-        <v>3.55</v>
+        <v>3.84</v>
       </c>
       <c r="N40">
-        <v>2.65</v>
+        <v>2.22</v>
       </c>
       <c r="O40">
         <v>0</v>
@@ -6166,10 +6166,10 @@
         <v>0</v>
       </c>
       <c r="AB40">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC40">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD40">
         <v>0</v>
@@ -6210,7 +6210,7 @@
         <v>97</v>
       </c>
       <c r="D41" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E41" t="s">
         <v>160</v>
@@ -6234,13 +6234,13 @@
         <v>391</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M41">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O41">
         <v>0</v>
@@ -6282,10 +6282,10 @@
         <v>0</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD41">
         <v>0</v>
@@ -6326,7 +6326,7 @@
         <v>98</v>
       </c>
       <c r="D42" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E42" t="s">
         <v>161</v>
@@ -6350,13 +6350,13 @@
         <v>391</v>
       </c>
       <c r="L42">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M42">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N42">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O42">
         <v>0</v>
@@ -6558,7 +6558,7 @@
         <v>100</v>
       </c>
       <c r="D44" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E44" t="s">
         <v>163</v>
@@ -6787,10 +6787,10 @@
         <v>52</v>
       </c>
       <c r="C46" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D46" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E46" t="s">
         <v>165</v>
@@ -7019,10 +7019,10 @@
         <v>52</v>
       </c>
       <c r="C48" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D48" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E48" t="s">
         <v>167</v>
@@ -7135,7 +7135,7 @@
         <v>52</v>
       </c>
       <c r="C49" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D49" t="s">
         <v>120</v>
@@ -7162,13 +7162,13 @@
         <v>391</v>
       </c>
       <c r="L49">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M49">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N49">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O49">
         <v>0</v>
@@ -7210,10 +7210,10 @@
         <v>0</v>
       </c>
       <c r="AB49">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC49">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD49">
         <v>0</v>
@@ -7251,7 +7251,7 @@
         <v>52</v>
       </c>
       <c r="C50" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D50" t="s">
         <v>120</v>
@@ -7278,13 +7278,13 @@
         <v>391</v>
       </c>
       <c r="L50">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M50">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O50">
         <v>0</v>
@@ -7326,10 +7326,10 @@
         <v>0</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD50">
         <v>0</v>
@@ -7483,10 +7483,10 @@
         <v>52</v>
       </c>
       <c r="C52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D52" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E52" t="s">
         <v>171</v>
@@ -7510,13 +7510,13 @@
         <v>391</v>
       </c>
       <c r="L52">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M52">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N52">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="O52">
         <v>0</v>
@@ -7715,7 +7715,7 @@
         <v>52</v>
       </c>
       <c r="C54" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="D54" t="s">
         <v>120</v>
@@ -7742,13 +7742,13 @@
         <v>391</v>
       </c>
       <c r="L54">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M54">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O54">
         <v>0</v>
@@ -7790,10 +7790,10 @@
         <v>0</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD54">
         <v>0</v>
@@ -7947,7 +7947,7 @@
         <v>52</v>
       </c>
       <c r="C56" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D56" t="s">
         <v>120</v>
@@ -7974,13 +7974,13 @@
         <v>391</v>
       </c>
       <c r="L56">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M56">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N56">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O56">
         <v>0</v>
@@ -8022,10 +8022,10 @@
         <v>0</v>
       </c>
       <c r="AB56">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC56">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD56">
         <v>0</v>
@@ -8063,10 +8063,10 @@
         <v>52</v>
       </c>
       <c r="C57" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D57" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E57" t="s">
         <v>176</v>
@@ -8090,13 +8090,13 @@
         <v>391</v>
       </c>
       <c r="L57">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M57">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="O57">
         <v>0</v>
@@ -8295,10 +8295,10 @@
         <v>53</v>
       </c>
       <c r="C59" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D59" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E59" t="s">
         <v>178</v>
@@ -8411,10 +8411,10 @@
         <v>53</v>
       </c>
       <c r="C60" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D60" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E60" t="s">
         <v>179</v>
@@ -8438,13 +8438,13 @@
         <v>391</v>
       </c>
       <c r="L60">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M60">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N60">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O60">
         <v>0</v>
@@ -8486,10 +8486,10 @@
         <v>0</v>
       </c>
       <c r="AB60">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC60">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AD60">
         <v>0</v>
@@ -8527,7 +8527,7 @@
         <v>53</v>
       </c>
       <c r="C61" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D61" t="s">
         <v>120</v>
@@ -8643,7 +8643,7 @@
         <v>53</v>
       </c>
       <c r="C62" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D62" t="s">
         <v>120</v>
@@ -8670,13 +8670,13 @@
         <v>391</v>
       </c>
       <c r="L62">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M62">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O62">
         <v>0</v>
@@ -8718,10 +8718,10 @@
         <v>0</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD62">
         <v>0</v>
@@ -8759,7 +8759,7 @@
         <v>54</v>
       </c>
       <c r="C63" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="D63" t="s">
         <v>120</v>
@@ -8786,13 +8786,13 @@
         <v>391</v>
       </c>
       <c r="L63">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M63">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O63">
         <v>0</v>
@@ -8834,10 +8834,10 @@
         <v>0</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD63">
         <v>0</v>
@@ -8875,10 +8875,10 @@
         <v>54</v>
       </c>
       <c r="C64" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D64" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E64" t="s">
         <v>183</v>
@@ -8902,13 +8902,13 @@
         <v>391</v>
       </c>
       <c r="L64">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M64">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N64">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O64">
         <v>0</v>
@@ -8950,10 +8950,10 @@
         <v>0</v>
       </c>
       <c r="AB64">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC64">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD64">
         <v>0</v>
@@ -8991,7 +8991,7 @@
         <v>54</v>
       </c>
       <c r="C65" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="D65" t="s">
         <v>119</v>
@@ -9018,13 +9018,13 @@
         <v>391</v>
       </c>
       <c r="L65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M65">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O65">
         <v>0</v>
@@ -9066,10 +9066,10 @@
         <v>0</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD65">
         <v>0</v>
@@ -9107,7 +9107,7 @@
         <v>54</v>
       </c>
       <c r="C66" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="D66" t="s">
         <v>120</v>
@@ -9134,13 +9134,13 @@
         <v>391</v>
       </c>
       <c r="L66">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M66">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -9182,10 +9182,10 @@
         <v>0</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD66">
         <v>0</v>
@@ -9223,7 +9223,7 @@
         <v>54</v>
       </c>
       <c r="C67" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="D67" t="s">
         <v>120</v>
@@ -9339,7 +9339,7 @@
         <v>54</v>
       </c>
       <c r="C68" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="D68" t="s">
         <v>119</v>
@@ -9366,13 +9366,13 @@
         <v>391</v>
       </c>
       <c r="L68">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M68">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O68">
         <v>0</v>
@@ -9414,10 +9414,10 @@
         <v>0</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD68">
         <v>0</v>
@@ -9455,7 +9455,7 @@
         <v>54</v>
       </c>
       <c r="C69" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="D69" t="s">
         <v>120</v>
@@ -9482,13 +9482,13 @@
         <v>391</v>
       </c>
       <c r="L69">
-        <v>2.95</v>
+        <v>1.47</v>
       </c>
       <c r="M69">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="N69">
-        <v>2.28</v>
+        <v>6.2</v>
       </c>
       <c r="O69">
         <v>0</v>
@@ -9530,10 +9530,10 @@
         <v>0</v>
       </c>
       <c r="AB69">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="AC69">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AD69">
         <v>0</v>
@@ -9687,10 +9687,10 @@
         <v>54</v>
       </c>
       <c r="C71" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D71" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E71" t="s">
         <v>190</v>
@@ -9803,7 +9803,7 @@
         <v>54</v>
       </c>
       <c r="C72" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D72" t="s">
         <v>120</v>
@@ -9919,7 +9919,7 @@
         <v>54</v>
       </c>
       <c r="C73" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="D73" t="s">
         <v>120</v>
@@ -10062,13 +10062,13 @@
         <v>391</v>
       </c>
       <c r="L74">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M74">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="N74">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="O74">
         <v>0</v>
@@ -10110,10 +10110,10 @@
         <v>0</v>
       </c>
       <c r="AB74">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AC74">
-        <v>2.31</v>
+        <v>2.22</v>
       </c>
       <c r="AD74">
         <v>0</v>
@@ -10151,7 +10151,7 @@
         <v>54</v>
       </c>
       <c r="C75" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="D75" t="s">
         <v>119</v>
@@ -10178,13 +10178,13 @@
         <v>391</v>
       </c>
       <c r="L75">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M75">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N75">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O75">
         <v>0</v>
@@ -10226,10 +10226,10 @@
         <v>0</v>
       </c>
       <c r="AB75">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC75">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD75">
         <v>0</v>
@@ -10267,10 +10267,10 @@
         <v>54</v>
       </c>
       <c r="C76" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D76" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E76" t="s">
         <v>195</v>
@@ -10294,13 +10294,13 @@
         <v>391</v>
       </c>
       <c r="L76">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M76">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N76">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O76">
         <v>0</v>
@@ -10342,10 +10342,10 @@
         <v>0</v>
       </c>
       <c r="AB76">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC76">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AD76">
         <v>0</v>
@@ -10499,7 +10499,7 @@
         <v>54</v>
       </c>
       <c r="C78" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="D78" t="s">
         <v>120</v>
@@ -10615,7 +10615,7 @@
         <v>54</v>
       </c>
       <c r="C79" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D79" t="s">
         <v>120</v>
@@ -10847,7 +10847,7 @@
         <v>54</v>
       </c>
       <c r="C81" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D81" t="s">
         <v>120</v>
@@ -10874,13 +10874,13 @@
         <v>391</v>
       </c>
       <c r="L81">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M81">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N81">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O81">
         <v>0</v>
@@ -10922,10 +10922,10 @@
         <v>0</v>
       </c>
       <c r="AB81">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC81">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD81">
         <v>0</v>
@@ -10963,10 +10963,10 @@
         <v>54</v>
       </c>
       <c r="C82" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="D82" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E82" t="s">
         <v>201</v>
@@ -11079,7 +11079,7 @@
         <v>55</v>
       </c>
       <c r="C83" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="D83" t="s">
         <v>120</v>
@@ -11106,13 +11106,13 @@
         <v>391</v>
       </c>
       <c r="L83">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M83">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O83">
         <v>0</v>
@@ -11195,7 +11195,7 @@
         <v>55</v>
       </c>
       <c r="C84" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="D84" t="s">
         <v>120</v>
@@ -11222,13 +11222,13 @@
         <v>391</v>
       </c>
       <c r="L84">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="M84">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N84">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O84">
         <v>0</v>
@@ -11270,16 +11270,16 @@
         <v>0</v>
       </c>
       <c r="AB84">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC84">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD84">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE84">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF84">
         <v>0</v>
@@ -11311,7 +11311,7 @@
         <v>55</v>
       </c>
       <c r="C85" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="D85" t="s">
         <v>120</v>
@@ -11338,13 +11338,13 @@
         <v>391</v>
       </c>
       <c r="L85">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M85">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O85">
         <v>0</v>
@@ -11427,7 +11427,7 @@
         <v>55</v>
       </c>
       <c r="C86" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D86" t="s">
         <v>120</v>
@@ -11454,13 +11454,13 @@
         <v>391</v>
       </c>
       <c r="L86">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M86">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N86">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O86">
         <v>0</v>
@@ -11502,10 +11502,10 @@
         <v>0</v>
       </c>
       <c r="AB86">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC86">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD86">
         <v>0</v>
@@ -11543,7 +11543,7 @@
         <v>55</v>
       </c>
       <c r="C87" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="D87" t="s">
         <v>120</v>
@@ -11570,13 +11570,13 @@
         <v>391</v>
       </c>
       <c r="L87">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="M87">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O87">
         <v>0</v>
@@ -11618,16 +11618,16 @@
         <v>0</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC87">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD87">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE87">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF87">
         <v>0</v>
@@ -11659,7 +11659,7 @@
         <v>55</v>
       </c>
       <c r="C88" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="D88" t="s">
         <v>120</v>
@@ -11686,13 +11686,13 @@
         <v>391</v>
       </c>
       <c r="L88">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M88">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N88">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O88">
         <v>0</v>
@@ -11775,7 +11775,7 @@
         <v>55</v>
       </c>
       <c r="C89" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="D89" t="s">
         <v>120</v>
@@ -11802,13 +11802,13 @@
         <v>391</v>
       </c>
       <c r="L89">
-        <v>3.15</v>
+        <v>2.6</v>
       </c>
       <c r="M89">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N89">
-        <v>2.17</v>
+        <v>2.6</v>
       </c>
       <c r="O89">
         <v>0</v>
@@ -11850,10 +11850,10 @@
         <v>0</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC89">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD89">
         <v>0</v>
@@ -12123,7 +12123,7 @@
         <v>57</v>
       </c>
       <c r="C92" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D92" t="s">
         <v>120</v>
@@ -12355,7 +12355,7 @@
         <v>57</v>
       </c>
       <c r="C94" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D94" t="s">
         <v>120</v>
@@ -12587,7 +12587,7 @@
         <v>57</v>
       </c>
       <c r="C96" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D96" t="s">
         <v>120</v>
@@ -12819,7 +12819,7 @@
         <v>59</v>
       </c>
       <c r="C98" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D98" t="s">
         <v>120</v>
@@ -13167,7 +13167,7 @@
         <v>60</v>
       </c>
       <c r="C101" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D101" t="s">
         <v>120</v>
@@ -13399,10 +13399,10 @@
         <v>60</v>
       </c>
       <c r="C103" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="D103" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E103" t="s">
         <v>222</v>
@@ -13515,7 +13515,7 @@
         <v>60</v>
       </c>
       <c r="C104" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D104" t="s">
         <v>120</v>
@@ -13631,10 +13631,10 @@
         <v>60</v>
       </c>
       <c r="C105" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="D105" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E105" t="s">
         <v>224</v>
@@ -13747,7 +13747,7 @@
         <v>60</v>
       </c>
       <c r="C106" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D106" t="s">
         <v>120</v>
@@ -13863,7 +13863,7 @@
         <v>60</v>
       </c>
       <c r="C107" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D107" t="s">
         <v>119</v>
@@ -14095,7 +14095,7 @@
         <v>60</v>
       </c>
       <c r="C109" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="D109" t="s">
         <v>120</v>
@@ -14211,7 +14211,7 @@
         <v>61</v>
       </c>
       <c r="C110" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D110" t="s">
         <v>120</v>
@@ -14327,7 +14327,7 @@
         <v>62</v>
       </c>
       <c r="C111" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D111" t="s">
         <v>120</v>
@@ -14559,7 +14559,7 @@
         <v>62</v>
       </c>
       <c r="C113" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D113" t="s">
         <v>120</v>
@@ -14675,7 +14675,7 @@
         <v>63</v>
       </c>
       <c r="C114" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="D114" t="s">
         <v>120</v>
@@ -14791,7 +14791,7 @@
         <v>63</v>
       </c>
       <c r="C115" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="D115" t="s">
         <v>120</v>
@@ -14907,7 +14907,7 @@
         <v>63</v>
       </c>
       <c r="C116" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D116" t="s">
         <v>119</v>
@@ -15371,10 +15371,10 @@
         <v>66</v>
       </c>
       <c r="C120" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D120" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E120" t="s">
         <v>239</v>
@@ -15398,13 +15398,13 @@
         <v>391</v>
       </c>
       <c r="L120">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M120">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O120">
         <v>0</v>
@@ -15440,16 +15440,16 @@
         <v>0</v>
       </c>
       <c r="Z120">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA120">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB120">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC120">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD120">
         <v>0</v>
@@ -15487,10 +15487,10 @@
         <v>66</v>
       </c>
       <c r="C121" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D121" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E121" t="s">
         <v>240</v>
@@ -15514,13 +15514,13 @@
         <v>391</v>
       </c>
       <c r="L121">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M121">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N121">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O121">
         <v>0</v>
@@ -15556,16 +15556,16 @@
         <v>0</v>
       </c>
       <c r="Z121">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA121">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB121">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC121">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD121">
         <v>0</v>
@@ -15603,7 +15603,7 @@
         <v>66</v>
       </c>
       <c r="C122" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D122" t="s">
         <v>119</v>
@@ -15630,13 +15630,13 @@
         <v>391</v>
       </c>
       <c r="L122">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M122">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N122">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O122">
         <v>0</v>
@@ -15678,10 +15678,10 @@
         <v>0</v>
       </c>
       <c r="AB122">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC122">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD122">
         <v>0</v>
@@ -15835,7 +15835,7 @@
         <v>66</v>
       </c>
       <c r="C124" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D124" t="s">
         <v>119</v>
@@ -15862,13 +15862,13 @@
         <v>391</v>
       </c>
       <c r="L124">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M124">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N124">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O124">
         <v>0</v>
@@ -15910,10 +15910,10 @@
         <v>0</v>
       </c>
       <c r="AB124">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC124">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD124">
         <v>0</v>
@@ -16067,7 +16067,7 @@
         <v>68</v>
       </c>
       <c r="C126" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D126" t="s">
         <v>119</v>
@@ -16094,13 +16094,13 @@
         <v>391</v>
       </c>
       <c r="L126">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M126">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O126">
         <v>0</v>
@@ -16142,10 +16142,10 @@
         <v>0</v>
       </c>
       <c r="AB126">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC126">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD126">
         <v>0</v>
@@ -16210,13 +16210,13 @@
         <v>391</v>
       </c>
       <c r="L127">
-        <v>2.09</v>
+        <v>3.8</v>
       </c>
       <c r="M127">
         <v>3.15</v>
       </c>
       <c r="N127">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="O127">
         <v>0</v>
@@ -16258,7 +16258,7 @@
         <v>0</v>
       </c>
       <c r="AB127">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC127">
         <v>1.57</v>
@@ -16299,7 +16299,7 @@
         <v>68</v>
       </c>
       <c r="C128" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D128" t="s">
         <v>119</v>
@@ -16415,7 +16415,7 @@
         <v>68</v>
       </c>
       <c r="C129" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D129" t="s">
         <v>119</v>
@@ -16442,13 +16442,13 @@
         <v>391</v>
       </c>
       <c r="L129">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M129">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N129">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O129">
         <v>0</v>
@@ -16490,10 +16490,10 @@
         <v>0</v>
       </c>
       <c r="AB129">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC129">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD129">
         <v>0</v>
@@ -16531,7 +16531,7 @@
         <v>69</v>
       </c>
       <c r="C130" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D130" t="s">
         <v>119</v>
@@ -16879,7 +16879,7 @@
         <v>71</v>
       </c>
       <c r="C133" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D133" t="s">
         <v>119</v>
@@ -17111,7 +17111,7 @@
         <v>73</v>
       </c>
       <c r="C135" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D135" t="s">
         <v>119</v>
@@ -17227,7 +17227,7 @@
         <v>74</v>
       </c>
       <c r="C136" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D136" t="s">
         <v>119</v>

--- a/jogos_2025-08-03.xlsx
+++ b/jogos_2025-08-03.xlsx
@@ -253,12 +253,12 @@
     <t>Austria 2. Liga</t>
   </si>
   <si>
+    <t>Japan J2 League</t>
+  </si>
+  <si>
     <t>Ukraine Ukrainian Premier League</t>
   </si>
   <si>
-    <t>Japan J2 League</t>
-  </si>
-  <si>
     <t>Russia Russian Premier League</t>
   </si>
   <si>
@@ -274,33 +274,33 @@
     <t>China Chinese Super League</t>
   </si>
   <si>
+    <t>Germany 3. Liga</t>
+  </si>
+  <si>
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
-    <t>Germany 3. Liga</t>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
+    <t>Denmark Superliga</t>
   </si>
   <si>
     <t>Switzerland Super League</t>
   </si>
   <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
     <t>Switzerland Challenge League</t>
   </si>
   <si>
-    <t>Denmark Superliga</t>
+    <t>Poland 1. Liga</t>
   </si>
   <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
@@ -310,12 +310,12 @@
     <t>Scotland Premiership</t>
   </si>
   <si>
+    <t>Finland Veikkausliiga</t>
+  </si>
+  <si>
     <t>Czech Republic First League</t>
   </si>
   <si>
-    <t>Finland Veikkausliiga</t>
-  </si>
-  <si>
     <t>Norway First Division</t>
   </si>
   <si>
@@ -331,24 +331,24 @@
     <t>Montenegro Montenegrin First League</t>
   </si>
   <si>
+    <t>Slovakia Super Liga</t>
+  </si>
+  <si>
+    <t>Uzbekistan Uzbekistan Super League</t>
+  </si>
+  <si>
     <t>Austria Bundesliga</t>
   </si>
   <si>
-    <t>Uzbekistan Uzbekistan Super League</t>
-  </si>
-  <si>
-    <t>Slovakia Super Liga</t>
-  </si>
-  <si>
     <t>Hungary NB II</t>
   </si>
   <si>
+    <t>Romania Liga I</t>
+  </si>
+  <si>
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
-    <t>Romania Liga I</t>
-  </si>
-  <si>
     <t>Hungary NB I</t>
   </si>
   <si>
@@ -358,12 +358,12 @@
     <t>USA NWSL</t>
   </si>
   <si>
+    <t>Serbia SuperLiga</t>
+  </si>
+  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
-    <t>Serbia SuperLiga</t>
-  </si>
-  <si>
     <t>Brazil Serie A</t>
   </si>
   <si>
@@ -382,33 +382,33 @@
     <t>Wollongong Wolves</t>
   </si>
   <si>
+    <t>Sydney United</t>
+  </si>
+  <si>
     <t>Blacktown City</t>
   </si>
   <si>
-    <t>Sydney United</t>
-  </si>
-  <si>
     <t>Central Coast II</t>
   </si>
   <si>
     <t>SKA Khabarovsk</t>
   </si>
   <si>
+    <t>Slavia Praha II</t>
+  </si>
+  <si>
     <t>Viktoria Žižkov</t>
   </si>
   <si>
-    <t>Slavia Praha II</t>
-  </si>
-  <si>
     <t>WSPG Wels</t>
   </si>
   <si>
+    <t>Roasso Kumamoto</t>
+  </si>
+  <si>
     <t>Kudrivka</t>
   </si>
   <si>
-    <t>Roasso Kumamoto</t>
-  </si>
-  <si>
     <t>Akron</t>
   </si>
   <si>
@@ -424,69 +424,69 @@
     <t>Dalian Zhixing</t>
   </si>
   <si>
+    <t>Erzgebirge Aue</t>
+  </si>
+  <si>
+    <t>Dongguan United</t>
+  </si>
+  <si>
+    <t>Qingdao Red Lions</t>
+  </si>
+  <si>
+    <t>Magdeburg</t>
+  </si>
+  <si>
     <t>Hannover 96</t>
   </si>
   <si>
-    <t>Dongguan United</t>
-  </si>
-  <si>
     <t>KRC Genk</t>
   </si>
   <si>
-    <t>Erzgebirge Aue</t>
-  </si>
-  <si>
-    <t>Magdeburg</t>
-  </si>
-  <si>
     <t>Greuther Fürth</t>
   </si>
   <si>
-    <t>Qingdao Red Lions</t>
-  </si>
-  <si>
     <t>Beijing Guoan</t>
   </si>
   <si>
     <t>Wuhan Three Towns</t>
   </si>
   <si>
+    <t>Sichuan Jiuniu</t>
+  </si>
+  <si>
+    <t>Häcken</t>
+  </si>
+  <si>
+    <t>SønderjyskE</t>
+  </si>
+  <si>
+    <t>Djurgården</t>
+  </si>
+  <si>
+    <t>Randers</t>
+  </si>
+  <si>
     <t>Thun</t>
   </si>
   <si>
-    <t>Sichuan Jiuniu</t>
-  </si>
-  <si>
-    <t>Djurgården</t>
+    <t>Spartak Kostroma</t>
   </si>
   <si>
     <t>Yverdon Sport</t>
   </si>
   <si>
-    <t>Randers</t>
-  </si>
-  <si>
-    <t>Häcken</t>
-  </si>
-  <si>
-    <t>SønderjyskE</t>
-  </si>
-  <si>
-    <t>Spartak Kostroma</t>
+    <t>Baník Ostrava II</t>
+  </si>
+  <si>
+    <t>Śląsk Wrocław</t>
+  </si>
+  <si>
+    <t>Epitsentr Dunayivtsi</t>
   </si>
   <si>
     <t>HamKam</t>
   </si>
   <si>
-    <t>Baník Ostrava II</t>
-  </si>
-  <si>
-    <t>Epitsentr Dunayivtsi</t>
-  </si>
-  <si>
-    <t>Śląsk Wrocław</t>
-  </si>
-  <si>
     <t>Baltika</t>
   </si>
   <si>
@@ -499,67 +499,109 @@
     <t>Falkirk</t>
   </si>
   <si>
+    <t>SJK</t>
+  </si>
+  <si>
     <t>Slovácko</t>
   </si>
   <si>
-    <t>SJK</t>
-  </si>
-  <si>
     <t>Sogndal</t>
   </si>
   <si>
     <t>Suduroy</t>
   </si>
   <si>
+    <t>Jeunesse Canach</t>
+  </si>
+  <si>
+    <t>Mondorf-les-Bains</t>
+  </si>
+  <si>
+    <t>Jeunesse d'Esch</t>
+  </si>
+  <si>
+    <t>Differdange 03</t>
+  </si>
+  <si>
+    <t>Hostert</t>
+  </si>
+  <si>
+    <t>F91 Dudelange</t>
+  </si>
+  <si>
+    <t>Rodange</t>
+  </si>
+  <si>
+    <t>Cercle Brugge</t>
+  </si>
+  <si>
+    <t>Harju Jalgpallikool</t>
+  </si>
+  <si>
     <t>EB - Streymur</t>
   </si>
   <si>
-    <t>Jeunesse d'Esch</t>
-  </si>
-  <si>
-    <t>F91 Dudelange</t>
-  </si>
-  <si>
-    <t>Jeunesse Canach</t>
-  </si>
-  <si>
     <t>Dundee</t>
   </si>
   <si>
-    <t>Differdange 03</t>
-  </si>
-  <si>
-    <t>Hostert</t>
-  </si>
-  <si>
-    <t>Mondorf-les-Bains</t>
-  </si>
-  <si>
-    <t>Cercle Brugge</t>
+    <t>AGF</t>
   </si>
   <si>
     <t>Swift Hesperange</t>
   </si>
   <si>
-    <t>AGF</t>
-  </si>
-  <si>
-    <t>Harju Jalgpallikool</t>
-  </si>
-  <si>
-    <t>Rodange</t>
+    <t>Viktoria Köln</t>
   </si>
   <si>
     <t>Étoile Carouge</t>
   </si>
   <si>
+    <t>Luzern</t>
+  </si>
+  <si>
     <t>Sirius</t>
   </si>
   <si>
-    <t>Viktoria Köln</t>
-  </si>
-  <si>
-    <t>Luzern</t>
+    <t>KFUM</t>
+  </si>
+  <si>
+    <t>Dečić</t>
+  </si>
+  <si>
+    <t>Pogoń Siedlce</t>
+  </si>
+  <si>
+    <t>Arsenal Tivat</t>
+  </si>
+  <si>
+    <t>Sutjeska</t>
+  </si>
+  <si>
+    <t>Strømsgodset</t>
+  </si>
+  <si>
+    <t>FK Jezero Plav</t>
+  </si>
+  <si>
+    <t>Petrovac</t>
+  </si>
+  <si>
+    <t>Molde</t>
+  </si>
+  <si>
+    <t>Trenčín</t>
+  </si>
+  <si>
+    <t>Vlašim</t>
+  </si>
+  <si>
+    <t>Zenit</t>
+  </si>
+  <si>
+    <t>Shortan</t>
+  </si>
+  <si>
+    <t>Rubin Kazan</t>
   </si>
   <si>
     <t>Karpaty</t>
@@ -571,78 +613,36 @@
     <t>Vålerenga</t>
   </si>
   <si>
-    <t>Zenit</t>
-  </si>
-  <si>
-    <t>FK Jezero Plav</t>
-  </si>
-  <si>
-    <t>KFUM</t>
+    <t>Grazer AK</t>
+  </si>
+  <si>
+    <t>Dukla Praha</t>
   </si>
   <si>
     <t>Rapid Wien</t>
   </si>
   <si>
-    <t>Vlašim</t>
-  </si>
-  <si>
-    <t>Rubin Kazan</t>
-  </si>
-  <si>
-    <t>Grazer AK</t>
-  </si>
-  <si>
-    <t>Pogoń Siedlce</t>
-  </si>
-  <si>
-    <t>Molde</t>
-  </si>
-  <si>
-    <t>Shortan</t>
-  </si>
-  <si>
-    <t>Dukla Praha</t>
-  </si>
-  <si>
-    <t>Dečić</t>
-  </si>
-  <si>
-    <t>Petrovac</t>
-  </si>
-  <si>
-    <t>Trenčín</t>
-  </si>
-  <si>
-    <t>Sutjeska</t>
-  </si>
-  <si>
-    <t>Arsenal Tivat</t>
-  </si>
-  <si>
-    <t>Strømsgodset</t>
-  </si>
-  <si>
     <t>Motor Lublin</t>
   </si>
   <si>
+    <t>Radomiak Radom</t>
+  </si>
+  <si>
+    <t>Szentlőrinc SE</t>
+  </si>
+  <si>
+    <t>Hermannstadt</t>
+  </si>
+  <si>
+    <t>Maribor</t>
+  </si>
+  <si>
     <t>Karcag SE</t>
   </si>
   <si>
-    <t>Radomiak Radom</t>
-  </si>
-  <si>
-    <t>Szentlőrinc SE</t>
-  </si>
-  <si>
     <t>Celtic</t>
   </si>
   <si>
-    <t>Maribor</t>
-  </si>
-  <si>
-    <t>Hermannstadt</t>
-  </si>
-  <si>
     <t>Várda SE</t>
   </si>
   <si>
@@ -652,78 +652,78 @@
     <t>Brøndby</t>
   </si>
   <si>
+    <t>Fakel</t>
+  </si>
+  <si>
+    <t>FK Chernomorets Novorossiysk</t>
+  </si>
+  <si>
     <t>Tammeka</t>
   </si>
   <si>
-    <t>FK Chernomorets Novorossiysk</t>
-  </si>
-  <si>
-    <t>Fakel</t>
-  </si>
-  <si>
     <t>Vysočina Jihlava</t>
   </si>
   <si>
     <t>B68</t>
   </si>
   <si>
+    <t>O'Higgins</t>
+  </si>
+  <si>
+    <t>Washington Spirit</t>
+  </si>
+  <si>
     <t>Union Saint-Gilloise</t>
   </si>
   <si>
-    <t>O'Higgins</t>
-  </si>
-  <si>
-    <t>Washington Spirit</t>
+    <t>Železničar Pančevo</t>
+  </si>
+  <si>
+    <t>Csákvári TK</t>
+  </si>
+  <si>
+    <t>Žilina</t>
+  </si>
+  <si>
+    <t>Honvéd W</t>
+  </si>
+  <si>
+    <t>Tiszakécske</t>
+  </si>
+  <si>
+    <t>Sporting KC II</t>
+  </si>
+  <si>
+    <t>MKK-Dnepr</t>
   </si>
   <si>
     <t>Békéscsaba</t>
   </si>
   <si>
-    <t>Tiszakécske</t>
-  </si>
-  <si>
-    <t>Honvéd W</t>
-  </si>
-  <si>
-    <t>Csákvári TK</t>
-  </si>
-  <si>
-    <t>MKK-Dnepr</t>
-  </si>
-  <si>
-    <t>Žilina</t>
-  </si>
-  <si>
-    <t>Sporting KC II</t>
-  </si>
-  <si>
     <t>Ajka</t>
   </si>
   <si>
-    <t>Železničar Pančevo</t>
-  </si>
-  <si>
     <t>Sporting Charleroi</t>
   </si>
   <si>
+    <t>Wehen Wiesbaden</t>
+  </si>
+  <si>
+    <t>Makhachkala</t>
+  </si>
+  <si>
     <t>Górnik Łęczna</t>
   </si>
   <si>
-    <t>Makhachkala</t>
-  </si>
-  <si>
-    <t>Wehen Wiesbaden</t>
-  </si>
-  <si>
     <t>Pardubice</t>
   </si>
   <si>
+    <t>Chicago Fire II</t>
+  </si>
+  <si>
     <t>Győri ETO</t>
   </si>
   <si>
-    <t>Chicago Fire II</t>
-  </si>
-  <si>
     <t>Olimpija</t>
   </si>
   <si>
@@ -736,39 +736,39 @@
     <t>Botafogo</t>
   </si>
   <si>
+    <t>Chapecoense</t>
+  </si>
+  <si>
+    <t>Corinthians</t>
+  </si>
+  <si>
     <t>Partizan</t>
   </si>
   <si>
     <t>Colo-Colo</t>
   </si>
   <si>
-    <t>Chapecoense</t>
-  </si>
-  <si>
-    <t>Corinthians</t>
-  </si>
-  <si>
     <t>Atlético Ottawa</t>
   </si>
   <si>
+    <t>Ñublense</t>
+  </si>
+  <si>
+    <t>Ceará</t>
+  </si>
+  <si>
+    <t>Atlético PR</t>
+  </si>
+  <si>
     <t>Atlético Mineiro</t>
   </si>
   <si>
-    <t>Ceará</t>
-  </si>
-  <si>
-    <t>Ñublense</t>
-  </si>
-  <si>
-    <t>Atlético PR</t>
+    <t>Orlando Pride</t>
   </si>
   <si>
     <t>Philadelphia Union II</t>
   </si>
   <si>
-    <t>Orlando Pride</t>
-  </si>
-  <si>
     <t>Vitória</t>
   </si>
   <si>
@@ -787,33 +787,33 @@
     <t>Sydney II</t>
   </si>
   <si>
+    <t>St. George Saints</t>
+  </si>
+  <si>
     <t>Mt Druitt Town</t>
   </si>
   <si>
-    <t>St. George Saints</t>
-  </si>
-  <si>
     <t>Marconi Stallions</t>
   </si>
   <si>
     <t>Torpedo Moskva</t>
   </si>
   <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
     <t>Prostějov</t>
   </si>
   <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
     <t>Floridsdorfer AC</t>
   </si>
   <si>
+    <t>Mito Hollyhock</t>
+  </si>
+  <si>
     <t>Oleksandria</t>
   </si>
   <si>
-    <t>Mito Hollyhock</t>
-  </si>
-  <si>
     <t>Spartak Moskva</t>
   </si>
   <si>
@@ -829,69 +829,69 @@
     <t>Qingdao Jonoon</t>
   </si>
   <si>
+    <t>Hansa Rostock</t>
+  </si>
+  <si>
+    <t>Nantong Zhiyun</t>
+  </si>
+  <si>
+    <t>Heilongjiang Lava Spring</t>
+  </si>
+  <si>
+    <t>Eintracht Braunschweig</t>
+  </si>
+  <si>
     <t>Kaiserslautern</t>
   </si>
   <si>
-    <t>Nantong Zhiyun</t>
-  </si>
-  <si>
     <t>Royal Antwerp FC</t>
   </si>
   <si>
-    <t>Hansa Rostock</t>
-  </si>
-  <si>
-    <t>Eintracht Braunschweig</t>
-  </si>
-  <si>
     <t>Dynamo Dresden</t>
   </si>
   <si>
-    <t>Heilongjiang Lava Spring</t>
-  </si>
-  <si>
     <t>Tianjin Teda</t>
   </si>
   <si>
     <t>Changchun Yatai</t>
   </si>
   <si>
+    <t>Zhejiang FC</t>
+  </si>
+  <si>
+    <t>Elfsborg</t>
+  </si>
+  <si>
+    <t>Nordsjælland</t>
+  </si>
+  <si>
+    <t>Halmstad</t>
+  </si>
+  <si>
+    <t>Silkeborg</t>
+  </si>
+  <si>
     <t>Lausanne Sport</t>
   </si>
   <si>
-    <t>Zhejiang FC</t>
-  </si>
-  <si>
-    <t>Halmstad</t>
+    <t>Neftekhimik</t>
   </si>
   <si>
     <t>Stade Lausanne-Ouchy</t>
   </si>
   <si>
-    <t>Silkeborg</t>
-  </si>
-  <si>
-    <t>Elfsborg</t>
-  </si>
-  <si>
-    <t>Nordsjælland</t>
-  </si>
-  <si>
-    <t>Neftekhimik</t>
+    <t>Líšeň</t>
+  </si>
+  <si>
+    <t>Ruch Chorzów</t>
+  </si>
+  <si>
+    <t>Shakhtar Donetsk</t>
   </si>
   <si>
     <t>FK Bodo - Glimt</t>
   </si>
   <si>
-    <t>Líšeň</t>
-  </si>
-  <si>
-    <t>Shakhtar Donetsk</t>
-  </si>
-  <si>
-    <t>Ruch Chorzów</t>
-  </si>
-  <si>
     <t>Orenburg</t>
   </si>
   <si>
@@ -904,67 +904,109 @@
     <t>Dundee United</t>
   </si>
   <si>
+    <t>KTP</t>
+  </si>
+  <si>
     <t>Slavia Praha</t>
   </si>
   <si>
-    <t>KTP</t>
-  </si>
-  <si>
     <t>Skeid</t>
   </si>
   <si>
     <t>HB</t>
   </si>
   <si>
+    <t>Mamer</t>
+  </si>
+  <si>
+    <t>UNA Strassen</t>
+  </si>
+  <si>
+    <t>UN Käerjéng</t>
+  </si>
+  <si>
+    <t>Atert Bissen</t>
+  </si>
+  <si>
+    <t>Victoria Rosport</t>
+  </si>
+  <si>
+    <t>Progrès Niederkorn</t>
+  </si>
+  <si>
+    <t>Racing</t>
+  </si>
+  <si>
+    <t>RSC Anderlecht</t>
+  </si>
+  <si>
+    <t>Paide</t>
+  </si>
+  <si>
     <t>KÍ</t>
   </si>
   <si>
-    <t>UN Käerjéng</t>
-  </si>
-  <si>
-    <t>Progrès Niederkorn</t>
-  </si>
-  <si>
-    <t>Mamer</t>
-  </si>
-  <si>
     <t>Hibernian</t>
   </si>
   <si>
-    <t>Atert Bissen</t>
-  </si>
-  <si>
-    <t>Victoria Rosport</t>
-  </si>
-  <si>
-    <t>UNA Strassen</t>
-  </si>
-  <si>
-    <t>RSC Anderlecht</t>
+    <t>Midtjylland</t>
   </si>
   <si>
     <t>UT Pétange</t>
   </si>
   <si>
-    <t>Midtjylland</t>
-  </si>
-  <si>
-    <t>Paide</t>
-  </si>
-  <si>
-    <t>Racing</t>
+    <t>Schweinfurt</t>
   </si>
   <si>
     <t>Vaduz</t>
   </si>
   <si>
+    <t>Zürich</t>
+  </si>
+  <si>
     <t>Öster</t>
   </si>
   <si>
-    <t>Schweinfurt</t>
-  </si>
-  <si>
-    <t>Zürich</t>
+    <t>Rosenborg</t>
+  </si>
+  <si>
+    <t>Mladost DG</t>
+  </si>
+  <si>
+    <t>Odra Opole</t>
+  </si>
+  <si>
+    <t>Jedinstvo</t>
+  </si>
+  <si>
+    <t>Mornar</t>
+  </si>
+  <si>
+    <t>Haugesund</t>
+  </si>
+  <si>
+    <t>Budućnost</t>
+  </si>
+  <si>
+    <t>Bokelj</t>
+  </si>
+  <si>
+    <t>Bryne</t>
+  </si>
+  <si>
+    <t>Spartak Trnava</t>
+  </si>
+  <si>
+    <t>Hanácká</t>
+  </si>
+  <si>
+    <t>CSKA Moskva</t>
+  </si>
+  <si>
+    <t>Xorazm</t>
+  </si>
+  <si>
+    <t>FK Sochi</t>
   </si>
   <si>
     <t>Polessya</t>
@@ -976,78 +1018,36 @@
     <t>Sandefjord</t>
   </si>
   <si>
-    <t>CSKA Moskva</t>
-  </si>
-  <si>
-    <t>Budućnost</t>
-  </si>
-  <si>
-    <t>Rosenborg</t>
+    <t>Austria Wien</t>
+  </si>
+  <si>
+    <t>Baník Ostrava</t>
   </si>
   <si>
     <t>Blau-Weiß Linz</t>
   </si>
   <si>
-    <t>Hanácká</t>
-  </si>
-  <si>
-    <t>FK Sochi</t>
-  </si>
-  <si>
-    <t>Austria Wien</t>
-  </si>
-  <si>
-    <t>Odra Opole</t>
-  </si>
-  <si>
-    <t>Bryne</t>
-  </si>
-  <si>
-    <t>Xorazm</t>
-  </si>
-  <si>
-    <t>Baník Ostrava</t>
-  </si>
-  <si>
-    <t>Mladost DG</t>
-  </si>
-  <si>
-    <t>Bokelj</t>
-  </si>
-  <si>
-    <t>Spartak Trnava</t>
-  </si>
-  <si>
-    <t>Mornar</t>
-  </si>
-  <si>
-    <t>Jedinstvo</t>
-  </si>
-  <si>
-    <t>Haugesund</t>
-  </si>
-  <si>
     <t>Jagiellonia Białystok</t>
   </si>
   <si>
+    <t>Raków Częstochowa</t>
+  </si>
+  <si>
+    <t>Kozármisleny</t>
+  </si>
+  <si>
+    <t>Universitatea Cluj</t>
+  </si>
+  <si>
+    <t>Koper</t>
+  </si>
+  <si>
     <t>Soroksár SC</t>
   </si>
   <si>
-    <t>Raków Częstochowa</t>
-  </si>
-  <si>
-    <t>Kozármisleny</t>
-  </si>
-  <si>
     <t>St. Mirren</t>
   </si>
   <si>
-    <t>Koper</t>
-  </si>
-  <si>
-    <t>Universitatea Cluj</t>
-  </si>
-  <si>
     <t>Paksi SE</t>
   </si>
   <si>
@@ -1057,78 +1057,78 @@
     <t>Viborg</t>
   </si>
   <si>
+    <t>Sokol Saratov</t>
+  </si>
+  <si>
+    <t>Arsenal Tula</t>
+  </si>
+  <si>
     <t>Nõmme Kalju</t>
   </si>
   <si>
-    <t>Arsenal Tula</t>
-  </si>
-  <si>
-    <t>Sokol Saratov</t>
-  </si>
-  <si>
     <t>Vyškov</t>
   </si>
   <si>
     <t>NSÍ</t>
   </si>
   <si>
+    <t>Unión La Calera</t>
+  </si>
+  <si>
+    <t>Portland Thorns</t>
+  </si>
+  <si>
     <t>OH Leuven</t>
   </si>
   <si>
-    <t>Unión La Calera</t>
-  </si>
-  <si>
-    <t>Portland Thorns</t>
+    <t>Napredak</t>
+  </si>
+  <si>
+    <t>BVSC</t>
+  </si>
+  <si>
+    <t>Tatran Prešov</t>
+  </si>
+  <si>
+    <t>Budafoki MTE</t>
+  </si>
+  <si>
+    <t>Mezőkövesd-Zsóry</t>
+  </si>
+  <si>
+    <t>Austin II</t>
+  </si>
+  <si>
+    <t>Slutsk</t>
   </si>
   <si>
     <t>Szeged 2011</t>
   </si>
   <si>
-    <t>Mezőkövesd-Zsóry</t>
-  </si>
-  <si>
-    <t>Budafoki MTE</t>
-  </si>
-  <si>
-    <t>BVSC</t>
-  </si>
-  <si>
-    <t>Slutsk</t>
-  </si>
-  <si>
-    <t>Tatran Prešov</t>
-  </si>
-  <si>
-    <t>Austin II</t>
-  </si>
-  <si>
     <t>Videoton</t>
   </si>
   <si>
-    <t>Napredak</t>
-  </si>
-  <si>
     <t>Sint-Truiden</t>
   </si>
   <si>
+    <t>Ulm</t>
+  </si>
+  <si>
+    <t>Akhmat Grozny</t>
+  </si>
+  <si>
     <t>Puszcza Niepołomice</t>
   </si>
   <si>
-    <t>Akhmat Grozny</t>
-  </si>
-  <si>
-    <t>Ulm</t>
-  </si>
-  <si>
     <t>Sparta Praha</t>
   </si>
   <si>
+    <t>Columbus Crew II</t>
+  </si>
+  <si>
     <t>Újpest</t>
   </si>
   <si>
-    <t>Columbus Crew II</t>
-  </si>
-  <si>
     <t>Celje</t>
   </si>
   <si>
@@ -1141,37 +1141,37 @@
     <t>Cruzeiro</t>
   </si>
   <si>
+    <t>CRB</t>
+  </si>
+  <si>
+    <t>Fortaleza</t>
+  </si>
+  <si>
     <t>Radnički Kragujevac</t>
   </si>
   <si>
     <t>Huachipato</t>
   </si>
   <si>
-    <t>CRB</t>
-  </si>
-  <si>
-    <t>Fortaleza</t>
-  </si>
-  <si>
     <t>York9 FC</t>
   </si>
   <si>
+    <t>Everton</t>
+  </si>
+  <si>
+    <t>Flamengo</t>
+  </si>
+  <si>
+    <t>Paysandu</t>
+  </si>
+  <si>
     <t>Bragantino</t>
   </si>
   <si>
-    <t>Flamengo</t>
-  </si>
-  <si>
-    <t>Everton</t>
-  </si>
-  <si>
-    <t>Paysandu</t>
+    <t>Utah Royals</t>
   </si>
   <si>
     <t>FC Cincinnati II</t>
-  </si>
-  <si>
-    <t>Utah Royals</t>
   </si>
   <si>
     <t>Palmeiras</t>
@@ -2614,7 +2614,7 @@
         <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E10" t="s">
         <v>129</v>
@@ -2638,13 +2638,13 @@
         <v>391</v>
       </c>
       <c r="L10">
-        <v>5.4</v>
+        <v>3.15</v>
       </c>
       <c r="M10">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N10">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -2680,16 +2680,16 @@
         <v>0</v>
       </c>
       <c r="Z10">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA10">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD10">
         <v>0</v>
@@ -2730,7 +2730,7 @@
         <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E11" t="s">
         <v>130</v>
@@ -2754,13 +2754,13 @@
         <v>391</v>
       </c>
       <c r="L11">
-        <v>3.15</v>
+        <v>5.4</v>
       </c>
       <c r="M11">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N11">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -2796,16 +2796,16 @@
         <v>0</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB11">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC11">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD11">
         <v>0</v>
@@ -3450,13 +3450,13 @@
         <v>391</v>
       </c>
       <c r="L17">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M17">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N17">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O17">
         <v>0</v>
@@ -3498,10 +3498,10 @@
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC17">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD17">
         <v>0</v>
@@ -3655,10 +3655,10 @@
         <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D19" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E19" t="s">
         <v>138</v>
@@ -3771,7 +3771,7 @@
         <v>45</v>
       </c>
       <c r="C20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D20" t="s">
         <v>120</v>
@@ -3798,13 +3798,13 @@
         <v>391</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -3846,10 +3846,10 @@
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD20">
         <v>0</v>
@@ -3887,7 +3887,7 @@
         <v>45</v>
       </c>
       <c r="C21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D21" t="s">
         <v>120</v>
@@ -3914,13 +3914,13 @@
         <v>391</v>
       </c>
       <c r="L21">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="M21">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="N21">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -3965,7 +3965,7 @@
         <v>1.6</v>
       </c>
       <c r="AC21">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AD21">
         <v>0</v>
@@ -4003,7 +4003,7 @@
         <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D22" t="s">
         <v>120</v>
@@ -4030,13 +4030,13 @@
         <v>391</v>
       </c>
       <c r="L22">
-        <v>2.26</v>
+        <v>1.61</v>
       </c>
       <c r="M22">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="N22">
-        <v>2.95</v>
+        <v>4.7</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -4078,16 +4078,16 @@
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC22">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD22">
         <v>2.3</v>
       </c>
       <c r="AE22">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AF22">
         <v>0</v>
@@ -4119,10 +4119,10 @@
         <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D23" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E23" t="s">
         <v>142</v>
@@ -4146,13 +4146,13 @@
         <v>391</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O23">
         <v>0</v>
@@ -4194,16 +4194,16 @@
         <v>0</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF23">
         <v>0</v>
@@ -4467,10 +4467,10 @@
         <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D26" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E26" t="s">
         <v>145</v>
@@ -4494,13 +4494,13 @@
         <v>391</v>
       </c>
       <c r="L26">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M26">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N26">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -4542,10 +4542,10 @@
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC26">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD26">
         <v>0</v>
@@ -4583,7 +4583,7 @@
         <v>47</v>
       </c>
       <c r="C27" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D27" t="s">
         <v>119</v>
@@ -4702,7 +4702,7 @@
         <v>90</v>
       </c>
       <c r="D28" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E28" t="s">
         <v>147</v>
@@ -4726,13 +4726,13 @@
         <v>391</v>
       </c>
       <c r="L28">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M28">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N28">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O28">
         <v>0</v>
@@ -4774,10 +4774,10 @@
         <v>0</v>
       </c>
       <c r="AB28">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC28">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD28">
         <v>0</v>
@@ -4815,10 +4815,10 @@
         <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D29" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E29" t="s">
         <v>148</v>
@@ -4842,13 +4842,13 @@
         <v>391</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O29">
         <v>0</v>
@@ -4890,10 +4890,10 @@
         <v>0</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD29">
         <v>0</v>
@@ -4931,7 +4931,7 @@
         <v>47</v>
       </c>
       <c r="C30" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D30" t="s">
         <v>120</v>
@@ -5047,10 +5047,10 @@
         <v>47</v>
       </c>
       <c r="C31" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D31" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E31" t="s">
         <v>150</v>
@@ -5074,13 +5074,13 @@
         <v>391</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O31">
         <v>0</v>
@@ -5122,10 +5122,10 @@
         <v>0</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD31">
         <v>0</v>
@@ -5163,7 +5163,7 @@
         <v>47</v>
       </c>
       <c r="C32" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="D32" t="s">
         <v>120</v>
@@ -5279,7 +5279,7 @@
         <v>47</v>
       </c>
       <c r="C33" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="D33" t="s">
         <v>120</v>
@@ -5395,10 +5395,10 @@
         <v>48</v>
       </c>
       <c r="C34" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="D34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E34" t="s">
         <v>153</v>
@@ -5511,7 +5511,7 @@
         <v>48</v>
       </c>
       <c r="C35" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="D35" t="s">
         <v>120</v>
@@ -5627,7 +5627,7 @@
         <v>48</v>
       </c>
       <c r="C36" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D36" t="s">
         <v>120</v>
@@ -5746,7 +5746,7 @@
         <v>94</v>
       </c>
       <c r="D37" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E37" t="s">
         <v>156</v>
@@ -6326,7 +6326,7 @@
         <v>98</v>
       </c>
       <c r="D42" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E42" t="s">
         <v>161</v>
@@ -6442,7 +6442,7 @@
         <v>99</v>
       </c>
       <c r="D43" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E43" t="s">
         <v>162</v>
@@ -6787,10 +6787,10 @@
         <v>52</v>
       </c>
       <c r="C46" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D46" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E46" t="s">
         <v>165</v>
@@ -7251,7 +7251,7 @@
         <v>52</v>
       </c>
       <c r="C50" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D50" t="s">
         <v>120</v>
@@ -7278,13 +7278,13 @@
         <v>391</v>
       </c>
       <c r="L50">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M50">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N50">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O50">
         <v>0</v>
@@ -7326,10 +7326,10 @@
         <v>0</v>
       </c>
       <c r="AB50">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC50">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD50">
         <v>0</v>
@@ -7599,7 +7599,7 @@
         <v>52</v>
       </c>
       <c r="C53" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="D53" t="s">
         <v>120</v>
@@ -7626,13 +7626,13 @@
         <v>391</v>
       </c>
       <c r="L53">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M53">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O53">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD53">
         <v>0</v>
@@ -7715,10 +7715,10 @@
         <v>52</v>
       </c>
       <c r="C54" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="D54" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E54" t="s">
         <v>173</v>
@@ -7742,13 +7742,13 @@
         <v>391</v>
       </c>
       <c r="L54">
-        <v>2.75</v>
+        <v>1.26</v>
       </c>
       <c r="M54">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="N54">
-        <v>2.33</v>
+        <v>9.4</v>
       </c>
       <c r="O54">
         <v>0</v>
@@ -7790,10 +7790,10 @@
         <v>0</v>
       </c>
       <c r="AB54">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC54">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD54">
         <v>0</v>
@@ -7831,10 +7831,10 @@
         <v>52</v>
       </c>
       <c r="C55" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D55" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E55" t="s">
         <v>174</v>
@@ -7947,7 +7947,7 @@
         <v>52</v>
       </c>
       <c r="C56" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D56" t="s">
         <v>120</v>
@@ -7974,13 +7974,13 @@
         <v>391</v>
       </c>
       <c r="L56">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M56">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O56">
         <v>0</v>
@@ -8022,10 +8022,10 @@
         <v>0</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD56">
         <v>0</v>
@@ -8063,10 +8063,10 @@
         <v>52</v>
       </c>
       <c r="C57" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="D57" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E57" t="s">
         <v>176</v>
@@ -8090,13 +8090,13 @@
         <v>391</v>
       </c>
       <c r="L57">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M57">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N57">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="O57">
         <v>0</v>
@@ -8295,7 +8295,7 @@
         <v>53</v>
       </c>
       <c r="C59" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D59" t="s">
         <v>120</v>
@@ -8411,10 +8411,10 @@
         <v>53</v>
       </c>
       <c r="C60" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D60" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E60" t="s">
         <v>179</v>
@@ -8527,7 +8527,7 @@
         <v>53</v>
       </c>
       <c r="C61" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D61" t="s">
         <v>120</v>
@@ -8554,13 +8554,13 @@
         <v>391</v>
       </c>
       <c r="L61">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M61">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O61">
         <v>0</v>
@@ -8602,10 +8602,10 @@
         <v>0</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD61">
         <v>0</v>
@@ -8646,7 +8646,7 @@
         <v>89</v>
       </c>
       <c r="D62" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E62" t="s">
         <v>181</v>
@@ -8670,13 +8670,13 @@
         <v>391</v>
       </c>
       <c r="L62">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M62">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N62">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O62">
         <v>0</v>
@@ -8718,10 +8718,10 @@
         <v>0</v>
       </c>
       <c r="AB62">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC62">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AD62">
         <v>0</v>
@@ -8759,10 +8759,10 @@
         <v>54</v>
       </c>
       <c r="C63" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="D63" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E63" t="s">
         <v>182</v>
@@ -8786,13 +8786,13 @@
         <v>391</v>
       </c>
       <c r="L63">
-        <v>2.95</v>
+        <v>2.5</v>
       </c>
       <c r="M63">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N63">
-        <v>2.28</v>
+        <v>2.65</v>
       </c>
       <c r="O63">
         <v>0</v>
@@ -8834,10 +8834,10 @@
         <v>0</v>
       </c>
       <c r="AB63">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AC63">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AD63">
         <v>0</v>
@@ -8875,10 +8875,10 @@
         <v>54</v>
       </c>
       <c r="C64" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="D64" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E64" t="s">
         <v>183</v>
@@ -8994,7 +8994,7 @@
         <v>93</v>
       </c>
       <c r="D65" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E65" t="s">
         <v>184</v>
@@ -9018,13 +9018,13 @@
         <v>391</v>
       </c>
       <c r="L65">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M65">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N65">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O65">
         <v>0</v>
@@ -9066,10 +9066,10 @@
         <v>0</v>
       </c>
       <c r="AB65">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC65">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AD65">
         <v>0</v>
@@ -9107,7 +9107,7 @@
         <v>54</v>
       </c>
       <c r="C66" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="D66" t="s">
         <v>120</v>
@@ -9134,13 +9134,13 @@
         <v>391</v>
       </c>
       <c r="L66">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M66">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N66">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -9182,10 +9182,10 @@
         <v>0</v>
       </c>
       <c r="AB66">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC66">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD66">
         <v>0</v>
@@ -9339,7 +9339,7 @@
         <v>54</v>
       </c>
       <c r="C68" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D68" t="s">
         <v>119</v>
@@ -9366,13 +9366,13 @@
         <v>391</v>
       </c>
       <c r="L68">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M68">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N68">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O68">
         <v>0</v>
@@ -9414,10 +9414,10 @@
         <v>0</v>
       </c>
       <c r="AB68">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC68">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD68">
         <v>0</v>
@@ -9455,7 +9455,7 @@
         <v>54</v>
       </c>
       <c r="C69" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D69" t="s">
         <v>120</v>
@@ -9482,13 +9482,13 @@
         <v>391</v>
       </c>
       <c r="L69">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M69">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N69">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O69">
         <v>0</v>
@@ -9530,10 +9530,10 @@
         <v>0</v>
       </c>
       <c r="AB69">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC69">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD69">
         <v>0</v>
@@ -9571,7 +9571,7 @@
         <v>54</v>
       </c>
       <c r="C70" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="D70" t="s">
         <v>120</v>
@@ -9687,10 +9687,10 @@
         <v>54</v>
       </c>
       <c r="C71" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="D71" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E71" t="s">
         <v>190</v>
@@ -9714,13 +9714,13 @@
         <v>391</v>
       </c>
       <c r="L71">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M71">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -9762,10 +9762,10 @@
         <v>0</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC71">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD71">
         <v>0</v>
@@ -9830,13 +9830,13 @@
         <v>391</v>
       </c>
       <c r="L72">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="M72">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="N72">
-        <v>1.84</v>
+        <v>2.04</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -9878,10 +9878,10 @@
         <v>0</v>
       </c>
       <c r="AB72">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="AC72">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="AD72">
         <v>0</v>
@@ -9919,7 +9919,7 @@
         <v>54</v>
       </c>
       <c r="C73" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="D73" t="s">
         <v>120</v>
@@ -10035,10 +10035,10 @@
         <v>54</v>
       </c>
       <c r="C74" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D74" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E74" t="s">
         <v>193</v>
@@ -10062,13 +10062,13 @@
         <v>391</v>
       </c>
       <c r="L74">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="M74">
-        <v>4.3</v>
+        <v>3.64</v>
       </c>
       <c r="N74">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="O74">
         <v>0</v>
@@ -10110,10 +10110,10 @@
         <v>0</v>
       </c>
       <c r="AB74">
-        <v>1.66</v>
+        <v>2.15</v>
       </c>
       <c r="AC74">
-        <v>2.22</v>
+        <v>1.7</v>
       </c>
       <c r="AD74">
         <v>0</v>
@@ -10267,7 +10267,7 @@
         <v>54</v>
       </c>
       <c r="C76" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="D76" t="s">
         <v>120</v>
@@ -10383,7 +10383,7 @@
         <v>54</v>
       </c>
       <c r="C77" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="D77" t="s">
         <v>120</v>
@@ -10410,13 +10410,13 @@
         <v>391</v>
       </c>
       <c r="L77">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M77">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O77">
         <v>0</v>
@@ -10458,10 +10458,10 @@
         <v>0</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD77">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>54</v>
       </c>
       <c r="C78" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="D78" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E78" t="s">
         <v>197</v>
@@ -10615,10 +10615,10 @@
         <v>54</v>
       </c>
       <c r="C79" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="D79" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E79" t="s">
         <v>198</v>
@@ -10642,13 +10642,13 @@
         <v>391</v>
       </c>
       <c r="L79">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M79">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O79">
         <v>0</v>
@@ -10690,10 +10690,10 @@
         <v>0</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD79">
         <v>0</v>
@@ -10731,7 +10731,7 @@
         <v>54</v>
       </c>
       <c r="C80" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D80" t="s">
         <v>120</v>
@@ -10758,13 +10758,13 @@
         <v>391</v>
       </c>
       <c r="L80">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M80">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O80">
         <v>0</v>
@@ -10806,10 +10806,10 @@
         <v>0</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD80">
         <v>0</v>
@@ -10847,7 +10847,7 @@
         <v>54</v>
       </c>
       <c r="C81" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D81" t="s">
         <v>120</v>
@@ -10963,10 +10963,10 @@
         <v>54</v>
       </c>
       <c r="C82" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D82" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E82" t="s">
         <v>201</v>
@@ -10990,13 +10990,13 @@
         <v>391</v>
       </c>
       <c r="L82">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M82">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O82">
         <v>0</v>
@@ -11038,10 +11038,10 @@
         <v>0</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD82">
         <v>0</v>
@@ -11195,7 +11195,7 @@
         <v>55</v>
       </c>
       <c r="C84" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="D84" t="s">
         <v>120</v>
@@ -11222,13 +11222,13 @@
         <v>391</v>
       </c>
       <c r="L84">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M84">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O84">
         <v>0</v>
@@ -11311,7 +11311,7 @@
         <v>55</v>
       </c>
       <c r="C85" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D85" t="s">
         <v>120</v>
@@ -11338,13 +11338,13 @@
         <v>391</v>
       </c>
       <c r="L85">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M85">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N85">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O85">
         <v>0</v>
@@ -11427,7 +11427,7 @@
         <v>55</v>
       </c>
       <c r="C86" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D86" t="s">
         <v>120</v>
@@ -11454,13 +11454,13 @@
         <v>391</v>
       </c>
       <c r="L86">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M86">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O86">
         <v>0</v>
@@ -11502,10 +11502,10 @@
         <v>0</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD86">
         <v>0</v>
@@ -11543,7 +11543,7 @@
         <v>55</v>
       </c>
       <c r="C87" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="D87" t="s">
         <v>120</v>
@@ -11570,13 +11570,13 @@
         <v>391</v>
       </c>
       <c r="L87">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="M87">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N87">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O87">
         <v>0</v>
@@ -11618,16 +11618,16 @@
         <v>0</v>
       </c>
       <c r="AB87">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC87">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD87">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE87">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF87">
         <v>0</v>
@@ -11659,7 +11659,7 @@
         <v>55</v>
       </c>
       <c r="C88" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D88" t="s">
         <v>120</v>
@@ -11775,7 +11775,7 @@
         <v>55</v>
       </c>
       <c r="C89" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="D89" t="s">
         <v>120</v>
@@ -11802,13 +11802,13 @@
         <v>391</v>
       </c>
       <c r="L89">
-        <v>2.6</v>
+        <v>1.24</v>
       </c>
       <c r="M89">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="N89">
-        <v>2.6</v>
+        <v>12</v>
       </c>
       <c r="O89">
         <v>0</v>
@@ -11850,16 +11850,16 @@
         <v>0</v>
       </c>
       <c r="AB89">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="AC89">
-        <v>1.6</v>
+        <v>2.75</v>
       </c>
       <c r="AD89">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF89">
         <v>0</v>
@@ -12123,7 +12123,7 @@
         <v>57</v>
       </c>
       <c r="C92" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D92" t="s">
         <v>120</v>
@@ -12239,10 +12239,10 @@
         <v>57</v>
       </c>
       <c r="C93" t="s">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="D93" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E93" t="s">
         <v>212</v>
@@ -12266,13 +12266,13 @@
         <v>391</v>
       </c>
       <c r="L93">
-        <v>6.27</v>
+        <v>0</v>
       </c>
       <c r="M93">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N93">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O93">
         <v>0</v>
@@ -12320,10 +12320,10 @@
         <v>0</v>
       </c>
       <c r="AD93">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE93">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF93">
         <v>0</v>
@@ -12471,10 +12471,10 @@
         <v>57</v>
       </c>
       <c r="C95" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="D95" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E95" t="s">
         <v>214</v>
@@ -12498,13 +12498,13 @@
         <v>391</v>
       </c>
       <c r="L95">
-        <v>0</v>
+        <v>6.27</v>
       </c>
       <c r="M95">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O95">
         <v>0</v>
@@ -12552,10 +12552,10 @@
         <v>0</v>
       </c>
       <c r="AD95">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE95">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF95">
         <v>0</v>
@@ -12819,10 +12819,10 @@
         <v>59</v>
       </c>
       <c r="C98" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="D98" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E98" t="s">
         <v>217</v>
@@ -12935,7 +12935,7 @@
         <v>59</v>
       </c>
       <c r="C99" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D99" t="s">
         <v>119</v>
@@ -13051,10 +13051,10 @@
         <v>59</v>
       </c>
       <c r="C100" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="D100" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E100" t="s">
         <v>219</v>
@@ -13078,13 +13078,13 @@
         <v>391</v>
       </c>
       <c r="L100">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M100">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O100">
         <v>0</v>
@@ -13126,10 +13126,10 @@
         <v>0</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC100">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD100">
         <v>0</v>
@@ -13167,7 +13167,7 @@
         <v>60</v>
       </c>
       <c r="C101" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D101" t="s">
         <v>120</v>
@@ -13399,7 +13399,7 @@
         <v>60</v>
       </c>
       <c r="C103" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D103" t="s">
         <v>120</v>
@@ -13631,10 +13631,10 @@
         <v>60</v>
       </c>
       <c r="C105" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="D105" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E105" t="s">
         <v>224</v>
@@ -13747,10 +13747,10 @@
         <v>60</v>
       </c>
       <c r="C106" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="D106" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E106" t="s">
         <v>225</v>
@@ -13863,7 +13863,7 @@
         <v>60</v>
       </c>
       <c r="C107" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="D107" t="s">
         <v>119</v>
@@ -14095,7 +14095,7 @@
         <v>60</v>
       </c>
       <c r="C109" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D109" t="s">
         <v>120</v>
@@ -14211,7 +14211,7 @@
         <v>61</v>
       </c>
       <c r="C110" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D110" t="s">
         <v>120</v>
@@ -14238,13 +14238,13 @@
         <v>391</v>
       </c>
       <c r="L110">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M110">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O110">
         <v>0</v>
@@ -14286,10 +14286,10 @@
         <v>0</v>
       </c>
       <c r="AB110">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC110">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD110">
         <v>0</v>
@@ -14327,7 +14327,7 @@
         <v>62</v>
       </c>
       <c r="C111" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D111" t="s">
         <v>120</v>
@@ -14559,7 +14559,7 @@
         <v>62</v>
       </c>
       <c r="C113" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D113" t="s">
         <v>120</v>
@@ -14675,7 +14675,7 @@
         <v>63</v>
       </c>
       <c r="C114" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D114" t="s">
         <v>120</v>
@@ -14791,10 +14791,10 @@
         <v>63</v>
       </c>
       <c r="C115" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D115" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E115" t="s">
         <v>234</v>
@@ -14907,10 +14907,10 @@
         <v>63</v>
       </c>
       <c r="C116" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D116" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E116" t="s">
         <v>235</v>
@@ -15023,7 +15023,7 @@
         <v>64</v>
       </c>
       <c r="C117" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D117" t="s">
         <v>120</v>
@@ -15050,13 +15050,13 @@
         <v>391</v>
       </c>
       <c r="L117">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M117">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O117">
         <v>0</v>
@@ -15255,7 +15255,7 @@
         <v>65</v>
       </c>
       <c r="C119" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D119" t="s">
         <v>120</v>
@@ -15487,10 +15487,10 @@
         <v>66</v>
       </c>
       <c r="C121" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D121" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E121" t="s">
         <v>240</v>
@@ -15603,7 +15603,7 @@
         <v>66</v>
       </c>
       <c r="C122" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D122" t="s">
         <v>119</v>
@@ -15630,13 +15630,13 @@
         <v>391</v>
       </c>
       <c r="L122">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M122">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N122">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O122">
         <v>0</v>
@@ -15678,10 +15678,10 @@
         <v>0</v>
       </c>
       <c r="AB122">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC122">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD122">
         <v>0</v>
@@ -15719,10 +15719,10 @@
         <v>66</v>
       </c>
       <c r="C123" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D123" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E123" t="s">
         <v>242</v>
@@ -15835,7 +15835,7 @@
         <v>66</v>
       </c>
       <c r="C124" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D124" t="s">
         <v>119</v>
@@ -15862,13 +15862,13 @@
         <v>391</v>
       </c>
       <c r="L124">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M124">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N124">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O124">
         <v>0</v>
@@ -15910,10 +15910,10 @@
         <v>0</v>
       </c>
       <c r="AB124">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC124">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD124">
         <v>0</v>
@@ -16067,7 +16067,7 @@
         <v>68</v>
       </c>
       <c r="C126" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D126" t="s">
         <v>119</v>
@@ -16094,13 +16094,13 @@
         <v>391</v>
       </c>
       <c r="L126">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M126">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N126">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O126">
         <v>0</v>
@@ -16142,10 +16142,10 @@
         <v>0</v>
       </c>
       <c r="AB126">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC126">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD126">
         <v>0</v>
@@ -16299,7 +16299,7 @@
         <v>68</v>
       </c>
       <c r="C128" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D128" t="s">
         <v>119</v>
@@ -16415,7 +16415,7 @@
         <v>68</v>
       </c>
       <c r="C129" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D129" t="s">
         <v>119</v>
@@ -16442,13 +16442,13 @@
         <v>391</v>
       </c>
       <c r="L129">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M129">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N129">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O129">
         <v>0</v>
@@ -16490,10 +16490,10 @@
         <v>0</v>
       </c>
       <c r="AB129">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC129">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD129">
         <v>0</v>
@@ -16531,7 +16531,7 @@
         <v>69</v>
       </c>
       <c r="C130" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D130" t="s">
         <v>119</v>
@@ -16647,7 +16647,7 @@
         <v>69</v>
       </c>
       <c r="C131" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D131" t="s">
         <v>119</v>
@@ -16879,7 +16879,7 @@
         <v>71</v>
       </c>
       <c r="C133" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D133" t="s">
         <v>119</v>
@@ -17111,7 +17111,7 @@
         <v>73</v>
       </c>
       <c r="C135" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D135" t="s">
         <v>119</v>
@@ -17227,7 +17227,7 @@
         <v>74</v>
       </c>
       <c r="C136" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D136" t="s">
         <v>119</v>

--- a/jogos_2025-08-03.xlsx
+++ b/jogos_2025-08-03.xlsx
@@ -130,6 +130,9 @@
     <t>DateTime</t>
   </si>
   <si>
+    <t>00:00</t>
+  </si>
+  <si>
     <t>02:00</t>
   </si>
   <si>
@@ -235,12 +238,12 @@
     <t>20:30</t>
   </si>
   <si>
-    <t>22:00</t>
-  </si>
-  <si>
     <t>23:00</t>
   </si>
   <si>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
     <t>Australia New South Wales NPL</t>
   </si>
   <si>
@@ -253,34 +256,37 @@
     <t>Austria 2. Liga</t>
   </si>
   <si>
+    <t>Ukraine Ukrainian Premier League</t>
+  </si>
+  <si>
     <t>Japan J2 League</t>
   </si>
   <si>
-    <t>Ukraine Ukrainian Premier League</t>
-  </si>
-  <si>
     <t>Russia Russian Premier League</t>
   </si>
   <si>
+    <t>China China League One</t>
+  </si>
+  <si>
     <t>England EFL League One</t>
   </si>
   <si>
+    <t>China Chinese Super League</t>
+  </si>
+  <si>
     <t>Belarus Vysheyshaya Liga</t>
   </si>
   <si>
-    <t>China China League One</t>
-  </si>
-  <si>
-    <t>China Chinese Super League</t>
+    <t>Belgium Pro League</t>
+  </si>
+  <si>
+    <t>Germany 2. Bundesliga</t>
   </si>
   <si>
     <t>Germany 3. Liga</t>
   </si>
   <si>
-    <t>Germany 2. Bundesliga</t>
-  </si>
-  <si>
-    <t>Belgium Pro League</t>
+    <t>Switzerland Super League</t>
   </si>
   <si>
     <t>Sweden Allsvenskan</t>
@@ -289,9 +295,6 @@
     <t>Denmark Superliga</t>
   </si>
   <si>
-    <t>Switzerland Super League</t>
-  </si>
-  <si>
     <t>Switzerland Challenge League</t>
   </si>
   <si>
@@ -304,21 +307,21 @@
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
+    <t>Finland Veikkausliiga</t>
+  </si>
+  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
     <t>Scotland Premiership</t>
   </si>
   <si>
-    <t>Finland Veikkausliiga</t>
-  </si>
-  <si>
     <t>Czech Republic First League</t>
   </si>
   <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
     <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
@@ -334,21 +337,21 @@
     <t>Slovakia Super Liga</t>
   </si>
   <si>
+    <t>Austria Bundesliga</t>
+  </si>
+  <si>
     <t>Uzbekistan Uzbekistan Super League</t>
   </si>
   <si>
-    <t>Austria Bundesliga</t>
+    <t>Romania Liga I</t>
+  </si>
+  <si>
+    <t>Slovenia PrvaLiga</t>
   </si>
   <si>
     <t>Hungary NB II</t>
   </si>
   <si>
-    <t>Romania Liga I</t>
-  </si>
-  <si>
-    <t>Slovenia PrvaLiga</t>
-  </si>
-  <si>
     <t>Hungary NB I</t>
   </si>
   <si>
@@ -361,9 +364,6 @@
     <t>Serbia SuperLiga</t>
   </si>
   <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
     <t>Brazil Serie A</t>
   </si>
   <si>
@@ -379,6 +379,12 @@
     <t>2025/2026</t>
   </si>
   <si>
+    <t>Portland Timbers II</t>
+  </si>
+  <si>
+    <t>Central Coast II</t>
+  </si>
+  <si>
     <t>Wollongong Wolves</t>
   </si>
   <si>
@@ -388,9 +394,6 @@
     <t>Blacktown City</t>
   </si>
   <si>
-    <t>Central Coast II</t>
-  </si>
-  <si>
     <t>SKA Khabarovsk</t>
   </si>
   <si>
@@ -403,25 +406,34 @@
     <t>WSPG Wels</t>
   </si>
   <si>
+    <t>Kudrivka</t>
+  </si>
+  <si>
     <t>Roasso Kumamoto</t>
   </si>
   <si>
-    <t>Kudrivka</t>
-  </si>
-  <si>
     <t>Akron</t>
   </si>
   <si>
+    <t>Suzhou Dongwu</t>
+  </si>
+  <si>
     <t>Stockport County</t>
   </si>
   <si>
+    <t>Dalian Zhixing</t>
+  </si>
+  <si>
     <t>Molodechno-DYuSSh 4</t>
   </si>
   <si>
-    <t>Suzhou Dongwu</t>
-  </si>
-  <si>
-    <t>Dalian Zhixing</t>
+    <t>KRC Genk</t>
+  </si>
+  <si>
+    <t>Magdeburg</t>
+  </si>
+  <si>
+    <t>Hannover 96</t>
   </si>
   <si>
     <t>Erzgebirge Aue</t>
@@ -433,273 +445,264 @@
     <t>Qingdao Red Lions</t>
   </si>
   <si>
-    <t>Magdeburg</t>
-  </si>
-  <si>
-    <t>Hannover 96</t>
-  </si>
-  <si>
-    <t>KRC Genk</t>
-  </si>
-  <si>
     <t>Greuther Fürth</t>
   </si>
   <si>
+    <t>Wuhan Three Towns</t>
+  </si>
+  <si>
     <t>Beijing Guoan</t>
   </si>
   <si>
-    <t>Wuhan Three Towns</t>
-  </si>
-  <si>
     <t>Sichuan Jiuniu</t>
   </si>
   <si>
+    <t>Thun</t>
+  </si>
+  <si>
     <t>Häcken</t>
   </si>
   <si>
     <t>SønderjyskE</t>
   </si>
   <si>
+    <t>Randers</t>
+  </si>
+  <si>
+    <t>Spartak Kostroma</t>
+  </si>
+  <si>
     <t>Djurgården</t>
   </si>
   <si>
-    <t>Randers</t>
-  </si>
-  <si>
-    <t>Thun</t>
-  </si>
-  <si>
-    <t>Spartak Kostroma</t>
-  </si>
-  <si>
     <t>Yverdon Sport</t>
   </si>
   <si>
+    <t>Śląsk Wrocław</t>
+  </si>
+  <si>
+    <t>HamKam</t>
+  </si>
+  <si>
+    <t>Epitsentr Dunayivtsi</t>
+  </si>
+  <si>
     <t>Baník Ostrava II</t>
   </si>
   <si>
-    <t>Śląsk Wrocław</t>
-  </si>
-  <si>
-    <t>Epitsentr Dunayivtsi</t>
-  </si>
-  <si>
-    <t>HamKam</t>
-  </si>
-  <si>
     <t>Baltika</t>
   </si>
   <si>
     <t>Cracovia Kraków</t>
   </si>
   <si>
+    <t>Sogndal</t>
+  </si>
+  <si>
+    <t>SJK</t>
+  </si>
+  <si>
     <t>Landskrona</t>
   </si>
   <si>
     <t>Falkirk</t>
   </si>
   <si>
-    <t>SJK</t>
-  </si>
-  <si>
     <t>Slovácko</t>
   </si>
   <si>
-    <t>Sogndal</t>
-  </si>
-  <si>
     <t>Suduroy</t>
   </si>
   <si>
+    <t>Mondorf-les-Bains</t>
+  </si>
+  <si>
+    <t>Hostert</t>
+  </si>
+  <si>
+    <t>F91 Dudelange</t>
+  </si>
+  <si>
     <t>Jeunesse Canach</t>
   </si>
   <si>
-    <t>Mondorf-les-Bains</t>
+    <t>Differdange 03</t>
   </si>
   <si>
     <t>Jeunesse d'Esch</t>
   </si>
   <si>
-    <t>Differdange 03</t>
-  </si>
-  <si>
-    <t>Hostert</t>
-  </si>
-  <si>
-    <t>F91 Dudelange</t>
+    <t>Swift Hesperange</t>
+  </si>
+  <si>
+    <t>Dundee</t>
+  </si>
+  <si>
+    <t>EB - Streymur</t>
+  </si>
+  <si>
+    <t>Harju Jalgpallikool</t>
+  </si>
+  <si>
+    <t>Cercle Brugge</t>
+  </si>
+  <si>
+    <t>AGF</t>
   </si>
   <si>
     <t>Rodange</t>
   </si>
   <si>
-    <t>Cercle Brugge</t>
-  </si>
-  <si>
-    <t>Harju Jalgpallikool</t>
-  </si>
-  <si>
-    <t>EB - Streymur</t>
-  </si>
-  <si>
-    <t>Dundee</t>
-  </si>
-  <si>
-    <t>AGF</t>
-  </si>
-  <si>
-    <t>Swift Hesperange</t>
+    <t>Luzern</t>
+  </si>
+  <si>
+    <t>Étoile Carouge</t>
   </si>
   <si>
     <t>Viktoria Köln</t>
   </si>
   <si>
-    <t>Étoile Carouge</t>
-  </si>
-  <si>
-    <t>Luzern</t>
-  </si>
-  <si>
     <t>Sirius</t>
   </si>
   <si>
+    <t>Petrovac</t>
+  </si>
+  <si>
+    <t>Karpaty</t>
+  </si>
+  <si>
+    <t>Sutjeska</t>
+  </si>
+  <si>
+    <t>Zenit</t>
+  </si>
+  <si>
+    <t>Vålerenga</t>
+  </si>
+  <si>
+    <t>Pogoń Siedlce</t>
+  </si>
+  <si>
+    <t>Arsenal Tivat</t>
+  </si>
+  <si>
+    <t>Trenčín</t>
+  </si>
+  <si>
+    <t>Dečić</t>
+  </si>
+  <si>
+    <t>FK Jezero Plav</t>
+  </si>
+  <si>
+    <t>Rapid Wien</t>
+  </si>
+  <si>
+    <t>Dukla Praha</t>
+  </si>
+  <si>
+    <t>Strømsgodset</t>
+  </si>
+  <si>
+    <t>Grazer AK</t>
+  </si>
+  <si>
+    <t>Torpedo BelAZ</t>
+  </si>
+  <si>
+    <t>Molde</t>
+  </si>
+  <si>
     <t>KFUM</t>
   </si>
   <si>
-    <t>Dečić</t>
-  </si>
-  <si>
-    <t>Pogoń Siedlce</t>
-  </si>
-  <si>
-    <t>Arsenal Tivat</t>
-  </si>
-  <si>
-    <t>Sutjeska</t>
-  </si>
-  <si>
-    <t>Strømsgodset</t>
-  </si>
-  <si>
-    <t>FK Jezero Plav</t>
-  </si>
-  <si>
-    <t>Petrovac</t>
-  </si>
-  <si>
-    <t>Molde</t>
-  </si>
-  <si>
-    <t>Trenčín</t>
+    <t>Rubin Kazan</t>
   </si>
   <si>
     <t>Vlašim</t>
   </si>
   <si>
-    <t>Zenit</t>
-  </si>
-  <si>
     <t>Shortan</t>
   </si>
   <si>
-    <t>Rubin Kazan</t>
-  </si>
-  <si>
-    <t>Karpaty</t>
-  </si>
-  <si>
-    <t>Torpedo BelAZ</t>
-  </si>
-  <si>
-    <t>Vålerenga</t>
-  </si>
-  <si>
-    <t>Grazer AK</t>
-  </si>
-  <si>
-    <t>Dukla Praha</t>
-  </si>
-  <si>
-    <t>Rapid Wien</t>
+    <t>Radomiak Radom</t>
+  </si>
+  <si>
+    <t>Celtic</t>
+  </si>
+  <si>
+    <t>Hermannstadt</t>
+  </si>
+  <si>
+    <t>Maribor</t>
   </si>
   <si>
     <t>Motor Lublin</t>
   </si>
   <si>
-    <t>Radomiak Radom</t>
+    <t>Karcag SE</t>
   </si>
   <si>
     <t>Szentlőrinc SE</t>
   </si>
   <si>
-    <t>Hermannstadt</t>
-  </si>
-  <si>
-    <t>Maribor</t>
-  </si>
-  <si>
-    <t>Karcag SE</t>
-  </si>
-  <si>
-    <t>Celtic</t>
-  </si>
-  <si>
     <t>Várda SE</t>
   </si>
   <si>
     <t>Puskás</t>
   </si>
   <si>
+    <t>Fakel</t>
+  </si>
+  <si>
+    <t>Vysočina Jihlava</t>
+  </si>
+  <si>
     <t>Brøndby</t>
   </si>
   <si>
-    <t>Fakel</t>
-  </si>
-  <si>
     <t>FK Chernomorets Novorossiysk</t>
   </si>
   <si>
     <t>Tammeka</t>
   </si>
   <si>
-    <t>Vysočina Jihlava</t>
-  </si>
-  <si>
     <t>B68</t>
   </si>
   <si>
+    <t>Union Saint-Gilloise</t>
+  </si>
+  <si>
     <t>O'Higgins</t>
   </si>
   <si>
     <t>Washington Spirit</t>
   </si>
   <si>
-    <t>Union Saint-Gilloise</t>
+    <t>Sporting KC II</t>
   </si>
   <si>
     <t>Železničar Pančevo</t>
   </si>
   <si>
+    <t>Žilina</t>
+  </si>
+  <si>
+    <t>MKK-Dnepr</t>
+  </si>
+  <si>
     <t>Csákvári TK</t>
   </si>
   <si>
-    <t>Žilina</t>
-  </si>
-  <si>
     <t>Honvéd W</t>
   </si>
   <si>
+    <t>Békéscsaba</t>
+  </si>
+  <si>
     <t>Tiszakécske</t>
   </si>
   <si>
-    <t>Sporting KC II</t>
-  </si>
-  <si>
-    <t>MKK-Dnepr</t>
-  </si>
-  <si>
-    <t>Békéscsaba</t>
-  </si>
-  <si>
     <t>Ajka</t>
   </si>
   <si>
@@ -715,15 +718,15 @@
     <t>Górnik Łęczna</t>
   </si>
   <si>
+    <t>Chicago Fire II</t>
+  </si>
+  <si>
+    <t>Győri ETO</t>
+  </si>
+  <si>
     <t>Pardubice</t>
   </si>
   <si>
-    <t>Chicago Fire II</t>
-  </si>
-  <si>
-    <t>Győri ETO</t>
-  </si>
-  <si>
     <t>Olimpija</t>
   </si>
   <si>
@@ -736,33 +739,33 @@
     <t>Botafogo</t>
   </si>
   <si>
+    <t>Colo-Colo</t>
+  </si>
+  <si>
+    <t>Partizan</t>
+  </si>
+  <si>
+    <t>Corinthians</t>
+  </si>
+  <si>
     <t>Chapecoense</t>
   </si>
   <si>
-    <t>Corinthians</t>
-  </si>
-  <si>
-    <t>Partizan</t>
-  </si>
-  <si>
-    <t>Colo-Colo</t>
-  </si>
-  <si>
     <t>Atlético Ottawa</t>
   </si>
   <si>
+    <t>Atlético Mineiro</t>
+  </si>
+  <si>
+    <t>Ceará</t>
+  </si>
+  <si>
     <t>Ñublense</t>
   </si>
   <si>
-    <t>Ceará</t>
-  </si>
-  <si>
     <t>Atlético PR</t>
   </si>
   <si>
-    <t>Atlético Mineiro</t>
-  </si>
-  <si>
     <t>Orlando Pride</t>
   </si>
   <si>
@@ -778,12 +781,15 @@
     <t>Internacional</t>
   </si>
   <si>
-    <t>Portland Timbers II</t>
-  </si>
-  <si>
     <t>Los Angeles II</t>
   </si>
   <si>
+    <t>Real Monarchs</t>
+  </si>
+  <si>
+    <t>Marconi Stallions</t>
+  </si>
+  <si>
     <t>Sydney II</t>
   </si>
   <si>
@@ -793,9 +799,6 @@
     <t>Mt Druitt Town</t>
   </si>
   <si>
-    <t>Marconi Stallions</t>
-  </si>
-  <si>
     <t>Torpedo Moskva</t>
   </si>
   <si>
@@ -808,25 +811,34 @@
     <t>Floridsdorfer AC</t>
   </si>
   <si>
+    <t>Oleksandria</t>
+  </si>
+  <si>
     <t>Mito Hollyhock</t>
   </si>
   <si>
-    <t>Oleksandria</t>
-  </si>
-  <si>
     <t>Spartak Moskva</t>
   </si>
   <si>
+    <t>Dalian Huayi</t>
+  </si>
+  <si>
     <t>Bolton Wanderers</t>
   </si>
   <si>
+    <t>Qingdao Jonoon</t>
+  </si>
+  <si>
     <t>Neman Grodno</t>
   </si>
   <si>
-    <t>Dalian Huayi</t>
-  </si>
-  <si>
-    <t>Qingdao Jonoon</t>
+    <t>Royal Antwerp FC</t>
+  </si>
+  <si>
+    <t>Eintracht Braunschweig</t>
+  </si>
+  <si>
+    <t>Kaiserslautern</t>
   </si>
   <si>
     <t>Hansa Rostock</t>
@@ -838,273 +850,264 @@
     <t>Heilongjiang Lava Spring</t>
   </si>
   <si>
-    <t>Eintracht Braunschweig</t>
-  </si>
-  <si>
-    <t>Kaiserslautern</t>
-  </si>
-  <si>
-    <t>Royal Antwerp FC</t>
-  </si>
-  <si>
     <t>Dynamo Dresden</t>
   </si>
   <si>
+    <t>Changchun Yatai</t>
+  </si>
+  <si>
     <t>Tianjin Teda</t>
   </si>
   <si>
-    <t>Changchun Yatai</t>
-  </si>
-  <si>
     <t>Zhejiang FC</t>
   </si>
   <si>
+    <t>Lausanne Sport</t>
+  </si>
+  <si>
     <t>Elfsborg</t>
   </si>
   <si>
     <t>Nordsjælland</t>
   </si>
   <si>
+    <t>Silkeborg</t>
+  </si>
+  <si>
+    <t>Neftekhimik</t>
+  </si>
+  <si>
     <t>Halmstad</t>
   </si>
   <si>
-    <t>Silkeborg</t>
-  </si>
-  <si>
-    <t>Lausanne Sport</t>
-  </si>
-  <si>
-    <t>Neftekhimik</t>
-  </si>
-  <si>
     <t>Stade Lausanne-Ouchy</t>
   </si>
   <si>
+    <t>Ruch Chorzów</t>
+  </si>
+  <si>
+    <t>FK Bodo - Glimt</t>
+  </si>
+  <si>
+    <t>Shakhtar Donetsk</t>
+  </si>
+  <si>
     <t>Líšeň</t>
   </si>
   <si>
-    <t>Ruch Chorzów</t>
-  </si>
-  <si>
-    <t>Shakhtar Donetsk</t>
-  </si>
-  <si>
-    <t>FK Bodo - Glimt</t>
-  </si>
-  <si>
     <t>Orenburg</t>
   </si>
   <si>
     <t>Lechia Gdańsk</t>
   </si>
   <si>
+    <t>Skeid</t>
+  </si>
+  <si>
+    <t>KTP</t>
+  </si>
+  <si>
     <t>Västerås SK</t>
   </si>
   <si>
     <t>Dundee United</t>
   </si>
   <si>
-    <t>KTP</t>
-  </si>
-  <si>
     <t>Slavia Praha</t>
   </si>
   <si>
-    <t>Skeid</t>
-  </si>
-  <si>
     <t>HB</t>
   </si>
   <si>
+    <t>UNA Strassen</t>
+  </si>
+  <si>
+    <t>Victoria Rosport</t>
+  </si>
+  <si>
+    <t>Progrès Niederkorn</t>
+  </si>
+  <si>
     <t>Mamer</t>
   </si>
   <si>
-    <t>UNA Strassen</t>
+    <t>Atert Bissen</t>
   </si>
   <si>
     <t>UN Käerjéng</t>
   </si>
   <si>
-    <t>Atert Bissen</t>
-  </si>
-  <si>
-    <t>Victoria Rosport</t>
-  </si>
-  <si>
-    <t>Progrès Niederkorn</t>
+    <t>UT Pétange</t>
+  </si>
+  <si>
+    <t>Hibernian</t>
+  </si>
+  <si>
+    <t>KÍ</t>
+  </si>
+  <si>
+    <t>Paide</t>
+  </si>
+  <si>
+    <t>RSC Anderlecht</t>
+  </si>
+  <si>
+    <t>Midtjylland</t>
   </si>
   <si>
     <t>Racing</t>
   </si>
   <si>
-    <t>RSC Anderlecht</t>
-  </si>
-  <si>
-    <t>Paide</t>
-  </si>
-  <si>
-    <t>KÍ</t>
-  </si>
-  <si>
-    <t>Hibernian</t>
-  </si>
-  <si>
-    <t>Midtjylland</t>
-  </si>
-  <si>
-    <t>UT Pétange</t>
+    <t>Zürich</t>
+  </si>
+  <si>
+    <t>Vaduz</t>
   </si>
   <si>
     <t>Schweinfurt</t>
   </si>
   <si>
-    <t>Vaduz</t>
-  </si>
-  <si>
-    <t>Zürich</t>
-  </si>
-  <si>
     <t>Öster</t>
   </si>
   <si>
+    <t>Bokelj</t>
+  </si>
+  <si>
+    <t>Polessya</t>
+  </si>
+  <si>
+    <t>Mornar</t>
+  </si>
+  <si>
+    <t>CSKA Moskva</t>
+  </si>
+  <si>
+    <t>Sandefjord</t>
+  </si>
+  <si>
+    <t>Odra Opole</t>
+  </si>
+  <si>
+    <t>Jedinstvo</t>
+  </si>
+  <si>
+    <t>Spartak Trnava</t>
+  </si>
+  <si>
+    <t>Mladost DG</t>
+  </si>
+  <si>
+    <t>Budućnost</t>
+  </si>
+  <si>
+    <t>Blau-Weiß Linz</t>
+  </si>
+  <si>
+    <t>Baník Ostrava</t>
+  </si>
+  <si>
+    <t>Haugesund</t>
+  </si>
+  <si>
+    <t>Austria Wien</t>
+  </si>
+  <si>
+    <t>Gomel</t>
+  </si>
+  <si>
+    <t>Bryne</t>
+  </si>
+  <si>
     <t>Rosenborg</t>
   </si>
   <si>
-    <t>Mladost DG</t>
-  </si>
-  <si>
-    <t>Odra Opole</t>
-  </si>
-  <si>
-    <t>Jedinstvo</t>
-  </si>
-  <si>
-    <t>Mornar</t>
-  </si>
-  <si>
-    <t>Haugesund</t>
-  </si>
-  <si>
-    <t>Budućnost</t>
-  </si>
-  <si>
-    <t>Bokelj</t>
-  </si>
-  <si>
-    <t>Bryne</t>
-  </si>
-  <si>
-    <t>Spartak Trnava</t>
+    <t>FK Sochi</t>
   </si>
   <si>
     <t>Hanácká</t>
   </si>
   <si>
-    <t>CSKA Moskva</t>
-  </si>
-  <si>
     <t>Xorazm</t>
   </si>
   <si>
-    <t>FK Sochi</t>
-  </si>
-  <si>
-    <t>Polessya</t>
-  </si>
-  <si>
-    <t>Gomel</t>
-  </si>
-  <si>
-    <t>Sandefjord</t>
-  </si>
-  <si>
-    <t>Austria Wien</t>
-  </si>
-  <si>
-    <t>Baník Ostrava</t>
-  </si>
-  <si>
-    <t>Blau-Weiß Linz</t>
+    <t>Raków Częstochowa</t>
+  </si>
+  <si>
+    <t>St. Mirren</t>
+  </si>
+  <si>
+    <t>Universitatea Cluj</t>
+  </si>
+  <si>
+    <t>Koper</t>
   </si>
   <si>
     <t>Jagiellonia Białystok</t>
   </si>
   <si>
-    <t>Raków Częstochowa</t>
+    <t>Soroksár SC</t>
   </si>
   <si>
     <t>Kozármisleny</t>
   </si>
   <si>
-    <t>Universitatea Cluj</t>
-  </si>
-  <si>
-    <t>Koper</t>
-  </si>
-  <si>
-    <t>Soroksár SC</t>
-  </si>
-  <si>
-    <t>St. Mirren</t>
-  </si>
-  <si>
     <t>Paksi SE</t>
   </si>
   <si>
     <t>Nyíregyháza Spartacus</t>
   </si>
   <si>
+    <t>Sokol Saratov</t>
+  </si>
+  <si>
+    <t>Vyškov</t>
+  </si>
+  <si>
     <t>Viborg</t>
   </si>
   <si>
-    <t>Sokol Saratov</t>
-  </si>
-  <si>
     <t>Arsenal Tula</t>
   </si>
   <si>
     <t>Nõmme Kalju</t>
   </si>
   <si>
-    <t>Vyškov</t>
-  </si>
-  <si>
     <t>NSÍ</t>
   </si>
   <si>
+    <t>OH Leuven</t>
+  </si>
+  <si>
     <t>Unión La Calera</t>
   </si>
   <si>
     <t>Portland Thorns</t>
   </si>
   <si>
-    <t>OH Leuven</t>
+    <t>Austin II</t>
   </si>
   <si>
     <t>Napredak</t>
   </si>
   <si>
+    <t>Tatran Prešov</t>
+  </si>
+  <si>
+    <t>Slutsk</t>
+  </si>
+  <si>
     <t>BVSC</t>
   </si>
   <si>
-    <t>Tatran Prešov</t>
-  </si>
-  <si>
     <t>Budafoki MTE</t>
   </si>
   <si>
+    <t>Szeged 2011</t>
+  </si>
+  <si>
     <t>Mezőkövesd-Zsóry</t>
   </si>
   <si>
-    <t>Austin II</t>
-  </si>
-  <si>
-    <t>Slutsk</t>
-  </si>
-  <si>
-    <t>Szeged 2011</t>
-  </si>
-  <si>
     <t>Videoton</t>
   </si>
   <si>
@@ -1120,15 +1123,15 @@
     <t>Puszcza Niepołomice</t>
   </si>
   <si>
+    <t>Columbus Crew II</t>
+  </si>
+  <si>
+    <t>Újpest</t>
+  </si>
+  <si>
     <t>Sparta Praha</t>
   </si>
   <si>
-    <t>Columbus Crew II</t>
-  </si>
-  <si>
-    <t>Újpest</t>
-  </si>
-  <si>
     <t>Celje</t>
   </si>
   <si>
@@ -1141,33 +1144,33 @@
     <t>Cruzeiro</t>
   </si>
   <si>
+    <t>Huachipato</t>
+  </si>
+  <si>
+    <t>Radnički Kragujevac</t>
+  </si>
+  <si>
+    <t>Fortaleza</t>
+  </si>
+  <si>
     <t>CRB</t>
   </si>
   <si>
-    <t>Fortaleza</t>
-  </si>
-  <si>
-    <t>Radnički Kragujevac</t>
-  </si>
-  <si>
-    <t>Huachipato</t>
-  </si>
-  <si>
     <t>York9 FC</t>
   </si>
   <si>
+    <t>Bragantino</t>
+  </si>
+  <si>
+    <t>Flamengo</t>
+  </si>
+  <si>
     <t>Everton</t>
   </si>
   <si>
-    <t>Flamengo</t>
-  </si>
-  <si>
     <t>Paysandu</t>
   </si>
   <si>
-    <t>Bragantino</t>
-  </si>
-  <si>
     <t>Utah Royals</t>
   </si>
   <si>
@@ -1181,9 +1184,6 @@
   </si>
   <si>
     <t>São Paulo</t>
-  </si>
-  <si>
-    <t>Real Monarchs</t>
   </si>
   <si>
     <t>San Jose Earthquakes II</t>
@@ -1788,7 +1788,7 @@
         <v>392</v>
       </c>
       <c r="AL2" s="3">
-        <v>45872.08333333334</v>
+        <v>45872</v>
       </c>
     </row>
     <row r="3" spans="1:38">
@@ -1796,10 +1796,10 @@
         <v>45872</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
         <v>119</v>
@@ -1912,10 +1912,10 @@
         <v>45872</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
         <v>119</v>
@@ -2028,10 +2028,10 @@
         <v>45872</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
         <v>119</v>
@@ -2150,7 +2150,7 @@
         <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E6" t="s">
         <v>125</v>
@@ -2252,7 +2252,7 @@
         <v>392</v>
       </c>
       <c r="AL6" s="3">
-        <v>45872.1875</v>
+        <v>45872.08333333334</v>
       </c>
     </row>
     <row r="7" spans="1:38">
@@ -2368,7 +2368,7 @@
         <v>392</v>
       </c>
       <c r="AL7" s="3">
-        <v>45872.21875</v>
+        <v>45872.1875</v>
       </c>
     </row>
     <row r="8" spans="1:38">
@@ -2376,10 +2376,10 @@
         <v>45872</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
         <v>120</v>
@@ -2600,7 +2600,7 @@
         <v>392</v>
       </c>
       <c r="AL9" s="3">
-        <v>45872.22916666666</v>
+        <v>45872.21875</v>
       </c>
     </row>
     <row r="10" spans="1:38">
@@ -2614,7 +2614,7 @@
         <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E10" t="s">
         <v>129</v>
@@ -2638,13 +2638,13 @@
         <v>391</v>
       </c>
       <c r="L10">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M10">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N10">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -2686,10 +2686,10 @@
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC10">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD10">
         <v>0</v>
@@ -2716,7 +2716,7 @@
         <v>392</v>
       </c>
       <c r="AL10" s="3">
-        <v>45872.29166666666</v>
+        <v>45872.22916666666</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -2724,7 +2724,7 @@
         <v>45872</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s">
         <v>80</v>
@@ -2846,7 +2846,7 @@
         <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E12" t="s">
         <v>131</v>
@@ -2870,13 +2870,13 @@
         <v>391</v>
       </c>
       <c r="L12">
-        <v>5.45</v>
+        <v>3.15</v>
       </c>
       <c r="M12">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="N12">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -2918,16 +2918,16 @@
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD12">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AE12">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF12">
         <v>0</v>
@@ -2948,7 +2948,7 @@
         <v>392</v>
       </c>
       <c r="AL12" s="3">
-        <v>45872.3125</v>
+        <v>45872.29166666666</v>
       </c>
     </row>
     <row r="13" spans="1:38">
@@ -2986,13 +2986,13 @@
         <v>391</v>
       </c>
       <c r="L13">
-        <v>2.1</v>
+        <v>5.45</v>
       </c>
       <c r="M13">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="N13">
-        <v>3.4</v>
+        <v>1.55</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -3034,16 +3034,16 @@
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF13">
         <v>0</v>
@@ -3064,7 +3064,7 @@
         <v>392</v>
       </c>
       <c r="AL13" s="3">
-        <v>45872.33333333334</v>
+        <v>45872.3125</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -3072,7 +3072,7 @@
         <v>45872</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
         <v>83</v>
@@ -3188,13 +3188,13 @@
         <v>45872</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
         <v>84</v>
       </c>
       <c r="D15" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E15" t="s">
         <v>134</v>
@@ -3218,13 +3218,13 @@
         <v>391</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -3266,10 +3266,10 @@
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD15">
         <v>0</v>
@@ -3304,7 +3304,7 @@
         <v>45872</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
         <v>85</v>
@@ -3426,7 +3426,7 @@
         <v>86</v>
       </c>
       <c r="D17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E17" t="s">
         <v>136</v>
@@ -3528,7 +3528,7 @@
         <v>392</v>
       </c>
       <c r="AL17" s="3">
-        <v>45872.35416666666</v>
+        <v>45872.33333333334</v>
       </c>
     </row>
     <row r="18" spans="1:38">
@@ -3536,13 +3536,13 @@
         <v>45872</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D18" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E18" t="s">
         <v>137</v>
@@ -3566,13 +3566,13 @@
         <v>391</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -3620,10 +3620,10 @@
         <v>0</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF18">
         <v>0</v>
@@ -3652,13 +3652,13 @@
         <v>45872</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D19" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E19" t="s">
         <v>138</v>
@@ -3682,13 +3682,13 @@
         <v>391</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -3730,10 +3730,10 @@
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD19">
         <v>0</v>
@@ -3768,10 +3768,10 @@
         <v>45872</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D20" t="s">
         <v>120</v>
@@ -3798,13 +3798,13 @@
         <v>391</v>
       </c>
       <c r="L20">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="M20">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="N20">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>1.6</v>
       </c>
       <c r="AC20">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AD20">
         <v>0</v>
@@ -3884,10 +3884,10 @@
         <v>45872</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C21" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D21" t="s">
         <v>120</v>
@@ -3914,13 +3914,13 @@
         <v>391</v>
       </c>
       <c r="L21">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M21">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N21">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -3962,10 +3962,10 @@
         <v>0</v>
       </c>
       <c r="AB21">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC21">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD21">
         <v>0</v>
@@ -4000,13 +4000,13 @@
         <v>45872</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C22" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E22" t="s">
         <v>141</v>
@@ -4030,13 +4030,13 @@
         <v>391</v>
       </c>
       <c r="L22">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M22">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N22">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -4084,10 +4084,10 @@
         <v>0</v>
       </c>
       <c r="AD22">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE22">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF22">
         <v>0</v>
@@ -4116,13 +4116,13 @@
         <v>45872</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E23" t="s">
         <v>142</v>
@@ -4146,13 +4146,13 @@
         <v>391</v>
       </c>
       <c r="L23">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M23">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N23">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O23">
         <v>0</v>
@@ -4194,16 +4194,16 @@
         <v>0</v>
       </c>
       <c r="AB23">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC23">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD23">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE23">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF23">
         <v>0</v>
@@ -4235,10 +4235,10 @@
         <v>46</v>
       </c>
       <c r="C24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D24" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E24" t="s">
         <v>143</v>
@@ -4262,13 +4262,13 @@
         <v>391</v>
       </c>
       <c r="L24">
-        <v>1.39</v>
+        <v>2.26</v>
       </c>
       <c r="M24">
-        <v>4.9</v>
+        <v>3.45</v>
       </c>
       <c r="N24">
-        <v>6.8</v>
+        <v>2.95</v>
       </c>
       <c r="O24">
         <v>0</v>
@@ -4310,16 +4310,16 @@
         <v>0</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF24">
         <v>0</v>
@@ -4340,7 +4340,7 @@
         <v>392</v>
       </c>
       <c r="AL24" s="3">
-        <v>45872.35763888889</v>
+        <v>45872.35416666666</v>
       </c>
     </row>
     <row r="25" spans="1:38">
@@ -4348,7 +4348,7 @@
         <v>45872</v>
       </c>
       <c r="B25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C25" t="s">
         <v>85</v>
@@ -4426,10 +4426,10 @@
         <v>0</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD25">
         <v>0</v>
@@ -4494,13 +4494,13 @@
         <v>391</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -4542,10 +4542,10 @@
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD26">
         <v>0</v>
@@ -4572,7 +4572,7 @@
         <v>392</v>
       </c>
       <c r="AL26" s="3">
-        <v>45872.375</v>
+        <v>45872.35763888889</v>
       </c>
     </row>
     <row r="27" spans="1:38">
@@ -4580,10 +4580,10 @@
         <v>45872</v>
       </c>
       <c r="B27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D27" t="s">
         <v>119</v>
@@ -4696,7 +4696,7 @@
         <v>45872</v>
       </c>
       <c r="B28" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C28" t="s">
         <v>90</v>
@@ -4726,13 +4726,13 @@
         <v>391</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O28">
         <v>0</v>
@@ -4774,10 +4774,10 @@
         <v>0</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD28">
         <v>0</v>
@@ -4812,10 +4812,10 @@
         <v>45872</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C29" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D29" t="s">
         <v>119</v>
@@ -4842,13 +4842,13 @@
         <v>391</v>
       </c>
       <c r="L29">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M29">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N29">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O29">
         <v>0</v>
@@ -4890,10 +4890,10 @@
         <v>0</v>
       </c>
       <c r="AB29">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC29">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD29">
         <v>0</v>
@@ -4928,10 +4928,10 @@
         <v>45872</v>
       </c>
       <c r="B30" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D30" t="s">
         <v>120</v>
@@ -5044,10 +5044,10 @@
         <v>45872</v>
       </c>
       <c r="B31" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C31" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D31" t="s">
         <v>120</v>
@@ -5074,13 +5074,13 @@
         <v>391</v>
       </c>
       <c r="L31">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M31">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N31">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O31">
         <v>0</v>
@@ -5122,10 +5122,10 @@
         <v>0</v>
       </c>
       <c r="AB31">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC31">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD31">
         <v>0</v>
@@ -5160,10 +5160,10 @@
         <v>45872</v>
       </c>
       <c r="B32" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C32" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D32" t="s">
         <v>120</v>
@@ -5276,13 +5276,13 @@
         <v>45872</v>
       </c>
       <c r="B33" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C33" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D33" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E33" t="s">
         <v>152</v>
@@ -5306,13 +5306,13 @@
         <v>391</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -5354,10 +5354,10 @@
         <v>0</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD33">
         <v>0</v>
@@ -5395,7 +5395,7 @@
         <v>48</v>
       </c>
       <c r="C34" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="D34" t="s">
         <v>120</v>
@@ -5500,7 +5500,7 @@
         <v>392</v>
       </c>
       <c r="AL34" s="3">
-        <v>45872.39583333334</v>
+        <v>45872.375</v>
       </c>
     </row>
     <row r="35" spans="1:38">
@@ -5508,10 +5508,10 @@
         <v>45872</v>
       </c>
       <c r="B35" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D35" t="s">
         <v>120</v>
@@ -5624,13 +5624,13 @@
         <v>45872</v>
       </c>
       <c r="B36" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C36" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="D36" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E36" t="s">
         <v>155</v>
@@ -5654,13 +5654,13 @@
         <v>391</v>
       </c>
       <c r="L36">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M36">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="N36">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="O36">
         <v>0</v>
@@ -5708,10 +5708,10 @@
         <v>0</v>
       </c>
       <c r="AD36">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE36">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AF36">
         <v>0</v>
@@ -5740,13 +5740,13 @@
         <v>45872</v>
       </c>
       <c r="B37" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C37" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="D37" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E37" t="s">
         <v>156</v>
@@ -5770,13 +5770,13 @@
         <v>391</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="O37">
         <v>0</v>
@@ -5824,10 +5824,10 @@
         <v>0</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF37">
         <v>0</v>
@@ -5859,7 +5859,7 @@
         <v>49</v>
       </c>
       <c r="C38" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D38" t="s">
         <v>120</v>
@@ -5886,13 +5886,13 @@
         <v>391</v>
       </c>
       <c r="L38">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M38">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N38">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="O38">
         <v>0</v>
@@ -5934,10 +5934,10 @@
         <v>0</v>
       </c>
       <c r="AB38">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC38">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD38">
         <v>0</v>
@@ -5964,7 +5964,7 @@
         <v>392</v>
       </c>
       <c r="AL38" s="3">
-        <v>45872.40625</v>
+        <v>45872.39583333334</v>
       </c>
     </row>
     <row r="39" spans="1:38">
@@ -5972,10 +5972,10 @@
         <v>45872</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C39" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="D39" t="s">
         <v>120</v>
@@ -6002,13 +6002,13 @@
         <v>391</v>
       </c>
       <c r="L39">
-        <v>1.94</v>
+        <v>2.09</v>
       </c>
       <c r="M39">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="N39">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="O39">
         <v>0</v>
@@ -6050,10 +6050,10 @@
         <v>0</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD39">
         <v>0</v>
@@ -6094,7 +6094,7 @@
         <v>96</v>
       </c>
       <c r="D40" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E40" t="s">
         <v>159</v>
@@ -6118,13 +6118,13 @@
         <v>391</v>
       </c>
       <c r="L40">
-        <v>2.39</v>
+        <v>1.94</v>
       </c>
       <c r="M40">
-        <v>3.84</v>
+        <v>3.25</v>
       </c>
       <c r="N40">
-        <v>2.22</v>
+        <v>3.6</v>
       </c>
       <c r="O40">
         <v>0</v>
@@ -6196,7 +6196,7 @@
         <v>392</v>
       </c>
       <c r="AL40" s="3">
-        <v>45872.41666666666</v>
+        <v>45872.40625</v>
       </c>
     </row>
     <row r="41" spans="1:38">
@@ -6204,13 +6204,13 @@
         <v>45872</v>
       </c>
       <c r="B41" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C41" t="s">
         <v>97</v>
       </c>
       <c r="D41" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E41" t="s">
         <v>160</v>
@@ -6234,13 +6234,13 @@
         <v>391</v>
       </c>
       <c r="L41">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M41">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N41">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O41">
         <v>0</v>
@@ -6282,10 +6282,10 @@
         <v>0</v>
       </c>
       <c r="AB41">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC41">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD41">
         <v>0</v>
@@ -6320,7 +6320,7 @@
         <v>45872</v>
       </c>
       <c r="B42" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C42" t="s">
         <v>98</v>
@@ -6436,13 +6436,13 @@
         <v>45872</v>
       </c>
       <c r="B43" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C43" t="s">
         <v>99</v>
       </c>
       <c r="D43" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E43" t="s">
         <v>162</v>
@@ -6466,13 +6466,13 @@
         <v>391</v>
       </c>
       <c r="L43">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M43">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O43">
         <v>0</v>
@@ -6520,10 +6520,10 @@
         <v>0</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF43">
         <v>0</v>
@@ -6552,13 +6552,13 @@
         <v>45872</v>
       </c>
       <c r="B44" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C44" t="s">
         <v>100</v>
       </c>
       <c r="D44" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E44" t="s">
         <v>163</v>
@@ -6582,13 +6582,13 @@
         <v>391</v>
       </c>
       <c r="L44">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M44">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -6630,10 +6630,10 @@
         <v>0</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD44">
         <v>0</v>
@@ -6674,7 +6674,7 @@
         <v>101</v>
       </c>
       <c r="D45" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E45" t="s">
         <v>164</v>
@@ -6776,7 +6776,7 @@
         <v>392</v>
       </c>
       <c r="AL45" s="3">
-        <v>45872.4375</v>
+        <v>45872.41666666666</v>
       </c>
     </row>
     <row r="46" spans="1:38">
@@ -6790,7 +6790,7 @@
         <v>102</v>
       </c>
       <c r="D46" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E46" t="s">
         <v>165</v>
@@ -6892,7 +6892,7 @@
         <v>392</v>
       </c>
       <c r="AL46" s="3">
-        <v>45872.45833333334</v>
+        <v>45872.4375</v>
       </c>
     </row>
     <row r="47" spans="1:38">
@@ -6900,10 +6900,10 @@
         <v>45872</v>
       </c>
       <c r="B47" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C47" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D47" t="s">
         <v>120</v>
@@ -7016,10 +7016,10 @@
         <v>45872</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C48" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D48" t="s">
         <v>120</v>
@@ -7132,10 +7132,10 @@
         <v>45872</v>
       </c>
       <c r="B49" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C49" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D49" t="s">
         <v>120</v>
@@ -7248,10 +7248,10 @@
         <v>45872</v>
       </c>
       <c r="B50" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C50" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D50" t="s">
         <v>120</v>
@@ -7364,10 +7364,10 @@
         <v>45872</v>
       </c>
       <c r="B51" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C51" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D51" t="s">
         <v>120</v>
@@ -7480,10 +7480,10 @@
         <v>45872</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C52" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D52" t="s">
         <v>120</v>
@@ -7596,10 +7596,10 @@
         <v>45872</v>
       </c>
       <c r="B53" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C53" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="D53" t="s">
         <v>120</v>
@@ -7626,13 +7626,13 @@
         <v>391</v>
       </c>
       <c r="L53">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M53">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N53">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O53">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="AB53">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC53">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD53">
         <v>0</v>
@@ -7712,13 +7712,13 @@
         <v>45872</v>
       </c>
       <c r="B54" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C54" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D54" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E54" t="s">
         <v>173</v>
@@ -7742,13 +7742,13 @@
         <v>391</v>
       </c>
       <c r="L54">
-        <v>1.26</v>
+        <v>2.6</v>
       </c>
       <c r="M54">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="N54">
-        <v>9.4</v>
+        <v>2.6</v>
       </c>
       <c r="O54">
         <v>0</v>
@@ -7790,10 +7790,10 @@
         <v>0</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD54">
         <v>0</v>
@@ -7828,10 +7828,10 @@
         <v>45872</v>
       </c>
       <c r="B55" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C55" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D55" t="s">
         <v>119</v>
@@ -7944,13 +7944,13 @@
         <v>45872</v>
       </c>
       <c r="B56" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C56" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="D56" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E56" t="s">
         <v>175</v>
@@ -7974,13 +7974,13 @@
         <v>391</v>
       </c>
       <c r="L56">
-        <v>2.6</v>
+        <v>1.26</v>
       </c>
       <c r="M56">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="N56">
-        <v>2.6</v>
+        <v>9.4</v>
       </c>
       <c r="O56">
         <v>0</v>
@@ -8022,10 +8022,10 @@
         <v>0</v>
       </c>
       <c r="AB56">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC56">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD56">
         <v>0</v>
@@ -8060,10 +8060,10 @@
         <v>45872</v>
       </c>
       <c r="B57" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C57" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D57" t="s">
         <v>120</v>
@@ -8090,13 +8090,13 @@
         <v>391</v>
       </c>
       <c r="L57">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M57">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O57">
         <v>0</v>
@@ -8138,10 +8138,10 @@
         <v>0</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD57">
         <v>0</v>
@@ -8176,10 +8176,10 @@
         <v>45872</v>
       </c>
       <c r="B58" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C58" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D58" t="s">
         <v>120</v>
@@ -8295,7 +8295,7 @@
         <v>53</v>
       </c>
       <c r="C59" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="D59" t="s">
         <v>120</v>
@@ -8400,7 +8400,7 @@
         <v>392</v>
       </c>
       <c r="AL59" s="3">
-        <v>45872.47916666666</v>
+        <v>45872.45833333334</v>
       </c>
     </row>
     <row r="60" spans="1:38">
@@ -8408,10 +8408,10 @@
         <v>45872</v>
       </c>
       <c r="B60" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C60" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D60" t="s">
         <v>120</v>
@@ -8438,13 +8438,13 @@
         <v>391</v>
       </c>
       <c r="L60">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M60">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O60">
         <v>0</v>
@@ -8486,10 +8486,10 @@
         <v>0</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD60">
         <v>0</v>
@@ -8524,10 +8524,10 @@
         <v>45872</v>
       </c>
       <c r="B61" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C61" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D61" t="s">
         <v>120</v>
@@ -8554,13 +8554,13 @@
         <v>391</v>
       </c>
       <c r="L61">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M61">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N61">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O61">
         <v>0</v>
@@ -8602,10 +8602,10 @@
         <v>0</v>
       </c>
       <c r="AB61">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC61">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AD61">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>45872</v>
       </c>
       <c r="B62" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C62" t="s">
         <v>89</v>
       </c>
       <c r="D62" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E62" t="s">
         <v>181</v>
@@ -8759,7 +8759,7 @@
         <v>54</v>
       </c>
       <c r="C63" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D63" t="s">
         <v>119</v>
@@ -8786,13 +8786,13 @@
         <v>391</v>
       </c>
       <c r="L63">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="M63">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="N63">
-        <v>2.65</v>
+        <v>4.5</v>
       </c>
       <c r="O63">
         <v>0</v>
@@ -8834,10 +8834,10 @@
         <v>0</v>
       </c>
       <c r="AB63">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="AC63">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="AD63">
         <v>0</v>
@@ -8864,7 +8864,7 @@
         <v>392</v>
       </c>
       <c r="AL63" s="3">
-        <v>45872.5</v>
+        <v>45872.47916666666</v>
       </c>
     </row>
     <row r="64" spans="1:38">
@@ -8872,10 +8872,10 @@
         <v>45872</v>
       </c>
       <c r="B64" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C64" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D64" t="s">
         <v>120</v>
@@ -8988,10 +8988,10 @@
         <v>45872</v>
       </c>
       <c r="B65" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C65" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="D65" t="s">
         <v>120</v>
@@ -9018,13 +9018,13 @@
         <v>391</v>
       </c>
       <c r="L65">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M65">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O65">
         <v>0</v>
@@ -9066,10 +9066,10 @@
         <v>0</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD65">
         <v>0</v>
@@ -9104,10 +9104,10 @@
         <v>45872</v>
       </c>
       <c r="B66" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C66" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D66" t="s">
         <v>120</v>
@@ -9220,10 +9220,10 @@
         <v>45872</v>
       </c>
       <c r="B67" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C67" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="D67" t="s">
         <v>120</v>
@@ -9250,13 +9250,13 @@
         <v>391</v>
       </c>
       <c r="L67">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M67">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O67">
         <v>0</v>
@@ -9298,10 +9298,10 @@
         <v>0</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD67">
         <v>0</v>
@@ -9336,10 +9336,10 @@
         <v>45872</v>
       </c>
       <c r="B68" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C68" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D68" t="s">
         <v>119</v>
@@ -9366,13 +9366,13 @@
         <v>391</v>
       </c>
       <c r="L68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M68">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O68">
         <v>0</v>
@@ -9414,10 +9414,10 @@
         <v>0</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD68">
         <v>0</v>
@@ -9452,10 +9452,10 @@
         <v>45872</v>
       </c>
       <c r="B69" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C69" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D69" t="s">
         <v>120</v>
@@ -9568,10 +9568,10 @@
         <v>45872</v>
       </c>
       <c r="B70" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C70" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D70" t="s">
         <v>120</v>
@@ -9684,13 +9684,13 @@
         <v>45872</v>
       </c>
       <c r="B71" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C71" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="D71" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E71" t="s">
         <v>190</v>
@@ -9714,13 +9714,13 @@
         <v>391</v>
       </c>
       <c r="L71">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="M71">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N71">
-        <v>5.5</v>
+        <v>2.04</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -9762,10 +9762,10 @@
         <v>0</v>
       </c>
       <c r="AB71">
-        <v>1.66</v>
+        <v>1.94</v>
       </c>
       <c r="AC71">
-        <v>2.22</v>
+        <v>1.74</v>
       </c>
       <c r="AD71">
         <v>0</v>
@@ -9800,7 +9800,7 @@
         <v>45872</v>
       </c>
       <c r="B72" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C72" t="s">
         <v>105</v>
@@ -9830,13 +9830,13 @@
         <v>391</v>
       </c>
       <c r="L72">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M72">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N72">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -9878,10 +9878,10 @@
         <v>0</v>
       </c>
       <c r="AB72">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC72">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AD72">
         <v>0</v>
@@ -9916,10 +9916,10 @@
         <v>45872</v>
       </c>
       <c r="B73" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C73" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="D73" t="s">
         <v>120</v>
@@ -10032,10 +10032,10 @@
         <v>45872</v>
       </c>
       <c r="B74" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C74" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="D74" t="s">
         <v>120</v>
@@ -10062,13 +10062,13 @@
         <v>391</v>
       </c>
       <c r="L74">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="M74">
-        <v>3.64</v>
+        <v>4.2</v>
       </c>
       <c r="N74">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="O74">
         <v>0</v>
@@ -10110,10 +10110,10 @@
         <v>0</v>
       </c>
       <c r="AB74">
-        <v>2.15</v>
+        <v>1.6</v>
       </c>
       <c r="AC74">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AD74">
         <v>0</v>
@@ -10148,13 +10148,13 @@
         <v>45872</v>
       </c>
       <c r="B75" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C75" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D75" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E75" t="s">
         <v>194</v>
@@ -10264,13 +10264,13 @@
         <v>45872</v>
       </c>
       <c r="B76" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C76" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="D76" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E76" t="s">
         <v>195</v>
@@ -10380,10 +10380,10 @@
         <v>45872</v>
       </c>
       <c r="B77" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C77" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="D77" t="s">
         <v>120</v>
@@ -10410,13 +10410,13 @@
         <v>391</v>
       </c>
       <c r="L77">
-        <v>2.95</v>
+        <v>3.85</v>
       </c>
       <c r="M77">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="N77">
-        <v>2.28</v>
+        <v>1.84</v>
       </c>
       <c r="O77">
         <v>0</v>
@@ -10458,10 +10458,10 @@
         <v>0</v>
       </c>
       <c r="AB77">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AC77">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AD77">
         <v>0</v>
@@ -10496,10 +10496,10 @@
         <v>45872</v>
       </c>
       <c r="B78" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C78" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D78" t="s">
         <v>119</v>
@@ -10612,10 +10612,10 @@
         <v>45872</v>
       </c>
       <c r="B79" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C79" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D79" t="s">
         <v>119</v>
@@ -10642,13 +10642,13 @@
         <v>391</v>
       </c>
       <c r="L79">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M79">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="N79">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="O79">
         <v>0</v>
@@ -10690,10 +10690,10 @@
         <v>0</v>
       </c>
       <c r="AB79">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AC79">
-        <v>2.31</v>
+        <v>2.22</v>
       </c>
       <c r="AD79">
         <v>0</v>
@@ -10728,13 +10728,13 @@
         <v>45872</v>
       </c>
       <c r="B80" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C80" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="D80" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E80" t="s">
         <v>199</v>
@@ -10758,13 +10758,13 @@
         <v>391</v>
       </c>
       <c r="L80">
-        <v>3.85</v>
+        <v>2.5</v>
       </c>
       <c r="M80">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="N80">
-        <v>1.84</v>
+        <v>2.65</v>
       </c>
       <c r="O80">
         <v>0</v>
@@ -10806,10 +10806,10 @@
         <v>0</v>
       </c>
       <c r="AB80">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AC80">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AD80">
         <v>0</v>
@@ -10844,10 +10844,10 @@
         <v>45872</v>
       </c>
       <c r="B81" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C81" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="D81" t="s">
         <v>120</v>
@@ -10960,10 +10960,10 @@
         <v>45872</v>
       </c>
       <c r="B82" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C82" t="s">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="D82" t="s">
         <v>120</v>
@@ -10990,13 +10990,13 @@
         <v>391</v>
       </c>
       <c r="L82">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M82">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N82">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O82">
         <v>0</v>
@@ -11038,10 +11038,10 @@
         <v>0</v>
       </c>
       <c r="AB82">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC82">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD82">
         <v>0</v>
@@ -11079,10 +11079,10 @@
         <v>55</v>
       </c>
       <c r="C83" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D83" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E83" t="s">
         <v>202</v>
@@ -11106,13 +11106,13 @@
         <v>391</v>
       </c>
       <c r="L83">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M83">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N83">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O83">
         <v>0</v>
@@ -11184,7 +11184,7 @@
         <v>392</v>
       </c>
       <c r="AL83" s="3">
-        <v>45872.52083333334</v>
+        <v>45872.5</v>
       </c>
     </row>
     <row r="84" spans="1:38">
@@ -11192,10 +11192,10 @@
         <v>45872</v>
       </c>
       <c r="B84" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C84" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D84" t="s">
         <v>120</v>
@@ -11308,10 +11308,10 @@
         <v>45872</v>
       </c>
       <c r="B85" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C85" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="D85" t="s">
         <v>120</v>
@@ -11338,13 +11338,13 @@
         <v>391</v>
       </c>
       <c r="L85">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="M85">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O85">
         <v>0</v>
@@ -11386,16 +11386,16 @@
         <v>0</v>
       </c>
       <c r="AB85">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC85">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD85">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF85">
         <v>0</v>
@@ -11424,7 +11424,7 @@
         <v>45872</v>
       </c>
       <c r="B86" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C86" t="s">
         <v>109</v>
@@ -11540,7 +11540,7 @@
         <v>45872</v>
       </c>
       <c r="B87" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C87" t="s">
         <v>110</v>
@@ -11656,10 +11656,10 @@
         <v>45872</v>
       </c>
       <c r="B88" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C88" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="D88" t="s">
         <v>120</v>
@@ -11686,13 +11686,13 @@
         <v>391</v>
       </c>
       <c r="L88">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M88">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O88">
         <v>0</v>
@@ -11772,10 +11772,10 @@
         <v>45872</v>
       </c>
       <c r="B89" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C89" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="D89" t="s">
         <v>120</v>
@@ -11802,13 +11802,13 @@
         <v>391</v>
       </c>
       <c r="L89">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="M89">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N89">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O89">
         <v>0</v>
@@ -11850,16 +11850,16 @@
         <v>0</v>
       </c>
       <c r="AB89">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC89">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD89">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE89">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF89">
         <v>0</v>
@@ -11996,7 +11996,7 @@
         <v>392</v>
       </c>
       <c r="AL90" s="3">
-        <v>45872.53125</v>
+        <v>45872.52083333334</v>
       </c>
     </row>
     <row r="91" spans="1:38">
@@ -12004,10 +12004,10 @@
         <v>45872</v>
       </c>
       <c r="B91" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C91" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D91" t="s">
         <v>120</v>
@@ -12123,7 +12123,7 @@
         <v>57</v>
       </c>
       <c r="C92" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="D92" t="s">
         <v>120</v>
@@ -12228,7 +12228,7 @@
         <v>392</v>
       </c>
       <c r="AL92" s="3">
-        <v>45872.54166666666</v>
+        <v>45872.53125</v>
       </c>
     </row>
     <row r="93" spans="1:38">
@@ -12236,10 +12236,10 @@
         <v>45872</v>
       </c>
       <c r="B93" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C93" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D93" t="s">
         <v>120</v>
@@ -12352,10 +12352,10 @@
         <v>45872</v>
       </c>
       <c r="B94" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C94" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D94" t="s">
         <v>120</v>
@@ -12468,13 +12468,13 @@
         <v>45872</v>
       </c>
       <c r="B95" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C95" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="D95" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E95" t="s">
         <v>214</v>
@@ -12498,13 +12498,13 @@
         <v>391</v>
       </c>
       <c r="L95">
-        <v>6.27</v>
+        <v>0</v>
       </c>
       <c r="M95">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N95">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O95">
         <v>0</v>
@@ -12552,10 +12552,10 @@
         <v>0</v>
       </c>
       <c r="AD95">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE95">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF95">
         <v>0</v>
@@ -12584,7 +12584,7 @@
         <v>45872</v>
       </c>
       <c r="B96" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C96" t="s">
         <v>77</v>
@@ -12703,7 +12703,7 @@
         <v>58</v>
       </c>
       <c r="C97" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D97" t="s">
         <v>119</v>
@@ -12730,13 +12730,13 @@
         <v>391</v>
       </c>
       <c r="L97">
-        <v>0</v>
+        <v>6.27</v>
       </c>
       <c r="M97">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O97">
         <v>0</v>
@@ -12784,10 +12784,10 @@
         <v>0</v>
       </c>
       <c r="AD97">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE97">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF97">
         <v>0</v>
@@ -12808,7 +12808,7 @@
         <v>392</v>
       </c>
       <c r="AL97" s="3">
-        <v>45872.55208333334</v>
+        <v>45872.54166666666</v>
       </c>
     </row>
     <row r="98" spans="1:38">
@@ -12819,7 +12819,7 @@
         <v>59</v>
       </c>
       <c r="C98" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="D98" t="s">
         <v>119</v>
@@ -12924,7 +12924,7 @@
         <v>392</v>
       </c>
       <c r="AL98" s="3">
-        <v>45872.5625</v>
+        <v>45872.55208333334</v>
       </c>
     </row>
     <row r="99" spans="1:38">
@@ -12932,13 +12932,13 @@
         <v>45872</v>
       </c>
       <c r="B99" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C99" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="D99" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E99" t="s">
         <v>218</v>
@@ -12962,13 +12962,13 @@
         <v>391</v>
       </c>
       <c r="L99">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M99">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O99">
         <v>0</v>
@@ -13010,10 +13010,10 @@
         <v>0</v>
       </c>
       <c r="AB99">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC99">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD99">
         <v>0</v>
@@ -13048,13 +13048,13 @@
         <v>45872</v>
       </c>
       <c r="B100" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C100" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="D100" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E100" t="s">
         <v>219</v>
@@ -13078,13 +13078,13 @@
         <v>391</v>
       </c>
       <c r="L100">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M100">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N100">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="O100">
         <v>0</v>
@@ -13126,10 +13126,10 @@
         <v>0</v>
       </c>
       <c r="AB100">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC100">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD100">
         <v>0</v>
@@ -13170,7 +13170,7 @@
         <v>114</v>
       </c>
       <c r="D101" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E101" t="s">
         <v>220</v>
@@ -13272,7 +13272,7 @@
         <v>392</v>
       </c>
       <c r="AL101" s="3">
-        <v>45872.58333333334</v>
+        <v>45872.5625</v>
       </c>
     </row>
     <row r="102" spans="1:38">
@@ -13280,13 +13280,13 @@
         <v>45872</v>
       </c>
       <c r="B102" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C102" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="D102" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E102" t="s">
         <v>221</v>
@@ -13396,10 +13396,10 @@
         <v>45872</v>
       </c>
       <c r="B103" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C103" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="D103" t="s">
         <v>120</v>
@@ -13512,10 +13512,10 @@
         <v>45872</v>
       </c>
       <c r="B104" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C104" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D104" t="s">
         <v>120</v>
@@ -13628,13 +13628,13 @@
         <v>45872</v>
       </c>
       <c r="B105" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C105" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="D105" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E105" t="s">
         <v>224</v>
@@ -13744,13 +13744,13 @@
         <v>45872</v>
       </c>
       <c r="B106" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C106" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D106" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E106" t="s">
         <v>225</v>
@@ -13860,13 +13860,13 @@
         <v>45872</v>
       </c>
       <c r="B107" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C107" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="D107" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E107" t="s">
         <v>226</v>
@@ -13976,10 +13976,10 @@
         <v>45872</v>
       </c>
       <c r="B108" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C108" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D108" t="s">
         <v>120</v>
@@ -14092,10 +14092,10 @@
         <v>45872</v>
       </c>
       <c r="B109" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C109" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D109" t="s">
         <v>120</v>
@@ -14211,7 +14211,7 @@
         <v>61</v>
       </c>
       <c r="C110" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="D110" t="s">
         <v>120</v>
@@ -14238,13 +14238,13 @@
         <v>391</v>
       </c>
       <c r="L110">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M110">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N110">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O110">
         <v>0</v>
@@ -14286,10 +14286,10 @@
         <v>0</v>
       </c>
       <c r="AB110">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC110">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD110">
         <v>0</v>
@@ -14316,7 +14316,7 @@
         <v>392</v>
       </c>
       <c r="AL110" s="3">
-        <v>45872.59375</v>
+        <v>45872.58333333334</v>
       </c>
     </row>
     <row r="111" spans="1:38">
@@ -14327,7 +14327,7 @@
         <v>62</v>
       </c>
       <c r="C111" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D111" t="s">
         <v>120</v>
@@ -14354,13 +14354,13 @@
         <v>391</v>
       </c>
       <c r="L111">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M111">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O111">
         <v>0</v>
@@ -14402,10 +14402,10 @@
         <v>0</v>
       </c>
       <c r="AB111">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC111">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD111">
         <v>0</v>
@@ -14432,7 +14432,7 @@
         <v>392</v>
       </c>
       <c r="AL111" s="3">
-        <v>45872.60416666666</v>
+        <v>45872.59375</v>
       </c>
     </row>
     <row r="112" spans="1:38">
@@ -14440,10 +14440,10 @@
         <v>45872</v>
       </c>
       <c r="B112" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C112" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D112" t="s">
         <v>120</v>
@@ -14470,13 +14470,13 @@
         <v>391</v>
       </c>
       <c r="L112">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M112">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N112">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="O112">
         <v>0</v>
@@ -14512,10 +14512,10 @@
         <v>0</v>
       </c>
       <c r="Z112">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA112">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB112">
         <v>0</v>
@@ -14556,10 +14556,10 @@
         <v>45872</v>
       </c>
       <c r="B113" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C113" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="D113" t="s">
         <v>120</v>
@@ -14586,13 +14586,13 @@
         <v>391</v>
       </c>
       <c r="L113">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M113">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="O113">
         <v>0</v>
@@ -14628,10 +14628,10 @@
         <v>0</v>
       </c>
       <c r="Z113">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA113">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB113">
         <v>0</v>
@@ -14675,7 +14675,7 @@
         <v>63</v>
       </c>
       <c r="C114" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D114" t="s">
         <v>120</v>
@@ -14780,7 +14780,7 @@
         <v>392</v>
       </c>
       <c r="AL114" s="3">
-        <v>45872.625</v>
+        <v>45872.60416666666</v>
       </c>
     </row>
     <row r="115" spans="1:38">
@@ -14788,10 +14788,10 @@
         <v>45872</v>
       </c>
       <c r="B115" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C115" t="s">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="D115" t="s">
         <v>119</v>
@@ -14904,10 +14904,10 @@
         <v>45872</v>
       </c>
       <c r="B116" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C116" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D116" t="s">
         <v>120</v>
@@ -15023,7 +15023,7 @@
         <v>64</v>
       </c>
       <c r="C117" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D117" t="s">
         <v>120</v>
@@ -15050,13 +15050,13 @@
         <v>391</v>
       </c>
       <c r="L117">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M117">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N117">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O117">
         <v>0</v>
@@ -15128,7 +15128,7 @@
         <v>392</v>
       </c>
       <c r="AL117" s="3">
-        <v>45872.63541666666</v>
+        <v>45872.625</v>
       </c>
     </row>
     <row r="118" spans="1:38">
@@ -15136,10 +15136,10 @@
         <v>45872</v>
       </c>
       <c r="B118" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C118" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="D118" t="s">
         <v>120</v>
@@ -15166,13 +15166,13 @@
         <v>391</v>
       </c>
       <c r="L118">
-        <v>1.51</v>
+        <v>2.11</v>
       </c>
       <c r="M118">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="N118">
-        <v>5.2</v>
+        <v>3.1</v>
       </c>
       <c r="O118">
         <v>0</v>
@@ -15255,7 +15255,7 @@
         <v>65</v>
       </c>
       <c r="C119" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="D119" t="s">
         <v>120</v>
@@ -15282,13 +15282,13 @@
         <v>391</v>
       </c>
       <c r="L119">
-        <v>2.15</v>
+        <v>1.51</v>
       </c>
       <c r="M119">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N119">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="O119">
         <v>0</v>
@@ -15330,10 +15330,10 @@
         <v>0</v>
       </c>
       <c r="AB119">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC119">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD119">
         <v>0</v>
@@ -15360,7 +15360,7 @@
         <v>392</v>
       </c>
       <c r="AL119" s="3">
-        <v>45872.64583333334</v>
+        <v>45872.63541666666</v>
       </c>
     </row>
     <row r="120" spans="1:38">
@@ -15371,10 +15371,10 @@
         <v>66</v>
       </c>
       <c r="C120" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D120" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E120" t="s">
         <v>239</v>
@@ -15398,13 +15398,13 @@
         <v>391</v>
       </c>
       <c r="L120">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="M120">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N120">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="O120">
         <v>0</v>
@@ -15440,16 +15440,16 @@
         <v>0</v>
       </c>
       <c r="Z120">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA120">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB120">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AC120">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AD120">
         <v>0</v>
@@ -15476,7 +15476,7 @@
         <v>392</v>
       </c>
       <c r="AL120" s="3">
-        <v>45872.66666666666</v>
+        <v>45872.64583333334</v>
       </c>
     </row>
     <row r="121" spans="1:38">
@@ -15484,10 +15484,10 @@
         <v>45872</v>
       </c>
       <c r="B121" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C121" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D121" t="s">
         <v>119</v>
@@ -15514,13 +15514,13 @@
         <v>391</v>
       </c>
       <c r="L121">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M121">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N121">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O121">
         <v>0</v>
@@ -15556,16 +15556,16 @@
         <v>0</v>
       </c>
       <c r="Z121">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA121">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB121">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC121">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD121">
         <v>0</v>
@@ -15600,10 +15600,10 @@
         <v>45872</v>
       </c>
       <c r="B122" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C122" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D122" t="s">
         <v>119</v>
@@ -15630,13 +15630,13 @@
         <v>391</v>
       </c>
       <c r="L122">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M122">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N122">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O122">
         <v>0</v>
@@ -15678,10 +15678,10 @@
         <v>0</v>
       </c>
       <c r="AB122">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC122">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD122">
         <v>0</v>
@@ -15716,10 +15716,10 @@
         <v>45872</v>
       </c>
       <c r="B123" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C123" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D123" t="s">
         <v>120</v>
@@ -15832,10 +15832,10 @@
         <v>45872</v>
       </c>
       <c r="B124" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C124" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D124" t="s">
         <v>119</v>
@@ -15862,13 +15862,13 @@
         <v>391</v>
       </c>
       <c r="L124">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M124">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N124">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O124">
         <v>0</v>
@@ -15910,10 +15910,10 @@
         <v>0</v>
       </c>
       <c r="AB124">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC124">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD124">
         <v>0</v>
@@ -15951,7 +15951,7 @@
         <v>67</v>
       </c>
       <c r="C125" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D125" t="s">
         <v>119</v>
@@ -16056,7 +16056,7 @@
         <v>392</v>
       </c>
       <c r="AL125" s="3">
-        <v>45872.70833333334</v>
+        <v>45872.66666666666</v>
       </c>
     </row>
     <row r="126" spans="1:38">
@@ -16067,7 +16067,7 @@
         <v>68</v>
       </c>
       <c r="C126" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D126" t="s">
         <v>119</v>
@@ -16172,7 +16172,7 @@
         <v>392</v>
       </c>
       <c r="AL126" s="3">
-        <v>45872.77083333334</v>
+        <v>45872.70833333334</v>
       </c>
     </row>
     <row r="127" spans="1:38">
@@ -16180,7 +16180,7 @@
         <v>45872</v>
       </c>
       <c r="B127" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C127" t="s">
         <v>116</v>
@@ -16210,13 +16210,13 @@
         <v>391</v>
       </c>
       <c r="L127">
-        <v>3.8</v>
+        <v>2.09</v>
       </c>
       <c r="M127">
         <v>3.15</v>
       </c>
       <c r="N127">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="O127">
         <v>0</v>
@@ -16258,7 +16258,7 @@
         <v>0</v>
       </c>
       <c r="AB127">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC127">
         <v>1.57</v>
@@ -16296,10 +16296,10 @@
         <v>45872</v>
       </c>
       <c r="B128" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C128" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D128" t="s">
         <v>119</v>
@@ -16326,13 +16326,13 @@
         <v>391</v>
       </c>
       <c r="L128">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M128">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N128">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O128">
         <v>0</v>
@@ -16374,10 +16374,10 @@
         <v>0</v>
       </c>
       <c r="AB128">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC128">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD128">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>45872</v>
       </c>
       <c r="B129" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C129" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D129" t="s">
         <v>119</v>
@@ -16442,13 +16442,13 @@
         <v>391</v>
       </c>
       <c r="L129">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M129">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N129">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O129">
         <v>0</v>
@@ -16490,10 +16490,10 @@
         <v>0</v>
       </c>
       <c r="AB129">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC129">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD129">
         <v>0</v>
@@ -16531,7 +16531,7 @@
         <v>69</v>
       </c>
       <c r="C130" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D130" t="s">
         <v>119</v>
@@ -16636,7 +16636,7 @@
         <v>392</v>
       </c>
       <c r="AL130" s="3">
-        <v>45872.79166666666</v>
+        <v>45872.77083333334</v>
       </c>
     </row>
     <row r="131" spans="1:38">
@@ -16644,10 +16644,10 @@
         <v>45872</v>
       </c>
       <c r="B131" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C131" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D131" t="s">
         <v>119</v>
@@ -16763,7 +16763,7 @@
         <v>70</v>
       </c>
       <c r="C132" t="s">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="D132" t="s">
         <v>119</v>
@@ -16790,13 +16790,13 @@
         <v>391</v>
       </c>
       <c r="L132">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M132">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N132">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O132">
         <v>0</v>
@@ -16838,10 +16838,10 @@
         <v>0</v>
       </c>
       <c r="AB132">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC132">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD132">
         <v>0</v>
@@ -16868,7 +16868,7 @@
         <v>392</v>
       </c>
       <c r="AL132" s="3">
-        <v>45872.8125</v>
+        <v>45872.79166666666</v>
       </c>
     </row>
     <row r="133" spans="1:38">
@@ -16879,7 +16879,7 @@
         <v>71</v>
       </c>
       <c r="C133" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D133" t="s">
         <v>119</v>
@@ -16906,13 +16906,13 @@
         <v>391</v>
       </c>
       <c r="L133">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M133">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N133">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O133">
         <v>0</v>
@@ -16954,10 +16954,10 @@
         <v>0</v>
       </c>
       <c r="AB133">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC133">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD133">
         <v>0</v>
@@ -16984,7 +16984,7 @@
         <v>392</v>
       </c>
       <c r="AL133" s="3">
-        <v>45872.83333333334</v>
+        <v>45872.8125</v>
       </c>
     </row>
     <row r="134" spans="1:38">
@@ -16995,7 +16995,7 @@
         <v>72</v>
       </c>
       <c r="C134" t="s">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="D134" t="s">
         <v>119</v>
@@ -17022,13 +17022,13 @@
         <v>391</v>
       </c>
       <c r="L134">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M134">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N134">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O134">
         <v>0</v>
@@ -17070,10 +17070,10 @@
         <v>0</v>
       </c>
       <c r="AB134">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC134">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD134">
         <v>0</v>
@@ -17100,7 +17100,7 @@
         <v>392</v>
       </c>
       <c r="AL134" s="3">
-        <v>45872.85416666666</v>
+        <v>45872.83333333334</v>
       </c>
     </row>
     <row r="135" spans="1:38">
@@ -17111,7 +17111,7 @@
         <v>73</v>
       </c>
       <c r="C135" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D135" t="s">
         <v>119</v>
@@ -17138,13 +17138,13 @@
         <v>391</v>
       </c>
       <c r="L135">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M135">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N135">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O135">
         <v>0</v>
@@ -17186,10 +17186,10 @@
         <v>0</v>
       </c>
       <c r="AB135">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC135">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD135">
         <v>0</v>
@@ -17216,7 +17216,7 @@
         <v>392</v>
       </c>
       <c r="AL135" s="3">
-        <v>45872.91666666666</v>
+        <v>45872.85416666666</v>
       </c>
     </row>
     <row r="136" spans="1:38">
@@ -17227,7 +17227,7 @@
         <v>74</v>
       </c>
       <c r="C136" t="s">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="D136" t="s">
         <v>119</v>

--- a/jogos_2025-08-03.xlsx
+++ b/jogos_2025-08-03.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="395">
   <si>
     <t>Date</t>
   </si>
@@ -256,15 +256,18 @@
     <t>Austria 2. Liga</t>
   </si>
   <si>
+    <t>Japan J2 League</t>
+  </si>
+  <si>
     <t>Ukraine Ukrainian Premier League</t>
   </si>
   <si>
-    <t>Japan J2 League</t>
-  </si>
-  <si>
     <t>Russia Russian Premier League</t>
   </si>
   <si>
+    <t>Belarus Vysheyshaya Liga</t>
+  </si>
+  <si>
     <t>China China League One</t>
   </si>
   <si>
@@ -274,54 +277,51 @@
     <t>China Chinese Super League</t>
   </si>
   <si>
-    <t>Belarus Vysheyshaya Liga</t>
+    <t>Germany 2. Bundesliga</t>
+  </si>
+  <si>
+    <t>Germany 3. Liga</t>
   </si>
   <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
-    <t>Germany 2. Bundesliga</t>
-  </si>
-  <si>
-    <t>Germany 3. Liga</t>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
+    <t>Denmark Superliga</t>
   </si>
   <si>
     <t>Switzerland Super League</t>
   </si>
   <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
     <t>Switzerland Challenge League</t>
   </si>
   <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
-    <t>Norway Eliteserien</t>
-  </si>
-  <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
+    <t>Finland Veikkausliiga</t>
+  </si>
+  <si>
+    <t>Czech Republic First League</t>
+  </si>
+  <si>
     <t>Norway First Division</t>
   </si>
   <si>
-    <t>Finland Veikkausliiga</t>
+    <t>Scotland Premiership</t>
   </si>
   <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
-    <t>Scotland Premiership</t>
-  </si>
-  <si>
-    <t>Czech Republic First League</t>
-  </si>
-  <si>
     <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
@@ -334,13 +334,16 @@
     <t>Montenegro Montenegrin First League</t>
   </si>
   <si>
+    <t>Uzbekistan Uzbekistan Super League</t>
+  </si>
+  <si>
     <t>Slovakia Super Liga</t>
   </si>
   <si>
     <t>Austria Bundesliga</t>
   </si>
   <si>
-    <t>Uzbekistan Uzbekistan Super League</t>
+    <t>Hungary NB II</t>
   </si>
   <si>
     <t>Romania Liga I</t>
@@ -349,18 +352,15 @@
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
-    <t>Hungary NB II</t>
-  </si>
-  <si>
     <t>Hungary NB I</t>
   </si>
   <si>
+    <t>USA NWSL</t>
+  </si>
+  <si>
     <t>Chile Primera División</t>
   </si>
   <si>
-    <t>USA NWSL</t>
-  </si>
-  <si>
     <t>Serbia SuperLiga</t>
   </si>
   <si>
@@ -382,6 +382,9 @@
     <t>Portland Timbers II</t>
   </si>
   <si>
+    <t>Blacktown City</t>
+  </si>
+  <si>
     <t>Central Coast II</t>
   </si>
   <si>
@@ -391,30 +394,30 @@
     <t>Sydney United</t>
   </si>
   <si>
-    <t>Blacktown City</t>
-  </si>
-  <si>
     <t>SKA Khabarovsk</t>
   </si>
   <si>
+    <t>Viktoria Žižkov</t>
+  </si>
+  <si>
     <t>Slavia Praha II</t>
   </si>
   <si>
-    <t>Viktoria Žižkov</t>
-  </si>
-  <si>
     <t>WSPG Wels</t>
   </si>
   <si>
+    <t>Roasso Kumamoto</t>
+  </si>
+  <si>
     <t>Kudrivka</t>
   </si>
   <si>
-    <t>Roasso Kumamoto</t>
-  </si>
-  <si>
     <t>Akron</t>
   </si>
   <si>
+    <t>Molodechno-DYuSSh 4</t>
+  </si>
+  <si>
     <t>Suzhou Dongwu</t>
   </si>
   <si>
@@ -424,135 +427,132 @@
     <t>Dalian Zhixing</t>
   </si>
   <si>
-    <t>Molodechno-DYuSSh 4</t>
+    <t>Magdeburg</t>
+  </si>
+  <si>
+    <t>Erzgebirge Aue</t>
+  </si>
+  <si>
+    <t>Hannover 96</t>
+  </si>
+  <si>
+    <t>Qingdao Red Lions</t>
+  </si>
+  <si>
+    <t>Dongguan United</t>
   </si>
   <si>
     <t>KRC Genk</t>
   </si>
   <si>
-    <t>Magdeburg</t>
-  </si>
-  <si>
-    <t>Hannover 96</t>
-  </si>
-  <si>
-    <t>Erzgebirge Aue</t>
-  </si>
-  <si>
-    <t>Dongguan United</t>
-  </si>
-  <si>
-    <t>Qingdao Red Lions</t>
-  </si>
-  <si>
     <t>Greuther Fürth</t>
   </si>
   <si>
+    <t>Beijing Guoan</t>
+  </si>
+  <si>
     <t>Wuhan Three Towns</t>
   </si>
   <si>
-    <t>Beijing Guoan</t>
-  </si>
-  <si>
     <t>Sichuan Jiuniu</t>
   </si>
   <si>
+    <t>Djurgården</t>
+  </si>
+  <si>
+    <t>Häcken</t>
+  </si>
+  <si>
+    <t>Randers</t>
+  </si>
+  <si>
+    <t>SønderjyskE</t>
+  </si>
+  <si>
     <t>Thun</t>
   </si>
   <si>
-    <t>Häcken</t>
-  </si>
-  <si>
-    <t>SønderjyskE</t>
-  </si>
-  <si>
-    <t>Randers</t>
-  </si>
-  <si>
     <t>Spartak Kostroma</t>
   </si>
   <si>
-    <t>Djurgården</t>
-  </si>
-  <si>
     <t>Yverdon Sport</t>
   </si>
   <si>
+    <t>Baník Ostrava II</t>
+  </si>
+  <si>
+    <t>HamKam</t>
+  </si>
+  <si>
     <t>Śląsk Wrocław</t>
   </si>
   <si>
-    <t>HamKam</t>
-  </si>
-  <si>
     <t>Epitsentr Dunayivtsi</t>
   </si>
   <si>
-    <t>Baník Ostrava II</t>
-  </si>
-  <si>
     <t>Baltika</t>
   </si>
   <si>
     <t>Cracovia Kraków</t>
   </si>
   <si>
+    <t>SJK</t>
+  </si>
+  <si>
+    <t>Slovácko</t>
+  </si>
+  <si>
     <t>Sogndal</t>
   </si>
   <si>
-    <t>SJK</t>
+    <t>Falkirk</t>
   </si>
   <si>
     <t>Landskrona</t>
   </si>
   <si>
-    <t>Falkirk</t>
-  </si>
-  <si>
-    <t>Slovácko</t>
-  </si>
-  <si>
     <t>Suduroy</t>
   </si>
   <si>
+    <t>Hostert</t>
+  </si>
+  <si>
+    <t>Dundee</t>
+  </si>
+  <si>
+    <t>F91 Dudelange</t>
+  </si>
+  <si>
     <t>Mondorf-les-Bains</t>
   </si>
   <si>
-    <t>Hostert</t>
-  </si>
-  <si>
-    <t>F91 Dudelange</t>
+    <t>AGF</t>
+  </si>
+  <si>
+    <t>EB - Streymur</t>
+  </si>
+  <si>
+    <t>Cercle Brugge</t>
+  </si>
+  <si>
+    <t>Differdange 03</t>
+  </si>
+  <si>
+    <t>Harju Jalgpallikool</t>
   </si>
   <si>
     <t>Jeunesse Canach</t>
   </si>
   <si>
-    <t>Differdange 03</t>
+    <t>Swift Hesperange</t>
+  </si>
+  <si>
+    <t>Rodange</t>
   </si>
   <si>
     <t>Jeunesse d'Esch</t>
   </si>
   <si>
-    <t>Swift Hesperange</t>
-  </si>
-  <si>
-    <t>Dundee</t>
-  </si>
-  <si>
-    <t>EB - Streymur</t>
-  </si>
-  <si>
-    <t>Harju Jalgpallikool</t>
-  </si>
-  <si>
-    <t>Cercle Brugge</t>
-  </si>
-  <si>
-    <t>AGF</t>
-  </si>
-  <si>
-    <t>Rodange</t>
-  </si>
-  <si>
     <t>Luzern</t>
   </si>
   <si>
@@ -565,165 +565,168 @@
     <t>Sirius</t>
   </si>
   <si>
+    <t>Vlašim</t>
+  </si>
+  <si>
+    <t>FK Jezero Plav</t>
+  </si>
+  <si>
+    <t>Arsenal Tivat</t>
+  </si>
+  <si>
+    <t>Shortan</t>
+  </si>
+  <si>
+    <t>Zenit</t>
+  </si>
+  <si>
+    <t>Trenčín</t>
+  </si>
+  <si>
+    <t>Torpedo BelAZ</t>
+  </si>
+  <si>
+    <t>Grazer AK</t>
+  </si>
+  <si>
+    <t>Rapid Wien</t>
+  </si>
+  <si>
+    <t>Pogoń Siedlce</t>
+  </si>
+  <si>
+    <t>KFUM</t>
+  </si>
+  <si>
     <t>Petrovac</t>
   </si>
   <si>
+    <t>Sutjeska</t>
+  </si>
+  <si>
+    <t>Kecskeméti TE</t>
+  </si>
+  <si>
+    <t>Strømsgodset</t>
+  </si>
+  <si>
     <t>Karpaty</t>
   </si>
   <si>
-    <t>Sutjeska</t>
-  </si>
-  <si>
-    <t>Zenit</t>
+    <t>Dečić</t>
+  </si>
+  <si>
+    <t>Dukla Praha</t>
+  </si>
+  <si>
+    <t>Rubin Kazan</t>
   </si>
   <si>
     <t>Vålerenga</t>
   </si>
   <si>
-    <t>Pogoń Siedlce</t>
-  </si>
-  <si>
-    <t>Arsenal Tivat</t>
-  </si>
-  <si>
-    <t>Trenčín</t>
-  </si>
-  <si>
-    <t>Dečić</t>
-  </si>
-  <si>
-    <t>FK Jezero Plav</t>
-  </si>
-  <si>
-    <t>Rapid Wien</t>
-  </si>
-  <si>
-    <t>Dukla Praha</t>
-  </si>
-  <si>
-    <t>Strømsgodset</t>
-  </si>
-  <si>
-    <t>Grazer AK</t>
-  </si>
-  <si>
-    <t>Torpedo BelAZ</t>
-  </si>
-  <si>
     <t>Molde</t>
   </si>
   <si>
-    <t>KFUM</t>
-  </si>
-  <si>
-    <t>Rubin Kazan</t>
-  </si>
-  <si>
-    <t>Vlašim</t>
-  </si>
-  <si>
-    <t>Shortan</t>
+    <t>Szentlőrinc SE</t>
+  </si>
+  <si>
+    <t>Hermannstadt</t>
+  </si>
+  <si>
+    <t>Motor Lublin</t>
   </si>
   <si>
     <t>Radomiak Radom</t>
   </si>
   <si>
+    <t>Maribor</t>
+  </si>
+  <si>
+    <t>Karcag SE</t>
+  </si>
+  <si>
     <t>Celtic</t>
   </si>
   <si>
-    <t>Hermannstadt</t>
-  </si>
-  <si>
-    <t>Maribor</t>
-  </si>
-  <si>
-    <t>Motor Lublin</t>
-  </si>
-  <si>
-    <t>Karcag SE</t>
-  </si>
-  <si>
-    <t>Szentlőrinc SE</t>
+    <t>Puskás</t>
   </si>
   <si>
     <t>Várda SE</t>
   </si>
   <si>
-    <t>Puskás</t>
-  </si>
-  <si>
     <t>Fakel</t>
   </si>
   <si>
+    <t>FK Chernomorets Novorossiysk</t>
+  </si>
+  <si>
+    <t>Brøndby</t>
+  </si>
+  <si>
+    <t>Tammeka</t>
+  </si>
+  <si>
     <t>Vysočina Jihlava</t>
   </si>
   <si>
-    <t>Brøndby</t>
-  </si>
-  <si>
-    <t>FK Chernomorets Novorossiysk</t>
-  </si>
-  <si>
-    <t>Tammeka</t>
-  </si>
-  <si>
     <t>B68</t>
   </si>
   <si>
     <t>Union Saint-Gilloise</t>
   </si>
   <si>
+    <t>Washington Spirit</t>
+  </si>
+  <si>
     <t>O'Higgins</t>
   </si>
   <si>
-    <t>Washington Spirit</t>
-  </si>
-  <si>
     <t>Sporting KC II</t>
   </si>
   <si>
+    <t>MKK-Dnepr</t>
+  </si>
+  <si>
+    <t>Békéscsaba</t>
+  </si>
+  <si>
     <t>Železničar Pančevo</t>
   </si>
   <si>
     <t>Žilina</t>
   </si>
   <si>
-    <t>MKK-Dnepr</t>
+    <t>Ajka</t>
   </si>
   <si>
     <t>Csákvári TK</t>
   </si>
   <si>
+    <t>Tiszakécske</t>
+  </si>
+  <si>
     <t>Honvéd W</t>
   </si>
   <si>
-    <t>Békéscsaba</t>
-  </si>
-  <si>
-    <t>Tiszakécske</t>
-  </si>
-  <si>
-    <t>Ajka</t>
-  </si>
-  <si>
     <t>Sporting Charleroi</t>
   </si>
   <si>
+    <t>Makhachkala</t>
+  </si>
+  <si>
+    <t>Górnik Łęczna</t>
+  </si>
+  <si>
     <t>Wehen Wiesbaden</t>
   </si>
   <si>
-    <t>Makhachkala</t>
-  </si>
-  <si>
-    <t>Górnik Łęczna</t>
+    <t>Győri ETO</t>
   </si>
   <si>
     <t>Chicago Fire II</t>
   </si>
   <si>
-    <t>Győri ETO</t>
-  </si>
-  <si>
     <t>Pardubice</t>
   </si>
   <si>
@@ -739,33 +742,33 @@
     <t>Botafogo</t>
   </si>
   <si>
+    <t>Corinthians</t>
+  </si>
+  <si>
+    <t>Chapecoense</t>
+  </si>
+  <si>
     <t>Colo-Colo</t>
   </si>
   <si>
     <t>Partizan</t>
   </si>
   <si>
-    <t>Corinthians</t>
-  </si>
-  <si>
-    <t>Chapecoense</t>
-  </si>
-  <si>
     <t>Atlético Ottawa</t>
   </si>
   <si>
+    <t>Ceará</t>
+  </si>
+  <si>
     <t>Atlético Mineiro</t>
   </si>
   <si>
-    <t>Ceará</t>
+    <t>Atlético PR</t>
   </si>
   <si>
     <t>Ñublense</t>
   </si>
   <si>
-    <t>Atlético PR</t>
-  </si>
-  <si>
     <t>Orlando Pride</t>
   </si>
   <si>
@@ -787,6 +790,9 @@
     <t>Real Monarchs</t>
   </si>
   <si>
+    <t>Mt Druitt Town</t>
+  </si>
+  <si>
     <t>Marconi Stallions</t>
   </si>
   <si>
@@ -796,30 +802,30 @@
     <t>St. George Saints</t>
   </si>
   <si>
-    <t>Mt Druitt Town</t>
-  </si>
-  <si>
     <t>Torpedo Moskva</t>
   </si>
   <si>
+    <t>Prostějov</t>
+  </si>
+  <si>
     <t>České Budějovice</t>
   </si>
   <si>
-    <t>Prostějov</t>
-  </si>
-  <si>
     <t>Floridsdorfer AC</t>
   </si>
   <si>
+    <t>Mito Hollyhock</t>
+  </si>
+  <si>
     <t>Oleksandria</t>
   </si>
   <si>
-    <t>Mito Hollyhock</t>
-  </si>
-  <si>
     <t>Spartak Moskva</t>
   </si>
   <si>
+    <t>Neman Grodno</t>
+  </si>
+  <si>
     <t>Dalian Huayi</t>
   </si>
   <si>
@@ -829,135 +835,132 @@
     <t>Qingdao Jonoon</t>
   </si>
   <si>
-    <t>Neman Grodno</t>
+    <t>Eintracht Braunschweig</t>
+  </si>
+  <si>
+    <t>Hansa Rostock</t>
+  </si>
+  <si>
+    <t>Kaiserslautern</t>
+  </si>
+  <si>
+    <t>Heilongjiang Lava Spring</t>
+  </si>
+  <si>
+    <t>Nantong Zhiyun</t>
   </si>
   <si>
     <t>Royal Antwerp FC</t>
   </si>
   <si>
-    <t>Eintracht Braunschweig</t>
-  </si>
-  <si>
-    <t>Kaiserslautern</t>
-  </si>
-  <si>
-    <t>Hansa Rostock</t>
-  </si>
-  <si>
-    <t>Nantong Zhiyun</t>
-  </si>
-  <si>
-    <t>Heilongjiang Lava Spring</t>
-  </si>
-  <si>
     <t>Dynamo Dresden</t>
   </si>
   <si>
+    <t>Tianjin Teda</t>
+  </si>
+  <si>
     <t>Changchun Yatai</t>
   </si>
   <si>
-    <t>Tianjin Teda</t>
-  </si>
-  <si>
     <t>Zhejiang FC</t>
   </si>
   <si>
+    <t>Halmstad</t>
+  </si>
+  <si>
+    <t>Elfsborg</t>
+  </si>
+  <si>
+    <t>Silkeborg</t>
+  </si>
+  <si>
+    <t>Nordsjælland</t>
+  </si>
+  <si>
     <t>Lausanne Sport</t>
   </si>
   <si>
-    <t>Elfsborg</t>
-  </si>
-  <si>
-    <t>Nordsjælland</t>
-  </si>
-  <si>
-    <t>Silkeborg</t>
-  </si>
-  <si>
     <t>Neftekhimik</t>
   </si>
   <si>
-    <t>Halmstad</t>
-  </si>
-  <si>
     <t>Stade Lausanne-Ouchy</t>
   </si>
   <si>
+    <t>Líšeň</t>
+  </si>
+  <si>
+    <t>FK Bodo - Glimt</t>
+  </si>
+  <si>
     <t>Ruch Chorzów</t>
   </si>
   <si>
-    <t>FK Bodo - Glimt</t>
-  </si>
-  <si>
     <t>Shakhtar Donetsk</t>
   </si>
   <si>
-    <t>Líšeň</t>
-  </si>
-  <si>
     <t>Orenburg</t>
   </si>
   <si>
     <t>Lechia Gdańsk</t>
   </si>
   <si>
+    <t>KTP</t>
+  </si>
+  <si>
+    <t>Slavia Praha</t>
+  </si>
+  <si>
     <t>Skeid</t>
   </si>
   <si>
-    <t>KTP</t>
+    <t>Dundee United</t>
   </si>
   <si>
     <t>Västerås SK</t>
   </si>
   <si>
-    <t>Dundee United</t>
-  </si>
-  <si>
-    <t>Slavia Praha</t>
-  </si>
-  <si>
     <t>HB</t>
   </si>
   <si>
+    <t>Victoria Rosport</t>
+  </si>
+  <si>
+    <t>Hibernian</t>
+  </si>
+  <si>
+    <t>Progrès Niederkorn</t>
+  </si>
+  <si>
     <t>UNA Strassen</t>
   </si>
   <si>
-    <t>Victoria Rosport</t>
-  </si>
-  <si>
-    <t>Progrès Niederkorn</t>
+    <t>Midtjylland</t>
+  </si>
+  <si>
+    <t>KÍ</t>
+  </si>
+  <si>
+    <t>RSC Anderlecht</t>
+  </si>
+  <si>
+    <t>Atert Bissen</t>
+  </si>
+  <si>
+    <t>Paide</t>
   </si>
   <si>
     <t>Mamer</t>
   </si>
   <si>
-    <t>Atert Bissen</t>
+    <t>UT Pétange</t>
+  </si>
+  <si>
+    <t>Racing</t>
   </si>
   <si>
     <t>UN Käerjéng</t>
   </si>
   <si>
-    <t>UT Pétange</t>
-  </si>
-  <si>
-    <t>Hibernian</t>
-  </si>
-  <si>
-    <t>KÍ</t>
-  </si>
-  <si>
-    <t>Paide</t>
-  </si>
-  <si>
-    <t>RSC Anderlecht</t>
-  </si>
-  <si>
-    <t>Midtjylland</t>
-  </si>
-  <si>
-    <t>Racing</t>
-  </si>
-  <si>
     <t>Zürich</t>
   </si>
   <si>
@@ -970,165 +973,168 @@
     <t>Öster</t>
   </si>
   <si>
+    <t>Hanácká</t>
+  </si>
+  <si>
+    <t>Budućnost</t>
+  </si>
+  <si>
+    <t>Jedinstvo</t>
+  </si>
+  <si>
+    <t>Xorazm</t>
+  </si>
+  <si>
+    <t>CSKA Moskva</t>
+  </si>
+  <si>
+    <t>Spartak Trnava</t>
+  </si>
+  <si>
+    <t>Gomel</t>
+  </si>
+  <si>
+    <t>Austria Wien</t>
+  </si>
+  <si>
+    <t>Blau-Weiß Linz</t>
+  </si>
+  <si>
+    <t>Odra Opole</t>
+  </si>
+  <si>
+    <t>Rosenborg</t>
+  </si>
+  <si>
     <t>Bokelj</t>
   </si>
   <si>
+    <t>Mornar</t>
+  </si>
+  <si>
+    <t>Vasas</t>
+  </si>
+  <si>
+    <t>Haugesund</t>
+  </si>
+  <si>
     <t>Polessya</t>
   </si>
   <si>
-    <t>Mornar</t>
-  </si>
-  <si>
-    <t>CSKA Moskva</t>
+    <t>Mladost DG</t>
+  </si>
+  <si>
+    <t>Baník Ostrava</t>
+  </si>
+  <si>
+    <t>FK Sochi</t>
   </si>
   <si>
     <t>Sandefjord</t>
   </si>
   <si>
-    <t>Odra Opole</t>
-  </si>
-  <si>
-    <t>Jedinstvo</t>
-  </si>
-  <si>
-    <t>Spartak Trnava</t>
-  </si>
-  <si>
-    <t>Mladost DG</t>
-  </si>
-  <si>
-    <t>Budućnost</t>
-  </si>
-  <si>
-    <t>Blau-Weiß Linz</t>
-  </si>
-  <si>
-    <t>Baník Ostrava</t>
-  </si>
-  <si>
-    <t>Haugesund</t>
-  </si>
-  <si>
-    <t>Austria Wien</t>
-  </si>
-  <si>
-    <t>Gomel</t>
-  </si>
-  <si>
     <t>Bryne</t>
   </si>
   <si>
-    <t>Rosenborg</t>
-  </si>
-  <si>
-    <t>FK Sochi</t>
-  </si>
-  <si>
-    <t>Hanácká</t>
-  </si>
-  <si>
-    <t>Xorazm</t>
+    <t>Kozármisleny</t>
+  </si>
+  <si>
+    <t>Universitatea Cluj</t>
+  </si>
+  <si>
+    <t>Jagiellonia Białystok</t>
   </si>
   <si>
     <t>Raków Częstochowa</t>
   </si>
   <si>
+    <t>Koper</t>
+  </si>
+  <si>
+    <t>Soroksár SC</t>
+  </si>
+  <si>
     <t>St. Mirren</t>
   </si>
   <si>
-    <t>Universitatea Cluj</t>
-  </si>
-  <si>
-    <t>Koper</t>
-  </si>
-  <si>
-    <t>Jagiellonia Białystok</t>
-  </si>
-  <si>
-    <t>Soroksár SC</t>
-  </si>
-  <si>
-    <t>Kozármisleny</t>
+    <t>Nyíregyháza Spartacus</t>
   </si>
   <si>
     <t>Paksi SE</t>
   </si>
   <si>
-    <t>Nyíregyháza Spartacus</t>
-  </si>
-  <si>
     <t>Sokol Saratov</t>
   </si>
   <si>
+    <t>Arsenal Tula</t>
+  </si>
+  <si>
+    <t>Viborg</t>
+  </si>
+  <si>
+    <t>Nõmme Kalju</t>
+  </si>
+  <si>
     <t>Vyškov</t>
   </si>
   <si>
-    <t>Viborg</t>
-  </si>
-  <si>
-    <t>Arsenal Tula</t>
-  </si>
-  <si>
-    <t>Nõmme Kalju</t>
-  </si>
-  <si>
     <t>NSÍ</t>
   </si>
   <si>
     <t>OH Leuven</t>
   </si>
   <si>
+    <t>Portland Thorns</t>
+  </si>
+  <si>
     <t>Unión La Calera</t>
   </si>
   <si>
-    <t>Portland Thorns</t>
-  </si>
-  <si>
     <t>Austin II</t>
   </si>
   <si>
+    <t>Slutsk</t>
+  </si>
+  <si>
+    <t>Szeged 2011</t>
+  </si>
+  <si>
     <t>Napredak</t>
   </si>
   <si>
     <t>Tatran Prešov</t>
   </si>
   <si>
-    <t>Slutsk</t>
+    <t>Videoton</t>
   </si>
   <si>
     <t>BVSC</t>
   </si>
   <si>
+    <t>Mezőkövesd-Zsóry</t>
+  </si>
+  <si>
     <t>Budafoki MTE</t>
   </si>
   <si>
-    <t>Szeged 2011</t>
-  </si>
-  <si>
-    <t>Mezőkövesd-Zsóry</t>
-  </si>
-  <si>
-    <t>Videoton</t>
-  </si>
-  <si>
     <t>Sint-Truiden</t>
   </si>
   <si>
+    <t>Akhmat Grozny</t>
+  </si>
+  <si>
+    <t>Puszcza Niepołomice</t>
+  </si>
+  <si>
     <t>Ulm</t>
   </si>
   <si>
-    <t>Akhmat Grozny</t>
-  </si>
-  <si>
-    <t>Puszcza Niepołomice</t>
+    <t>Újpest</t>
   </si>
   <si>
     <t>Columbus Crew II</t>
   </si>
   <si>
-    <t>Újpest</t>
-  </si>
-  <si>
     <t>Sparta Praha</t>
   </si>
   <si>
@@ -1144,31 +1150,31 @@
     <t>Cruzeiro</t>
   </si>
   <si>
+    <t>Fortaleza</t>
+  </si>
+  <si>
+    <t>CRB</t>
+  </si>
+  <si>
     <t>Huachipato</t>
   </si>
   <si>
     <t>Radnički Kragujevac</t>
   </si>
   <si>
-    <t>Fortaleza</t>
-  </si>
-  <si>
-    <t>CRB</t>
-  </si>
-  <si>
     <t>York9 FC</t>
   </si>
   <si>
+    <t>Flamengo</t>
+  </si>
+  <si>
     <t>Bragantino</t>
   </si>
   <si>
-    <t>Flamengo</t>
+    <t>Paysandu</t>
   </si>
   <si>
     <t>Everton</t>
-  </si>
-  <si>
-    <t>Paysandu</t>
   </si>
   <si>
     <t>Utah Royals</t>
@@ -1556,7 +1562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL136"/>
+  <dimension ref="A1:AL137"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:38">
@@ -1692,7 +1698,7 @@
         <v>121</v>
       </c>
       <c r="F2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1707,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -1782,10 +1788,10 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL2" s="3">
         <v>45872</v>
@@ -1808,7 +1814,7 @@
         <v>122</v>
       </c>
       <c r="F3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1823,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -1898,10 +1904,10 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK3" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL3" s="3">
         <v>45872.08333333334</v>
@@ -1924,7 +1930,7 @@
         <v>123</v>
       </c>
       <c r="F4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1939,7 +1945,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -2014,10 +2020,10 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK4" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL4" s="3">
         <v>45872.08333333334</v>
@@ -2040,7 +2046,7 @@
         <v>124</v>
       </c>
       <c r="F5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -2055,7 +2061,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -2130,10 +2136,10 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK5" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL5" s="3">
         <v>45872.08333333334</v>
@@ -2156,7 +2162,7 @@
         <v>125</v>
       </c>
       <c r="F6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -2171,7 +2177,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -2246,10 +2252,10 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL6" s="3">
         <v>45872.08333333334</v>
@@ -2272,7 +2278,7 @@
         <v>126</v>
       </c>
       <c r="F7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -2287,7 +2293,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2362,10 +2368,10 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK7" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL7" s="3">
         <v>45872.1875</v>
@@ -2388,7 +2394,7 @@
         <v>127</v>
       </c>
       <c r="F8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2403,7 +2409,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2478,10 +2484,10 @@
         <v>0</v>
       </c>
       <c r="AJ8" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK8" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL8" s="3">
         <v>45872.21875</v>
@@ -2504,7 +2510,7 @@
         <v>128</v>
       </c>
       <c r="F9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2519,7 +2525,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -2594,10 +2600,10 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK9" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL9" s="3">
         <v>45872.21875</v>
@@ -2620,7 +2626,7 @@
         <v>129</v>
       </c>
       <c r="F10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2635,7 +2641,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -2710,10 +2716,10 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK10" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL10" s="3">
         <v>45872.22916666666</v>
@@ -2730,13 +2736,13 @@
         <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E11" t="s">
         <v>130</v>
       </c>
       <c r="F11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2751,16 +2757,16 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L11">
-        <v>5.4</v>
+        <v>3.15</v>
       </c>
       <c r="M11">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N11">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -2796,16 +2802,16 @@
         <v>0</v>
       </c>
       <c r="Z11">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD11">
         <v>0</v>
@@ -2826,10 +2832,10 @@
         <v>0</v>
       </c>
       <c r="AJ11" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK11" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL11" s="3">
         <v>45872.29166666666</v>
@@ -2846,13 +2852,13 @@
         <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E12" t="s">
         <v>131</v>
       </c>
       <c r="F12" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2867,16 +2873,16 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L12">
-        <v>3.15</v>
+        <v>5.4</v>
       </c>
       <c r="M12">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N12">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -2912,16 +2918,16 @@
         <v>0</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB12">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC12">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD12">
         <v>0</v>
@@ -2942,10 +2948,10 @@
         <v>0</v>
       </c>
       <c r="AJ12" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK12" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL12" s="3">
         <v>45872.29166666666</v>
@@ -2968,7 +2974,7 @@
         <v>132</v>
       </c>
       <c r="F13" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2983,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L13">
         <v>5.45</v>
@@ -3058,10 +3064,10 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK13" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL13" s="3">
         <v>45872.3125</v>
@@ -3084,7 +3090,7 @@
         <v>133</v>
       </c>
       <c r="F14" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -3099,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -3174,10 +3180,10 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK14" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL14" s="3">
         <v>45872.33333333334</v>
@@ -3194,13 +3200,13 @@
         <v>84</v>
       </c>
       <c r="D15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E15" t="s">
         <v>134</v>
       </c>
       <c r="F15" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -3215,16 +3221,16 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L15">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M15">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N15">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -3266,10 +3272,10 @@
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD15">
         <v>0</v>
@@ -3290,10 +3296,10 @@
         <v>0</v>
       </c>
       <c r="AJ15" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK15" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL15" s="3">
         <v>45872.33333333334</v>
@@ -3310,13 +3316,13 @@
         <v>85</v>
       </c>
       <c r="D16" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E16" t="s">
         <v>135</v>
       </c>
       <c r="F16" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -3331,16 +3337,16 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O16">
         <v>0</v>
@@ -3382,10 +3388,10 @@
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD16">
         <v>0</v>
@@ -3406,10 +3412,10 @@
         <v>0</v>
       </c>
       <c r="AJ16" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK16" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL16" s="3">
         <v>45872.33333333334</v>
@@ -3432,7 +3438,7 @@
         <v>136</v>
       </c>
       <c r="F17" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -3447,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -3522,10 +3528,10 @@
         <v>0</v>
       </c>
       <c r="AJ17" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK17" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL17" s="3">
         <v>45872.33333333334</v>
@@ -3548,7 +3554,7 @@
         <v>137</v>
       </c>
       <c r="F18" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -3563,16 +3569,16 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L18">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="M18">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="N18">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -3614,16 +3620,16 @@
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD18">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE18">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF18">
         <v>0</v>
@@ -3638,10 +3644,10 @@
         <v>0</v>
       </c>
       <c r="AJ18" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK18" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL18" s="3">
         <v>45872.35416666666</v>
@@ -3664,7 +3670,7 @@
         <v>138</v>
       </c>
       <c r="F19" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -3679,16 +3685,16 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L19">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M19">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N19">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -3730,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC19">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD19">
         <v>0</v>
@@ -3754,10 +3760,10 @@
         <v>0</v>
       </c>
       <c r="AJ19" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK19" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL19" s="3">
         <v>45872.35416666666</v>
@@ -3771,7 +3777,7 @@
         <v>46</v>
       </c>
       <c r="C20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D20" t="s">
         <v>120</v>
@@ -3780,7 +3786,7 @@
         <v>139</v>
       </c>
       <c r="F20" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -3795,7 +3801,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L20">
         <v>1.71</v>
@@ -3870,10 +3876,10 @@
         <v>0</v>
       </c>
       <c r="AJ20" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK20" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL20" s="3">
         <v>45872.35416666666</v>
@@ -3887,16 +3893,16 @@
         <v>46</v>
       </c>
       <c r="C21" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D21" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E21" t="s">
         <v>140</v>
       </c>
       <c r="F21" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3911,7 +3917,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -3986,10 +3992,10 @@
         <v>0</v>
       </c>
       <c r="AJ21" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK21" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL21" s="3">
         <v>45872.35416666666</v>
@@ -4003,7 +4009,7 @@
         <v>46</v>
       </c>
       <c r="C22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D22" t="s">
         <v>119</v>
@@ -4012,7 +4018,7 @@
         <v>141</v>
       </c>
       <c r="F22" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -4027,7 +4033,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -4102,10 +4108,10 @@
         <v>0</v>
       </c>
       <c r="AJ22" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK22" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL22" s="3">
         <v>45872.35416666666</v>
@@ -4119,16 +4125,16 @@
         <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D23" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E23" t="s">
         <v>142</v>
       </c>
       <c r="F23" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -4143,16 +4149,16 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O23">
         <v>0</v>
@@ -4200,10 +4206,10 @@
         <v>0</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF23">
         <v>0</v>
@@ -4218,10 +4224,10 @@
         <v>0</v>
       </c>
       <c r="AJ23" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK23" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL23" s="3">
         <v>45872.35416666666</v>
@@ -4235,7 +4241,7 @@
         <v>46</v>
       </c>
       <c r="C24" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D24" t="s">
         <v>120</v>
@@ -4244,7 +4250,7 @@
         <v>143</v>
       </c>
       <c r="F24" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -4259,7 +4265,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L24">
         <v>2.26</v>
@@ -4334,10 +4340,10 @@
         <v>0</v>
       </c>
       <c r="AJ24" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK24" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL24" s="3">
         <v>45872.35416666666</v>
@@ -4351,7 +4357,7 @@
         <v>47</v>
       </c>
       <c r="C25" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D25" t="s">
         <v>119</v>
@@ -4360,7 +4366,7 @@
         <v>144</v>
       </c>
       <c r="F25" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -4375,16 +4381,16 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L25">
-        <v>1.64</v>
+        <v>1.39</v>
       </c>
       <c r="M25">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="N25">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="O25">
         <v>0</v>
@@ -4426,10 +4432,10 @@
         <v>0</v>
       </c>
       <c r="AB25">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AC25">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AD25">
         <v>0</v>
@@ -4450,10 +4456,10 @@
         <v>0</v>
       </c>
       <c r="AJ25" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK25" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL25" s="3">
         <v>45872.35763888889</v>
@@ -4467,7 +4473,7 @@
         <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D26" t="s">
         <v>119</v>
@@ -4476,7 +4482,7 @@
         <v>145</v>
       </c>
       <c r="F26" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -4491,16 +4497,16 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L26">
-        <v>1.39</v>
+        <v>1.64</v>
       </c>
       <c r="M26">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="N26">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -4542,10 +4548,10 @@
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AC26">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AD26">
         <v>0</v>
@@ -4566,10 +4572,10 @@
         <v>0</v>
       </c>
       <c r="AJ26" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK26" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL26" s="3">
         <v>45872.35763888889</v>
@@ -4583,7 +4589,7 @@
         <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D27" t="s">
         <v>119</v>
@@ -4592,7 +4598,7 @@
         <v>146</v>
       </c>
       <c r="F27" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -4607,7 +4613,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -4682,10 +4688,10 @@
         <v>0</v>
       </c>
       <c r="AJ27" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK27" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL27" s="3">
         <v>45872.375</v>
@@ -4702,13 +4708,13 @@
         <v>90</v>
       </c>
       <c r="D28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E28" t="s">
         <v>147</v>
       </c>
       <c r="F28" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -4723,16 +4729,16 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L28">
-        <v>3.15</v>
+        <v>1.33</v>
       </c>
       <c r="M28">
-        <v>3.35</v>
+        <v>5</v>
       </c>
       <c r="N28">
-        <v>2.17</v>
+        <v>8</v>
       </c>
       <c r="O28">
         <v>0</v>
@@ -4774,10 +4780,10 @@
         <v>0</v>
       </c>
       <c r="AB28">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC28">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="AD28">
         <v>0</v>
@@ -4798,10 +4804,10 @@
         <v>0</v>
       </c>
       <c r="AJ28" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK28" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL28" s="3">
         <v>45872.375</v>
@@ -4815,7 +4821,7 @@
         <v>48</v>
       </c>
       <c r="C29" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D29" t="s">
         <v>119</v>
@@ -4824,7 +4830,7 @@
         <v>148</v>
       </c>
       <c r="F29" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -4839,7 +4845,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -4914,10 +4920,10 @@
         <v>0</v>
       </c>
       <c r="AJ29" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK29" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL29" s="3">
         <v>45872.375</v>
@@ -4931,7 +4937,7 @@
         <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D30" t="s">
         <v>120</v>
@@ -4940,7 +4946,7 @@
         <v>149</v>
       </c>
       <c r="F30" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -4955,7 +4961,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -5030,10 +5036,10 @@
         <v>0</v>
       </c>
       <c r="AJ30" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK30" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL30" s="3">
         <v>45872.375</v>
@@ -5047,7 +5053,7 @@
         <v>48</v>
       </c>
       <c r="C31" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D31" t="s">
         <v>120</v>
@@ -5056,7 +5062,7 @@
         <v>150</v>
       </c>
       <c r="F31" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -5071,7 +5077,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -5146,10 +5152,10 @@
         <v>0</v>
       </c>
       <c r="AJ31" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK31" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL31" s="3">
         <v>45872.375</v>
@@ -5163,7 +5169,7 @@
         <v>48</v>
       </c>
       <c r="C32" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="D32" t="s">
         <v>120</v>
@@ -5172,7 +5178,7 @@
         <v>151</v>
       </c>
       <c r="F32" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -5187,16 +5193,16 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O32">
         <v>0</v>
@@ -5238,10 +5244,10 @@
         <v>0</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD32">
         <v>0</v>
@@ -5262,10 +5268,10 @@
         <v>0</v>
       </c>
       <c r="AJ32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK32" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL32" s="3">
         <v>45872.375</v>
@@ -5279,16 +5285,16 @@
         <v>48</v>
       </c>
       <c r="C33" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="D33" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E33" t="s">
         <v>152</v>
       </c>
       <c r="F33" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -5303,16 +5309,16 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L33">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M33">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N33">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -5354,10 +5360,10 @@
         <v>0</v>
       </c>
       <c r="AB33">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC33">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD33">
         <v>0</v>
@@ -5378,10 +5384,10 @@
         <v>0</v>
       </c>
       <c r="AJ33" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK33" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL33" s="3">
         <v>45872.375</v>
@@ -5404,7 +5410,7 @@
         <v>153</v>
       </c>
       <c r="F34" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -5419,7 +5425,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -5494,10 +5500,10 @@
         <v>0</v>
       </c>
       <c r="AJ34" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK34" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL34" s="3">
         <v>45872.375</v>
@@ -5511,7 +5517,7 @@
         <v>49</v>
       </c>
       <c r="C35" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="D35" t="s">
         <v>120</v>
@@ -5520,7 +5526,7 @@
         <v>154</v>
       </c>
       <c r="F35" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -5535,7 +5541,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -5610,10 +5616,10 @@
         <v>0</v>
       </c>
       <c r="AJ35" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK35" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL35" s="3">
         <v>45872.39583333334</v>
@@ -5627,7 +5633,7 @@
         <v>49</v>
       </c>
       <c r="C36" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D36" t="s">
         <v>119</v>
@@ -5636,7 +5642,7 @@
         <v>155</v>
       </c>
       <c r="F36" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -5651,7 +5657,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -5726,10 +5732,10 @@
         <v>0</v>
       </c>
       <c r="AJ36" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK36" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL36" s="3">
         <v>45872.39583333334</v>
@@ -5743,7 +5749,7 @@
         <v>49</v>
       </c>
       <c r="C37" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="D37" t="s">
         <v>120</v>
@@ -5752,7 +5758,7 @@
         <v>156</v>
       </c>
       <c r="F37" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -5767,16 +5773,16 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L37">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M37">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="N37">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="O37">
         <v>0</v>
@@ -5824,10 +5830,10 @@
         <v>0</v>
       </c>
       <c r="AD37">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE37">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AF37">
         <v>0</v>
@@ -5842,10 +5848,10 @@
         <v>0</v>
       </c>
       <c r="AJ37" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK37" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL37" s="3">
         <v>45872.39583333334</v>
@@ -5859,7 +5865,7 @@
         <v>49</v>
       </c>
       <c r="C38" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D38" t="s">
         <v>120</v>
@@ -5868,7 +5874,7 @@
         <v>157</v>
       </c>
       <c r="F38" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -5883,16 +5889,16 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="O38">
         <v>0</v>
@@ -5940,10 +5946,10 @@
         <v>0</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF38">
         <v>0</v>
@@ -5958,10 +5964,10 @@
         <v>0</v>
       </c>
       <c r="AJ38" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK38" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL38" s="3">
         <v>45872.39583333334</v>
@@ -5984,7 +5990,7 @@
         <v>158</v>
       </c>
       <c r="F39" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -5999,7 +6005,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L39">
         <v>2.09</v>
@@ -6074,10 +6080,10 @@
         <v>0</v>
       </c>
       <c r="AJ39" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK39" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL39" s="3">
         <v>45872.40625</v>
@@ -6100,7 +6106,7 @@
         <v>159</v>
       </c>
       <c r="F40" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -6115,7 +6121,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L40">
         <v>1.94</v>
@@ -6190,10 +6196,10 @@
         <v>0</v>
       </c>
       <c r="AJ40" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK40" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL40" s="3">
         <v>45872.40625</v>
@@ -6216,7 +6222,7 @@
         <v>160</v>
       </c>
       <c r="F41" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -6231,7 +6237,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -6306,10 +6312,10 @@
         <v>0</v>
       </c>
       <c r="AJ41" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK41" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL41" s="3">
         <v>45872.41666666666</v>
@@ -6326,13 +6332,13 @@
         <v>98</v>
       </c>
       <c r="D42" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E42" t="s">
         <v>161</v>
       </c>
       <c r="F42" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -6347,7 +6353,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -6422,10 +6428,10 @@
         <v>0</v>
       </c>
       <c r="AJ42" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK42" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL42" s="3">
         <v>45872.41666666666</v>
@@ -6448,7 +6454,7 @@
         <v>162</v>
       </c>
       <c r="F43" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -6463,16 +6469,16 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L43">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M43">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N43">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O43">
         <v>0</v>
@@ -6520,10 +6526,10 @@
         <v>0</v>
       </c>
       <c r="AD43">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE43">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF43">
         <v>0</v>
@@ -6538,10 +6544,10 @@
         <v>0</v>
       </c>
       <c r="AJ43" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK43" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL43" s="3">
         <v>45872.41666666666</v>
@@ -6564,7 +6570,7 @@
         <v>163</v>
       </c>
       <c r="F44" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -6579,7 +6585,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L44">
         <v>2.37</v>
@@ -6654,10 +6660,10 @@
         <v>0</v>
       </c>
       <c r="AJ44" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK44" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL44" s="3">
         <v>45872.41666666666</v>
@@ -6674,13 +6680,13 @@
         <v>101</v>
       </c>
       <c r="D45" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E45" t="s">
         <v>164</v>
       </c>
       <c r="F45" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -6695,16 +6701,16 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L45">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M45">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O45">
         <v>0</v>
@@ -6752,10 +6758,10 @@
         <v>0</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF45">
         <v>0</v>
@@ -6770,10 +6776,10 @@
         <v>0</v>
       </c>
       <c r="AJ45" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK45" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL45" s="3">
         <v>45872.41666666666</v>
@@ -6796,7 +6802,7 @@
         <v>165</v>
       </c>
       <c r="F46" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -6811,7 +6817,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -6886,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AJ46" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK46" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL46" s="3">
         <v>45872.4375</v>
@@ -6912,7 +6918,7 @@
         <v>166</v>
       </c>
       <c r="F47" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -6927,7 +6933,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -7002,10 +7008,10 @@
         <v>0</v>
       </c>
       <c r="AJ47" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK47" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL47" s="3">
         <v>45872.45833333334</v>
@@ -7019,7 +7025,7 @@
         <v>53</v>
       </c>
       <c r="C48" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D48" t="s">
         <v>120</v>
@@ -7028,7 +7034,7 @@
         <v>167</v>
       </c>
       <c r="F48" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -7043,16 +7049,16 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L48">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M48">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O48">
         <v>0</v>
@@ -7094,10 +7100,10 @@
         <v>0</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD48">
         <v>0</v>
@@ -7118,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="AJ48" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK48" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL48" s="3">
         <v>45872.45833333334</v>
@@ -7144,7 +7150,7 @@
         <v>168</v>
       </c>
       <c r="F49" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -7159,7 +7165,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -7234,10 +7240,10 @@
         <v>0</v>
       </c>
       <c r="AJ49" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK49" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL49" s="3">
         <v>45872.45833333334</v>
@@ -7260,7 +7266,7 @@
         <v>169</v>
       </c>
       <c r="F50" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -7275,7 +7281,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -7350,10 +7356,10 @@
         <v>0</v>
       </c>
       <c r="AJ50" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK50" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL50" s="3">
         <v>45872.45833333334</v>
@@ -7367,7 +7373,7 @@
         <v>53</v>
       </c>
       <c r="C51" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="D51" t="s">
         <v>120</v>
@@ -7376,7 +7382,7 @@
         <v>170</v>
       </c>
       <c r="F51" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -7391,7 +7397,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -7466,10 +7472,10 @@
         <v>0</v>
       </c>
       <c r="AJ51" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK51" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL51" s="3">
         <v>45872.45833333334</v>
@@ -7483,16 +7489,16 @@
         <v>53</v>
       </c>
       <c r="C52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D52" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E52" t="s">
         <v>171</v>
       </c>
       <c r="F52" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -7507,7 +7513,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -7582,10 +7588,10 @@
         <v>0</v>
       </c>
       <c r="AJ52" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK52" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL52" s="3">
         <v>45872.45833333334</v>
@@ -7599,7 +7605,7 @@
         <v>53</v>
       </c>
       <c r="C53" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="D53" t="s">
         <v>120</v>
@@ -7608,7 +7614,7 @@
         <v>172</v>
       </c>
       <c r="F53" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -7623,16 +7629,16 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L53">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M53">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O53">
         <v>0</v>
@@ -7674,10 +7680,10 @@
         <v>0</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD53">
         <v>0</v>
@@ -7698,10 +7704,10 @@
         <v>0</v>
       </c>
       <c r="AJ53" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK53" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL53" s="3">
         <v>45872.45833333334</v>
@@ -7715,7 +7721,7 @@
         <v>53</v>
       </c>
       <c r="C54" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D54" t="s">
         <v>120</v>
@@ -7724,7 +7730,7 @@
         <v>173</v>
       </c>
       <c r="F54" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -7739,16 +7745,16 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L54">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M54">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N54">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O54">
         <v>0</v>
@@ -7790,10 +7796,10 @@
         <v>0</v>
       </c>
       <c r="AB54">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC54">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD54">
         <v>0</v>
@@ -7814,10 +7820,10 @@
         <v>0</v>
       </c>
       <c r="AJ54" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK54" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL54" s="3">
         <v>45872.45833333334</v>
@@ -7831,7 +7837,7 @@
         <v>53</v>
       </c>
       <c r="C55" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D55" t="s">
         <v>119</v>
@@ -7840,7 +7846,7 @@
         <v>174</v>
       </c>
       <c r="F55" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -7855,16 +7861,16 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L55">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M55">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="O55">
         <v>0</v>
@@ -7930,10 +7936,10 @@
         <v>0</v>
       </c>
       <c r="AJ55" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK55" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL55" s="3">
         <v>45872.45833333334</v>
@@ -7947,16 +7953,16 @@
         <v>53</v>
       </c>
       <c r="C56" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E56" t="s">
         <v>175</v>
       </c>
       <c r="F56" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -7971,16 +7977,16 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L56">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M56">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N56">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="O56">
         <v>0</v>
@@ -8046,10 +8052,10 @@
         <v>0</v>
       </c>
       <c r="AJ56" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK56" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL56" s="3">
         <v>45872.45833333334</v>
@@ -8063,7 +8069,7 @@
         <v>53</v>
       </c>
       <c r="C57" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="D57" t="s">
         <v>120</v>
@@ -8072,7 +8078,7 @@
         <v>176</v>
       </c>
       <c r="F57" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -8087,16 +8093,16 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L57">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M57">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N57">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O57">
         <v>0</v>
@@ -8138,10 +8144,10 @@
         <v>0</v>
       </c>
       <c r="AB57">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC57">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD57">
         <v>0</v>
@@ -8162,10 +8168,10 @@
         <v>0</v>
       </c>
       <c r="AJ57" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK57" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL57" s="3">
         <v>45872.45833333334</v>
@@ -8179,7 +8185,7 @@
         <v>53</v>
       </c>
       <c r="C58" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="D58" t="s">
         <v>120</v>
@@ -8188,7 +8194,7 @@
         <v>177</v>
       </c>
       <c r="F58" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -8203,7 +8209,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -8278,10 +8284,10 @@
         <v>0</v>
       </c>
       <c r="AJ58" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK58" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL58" s="3">
         <v>45872.45833333334</v>
@@ -8304,7 +8310,7 @@
         <v>178</v>
       </c>
       <c r="F59" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -8319,7 +8325,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -8394,10 +8400,10 @@
         <v>0</v>
       </c>
       <c r="AJ59" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK59" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL59" s="3">
         <v>45872.45833333334</v>
@@ -8411,7 +8417,7 @@
         <v>54</v>
       </c>
       <c r="C60" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D60" t="s">
         <v>120</v>
@@ -8420,7 +8426,7 @@
         <v>179</v>
       </c>
       <c r="F60" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -8435,7 +8441,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L60">
         <v>2.07</v>
@@ -8510,10 +8516,10 @@
         <v>0</v>
       </c>
       <c r="AJ60" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK60" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL60" s="3">
         <v>45872.47916666666</v>
@@ -8536,7 +8542,7 @@
         <v>180</v>
       </c>
       <c r="F61" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -8551,7 +8557,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -8626,10 +8632,10 @@
         <v>0</v>
       </c>
       <c r="AJ61" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK61" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL61" s="3">
         <v>45872.47916666666</v>
@@ -8643,7 +8649,7 @@
         <v>54</v>
       </c>
       <c r="C62" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D62" t="s">
         <v>120</v>
@@ -8652,7 +8658,7 @@
         <v>181</v>
       </c>
       <c r="F62" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -8667,7 +8673,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -8742,10 +8748,10 @@
         <v>0</v>
       </c>
       <c r="AJ62" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK62" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL62" s="3">
         <v>45872.47916666666</v>
@@ -8759,7 +8765,7 @@
         <v>54</v>
       </c>
       <c r="C63" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D63" t="s">
         <v>119</v>
@@ -8768,7 +8774,7 @@
         <v>182</v>
       </c>
       <c r="F63" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -8783,7 +8789,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L63">
         <v>1.65</v>
@@ -8858,10 +8864,10 @@
         <v>0</v>
       </c>
       <c r="AJ63" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK63" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL63" s="3">
         <v>45872.47916666666</v>
@@ -8875,7 +8881,7 @@
         <v>55</v>
       </c>
       <c r="C64" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="D64" t="s">
         <v>120</v>
@@ -8884,7 +8890,7 @@
         <v>183</v>
       </c>
       <c r="F64" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -8899,7 +8905,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L64">
         <v>0</v>
@@ -8974,10 +8980,10 @@
         <v>0</v>
       </c>
       <c r="AJ64" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK64" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL64" s="3">
         <v>45872.5</v>
@@ -8991,7 +8997,7 @@
         <v>55</v>
       </c>
       <c r="C65" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="D65" t="s">
         <v>120</v>
@@ -9000,7 +9006,7 @@
         <v>184</v>
       </c>
       <c r="F65" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -9015,16 +9021,16 @@
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L65">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M65">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N65">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O65">
         <v>0</v>
@@ -9066,10 +9072,10 @@
         <v>0</v>
       </c>
       <c r="AB65">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC65">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD65">
         <v>0</v>
@@ -9090,10 +9096,10 @@
         <v>0</v>
       </c>
       <c r="AJ65" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK65" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL65" s="3">
         <v>45872.5</v>
@@ -9116,7 +9122,7 @@
         <v>185</v>
       </c>
       <c r="F66" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -9131,7 +9137,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L66">
         <v>0</v>
@@ -9206,10 +9212,10 @@
         <v>0</v>
       </c>
       <c r="AJ66" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK66" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL66" s="3">
         <v>45872.5</v>
@@ -9223,16 +9229,16 @@
         <v>55</v>
       </c>
       <c r="C67" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="D67" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E67" t="s">
         <v>186</v>
       </c>
       <c r="F67" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -9247,16 +9253,16 @@
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L67">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M67">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N67">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O67">
         <v>0</v>
@@ -9298,10 +9304,10 @@
         <v>0</v>
       </c>
       <c r="AB67">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC67">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD67">
         <v>0</v>
@@ -9322,10 +9328,10 @@
         <v>0</v>
       </c>
       <c r="AJ67" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK67" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL67" s="3">
         <v>45872.5</v>
@@ -9339,16 +9345,16 @@
         <v>55</v>
       </c>
       <c r="C68" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="D68" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E68" t="s">
         <v>187</v>
       </c>
       <c r="F68" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -9363,16 +9369,16 @@
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L68">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="M68">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="N68">
-        <v>3.3</v>
+        <v>5.3</v>
       </c>
       <c r="O68">
         <v>0</v>
@@ -9414,10 +9420,10 @@
         <v>0</v>
       </c>
       <c r="AB68">
-        <v>1.61</v>
+        <v>2.15</v>
       </c>
       <c r="AC68">
-        <v>2.31</v>
+        <v>1.7</v>
       </c>
       <c r="AD68">
         <v>0</v>
@@ -9438,10 +9444,10 @@
         <v>0</v>
       </c>
       <c r="AJ68" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK68" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL68" s="3">
         <v>45872.5</v>
@@ -9455,7 +9461,7 @@
         <v>55</v>
       </c>
       <c r="C69" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="D69" t="s">
         <v>120</v>
@@ -9464,7 +9470,7 @@
         <v>188</v>
       </c>
       <c r="F69" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -9479,16 +9485,16 @@
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L69">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M69">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O69">
         <v>0</v>
@@ -9530,10 +9536,10 @@
         <v>0</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD69">
         <v>0</v>
@@ -9554,10 +9560,10 @@
         <v>0</v>
       </c>
       <c r="AJ69" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK69" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL69" s="3">
         <v>45872.5</v>
@@ -9571,16 +9577,16 @@
         <v>55</v>
       </c>
       <c r="C70" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="D70" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E70" t="s">
         <v>189</v>
       </c>
       <c r="F70" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -9595,7 +9601,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L70">
         <v>0</v>
@@ -9670,10 +9676,10 @@
         <v>0</v>
       </c>
       <c r="AJ70" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK70" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL70" s="3">
         <v>45872.5</v>
@@ -9687,7 +9693,7 @@
         <v>55</v>
       </c>
       <c r="C71" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D71" t="s">
         <v>120</v>
@@ -9696,7 +9702,7 @@
         <v>190</v>
       </c>
       <c r="F71" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -9711,16 +9717,16 @@
         <v>0</v>
       </c>
       <c r="K71" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L71">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="M71">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="N71">
-        <v>2.04</v>
+        <v>1.84</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -9762,10 +9768,10 @@
         <v>0</v>
       </c>
       <c r="AB71">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="AC71">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="AD71">
         <v>0</v>
@@ -9786,10 +9792,10 @@
         <v>0</v>
       </c>
       <c r="AJ71" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK71" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL71" s="3">
         <v>45872.5</v>
@@ -9803,7 +9809,7 @@
         <v>55</v>
       </c>
       <c r="C72" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D72" t="s">
         <v>120</v>
@@ -9812,7 +9818,7 @@
         <v>191</v>
       </c>
       <c r="F72" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -9827,16 +9833,16 @@
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L72">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M72">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -9878,10 +9884,10 @@
         <v>0</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC72">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD72">
         <v>0</v>
@@ -9902,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AJ72" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK72" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL72" s="3">
         <v>45872.5</v>
@@ -9919,7 +9925,7 @@
         <v>55</v>
       </c>
       <c r="C73" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D73" t="s">
         <v>120</v>
@@ -9928,7 +9934,7 @@
         <v>192</v>
       </c>
       <c r="F73" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -9943,7 +9949,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L73">
         <v>0</v>
@@ -10018,10 +10024,10 @@
         <v>0</v>
       </c>
       <c r="AJ73" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK73" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL73" s="3">
         <v>45872.5</v>
@@ -10035,16 +10041,16 @@
         <v>55</v>
       </c>
       <c r="C74" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="D74" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E74" t="s">
         <v>193</v>
       </c>
       <c r="F74" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -10059,16 +10065,16 @@
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L74">
-        <v>1.47</v>
+        <v>2.5</v>
       </c>
       <c r="M74">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="N74">
-        <v>6.2</v>
+        <v>2.65</v>
       </c>
       <c r="O74">
         <v>0</v>
@@ -10110,10 +10116,10 @@
         <v>0</v>
       </c>
       <c r="AB74">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="AC74">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AD74">
         <v>0</v>
@@ -10134,10 +10140,10 @@
         <v>0</v>
       </c>
       <c r="AJ74" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK74" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL74" s="3">
         <v>45872.5</v>
@@ -10151,7 +10157,7 @@
         <v>55</v>
       </c>
       <c r="C75" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D75" t="s">
         <v>120</v>
@@ -10160,7 +10166,7 @@
         <v>194</v>
       </c>
       <c r="F75" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -10175,7 +10181,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L75">
         <v>0</v>
@@ -10250,10 +10256,10 @@
         <v>0</v>
       </c>
       <c r="AJ75" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK75" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL75" s="3">
         <v>45872.5</v>
@@ -10267,16 +10273,16 @@
         <v>55</v>
       </c>
       <c r="C76" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="D76" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E76" t="s">
         <v>195</v>
       </c>
       <c r="F76" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -10291,7 +10297,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L76">
         <v>0</v>
@@ -10366,10 +10372,10 @@
         <v>0</v>
       </c>
       <c r="AJ76" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK76" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL76" s="3">
         <v>45872.5</v>
@@ -10383,7 +10389,7 @@
         <v>55</v>
       </c>
       <c r="C77" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D77" t="s">
         <v>120</v>
@@ -10392,7 +10398,7 @@
         <v>196</v>
       </c>
       <c r="F77" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -10407,16 +10413,16 @@
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L77">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M77">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N77">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O77">
         <v>0</v>
@@ -10458,10 +10464,10 @@
         <v>0</v>
       </c>
       <c r="AB77">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC77">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD77">
         <v>0</v>
@@ -10482,10 +10488,10 @@
         <v>0</v>
       </c>
       <c r="AJ77" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK77" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL77" s="3">
         <v>45872.5</v>
@@ -10499,7 +10505,7 @@
         <v>55</v>
       </c>
       <c r="C78" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="D78" t="s">
         <v>119</v>
@@ -10508,7 +10514,7 @@
         <v>197</v>
       </c>
       <c r="F78" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -10523,7 +10529,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L78">
         <v>0</v>
@@ -10598,10 +10604,10 @@
         <v>0</v>
       </c>
       <c r="AJ78" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK78" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL78" s="3">
         <v>45872.5</v>
@@ -10615,16 +10621,16 @@
         <v>55</v>
       </c>
       <c r="C79" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="D79" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E79" t="s">
         <v>198</v>
       </c>
       <c r="F79" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -10639,16 +10645,16 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L79">
-        <v>1.5</v>
+        <v>2.95</v>
       </c>
       <c r="M79">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="N79">
-        <v>5.5</v>
+        <v>2.28</v>
       </c>
       <c r="O79">
         <v>0</v>
@@ -10690,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AB79">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="AC79">
-        <v>2.22</v>
+        <v>1.67</v>
       </c>
       <c r="AD79">
         <v>0</v>
@@ -10714,10 +10720,10 @@
         <v>0</v>
       </c>
       <c r="AJ79" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK79" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL79" s="3">
         <v>45872.5</v>
@@ -10731,16 +10737,16 @@
         <v>55</v>
       </c>
       <c r="C80" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="D80" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E80" t="s">
         <v>199</v>
       </c>
       <c r="F80" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -10755,16 +10761,16 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L80">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M80">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N80">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O80">
         <v>0</v>
@@ -10806,10 +10812,10 @@
         <v>0</v>
       </c>
       <c r="AB80">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC80">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD80">
         <v>0</v>
@@ -10830,10 +10836,10 @@
         <v>0</v>
       </c>
       <c r="AJ80" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK80" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL80" s="3">
         <v>45872.5</v>
@@ -10847,7 +10853,7 @@
         <v>55</v>
       </c>
       <c r="C81" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="D81" t="s">
         <v>120</v>
@@ -10856,7 +10862,7 @@
         <v>200</v>
       </c>
       <c r="F81" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -10871,7 +10877,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L81">
         <v>0</v>
@@ -10946,10 +10952,10 @@
         <v>0</v>
       </c>
       <c r="AJ81" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK81" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL81" s="3">
         <v>45872.5</v>
@@ -10963,7 +10969,7 @@
         <v>55</v>
       </c>
       <c r="C82" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D82" t="s">
         <v>120</v>
@@ -10972,7 +10978,7 @@
         <v>201</v>
       </c>
       <c r="F82" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -10987,7 +10993,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L82">
         <v>0</v>
@@ -11062,10 +11068,10 @@
         <v>0</v>
       </c>
       <c r="AJ82" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK82" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL82" s="3">
         <v>45872.5</v>
@@ -11079,7 +11085,7 @@
         <v>55</v>
       </c>
       <c r="C83" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="D83" t="s">
         <v>119</v>
@@ -11088,7 +11094,7 @@
         <v>202</v>
       </c>
       <c r="F83" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -11103,16 +11109,16 @@
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L83">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M83">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O83">
         <v>0</v>
@@ -11154,10 +11160,10 @@
         <v>0</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD83">
         <v>0</v>
@@ -11178,10 +11184,10 @@
         <v>0</v>
       </c>
       <c r="AJ83" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK83" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL83" s="3">
         <v>45872.5</v>
@@ -11192,19 +11198,19 @@
         <v>45872</v>
       </c>
       <c r="B84" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C84" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D84" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E84" t="s">
         <v>203</v>
       </c>
       <c r="F84" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -11219,16 +11225,16 @@
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L84">
-        <v>3.15</v>
+        <v>1.5</v>
       </c>
       <c r="M84">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="N84">
-        <v>2.17</v>
+        <v>5.5</v>
       </c>
       <c r="O84">
         <v>0</v>
@@ -11270,10 +11276,10 @@
         <v>0</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD84">
         <v>0</v>
@@ -11294,13 +11300,13 @@
         <v>0</v>
       </c>
       <c r="AJ84" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK84" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL84" s="3">
-        <v>45872.52083333334</v>
+        <v>45872.5</v>
       </c>
     </row>
     <row r="85" spans="1:38">
@@ -11311,7 +11317,7 @@
         <v>56</v>
       </c>
       <c r="C85" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="D85" t="s">
         <v>120</v>
@@ -11320,7 +11326,7 @@
         <v>204</v>
       </c>
       <c r="F85" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -11335,16 +11341,16 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L85">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="M85">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N85">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O85">
         <v>0</v>
@@ -11386,16 +11392,16 @@
         <v>0</v>
       </c>
       <c r="AB85">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC85">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD85">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE85">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF85">
         <v>0</v>
@@ -11410,10 +11416,10 @@
         <v>0</v>
       </c>
       <c r="AJ85" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK85" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL85" s="3">
         <v>45872.52083333334</v>
@@ -11427,7 +11433,7 @@
         <v>56</v>
       </c>
       <c r="C86" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D86" t="s">
         <v>120</v>
@@ -11436,7 +11442,7 @@
         <v>205</v>
       </c>
       <c r="F86" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -11451,7 +11457,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L86">
         <v>2.6</v>
@@ -11526,10 +11532,10 @@
         <v>0</v>
       </c>
       <c r="AJ86" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK86" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL86" s="3">
         <v>45872.52083333334</v>
@@ -11543,7 +11549,7 @@
         <v>56</v>
       </c>
       <c r="C87" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="D87" t="s">
         <v>120</v>
@@ -11552,7 +11558,7 @@
         <v>206</v>
       </c>
       <c r="F87" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -11567,16 +11573,16 @@
         <v>0</v>
       </c>
       <c r="K87" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L87">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M87">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O87">
         <v>0</v>
@@ -11642,10 +11648,10 @@
         <v>0</v>
       </c>
       <c r="AJ87" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK87" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL87" s="3">
         <v>45872.52083333334</v>
@@ -11668,7 +11674,7 @@
         <v>207</v>
       </c>
       <c r="F88" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -11683,16 +11689,16 @@
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L88">
-        <v>2.65</v>
+        <v>3.15</v>
       </c>
       <c r="M88">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N88">
-        <v>2.41</v>
+        <v>2.17</v>
       </c>
       <c r="O88">
         <v>0</v>
@@ -11758,10 +11764,10 @@
         <v>0</v>
       </c>
       <c r="AJ88" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK88" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL88" s="3">
         <v>45872.52083333334</v>
@@ -11784,7 +11790,7 @@
         <v>208</v>
       </c>
       <c r="F89" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -11799,7 +11805,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L89">
         <v>0</v>
@@ -11874,10 +11880,10 @@
         <v>0</v>
       </c>
       <c r="AJ89" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK89" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL89" s="3">
         <v>45872.52083333334</v>
@@ -11891,7 +11897,7 @@
         <v>56</v>
       </c>
       <c r="C90" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D90" t="s">
         <v>120</v>
@@ -11900,7 +11906,7 @@
         <v>209</v>
       </c>
       <c r="F90" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -11915,7 +11921,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L90">
         <v>0</v>
@@ -11990,10 +11996,10 @@
         <v>0</v>
       </c>
       <c r="AJ90" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK90" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL90" s="3">
         <v>45872.52083333334</v>
@@ -12004,10 +12010,10 @@
         <v>45872</v>
       </c>
       <c r="B91" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C91" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="D91" t="s">
         <v>120</v>
@@ -12016,7 +12022,7 @@
         <v>210</v>
       </c>
       <c r="F91" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -12031,16 +12037,16 @@
         <v>0</v>
       </c>
       <c r="K91" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L91">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="M91">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O91">
         <v>0</v>
@@ -12082,16 +12088,16 @@
         <v>0</v>
       </c>
       <c r="AB91">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC91">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD91">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE91">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF91">
         <v>0</v>
@@ -12106,13 +12112,13 @@
         <v>0</v>
       </c>
       <c r="AJ91" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK91" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL91" s="3">
-        <v>45872.53125</v>
+        <v>45872.52083333334</v>
       </c>
     </row>
     <row r="92" spans="1:38">
@@ -12132,7 +12138,7 @@
         <v>211</v>
       </c>
       <c r="F92" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -12147,7 +12153,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -12222,10 +12228,10 @@
         <v>0</v>
       </c>
       <c r="AJ92" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK92" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL92" s="3">
         <v>45872.53125</v>
@@ -12236,10 +12242,10 @@
         <v>45872</v>
       </c>
       <c r="B93" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C93" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="D93" t="s">
         <v>120</v>
@@ -12248,7 +12254,7 @@
         <v>212</v>
       </c>
       <c r="F93" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -12263,7 +12269,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L93">
         <v>0</v>
@@ -12338,13 +12344,13 @@
         <v>0</v>
       </c>
       <c r="AJ93" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK93" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL93" s="3">
-        <v>45872.54166666666</v>
+        <v>45872.53125</v>
       </c>
     </row>
     <row r="94" spans="1:38">
@@ -12355,7 +12361,7 @@
         <v>58</v>
       </c>
       <c r="C94" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D94" t="s">
         <v>120</v>
@@ -12364,7 +12370,7 @@
         <v>213</v>
       </c>
       <c r="F94" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -12379,7 +12385,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L94">
         <v>0</v>
@@ -12454,10 +12460,10 @@
         <v>0</v>
       </c>
       <c r="AJ94" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK94" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL94" s="3">
         <v>45872.54166666666</v>
@@ -12471,7 +12477,7 @@
         <v>58</v>
       </c>
       <c r="C95" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="D95" t="s">
         <v>120</v>
@@ -12480,7 +12486,7 @@
         <v>214</v>
       </c>
       <c r="F95" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -12495,7 +12501,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L95">
         <v>0</v>
@@ -12570,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="AJ95" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK95" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL95" s="3">
         <v>45872.54166666666</v>
@@ -12587,7 +12593,7 @@
         <v>58</v>
       </c>
       <c r="C96" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="D96" t="s">
         <v>120</v>
@@ -12596,7 +12602,7 @@
         <v>215</v>
       </c>
       <c r="F96" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -12611,7 +12617,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L96">
         <v>0</v>
@@ -12686,10 +12692,10 @@
         <v>0</v>
       </c>
       <c r="AJ96" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK96" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL96" s="3">
         <v>45872.54166666666</v>
@@ -12712,7 +12718,7 @@
         <v>216</v>
       </c>
       <c r="F97" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -12727,7 +12733,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L97">
         <v>6.27</v>
@@ -12802,10 +12808,10 @@
         <v>0</v>
       </c>
       <c r="AJ97" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK97" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL97" s="3">
         <v>45872.54166666666</v>
@@ -12816,19 +12822,19 @@
         <v>45872</v>
       </c>
       <c r="B98" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C98" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="D98" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E98" t="s">
         <v>217</v>
       </c>
       <c r="F98" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -12843,7 +12849,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L98">
         <v>0</v>
@@ -12918,13 +12924,13 @@
         <v>0</v>
       </c>
       <c r="AJ98" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK98" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL98" s="3">
-        <v>45872.55208333334</v>
+        <v>45872.54166666666</v>
       </c>
     </row>
     <row r="99" spans="1:38">
@@ -12932,19 +12938,19 @@
         <v>45872</v>
       </c>
       <c r="B99" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C99" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="D99" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E99" t="s">
         <v>218</v>
       </c>
       <c r="F99" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -12959,16 +12965,16 @@
         <v>0</v>
       </c>
       <c r="K99" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L99">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M99">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N99">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="O99">
         <v>0</v>
@@ -13010,10 +13016,10 @@
         <v>0</v>
       </c>
       <c r="AB99">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC99">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD99">
         <v>0</v>
@@ -13034,13 +13040,13 @@
         <v>0</v>
       </c>
       <c r="AJ99" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK99" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL99" s="3">
-        <v>45872.5625</v>
+        <v>45872.55208333334</v>
       </c>
     </row>
     <row r="100" spans="1:38">
@@ -13051,16 +13057,16 @@
         <v>60</v>
       </c>
       <c r="C100" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="D100" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E100" t="s">
         <v>219</v>
       </c>
       <c r="F100" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -13075,16 +13081,16 @@
         <v>0</v>
       </c>
       <c r="K100" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L100">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M100">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O100">
         <v>0</v>
@@ -13126,10 +13132,10 @@
         <v>0</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC100">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD100">
         <v>0</v>
@@ -13150,10 +13156,10 @@
         <v>0</v>
       </c>
       <c r="AJ100" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK100" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL100" s="3">
         <v>45872.5625</v>
@@ -13167,7 +13173,7 @@
         <v>60</v>
       </c>
       <c r="C101" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D101" t="s">
         <v>119</v>
@@ -13176,7 +13182,7 @@
         <v>220</v>
       </c>
       <c r="F101" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G101">
         <v>0</v>
@@ -13191,7 +13197,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L101">
         <v>0</v>
@@ -13266,10 +13272,10 @@
         <v>0</v>
       </c>
       <c r="AJ101" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK101" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL101" s="3">
         <v>45872.5625</v>
@@ -13280,10 +13286,10 @@
         <v>45872</v>
       </c>
       <c r="B102" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C102" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="D102" t="s">
         <v>119</v>
@@ -13292,7 +13298,7 @@
         <v>221</v>
       </c>
       <c r="F102" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G102">
         <v>0</v>
@@ -13307,7 +13313,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L102">
         <v>0</v>
@@ -13382,13 +13388,13 @@
         <v>0</v>
       </c>
       <c r="AJ102" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK102" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL102" s="3">
-        <v>45872.58333333334</v>
+        <v>45872.5625</v>
       </c>
     </row>
     <row r="103" spans="1:38">
@@ -13399,16 +13405,16 @@
         <v>61</v>
       </c>
       <c r="C103" t="s">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="D103" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E103" t="s">
         <v>222</v>
       </c>
       <c r="F103" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G103">
         <v>0</v>
@@ -13423,7 +13429,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L103">
         <v>0</v>
@@ -13498,10 +13504,10 @@
         <v>0</v>
       </c>
       <c r="AJ103" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK103" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL103" s="3">
         <v>45872.58333333334</v>
@@ -13515,16 +13521,16 @@
         <v>61</v>
       </c>
       <c r="C104" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="D104" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E104" t="s">
         <v>223</v>
       </c>
       <c r="F104" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G104">
         <v>0</v>
@@ -13539,7 +13545,7 @@
         <v>0</v>
       </c>
       <c r="K104" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L104">
         <v>0</v>
@@ -13614,10 +13620,10 @@
         <v>0</v>
       </c>
       <c r="AJ104" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK104" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL104" s="3">
         <v>45872.58333333334</v>
@@ -13631,16 +13637,16 @@
         <v>61</v>
       </c>
       <c r="C105" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="D105" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E105" t="s">
         <v>224</v>
       </c>
       <c r="F105" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="G105">
         <v>0</v>
@@ -13655,7 +13661,7 @@
         <v>0</v>
       </c>
       <c r="K105" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L105">
         <v>0</v>
@@ -13730,10 +13736,10 @@
         <v>0</v>
       </c>
       <c r="AJ105" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK105" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL105" s="3">
         <v>45872.58333333334</v>
@@ -13747,7 +13753,7 @@
         <v>61</v>
       </c>
       <c r="C106" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D106" t="s">
         <v>120</v>
@@ -13756,7 +13762,7 @@
         <v>225</v>
       </c>
       <c r="F106" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G106">
         <v>0</v>
@@ -13771,7 +13777,7 @@
         <v>0</v>
       </c>
       <c r="K106" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L106">
         <v>0</v>
@@ -13846,10 +13852,10 @@
         <v>0</v>
       </c>
       <c r="AJ106" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK106" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL106" s="3">
         <v>45872.58333333334</v>
@@ -13863,7 +13869,7 @@
         <v>61</v>
       </c>
       <c r="C107" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D107" t="s">
         <v>120</v>
@@ -13872,7 +13878,7 @@
         <v>226</v>
       </c>
       <c r="F107" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G107">
         <v>0</v>
@@ -13887,7 +13893,7 @@
         <v>0</v>
       </c>
       <c r="K107" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L107">
         <v>0</v>
@@ -13962,10 +13968,10 @@
         <v>0</v>
       </c>
       <c r="AJ107" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK107" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL107" s="3">
         <v>45872.58333333334</v>
@@ -13979,7 +13985,7 @@
         <v>61</v>
       </c>
       <c r="C108" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D108" t="s">
         <v>120</v>
@@ -13988,7 +13994,7 @@
         <v>227</v>
       </c>
       <c r="F108" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G108">
         <v>0</v>
@@ -14003,7 +14009,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L108">
         <v>0</v>
@@ -14078,10 +14084,10 @@
         <v>0</v>
       </c>
       <c r="AJ108" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK108" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL108" s="3">
         <v>45872.58333333334</v>
@@ -14095,7 +14101,7 @@
         <v>61</v>
       </c>
       <c r="C109" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D109" t="s">
         <v>120</v>
@@ -14104,7 +14110,7 @@
         <v>228</v>
       </c>
       <c r="F109" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G109">
         <v>0</v>
@@ -14119,7 +14125,7 @@
         <v>0</v>
       </c>
       <c r="K109" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L109">
         <v>0</v>
@@ -14194,10 +14200,10 @@
         <v>0</v>
       </c>
       <c r="AJ109" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK109" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL109" s="3">
         <v>45872.58333333334</v>
@@ -14211,7 +14217,7 @@
         <v>61</v>
       </c>
       <c r="C110" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D110" t="s">
         <v>120</v>
@@ -14220,7 +14226,7 @@
         <v>229</v>
       </c>
       <c r="F110" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G110">
         <v>0</v>
@@ -14235,7 +14241,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L110">
         <v>0</v>
@@ -14310,10 +14316,10 @@
         <v>0</v>
       </c>
       <c r="AJ110" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK110" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL110" s="3">
         <v>45872.58333333334</v>
@@ -14324,10 +14330,10 @@
         <v>45872</v>
       </c>
       <c r="B111" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C111" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="D111" t="s">
         <v>120</v>
@@ -14336,7 +14342,7 @@
         <v>230</v>
       </c>
       <c r="F111" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G111">
         <v>0</v>
@@ -14351,16 +14357,16 @@
         <v>0</v>
       </c>
       <c r="K111" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L111">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M111">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N111">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O111">
         <v>0</v>
@@ -14402,10 +14408,10 @@
         <v>0</v>
       </c>
       <c r="AB111">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC111">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD111">
         <v>0</v>
@@ -14426,13 +14432,13 @@
         <v>0</v>
       </c>
       <c r="AJ111" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK111" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL111" s="3">
-        <v>45872.59375</v>
+        <v>45872.58333333334</v>
       </c>
     </row>
     <row r="112" spans="1:38">
@@ -14440,7 +14446,7 @@
         <v>45872</v>
       </c>
       <c r="B112" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C112" t="s">
         <v>89</v>
@@ -14452,7 +14458,7 @@
         <v>231</v>
       </c>
       <c r="F112" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G112">
         <v>0</v>
@@ -14467,16 +14473,16 @@
         <v>0</v>
       </c>
       <c r="K112" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L112">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M112">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O112">
         <v>0</v>
@@ -14518,10 +14524,10 @@
         <v>0</v>
       </c>
       <c r="AB112">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC112">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD112">
         <v>0</v>
@@ -14542,13 +14548,13 @@
         <v>0</v>
       </c>
       <c r="AJ112" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK112" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL112" s="3">
-        <v>45872.60416666666</v>
+        <v>45872.59375</v>
       </c>
     </row>
     <row r="113" spans="1:38">
@@ -14568,7 +14574,7 @@
         <v>232</v>
       </c>
       <c r="F113" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G113">
         <v>0</v>
@@ -14583,7 +14589,7 @@
         <v>0</v>
       </c>
       <c r="K113" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L113">
         <v>2.46</v>
@@ -14658,10 +14664,10 @@
         <v>0</v>
       </c>
       <c r="AJ113" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK113" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL113" s="3">
         <v>45872.60416666666</v>
@@ -14675,7 +14681,7 @@
         <v>63</v>
       </c>
       <c r="C114" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D114" t="s">
         <v>120</v>
@@ -14684,7 +14690,7 @@
         <v>233</v>
       </c>
       <c r="F114" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G114">
         <v>0</v>
@@ -14699,7 +14705,7 @@
         <v>0</v>
       </c>
       <c r="K114" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L114">
         <v>0</v>
@@ -14774,10 +14780,10 @@
         <v>0</v>
       </c>
       <c r="AJ114" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK114" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL114" s="3">
         <v>45872.60416666666</v>
@@ -14788,19 +14794,19 @@
         <v>45872</v>
       </c>
       <c r="B115" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C115" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D115" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E115" t="s">
         <v>234</v>
       </c>
       <c r="F115" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G115">
         <v>0</v>
@@ -14815,7 +14821,7 @@
         <v>0</v>
       </c>
       <c r="K115" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L115">
         <v>0</v>
@@ -14890,13 +14896,13 @@
         <v>0</v>
       </c>
       <c r="AJ115" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK115" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL115" s="3">
-        <v>45872.625</v>
+        <v>45872.60416666666</v>
       </c>
     </row>
     <row r="116" spans="1:38">
@@ -14916,7 +14922,7 @@
         <v>235</v>
       </c>
       <c r="F116" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="G116">
         <v>0</v>
@@ -14931,7 +14937,7 @@
         <v>0</v>
       </c>
       <c r="K116" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L116">
         <v>0</v>
@@ -15006,10 +15012,10 @@
         <v>0</v>
       </c>
       <c r="AJ116" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK116" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL116" s="3">
         <v>45872.625</v>
@@ -15023,16 +15029,16 @@
         <v>64</v>
       </c>
       <c r="C117" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D117" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E117" t="s">
         <v>236</v>
       </c>
       <c r="F117" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G117">
         <v>0</v>
@@ -15047,7 +15053,7 @@
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L117">
         <v>0</v>
@@ -15122,10 +15128,10 @@
         <v>0</v>
       </c>
       <c r="AJ117" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK117" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL117" s="3">
         <v>45872.625</v>
@@ -15136,10 +15142,10 @@
         <v>45872</v>
       </c>
       <c r="B118" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C118" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="D118" t="s">
         <v>120</v>
@@ -15148,7 +15154,7 @@
         <v>237</v>
       </c>
       <c r="F118" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G118">
         <v>0</v>
@@ -15163,16 +15169,16 @@
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L118">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M118">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N118">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O118">
         <v>0</v>
@@ -15238,13 +15244,13 @@
         <v>0</v>
       </c>
       <c r="AJ118" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK118" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL118" s="3">
-        <v>45872.63541666666</v>
+        <v>45872.625</v>
       </c>
     </row>
     <row r="119" spans="1:38">
@@ -15255,7 +15261,7 @@
         <v>65</v>
       </c>
       <c r="C119" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="D119" t="s">
         <v>120</v>
@@ -15264,7 +15270,7 @@
         <v>238</v>
       </c>
       <c r="F119" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G119">
         <v>0</v>
@@ -15279,16 +15285,16 @@
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L119">
-        <v>1.51</v>
+        <v>2.11</v>
       </c>
       <c r="M119">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="N119">
-        <v>5.2</v>
+        <v>3.1</v>
       </c>
       <c r="O119">
         <v>0</v>
@@ -15354,10 +15360,10 @@
         <v>0</v>
       </c>
       <c r="AJ119" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK119" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL119" s="3">
         <v>45872.63541666666</v>
@@ -15368,10 +15374,10 @@
         <v>45872</v>
       </c>
       <c r="B120" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C120" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="D120" t="s">
         <v>120</v>
@@ -15380,7 +15386,7 @@
         <v>239</v>
       </c>
       <c r="F120" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="G120">
         <v>0</v>
@@ -15395,16 +15401,16 @@
         <v>0</v>
       </c>
       <c r="K120" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L120">
-        <v>2.15</v>
+        <v>1.51</v>
       </c>
       <c r="M120">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N120">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="O120">
         <v>0</v>
@@ -15446,10 +15452,10 @@
         <v>0</v>
       </c>
       <c r="AB120">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC120">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD120">
         <v>0</v>
@@ -15470,13 +15476,13 @@
         <v>0</v>
       </c>
       <c r="AJ120" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK120" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL120" s="3">
-        <v>45872.64583333334</v>
+        <v>45872.63541666666</v>
       </c>
     </row>
     <row r="121" spans="1:38">
@@ -15484,19 +15490,19 @@
         <v>45872</v>
       </c>
       <c r="B121" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C121" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D121" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E121" t="s">
         <v>240</v>
       </c>
       <c r="F121" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="G121">
         <v>0</v>
@@ -15511,16 +15517,16 @@
         <v>0</v>
       </c>
       <c r="K121" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L121">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="M121">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N121">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="O121">
         <v>0</v>
@@ -15556,16 +15562,16 @@
         <v>0</v>
       </c>
       <c r="Z121">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA121">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB121">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AC121">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AD121">
         <v>0</v>
@@ -15586,13 +15592,13 @@
         <v>0</v>
       </c>
       <c r="AJ121" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK121" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL121" s="3">
-        <v>45872.66666666666</v>
+        <v>45872.64583333334</v>
       </c>
     </row>
     <row r="122" spans="1:38">
@@ -15603,7 +15609,7 @@
         <v>67</v>
       </c>
       <c r="C122" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D122" t="s">
         <v>119</v>
@@ -15612,7 +15618,7 @@
         <v>241</v>
       </c>
       <c r="F122" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G122">
         <v>0</v>
@@ -15627,16 +15633,16 @@
         <v>0</v>
       </c>
       <c r="K122" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L122">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M122">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N122">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O122">
         <v>0</v>
@@ -15672,16 +15678,16 @@
         <v>0</v>
       </c>
       <c r="Z122">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA122">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB122">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC122">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD122">
         <v>0</v>
@@ -15702,10 +15708,10 @@
         <v>0</v>
       </c>
       <c r="AJ122" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK122" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL122" s="3">
         <v>45872.66666666666</v>
@@ -15719,16 +15725,16 @@
         <v>67</v>
       </c>
       <c r="C123" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D123" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E123" t="s">
         <v>242</v>
       </c>
       <c r="F123" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G123">
         <v>0</v>
@@ -15743,16 +15749,16 @@
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L123">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M123">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N123">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O123">
         <v>0</v>
@@ -15794,10 +15800,10 @@
         <v>0</v>
       </c>
       <c r="AB123">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC123">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD123">
         <v>0</v>
@@ -15818,10 +15824,10 @@
         <v>0</v>
       </c>
       <c r="AJ123" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK123" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL123" s="3">
         <v>45872.66666666666</v>
@@ -15835,7 +15841,7 @@
         <v>67</v>
       </c>
       <c r="C124" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D124" t="s">
         <v>119</v>
@@ -15844,7 +15850,7 @@
         <v>243</v>
       </c>
       <c r="F124" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G124">
         <v>0</v>
@@ -15859,16 +15865,16 @@
         <v>0</v>
       </c>
       <c r="K124" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L124">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M124">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N124">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O124">
         <v>0</v>
@@ -15910,10 +15916,10 @@
         <v>0</v>
       </c>
       <c r="AB124">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC124">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD124">
         <v>0</v>
@@ -15934,10 +15940,10 @@
         <v>0</v>
       </c>
       <c r="AJ124" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK124" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL124" s="3">
         <v>45872.66666666666</v>
@@ -15951,7 +15957,7 @@
         <v>67</v>
       </c>
       <c r="C125" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D125" t="s">
         <v>119</v>
@@ -15960,7 +15966,7 @@
         <v>244</v>
       </c>
       <c r="F125" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G125">
         <v>0</v>
@@ -15975,7 +15981,7 @@
         <v>0</v>
       </c>
       <c r="K125" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L125">
         <v>0</v>
@@ -16050,10 +16056,10 @@
         <v>0</v>
       </c>
       <c r="AJ125" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK125" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL125" s="3">
         <v>45872.66666666666</v>
@@ -16064,19 +16070,19 @@
         <v>45872</v>
       </c>
       <c r="B126" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C126" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D126" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E126" t="s">
         <v>245</v>
       </c>
       <c r="F126" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G126">
         <v>0</v>
@@ -16091,7 +16097,7 @@
         <v>0</v>
       </c>
       <c r="K126" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L126">
         <v>0</v>
@@ -16166,13 +16172,13 @@
         <v>0</v>
       </c>
       <c r="AJ126" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK126" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL126" s="3">
-        <v>45872.70833333334</v>
+        <v>45872.66666666666</v>
       </c>
     </row>
     <row r="127" spans="1:38">
@@ -16180,10 +16186,10 @@
         <v>45872</v>
       </c>
       <c r="B127" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C127" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D127" t="s">
         <v>119</v>
@@ -16192,7 +16198,7 @@
         <v>246</v>
       </c>
       <c r="F127" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G127">
         <v>0</v>
@@ -16207,16 +16213,16 @@
         <v>0</v>
       </c>
       <c r="K127" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L127">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M127">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N127">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O127">
         <v>0</v>
@@ -16258,10 +16264,10 @@
         <v>0</v>
       </c>
       <c r="AB127">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC127">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD127">
         <v>0</v>
@@ -16282,13 +16288,13 @@
         <v>0</v>
       </c>
       <c r="AJ127" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK127" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL127" s="3">
-        <v>45872.77083333334</v>
+        <v>45872.70833333334</v>
       </c>
     </row>
     <row r="128" spans="1:38">
@@ -16308,7 +16314,7 @@
         <v>247</v>
       </c>
       <c r="F128" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G128">
         <v>0</v>
@@ -16323,7 +16329,7 @@
         <v>0</v>
       </c>
       <c r="K128" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L128">
         <v>3.8</v>
@@ -16398,10 +16404,10 @@
         <v>0</v>
       </c>
       <c r="AJ128" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK128" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL128" s="3">
         <v>45872.77083333334</v>
@@ -16415,7 +16421,7 @@
         <v>69</v>
       </c>
       <c r="C129" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D129" t="s">
         <v>119</v>
@@ -16424,7 +16430,7 @@
         <v>248</v>
       </c>
       <c r="F129" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G129">
         <v>0</v>
@@ -16439,16 +16445,16 @@
         <v>0</v>
       </c>
       <c r="K129" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L129">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M129">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N129">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O129">
         <v>0</v>
@@ -16490,10 +16496,10 @@
         <v>0</v>
       </c>
       <c r="AB129">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC129">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD129">
         <v>0</v>
@@ -16514,10 +16520,10 @@
         <v>0</v>
       </c>
       <c r="AJ129" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK129" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL129" s="3">
         <v>45872.77083333334</v>
@@ -16540,7 +16546,7 @@
         <v>249</v>
       </c>
       <c r="F130" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G130">
         <v>0</v>
@@ -16555,7 +16561,7 @@
         <v>0</v>
       </c>
       <c r="K130" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L130">
         <v>0</v>
@@ -16630,10 +16636,10 @@
         <v>0</v>
       </c>
       <c r="AJ130" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK130" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL130" s="3">
         <v>45872.77083333334</v>
@@ -16644,7 +16650,7 @@
         <v>45872</v>
       </c>
       <c r="B131" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C131" t="s">
         <v>114</v>
@@ -16656,7 +16662,7 @@
         <v>250</v>
       </c>
       <c r="F131" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="G131">
         <v>0</v>
@@ -16671,7 +16677,7 @@
         <v>0</v>
       </c>
       <c r="K131" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L131">
         <v>0</v>
@@ -16746,13 +16752,13 @@
         <v>0</v>
       </c>
       <c r="AJ131" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK131" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL131" s="3">
-        <v>45872.79166666666</v>
+        <v>45872.77083333334</v>
       </c>
     </row>
     <row r="132" spans="1:38">
@@ -16763,7 +16769,7 @@
         <v>70</v>
       </c>
       <c r="C132" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="D132" t="s">
         <v>119</v>
@@ -16772,7 +16778,7 @@
         <v>251</v>
       </c>
       <c r="F132" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G132">
         <v>0</v>
@@ -16787,7 +16793,7 @@
         <v>0</v>
       </c>
       <c r="K132" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L132">
         <v>0</v>
@@ -16862,10 +16868,10 @@
         <v>0</v>
       </c>
       <c r="AJ132" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK132" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL132" s="3">
         <v>45872.79166666666</v>
@@ -16876,10 +16882,10 @@
         <v>45872</v>
       </c>
       <c r="B133" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C133" t="s">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="D133" t="s">
         <v>119</v>
@@ -16888,7 +16894,7 @@
         <v>252</v>
       </c>
       <c r="F133" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G133">
         <v>0</v>
@@ -16903,16 +16909,16 @@
         <v>0</v>
       </c>
       <c r="K133" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L133">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M133">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N133">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O133">
         <v>0</v>
@@ -16954,10 +16960,10 @@
         <v>0</v>
       </c>
       <c r="AB133">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC133">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD133">
         <v>0</v>
@@ -16978,13 +16984,13 @@
         <v>0</v>
       </c>
       <c r="AJ133" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK133" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL133" s="3">
-        <v>45872.8125</v>
+        <v>45872.79166666666</v>
       </c>
     </row>
     <row r="134" spans="1:38">
@@ -16992,10 +16998,10 @@
         <v>45872</v>
       </c>
       <c r="B134" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C134" t="s">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="D134" t="s">
         <v>119</v>
@@ -17004,7 +17010,7 @@
         <v>253</v>
       </c>
       <c r="F134" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G134">
         <v>0</v>
@@ -17019,16 +17025,16 @@
         <v>0</v>
       </c>
       <c r="K134" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L134">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M134">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N134">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O134">
         <v>0</v>
@@ -17070,10 +17076,10 @@
         <v>0</v>
       </c>
       <c r="AB134">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC134">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD134">
         <v>0</v>
@@ -17094,13 +17100,13 @@
         <v>0</v>
       </c>
       <c r="AJ134" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK134" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL134" s="3">
-        <v>45872.83333333334</v>
+        <v>45872.8125</v>
       </c>
     </row>
     <row r="135" spans="1:38">
@@ -17108,10 +17114,10 @@
         <v>45872</v>
       </c>
       <c r="B135" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C135" t="s">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="D135" t="s">
         <v>119</v>
@@ -17120,7 +17126,7 @@
         <v>254</v>
       </c>
       <c r="F135" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G135">
         <v>0</v>
@@ -17135,16 +17141,16 @@
         <v>0</v>
       </c>
       <c r="K135" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L135">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M135">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N135">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O135">
         <v>0</v>
@@ -17186,10 +17192,10 @@
         <v>0</v>
       </c>
       <c r="AB135">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC135">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD135">
         <v>0</v>
@@ -17210,13 +17216,13 @@
         <v>0</v>
       </c>
       <c r="AJ135" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AK135" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AL135" s="3">
-        <v>45872.85416666666</v>
+        <v>45872.83333333334</v>
       </c>
     </row>
     <row r="136" spans="1:38">
@@ -17224,10 +17230,10 @@
         <v>45872</v>
       </c>
       <c r="B136" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C136" t="s">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="D136" t="s">
         <v>119</v>
@@ -17236,7 +17242,7 @@
         <v>255</v>
       </c>
       <c r="F136" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G136">
         <v>0</v>
@@ -17251,16 +17257,16 @@
         <v>0</v>
       </c>
       <c r="K136" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L136">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M136">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N136">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O136">
         <v>0</v>
@@ -17302,10 +17308,10 @@
         <v>0</v>
       </c>
       <c r="AB136">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC136">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD136">
         <v>0</v>
@@ -17326,12 +17332,128 @@
         <v>0</v>
       </c>
       <c r="AJ136" t="s">
+        <v>394</v>
+      </c>
+      <c r="AK136" t="s">
+        <v>394</v>
+      </c>
+      <c r="AL136" s="3">
+        <v>45872.85416666666</v>
+      </c>
+    </row>
+    <row r="137" spans="1:38">
+      <c r="A137" s="2">
+        <v>45872</v>
+      </c>
+      <c r="B137" t="s">
+        <v>74</v>
+      </c>
+      <c r="C137" t="s">
+        <v>75</v>
+      </c>
+      <c r="D137" t="s">
+        <v>119</v>
+      </c>
+      <c r="E137" t="s">
+        <v>256</v>
+      </c>
+      <c r="F137" t="s">
         <v>392</v>
       </c>
-      <c r="AK136" t="s">
-        <v>392</v>
-      </c>
-      <c r="AL136" s="3">
+      <c r="G137">
+        <v>0</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="J137">
+        <v>0</v>
+      </c>
+      <c r="K137" t="s">
+        <v>393</v>
+      </c>
+      <c r="L137">
+        <v>0</v>
+      </c>
+      <c r="M137">
+        <v>0</v>
+      </c>
+      <c r="N137">
+        <v>0</v>
+      </c>
+      <c r="O137">
+        <v>0</v>
+      </c>
+      <c r="P137">
+        <v>0</v>
+      </c>
+      <c r="Q137">
+        <v>0</v>
+      </c>
+      <c r="R137">
+        <v>0</v>
+      </c>
+      <c r="S137">
+        <v>0</v>
+      </c>
+      <c r="T137">
+        <v>0</v>
+      </c>
+      <c r="U137">
+        <v>0</v>
+      </c>
+      <c r="V137">
+        <v>0</v>
+      </c>
+      <c r="W137">
+        <v>0</v>
+      </c>
+      <c r="X137">
+        <v>0</v>
+      </c>
+      <c r="Y137">
+        <v>0</v>
+      </c>
+      <c r="Z137">
+        <v>0</v>
+      </c>
+      <c r="AA137">
+        <v>0</v>
+      </c>
+      <c r="AB137">
+        <v>0</v>
+      </c>
+      <c r="AC137">
+        <v>0</v>
+      </c>
+      <c r="AD137">
+        <v>0</v>
+      </c>
+      <c r="AE137">
+        <v>0</v>
+      </c>
+      <c r="AF137">
+        <v>0</v>
+      </c>
+      <c r="AG137">
+        <v>0</v>
+      </c>
+      <c r="AH137">
+        <v>0</v>
+      </c>
+      <c r="AI137">
+        <v>0</v>
+      </c>
+      <c r="AJ137" t="s">
+        <v>394</v>
+      </c>
+      <c r="AK137" t="s">
+        <v>394</v>
+      </c>
+      <c r="AL137" s="3">
         <v>45872.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-03.xlsx
+++ b/jogos_2025-08-03.xlsx
@@ -259,12 +259,12 @@
     <t>Russia Russian Premier League</t>
   </si>
   <si>
+    <t>England EFL League One</t>
+  </si>
+  <si>
     <t>China Chinese Super League</t>
   </si>
   <si>
-    <t>England EFL League One</t>
-  </si>
-  <si>
     <t>China China League One</t>
   </si>
   <si>
@@ -274,48 +274,48 @@
     <t>Germany 2. Bundesliga</t>
   </si>
   <si>
+    <t>Belgium Pro League</t>
+  </si>
+  <si>
     <t>Germany 3. Liga</t>
   </si>
   <si>
-    <t>Belgium Pro League</t>
-  </si>
-  <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
+    <t>Switzerland Super League</t>
+  </si>
+  <si>
     <t>Denmark Superliga</t>
   </si>
   <si>
     <t>Switzerland Challenge League</t>
   </si>
   <si>
-    <t>Switzerland Super League</t>
+    <t>Norway Eliteserien</t>
   </si>
   <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
-    <t>Norway Eliteserien</t>
-  </si>
-  <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
+    <t>Czech Republic First League</t>
+  </si>
+  <si>
+    <t>Scotland Premiership</t>
+  </si>
+  <si>
     <t>Finland Veikkausliiga</t>
   </si>
   <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
-    <t>Czech Republic First League</t>
-  </si>
-  <si>
-    <t>Scotland Premiership</t>
-  </si>
-  <si>
     <t>Faroe Islands Faroe Islands Premier League</t>
   </si>
   <si>
@@ -382,18 +382,18 @@
     <t>2025/2026</t>
   </si>
   <si>
+    <t>Blacktown City</t>
+  </si>
+  <si>
+    <t>Sydney United</t>
+  </si>
+  <si>
     <t>Central Coast II</t>
   </si>
   <si>
     <t>Wollongong Wolves</t>
   </si>
   <si>
-    <t>Sydney United</t>
-  </si>
-  <si>
-    <t>Blacktown City</t>
-  </si>
-  <si>
     <t>SKA Khabarovsk</t>
   </si>
   <si>
@@ -412,12 +412,12 @@
     <t>Akron</t>
   </si>
   <si>
+    <t>Stockport County</t>
+  </si>
+  <si>
     <t>Dalian Zhixing</t>
   </si>
   <si>
-    <t>Stockport County</t>
-  </si>
-  <si>
     <t>Suzhou Dongwu</t>
   </si>
   <si>
@@ -430,21 +430,21 @@
     <t>Hannover 96</t>
   </si>
   <si>
+    <t>Magdeburg</t>
+  </si>
+  <si>
+    <t>KRC Genk</t>
+  </si>
+  <si>
+    <t>Qingdao Red Lions</t>
+  </si>
+  <si>
     <t>Dongguan United</t>
   </si>
   <si>
-    <t>Qingdao Red Lions</t>
-  </si>
-  <si>
     <t>Erzgebirge Aue</t>
   </si>
   <si>
-    <t>KRC Genk</t>
-  </si>
-  <si>
-    <t>Magdeburg</t>
-  </si>
-  <si>
     <t>Wuhan Three Towns</t>
   </si>
   <si>
@@ -454,25 +454,31 @@
     <t>Sichuan Jiuniu</t>
   </si>
   <si>
+    <t>Djurgården</t>
+  </si>
+  <si>
+    <t>Thun</t>
+  </si>
+  <si>
+    <t>SønderjyskE</t>
+  </si>
+  <si>
+    <t>Randers</t>
+  </si>
+  <si>
+    <t>Spartak Kostroma</t>
+  </si>
+  <si>
     <t>Häcken</t>
   </si>
   <si>
-    <t>SønderjyskE</t>
-  </si>
-  <si>
-    <t>Randers</t>
-  </si>
-  <si>
-    <t>Spartak Kostroma</t>
-  </si>
-  <si>
     <t>Yverdon Sport</t>
   </si>
   <si>
-    <t>Thun</t>
-  </si>
-  <si>
-    <t>Djurgården</t>
+    <t>HamKam</t>
+  </si>
+  <si>
+    <t>Baník Ostrava II</t>
   </si>
   <si>
     <t>Epitsentr Dunayivtsi</t>
@@ -481,33 +487,27 @@
     <t>Śląsk Wrocław</t>
   </si>
   <si>
-    <t>Baník Ostrava II</t>
-  </si>
-  <si>
-    <t>HamKam</t>
-  </si>
-  <si>
     <t>Baltika</t>
   </si>
   <si>
     <t>Cracovia Kraków</t>
   </si>
   <si>
+    <t>Sogndal</t>
+  </si>
+  <si>
+    <t>Landskrona</t>
+  </si>
+  <si>
+    <t>Slovácko</t>
+  </si>
+  <si>
+    <t>Falkirk</t>
+  </si>
+  <si>
     <t>SJK</t>
   </si>
   <si>
-    <t>Sogndal</t>
-  </si>
-  <si>
-    <t>Landskrona</t>
-  </si>
-  <si>
-    <t>Slovácko</t>
-  </si>
-  <si>
-    <t>Falkirk</t>
-  </si>
-  <si>
     <t>Suduroy</t>
   </si>
   <si>
@@ -562,66 +562,66 @@
     <t>Sirius</t>
   </si>
   <si>
+    <t>Pogoń Siedlce</t>
+  </si>
+  <si>
+    <t>Vålerenga</t>
+  </si>
+  <si>
+    <t>Vlašim</t>
+  </si>
+  <si>
+    <t>Petrovac</t>
+  </si>
+  <si>
+    <t>FK Jezero Plav</t>
+  </si>
+  <si>
+    <t>Dečić</t>
+  </si>
+  <si>
+    <t>Rubin Kazan</t>
+  </si>
+  <si>
+    <t>Zenit</t>
+  </si>
+  <si>
     <t>Sutjeska</t>
   </si>
   <si>
-    <t>Vålerenga</t>
-  </si>
-  <si>
-    <t>Pogoń Siedlce</t>
+    <t>Strømsgodset</t>
+  </si>
+  <si>
+    <t>Torpedo BelAZ</t>
+  </si>
+  <si>
+    <t>Karpaty</t>
+  </si>
+  <si>
+    <t>Grazer AK</t>
+  </si>
+  <si>
+    <t>Trenčín</t>
+  </si>
+  <si>
+    <t>Rapid Wien</t>
+  </si>
+  <si>
+    <t>Dukla Praha</t>
+  </si>
+  <si>
+    <t>KFUM</t>
+  </si>
+  <si>
+    <t>Molde</t>
+  </si>
+  <si>
+    <t>Shortan</t>
   </si>
   <si>
     <t>Arsenal Tivat</t>
   </si>
   <si>
-    <t>Petrovac</t>
-  </si>
-  <si>
-    <t>FK Jezero Plav</t>
-  </si>
-  <si>
-    <t>Dečić</t>
-  </si>
-  <si>
-    <t>Rubin Kazan</t>
-  </si>
-  <si>
-    <t>Zenit</t>
-  </si>
-  <si>
-    <t>Strømsgodset</t>
-  </si>
-  <si>
-    <t>Karpaty</t>
-  </si>
-  <si>
-    <t>Vlašim</t>
-  </si>
-  <si>
-    <t>Grazer AK</t>
-  </si>
-  <si>
-    <t>Rapid Wien</t>
-  </si>
-  <si>
-    <t>Trenčín</t>
-  </si>
-  <si>
-    <t>Dukla Praha</t>
-  </si>
-  <si>
-    <t>KFUM</t>
-  </si>
-  <si>
-    <t>Molde</t>
-  </si>
-  <si>
-    <t>Shortan</t>
-  </si>
-  <si>
-    <t>Torpedo BelAZ</t>
-  </si>
-  <si>
     <t>Hermannstadt</t>
   </si>
   <si>
@@ -631,15 +631,15 @@
     <t>Karcag SE</t>
   </si>
   <si>
+    <t>Szentlőrinc SE</t>
+  </si>
+  <si>
+    <t>Radomiak Radom</t>
+  </si>
+  <si>
     <t>Maribor</t>
   </si>
   <si>
-    <t>Szentlőrinc SE</t>
-  </si>
-  <si>
-    <t>Radomiak Radom</t>
-  </si>
-  <si>
     <t>Celtic</t>
   </si>
   <si>
@@ -694,72 +694,72 @@
     <t>Ajka</t>
   </si>
   <si>
+    <t>Békéscsaba</t>
+  </si>
+  <si>
+    <t>Csákvári TK</t>
+  </si>
+  <si>
+    <t>Sporting KC II</t>
+  </si>
+  <si>
     <t>MKK-Dnepr</t>
   </si>
   <si>
-    <t>Csákvári TK</t>
-  </si>
-  <si>
-    <t>Sporting KC II</t>
-  </si>
-  <si>
     <t>Honvéd W</t>
   </si>
   <si>
-    <t>Békéscsaba</t>
-  </si>
-  <si>
     <t>Sporting Charleroi</t>
   </si>
   <si>
+    <t>Makhachkala</t>
+  </si>
+  <si>
     <t>Górnik Łęczna</t>
   </si>
   <si>
-    <t>Makhachkala</t>
-  </si>
-  <si>
     <t>Wehen Wiesbaden</t>
   </si>
   <si>
+    <t>Chicago Fire II</t>
+  </si>
+  <si>
     <t>Győri ETO</t>
   </si>
   <si>
-    <t>Chicago Fire II</t>
-  </si>
-  <si>
     <t>Pardubice</t>
   </si>
   <si>
+    <t>Olimpija</t>
+  </si>
+  <si>
+    <t>Levski Sofia</t>
+  </si>
+  <si>
     <t>Legia Warszawa</t>
   </si>
   <si>
-    <t>Olimpija</t>
-  </si>
-  <si>
-    <t>Levski Sofia</t>
-  </si>
-  <si>
     <t>CFR Cluj</t>
   </si>
   <si>
     <t>Botafogo</t>
   </si>
   <si>
+    <t>Hajduk Split</t>
+  </si>
+  <si>
+    <t>Corinthians</t>
+  </si>
+  <si>
+    <t>Colo-Colo</t>
+  </si>
+  <si>
+    <t>Chapecoense</t>
+  </si>
+  <si>
     <t>Partizan</t>
   </si>
   <si>
-    <t>Hajduk Split</t>
-  </si>
-  <si>
-    <t>Colo-Colo</t>
-  </si>
-  <si>
-    <t>Chapecoense</t>
-  </si>
-  <si>
-    <t>Corinthians</t>
-  </si>
-  <si>
     <t>Atlético Ottawa</t>
   </si>
   <si>
@@ -796,18 +796,18 @@
     <t>Los Angeles II</t>
   </si>
   <si>
+    <t>Mt Druitt Town</t>
+  </si>
+  <si>
+    <t>St. George Saints</t>
+  </si>
+  <si>
     <t>Marconi Stallions</t>
   </si>
   <si>
     <t>Sydney II</t>
   </si>
   <si>
-    <t>St. George Saints</t>
-  </si>
-  <si>
-    <t>Mt Druitt Town</t>
-  </si>
-  <si>
     <t>Torpedo Moskva</t>
   </si>
   <si>
@@ -826,12 +826,12 @@
     <t>Spartak Moskva</t>
   </si>
   <si>
+    <t>Bolton Wanderers</t>
+  </si>
+  <si>
     <t>Qingdao Jonoon</t>
   </si>
   <si>
-    <t>Bolton Wanderers</t>
-  </si>
-  <si>
     <t>Dalian Huayi</t>
   </si>
   <si>
@@ -844,21 +844,21 @@
     <t>Kaiserslautern</t>
   </si>
   <si>
+    <t>Eintracht Braunschweig</t>
+  </si>
+  <si>
+    <t>Royal Antwerp FC</t>
+  </si>
+  <si>
+    <t>Heilongjiang Lava Spring</t>
+  </si>
+  <si>
     <t>Nantong Zhiyun</t>
   </si>
   <si>
-    <t>Heilongjiang Lava Spring</t>
-  </si>
-  <si>
     <t>Hansa Rostock</t>
   </si>
   <si>
-    <t>Royal Antwerp FC</t>
-  </si>
-  <si>
-    <t>Eintracht Braunschweig</t>
-  </si>
-  <si>
     <t>Changchun Yatai</t>
   </si>
   <si>
@@ -868,25 +868,31 @@
     <t>Zhejiang FC</t>
   </si>
   <si>
+    <t>Halmstad</t>
+  </si>
+  <si>
+    <t>Lausanne Sport</t>
+  </si>
+  <si>
+    <t>Nordsjælland</t>
+  </si>
+  <si>
+    <t>Silkeborg</t>
+  </si>
+  <si>
+    <t>Neftekhimik</t>
+  </si>
+  <si>
     <t>Elfsborg</t>
   </si>
   <si>
-    <t>Nordsjælland</t>
-  </si>
-  <si>
-    <t>Silkeborg</t>
-  </si>
-  <si>
-    <t>Neftekhimik</t>
-  </si>
-  <si>
     <t>Stade Lausanne-Ouchy</t>
   </si>
   <si>
-    <t>Lausanne Sport</t>
-  </si>
-  <si>
-    <t>Halmstad</t>
+    <t>FK Bodo - Glimt</t>
+  </si>
+  <si>
+    <t>Líšeň</t>
   </si>
   <si>
     <t>Shakhtar Donetsk</t>
@@ -895,33 +901,27 @@
     <t>Ruch Chorzów</t>
   </si>
   <si>
-    <t>Líšeň</t>
-  </si>
-  <si>
-    <t>FK Bodo - Glimt</t>
-  </si>
-  <si>
     <t>Orenburg</t>
   </si>
   <si>
     <t>Lechia Gdańsk</t>
   </si>
   <si>
+    <t>Skeid</t>
+  </si>
+  <si>
+    <t>Västerås SK</t>
+  </si>
+  <si>
+    <t>Slavia Praha</t>
+  </si>
+  <si>
+    <t>Dundee United</t>
+  </si>
+  <si>
     <t>KTP</t>
   </si>
   <si>
-    <t>Skeid</t>
-  </si>
-  <si>
-    <t>Västerås SK</t>
-  </si>
-  <si>
-    <t>Slavia Praha</t>
-  </si>
-  <si>
-    <t>Dundee United</t>
-  </si>
-  <si>
     <t>HB</t>
   </si>
   <si>
@@ -976,66 +976,66 @@
     <t>Öster</t>
   </si>
   <si>
+    <t>Odra Opole</t>
+  </si>
+  <si>
+    <t>Sandefjord</t>
+  </si>
+  <si>
+    <t>Hanácká</t>
+  </si>
+  <si>
+    <t>Bokelj</t>
+  </si>
+  <si>
+    <t>Budućnost</t>
+  </si>
+  <si>
+    <t>Mladost DG</t>
+  </si>
+  <si>
+    <t>FK Sochi</t>
+  </si>
+  <si>
+    <t>CSKA Moskva</t>
+  </si>
+  <si>
     <t>Mornar</t>
   </si>
   <si>
-    <t>Sandefjord</t>
-  </si>
-  <si>
-    <t>Odra Opole</t>
+    <t>Haugesund</t>
+  </si>
+  <si>
+    <t>Gomel</t>
+  </si>
+  <si>
+    <t>Polessya</t>
+  </si>
+  <si>
+    <t>Austria Wien</t>
+  </si>
+  <si>
+    <t>Spartak Trnava</t>
+  </si>
+  <si>
+    <t>Blau-Weiß Linz</t>
+  </si>
+  <si>
+    <t>Baník Ostrava</t>
+  </si>
+  <si>
+    <t>Rosenborg</t>
+  </si>
+  <si>
+    <t>Bryne</t>
+  </si>
+  <si>
+    <t>Xorazm</t>
   </si>
   <si>
     <t>Jedinstvo</t>
   </si>
   <si>
-    <t>Bokelj</t>
-  </si>
-  <si>
-    <t>Budućnost</t>
-  </si>
-  <si>
-    <t>Mladost DG</t>
-  </si>
-  <si>
-    <t>FK Sochi</t>
-  </si>
-  <si>
-    <t>CSKA Moskva</t>
-  </si>
-  <si>
-    <t>Haugesund</t>
-  </si>
-  <si>
-    <t>Polessya</t>
-  </si>
-  <si>
-    <t>Hanácká</t>
-  </si>
-  <si>
-    <t>Austria Wien</t>
-  </si>
-  <si>
-    <t>Blau-Weiß Linz</t>
-  </si>
-  <si>
-    <t>Spartak Trnava</t>
-  </si>
-  <si>
-    <t>Baník Ostrava</t>
-  </si>
-  <si>
-    <t>Rosenborg</t>
-  </si>
-  <si>
-    <t>Bryne</t>
-  </si>
-  <si>
-    <t>Xorazm</t>
-  </si>
-  <si>
-    <t>Gomel</t>
-  </si>
-  <si>
     <t>Universitatea Cluj</t>
   </si>
   <si>
@@ -1045,15 +1045,15 @@
     <t>Soroksár SC</t>
   </si>
   <si>
+    <t>Kozármisleny</t>
+  </si>
+  <si>
+    <t>Raków Częstochowa</t>
+  </si>
+  <si>
     <t>Koper</t>
   </si>
   <si>
-    <t>Kozármisleny</t>
-  </si>
-  <si>
-    <t>Raków Częstochowa</t>
-  </si>
-  <si>
     <t>St. Mirren</t>
   </si>
   <si>
@@ -1108,70 +1108,70 @@
     <t>Videoton</t>
   </si>
   <si>
+    <t>Szeged 2011</t>
+  </si>
+  <si>
+    <t>BVSC</t>
+  </si>
+  <si>
+    <t>Austin II</t>
+  </si>
+  <si>
     <t>Slutsk</t>
   </si>
   <si>
-    <t>BVSC</t>
-  </si>
-  <si>
-    <t>Austin II</t>
-  </si>
-  <si>
     <t>Budafoki MTE</t>
   </si>
   <si>
-    <t>Szeged 2011</t>
-  </si>
-  <si>
     <t>Sint-Truiden</t>
   </si>
   <si>
+    <t>Akhmat Grozny</t>
+  </si>
+  <si>
     <t>Puszcza Niepołomice</t>
   </si>
   <si>
-    <t>Akhmat Grozny</t>
-  </si>
-  <si>
     <t>Ulm</t>
   </si>
   <si>
+    <t>Columbus Crew II</t>
+  </si>
+  <si>
     <t>Újpest</t>
   </si>
   <si>
-    <t>Columbus Crew II</t>
-  </si>
-  <si>
     <t>Sparta Praha</t>
   </si>
   <si>
+    <t>Celje</t>
+  </si>
+  <si>
+    <t>Slavia Sofia</t>
+  </si>
+  <si>
     <t>Arka Gdynia</t>
   </si>
   <si>
-    <t>Celje</t>
-  </si>
-  <si>
-    <t>Slavia Sofia</t>
-  </si>
-  <si>
     <t>CS U Craiova</t>
   </si>
   <si>
     <t>Cruzeiro</t>
   </si>
   <si>
+    <t>Istra 1961</t>
+  </si>
+  <si>
+    <t>Fortaleza</t>
+  </si>
+  <si>
+    <t>Huachipato</t>
+  </si>
+  <si>
+    <t>CRB</t>
+  </si>
+  <si>
     <t>Radnički Kragujevac</t>
-  </si>
-  <si>
-    <t>Istra 1961</t>
-  </si>
-  <si>
-    <t>Huachipato</t>
-  </si>
-  <si>
-    <t>CRB</t>
-  </si>
-  <si>
-    <t>Fortaleza</t>
   </si>
   <si>
     <t>York9 FC</t>
@@ -2867,7 +2867,7 @@
         <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E12" t="s">
         <v>132</v>
@@ -2891,13 +2891,13 @@
         <v>398</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -2939,10 +2939,10 @@
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AD12">
         <v>0</v>
@@ -2983,7 +2983,7 @@
         <v>82</v>
       </c>
       <c r="D13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E13" t="s">
         <v>133</v>
@@ -3007,13 +3007,13 @@
         <v>398</v>
       </c>
       <c r="L13">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M13">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N13">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -3055,10 +3055,10 @@
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC13">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AD13">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>44</v>
       </c>
       <c r="C18" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D18" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E18" t="s">
         <v>138</v>
@@ -3587,13 +3587,13 @@
         <v>398</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -3635,10 +3635,10 @@
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD18">
         <v>0</v>
@@ -3676,10 +3676,10 @@
         <v>44</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D19" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E19" t="s">
         <v>139</v>
@@ -3703,13 +3703,13 @@
         <v>398</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -3757,10 +3757,10 @@
         <v>0</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF19">
         <v>0</v>
@@ -3792,10 +3792,10 @@
         <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E20" t="s">
         <v>140</v>
@@ -3908,10 +3908,10 @@
         <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D21" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E21" t="s">
         <v>141</v>
@@ -3935,13 +3935,13 @@
         <v>398</v>
       </c>
       <c r="L21">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M21">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N21">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -3989,10 +3989,10 @@
         <v>0</v>
       </c>
       <c r="AD21">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE21">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF21">
         <v>0</v>
@@ -4024,7 +4024,7 @@
         <v>44</v>
       </c>
       <c r="C22" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D22" t="s">
         <v>121</v>
@@ -4051,13 +4051,13 @@
         <v>398</v>
       </c>
       <c r="L22">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M22">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N22">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -4099,10 +4099,10 @@
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC22">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD22">
         <v>0</v>
@@ -4140,7 +4140,7 @@
         <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D23" t="s">
         <v>120</v>
@@ -4256,7 +4256,7 @@
         <v>45</v>
       </c>
       <c r="C24" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D24" t="s">
         <v>120</v>
@@ -4372,7 +4372,7 @@
         <v>46</v>
       </c>
       <c r="C25" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D25" t="s">
         <v>120</v>
@@ -4515,13 +4515,13 @@
         <v>398</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -4563,10 +4563,10 @@
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD26">
         <v>0</v>
@@ -4631,13 +4631,13 @@
         <v>398</v>
       </c>
       <c r="L27">
-        <v>4.1</v>
+        <v>2.72</v>
       </c>
       <c r="M27">
-        <v>3.95</v>
+        <v>3.38</v>
       </c>
       <c r="N27">
-        <v>1.75</v>
+        <v>2.19</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -4679,10 +4679,10 @@
         <v>0</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD27">
         <v>0</v>
@@ -4720,7 +4720,7 @@
         <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D28" t="s">
         <v>121</v>
@@ -4747,13 +4747,13 @@
         <v>398</v>
       </c>
       <c r="L28">
-        <v>1.89</v>
+        <v>4.1</v>
       </c>
       <c r="M28">
-        <v>3.53</v>
+        <v>3.95</v>
       </c>
       <c r="N28">
-        <v>3.25</v>
+        <v>1.75</v>
       </c>
       <c r="O28">
         <v>0</v>
@@ -4795,10 +4795,10 @@
         <v>0</v>
       </c>
       <c r="AB28">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC28">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD28">
         <v>0</v>
@@ -4836,7 +4836,7 @@
         <v>46</v>
       </c>
       <c r="C29" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="D29" t="s">
         <v>121</v>
@@ -4863,13 +4863,13 @@
         <v>398</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O29">
         <v>0</v>
@@ -4911,10 +4911,10 @@
         <v>0</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD29">
         <v>0</v>
@@ -4952,7 +4952,7 @@
         <v>46</v>
       </c>
       <c r="C30" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="D30" t="s">
         <v>121</v>
@@ -5068,10 +5068,10 @@
         <v>46</v>
       </c>
       <c r="C31" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D31" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E31" t="s">
         <v>151</v>
@@ -5095,13 +5095,13 @@
         <v>398</v>
       </c>
       <c r="L31">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="M31">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N31">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O31">
         <v>0</v>
@@ -5143,10 +5143,10 @@
         <v>0</v>
       </c>
       <c r="AB31">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC31">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD31">
         <v>0</v>
@@ -5184,10 +5184,10 @@
         <v>46</v>
       </c>
       <c r="C32" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D32" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E32" t="s">
         <v>152</v>
@@ -5211,13 +5211,13 @@
         <v>398</v>
       </c>
       <c r="L32">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="M32">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N32">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="O32">
         <v>0</v>
@@ -5259,10 +5259,10 @@
         <v>0</v>
       </c>
       <c r="AB32">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC32">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD32">
         <v>0</v>
@@ -5300,10 +5300,10 @@
         <v>47</v>
       </c>
       <c r="C33" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="D33" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E33" t="s">
         <v>153</v>
@@ -5327,13 +5327,13 @@
         <v>398</v>
       </c>
       <c r="L33">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="M33">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N33">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -5381,10 +5381,10 @@
         <v>0</v>
       </c>
       <c r="AD33">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE33">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AF33">
         <v>0</v>
@@ -5416,7 +5416,7 @@
         <v>47</v>
       </c>
       <c r="C34" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="D34" t="s">
         <v>121</v>
@@ -5532,7 +5532,7 @@
         <v>47</v>
       </c>
       <c r="C35" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D35" t="s">
         <v>121</v>
@@ -5559,13 +5559,13 @@
         <v>398</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O35">
         <v>0</v>
@@ -5613,10 +5613,10 @@
         <v>0</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF35">
         <v>0</v>
@@ -5651,7 +5651,7 @@
         <v>93</v>
       </c>
       <c r="D36" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E36" t="s">
         <v>156</v>
@@ -6023,13 +6023,13 @@
         <v>398</v>
       </c>
       <c r="L39">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M39">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N39">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O39">
         <v>0</v>
@@ -6077,10 +6077,10 @@
         <v>0</v>
       </c>
       <c r="AD39">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE39">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF39">
         <v>0</v>
@@ -6139,13 +6139,13 @@
         <v>398</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M40">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O40">
         <v>0</v>
@@ -6193,10 +6193,10 @@
         <v>0</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF40">
         <v>0</v>
@@ -6231,7 +6231,7 @@
         <v>97</v>
       </c>
       <c r="D41" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E41" t="s">
         <v>161</v>
@@ -6255,13 +6255,13 @@
         <v>398</v>
       </c>
       <c r="L41">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M41">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N41">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O41">
         <v>0</v>
@@ -6309,10 +6309,10 @@
         <v>0</v>
       </c>
       <c r="AD41">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE41">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF41">
         <v>0</v>
@@ -6371,13 +6371,13 @@
         <v>398</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M42">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O42">
         <v>0</v>
@@ -6419,10 +6419,10 @@
         <v>0</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD42">
         <v>0</v>
@@ -6463,7 +6463,7 @@
         <v>99</v>
       </c>
       <c r="D43" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E43" t="s">
         <v>163</v>
@@ -6487,64 +6487,64 @@
         <v>398</v>
       </c>
       <c r="L43">
+        <v>1.42</v>
+      </c>
+      <c r="M43">
+        <v>4.33</v>
+      </c>
+      <c r="N43">
+        <v>5.4</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>0</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
+        <v>0</v>
+      </c>
+      <c r="T43">
+        <v>0</v>
+      </c>
+      <c r="U43">
+        <v>0</v>
+      </c>
+      <c r="V43">
+        <v>0</v>
+      </c>
+      <c r="W43">
+        <v>0</v>
+      </c>
+      <c r="X43">
+        <v>0</v>
+      </c>
+      <c r="Y43">
+        <v>0</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+      <c r="AA43">
+        <v>0</v>
+      </c>
+      <c r="AB43">
+        <v>0</v>
+      </c>
+      <c r="AC43">
+        <v>0</v>
+      </c>
+      <c r="AD43">
+        <v>1.9</v>
+      </c>
+      <c r="AE43">
         <v>1.8</v>
-      </c>
-      <c r="M43">
-        <v>3.39</v>
-      </c>
-      <c r="N43">
-        <v>3.71</v>
-      </c>
-      <c r="O43">
-        <v>0</v>
-      </c>
-      <c r="P43">
-        <v>0</v>
-      </c>
-      <c r="Q43">
-        <v>0</v>
-      </c>
-      <c r="R43">
-        <v>0</v>
-      </c>
-      <c r="S43">
-        <v>0</v>
-      </c>
-      <c r="T43">
-        <v>0</v>
-      </c>
-      <c r="U43">
-        <v>0</v>
-      </c>
-      <c r="V43">
-        <v>0</v>
-      </c>
-      <c r="W43">
-        <v>0</v>
-      </c>
-      <c r="X43">
-        <v>0</v>
-      </c>
-      <c r="Y43">
-        <v>0</v>
-      </c>
-      <c r="Z43">
-        <v>0</v>
-      </c>
-      <c r="AA43">
-        <v>0</v>
-      </c>
-      <c r="AB43">
-        <v>1.7</v>
-      </c>
-      <c r="AC43">
-        <v>2.1</v>
-      </c>
-      <c r="AD43">
-        <v>0</v>
-      </c>
-      <c r="AE43">
-        <v>0</v>
       </c>
       <c r="AF43">
         <v>0</v>
@@ -7156,7 +7156,7 @@
         <v>51</v>
       </c>
       <c r="C49" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D49" t="s">
         <v>121</v>
@@ -7272,7 +7272,7 @@
         <v>51</v>
       </c>
       <c r="C50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D50" t="s">
         <v>121</v>
@@ -7388,7 +7388,7 @@
         <v>51</v>
       </c>
       <c r="C51" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D51" t="s">
         <v>121</v>
@@ -8200,7 +8200,7 @@
         <v>52</v>
       </c>
       <c r="C58" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D58" t="s">
         <v>121</v>
@@ -8316,7 +8316,7 @@
         <v>52</v>
       </c>
       <c r="C59" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D59" t="s">
         <v>121</v>
@@ -8432,7 +8432,7 @@
         <v>52</v>
       </c>
       <c r="C60" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D60" t="s">
         <v>121</v>
@@ -8664,7 +8664,7 @@
         <v>53</v>
       </c>
       <c r="C62" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D62" t="s">
         <v>121</v>
@@ -8691,13 +8691,13 @@
         <v>398</v>
       </c>
       <c r="L62">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M62">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O62">
         <v>0</v>
@@ -8780,7 +8780,7 @@
         <v>53</v>
       </c>
       <c r="C63" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D63" t="s">
         <v>120</v>
@@ -8896,7 +8896,7 @@
         <v>53</v>
       </c>
       <c r="C64" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="D64" t="s">
         <v>121</v>
@@ -8923,13 +8923,13 @@
         <v>398</v>
       </c>
       <c r="L64">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M64">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N64">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O64">
         <v>0</v>
@@ -9360,7 +9360,7 @@
         <v>53</v>
       </c>
       <c r="C68" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="D68" t="s">
         <v>121</v>
@@ -9503,13 +9503,13 @@
         <v>398</v>
       </c>
       <c r="L69">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M69">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O69">
         <v>0</v>
@@ -9551,10 +9551,10 @@
         <v>0</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD69">
         <v>0</v>
@@ -9592,7 +9592,7 @@
         <v>53</v>
       </c>
       <c r="C70" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="D70" t="s">
         <v>121</v>
@@ -9619,13 +9619,13 @@
         <v>398</v>
       </c>
       <c r="L70">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M70">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N70">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O70">
         <v>0</v>
@@ -9667,10 +9667,10 @@
         <v>0</v>
       </c>
       <c r="AB70">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC70">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD70">
         <v>0</v>
@@ -9708,7 +9708,7 @@
         <v>53</v>
       </c>
       <c r="C71" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D71" t="s">
         <v>120</v>
@@ -9824,10 +9824,10 @@
         <v>53</v>
       </c>
       <c r="C72" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D72" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E72" t="s">
         <v>192</v>
@@ -9851,13 +9851,13 @@
         <v>398</v>
       </c>
       <c r="L72">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="M72">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N72">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -9899,10 +9899,10 @@
         <v>0</v>
       </c>
       <c r="AB72">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC72">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD72">
         <v>0</v>
@@ -9940,7 +9940,7 @@
         <v>53</v>
       </c>
       <c r="C73" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D73" t="s">
         <v>121</v>
@@ -9967,13 +9967,13 @@
         <v>398</v>
       </c>
       <c r="L73">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="M73">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O73">
         <v>0</v>
@@ -10015,10 +10015,10 @@
         <v>0</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD73">
         <v>0</v>
@@ -10172,7 +10172,7 @@
         <v>53</v>
       </c>
       <c r="C75" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D75" t="s">
         <v>121</v>
@@ -10199,13 +10199,13 @@
         <v>398</v>
       </c>
       <c r="L75">
-        <v>1.44</v>
+        <v>3.56</v>
       </c>
       <c r="M75">
-        <v>4.2</v>
+        <v>3.32</v>
       </c>
       <c r="N75">
-        <v>5.4</v>
+        <v>1.86</v>
       </c>
       <c r="O75">
         <v>0</v>
@@ -10247,10 +10247,10 @@
         <v>0</v>
       </c>
       <c r="AB75">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AC75">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AD75">
         <v>0</v>
@@ -10288,7 +10288,7 @@
         <v>53</v>
       </c>
       <c r="C76" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D76" t="s">
         <v>121</v>
@@ -10315,13 +10315,13 @@
         <v>398</v>
       </c>
       <c r="L76">
-        <v>3.56</v>
+        <v>1.44</v>
       </c>
       <c r="M76">
-        <v>3.32</v>
+        <v>4.2</v>
       </c>
       <c r="N76">
-        <v>1.86</v>
+        <v>5.4</v>
       </c>
       <c r="O76">
         <v>0</v>
@@ -10363,10 +10363,10 @@
         <v>0</v>
       </c>
       <c r="AB76">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AC76">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AD76">
         <v>0</v>
@@ -10404,7 +10404,7 @@
         <v>53</v>
       </c>
       <c r="C77" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D77" t="s">
         <v>121</v>
@@ -10520,7 +10520,7 @@
         <v>53</v>
       </c>
       <c r="C78" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D78" t="s">
         <v>120</v>
@@ -10636,7 +10636,7 @@
         <v>53</v>
       </c>
       <c r="C79" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D79" t="s">
         <v>120</v>
@@ -10868,10 +10868,10 @@
         <v>53</v>
       </c>
       <c r="C81" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="D81" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E81" t="s">
         <v>201</v>
@@ -11332,7 +11332,7 @@
         <v>54</v>
       </c>
       <c r="C85" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D85" t="s">
         <v>121</v>
@@ -11448,7 +11448,7 @@
         <v>54</v>
       </c>
       <c r="C86" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="D86" t="s">
         <v>121</v>
@@ -11475,13 +11475,13 @@
         <v>398</v>
       </c>
       <c r="L86">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="M86">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O86">
         <v>0</v>
@@ -11523,10 +11523,10 @@
         <v>0</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD86">
         <v>0</v>
@@ -11564,7 +11564,7 @@
         <v>54</v>
       </c>
       <c r="C87" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="D87" t="s">
         <v>121</v>
@@ -11591,13 +11591,13 @@
         <v>398</v>
       </c>
       <c r="L87">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="M87">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N87">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O87">
         <v>0</v>
@@ -11639,10 +11639,10 @@
         <v>0</v>
       </c>
       <c r="AB87">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC87">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AD87">
         <v>0</v>
@@ -11680,7 +11680,7 @@
         <v>54</v>
       </c>
       <c r="C88" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D88" t="s">
         <v>121</v>
@@ -12492,7 +12492,7 @@
         <v>56</v>
       </c>
       <c r="C95" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D95" t="s">
         <v>121</v>
@@ -12956,7 +12956,7 @@
         <v>58</v>
       </c>
       <c r="C99" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D99" t="s">
         <v>121</v>
@@ -13768,10 +13768,10 @@
         <v>60</v>
       </c>
       <c r="C106" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="D106" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E106" t="s">
         <v>226</v>
@@ -14116,10 +14116,10 @@
         <v>60</v>
       </c>
       <c r="C109" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="D109" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E109" t="s">
         <v>229</v>
@@ -14348,7 +14348,7 @@
         <v>61</v>
       </c>
       <c r="C111" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D111" t="s">
         <v>121</v>
@@ -14464,7 +14464,7 @@
         <v>62</v>
       </c>
       <c r="C112" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D112" t="s">
         <v>121</v>
@@ -14491,13 +14491,13 @@
         <v>398</v>
       </c>
       <c r="L112">
-        <v>2.39</v>
+        <v>2.46</v>
       </c>
       <c r="M112">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="N112">
-        <v>2.73</v>
+        <v>3.14</v>
       </c>
       <c r="O112">
         <v>0</v>
@@ -14533,16 +14533,16 @@
         <v>0</v>
       </c>
       <c r="Z112">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA112">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB112">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC112">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD112">
         <v>0</v>
@@ -14580,7 +14580,7 @@
         <v>62</v>
       </c>
       <c r="C113" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="D113" t="s">
         <v>121</v>
@@ -14607,13 +14607,13 @@
         <v>398</v>
       </c>
       <c r="L113">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="M113">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="N113">
-        <v>3.14</v>
+        <v>2.73</v>
       </c>
       <c r="O113">
         <v>0</v>
@@ -14649,16 +14649,16 @@
         <v>0</v>
       </c>
       <c r="Z113">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA113">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB113">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC113">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD113">
         <v>0</v>
@@ -14696,7 +14696,7 @@
         <v>62</v>
       </c>
       <c r="C114" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D114" t="s">
         <v>121</v>
@@ -14812,10 +14812,10 @@
         <v>63</v>
       </c>
       <c r="C115" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D115" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E115" t="s">
         <v>235</v>
@@ -14839,13 +14839,13 @@
         <v>398</v>
       </c>
       <c r="L115">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M115">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N115">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O115">
         <v>0</v>
@@ -14887,10 +14887,10 @@
         <v>0</v>
       </c>
       <c r="AB115">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC115">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD115">
         <v>0</v>
@@ -14928,10 +14928,10 @@
         <v>63</v>
       </c>
       <c r="C116" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D116" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E116" t="s">
         <v>236</v>
@@ -14955,13 +14955,13 @@
         <v>398</v>
       </c>
       <c r="L116">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M116">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O116">
         <v>0</v>
@@ -15003,10 +15003,10 @@
         <v>0</v>
       </c>
       <c r="AB116">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC116">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD116">
         <v>0</v>
@@ -15044,7 +15044,7 @@
         <v>63</v>
       </c>
       <c r="C117" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D117" t="s">
         <v>121</v>
@@ -15160,7 +15160,7 @@
         <v>64</v>
       </c>
       <c r="C118" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="D118" t="s">
         <v>121</v>
@@ -15187,13 +15187,13 @@
         <v>398</v>
       </c>
       <c r="L118">
-        <v>1.51</v>
+        <v>2.11</v>
       </c>
       <c r="M118">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="N118">
-        <v>5.2</v>
+        <v>3.1</v>
       </c>
       <c r="O118">
         <v>0</v>
@@ -15276,7 +15276,7 @@
         <v>64</v>
       </c>
       <c r="C119" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D119" t="s">
         <v>121</v>
@@ -15303,13 +15303,13 @@
         <v>398</v>
       </c>
       <c r="L119">
-        <v>2.11</v>
+        <v>1.5</v>
       </c>
       <c r="M119">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="N119">
-        <v>3.1</v>
+        <v>5.6</v>
       </c>
       <c r="O119">
         <v>0</v>
@@ -15351,10 +15351,10 @@
         <v>0</v>
       </c>
       <c r="AB119">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC119">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD119">
         <v>0</v>
@@ -15392,7 +15392,7 @@
         <v>64</v>
       </c>
       <c r="C120" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="D120" t="s">
         <v>121</v>
@@ -15419,13 +15419,13 @@
         <v>398</v>
       </c>
       <c r="L120">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M120">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="N120">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="O120">
         <v>0</v>
@@ -15467,10 +15467,10 @@
         <v>0</v>
       </c>
       <c r="AB120">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC120">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD120">
         <v>0</v>
@@ -15740,7 +15740,7 @@
         <v>66</v>
       </c>
       <c r="C123" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D123" t="s">
         <v>121</v>
@@ -15767,13 +15767,13 @@
         <v>398</v>
       </c>
       <c r="L123">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M123">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="N123">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="O123">
         <v>0</v>
@@ -15815,10 +15815,10 @@
         <v>0</v>
       </c>
       <c r="AB123">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC123">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD123">
         <v>0</v>
@@ -15856,10 +15856,10 @@
         <v>66</v>
       </c>
       <c r="C124" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D124" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E124" t="s">
         <v>244</v>
@@ -15883,13 +15883,13 @@
         <v>398</v>
       </c>
       <c r="L124">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="M124">
-        <v>3.88</v>
+        <v>3.19</v>
       </c>
       <c r="N124">
-        <v>5.06</v>
+        <v>4.9</v>
       </c>
       <c r="O124">
         <v>0</v>
@@ -15931,10 +15931,10 @@
         <v>0</v>
       </c>
       <c r="AB124">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AC124">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AD124">
         <v>0</v>
@@ -16204,10 +16204,10 @@
         <v>66</v>
       </c>
       <c r="C127" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D127" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E127" t="s">
         <v>247</v>
@@ -16231,13 +16231,13 @@
         <v>398</v>
       </c>
       <c r="L127">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M127">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N127">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O127">
         <v>0</v>
@@ -16279,10 +16279,10 @@
         <v>0</v>
       </c>
       <c r="AB127">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC127">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD127">
         <v>0</v>

--- a/jogos_2025-08-03.xlsx
+++ b/jogos_2025-08-03.xlsx
@@ -648,12 +648,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Central Coast II</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mt Druitt Town</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>Mt Druitt Town</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Central Coast II</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>Roasso Kumamoto</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Oleksandria</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>5.3</v>
+        <v>3.15</v>
       </c>
       <c r="M9" t="n">
-        <v>3.41</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1640,16 +1640,16 @@
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Roasso Kumamoto</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Oleksandria</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.15</v>
+        <v>5.3</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>3.41</v>
       </c>
       <c r="N10" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1772,16 +1772,16 @@
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Molodechno-DYuSSh 4</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Molodechno-DYuSSh 4</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.09</v>
+        <v>1.8</v>
       </c>
       <c r="M16" t="n">
-        <v>3.74</v>
+        <v>3.53</v>
       </c>
       <c r="N16" t="n">
-        <v>3.08</v>
+        <v>4.33</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,16 +2570,16 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,16 +2702,16 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,16 +2834,16 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,16 +3098,16 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,10 +3230,10 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3278,22 +3278,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.39</v>
+        <v>1.64</v>
       </c>
       <c r="M23" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="N23" t="n">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.64</v>
+        <v>1.39</v>
       </c>
       <c r="M24" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="N24" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.41</v>
+        <v>3.34</v>
       </c>
       <c r="M26" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N26" t="n">
-        <v>2.46</v>
+        <v>1.89</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,16 +3890,16 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -3938,22 +3938,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4070,22 +4070,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.34</v>
+        <v>2.41</v>
       </c>
       <c r="M28" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N28" t="n">
-        <v>1.89</v>
+        <v>2.46</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4154,16 +4154,16 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -4202,22 +4202,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4286,10 +4286,10 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4334,22 +4334,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.24</v>
+        <v>3.24</v>
       </c>
       <c r="M30" t="n">
-        <v>5</v>
+        <v>2.98</v>
       </c>
       <c r="N30" t="n">
-        <v>8.800000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4418,10 +4418,10 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -4466,22 +4466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4946,16 +4946,16 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5078,16 +5078,16 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.45</v>
+        <v>1.85</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.55</v>
+        <v>1.85</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
         <v>0</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.76</v>
+        <v>2.06</v>
       </c>
       <c r="M37" t="n">
-        <v>3.53</v>
+        <v>3.2</v>
       </c>
       <c r="N37" t="n">
-        <v>3.73</v>
+        <v>3.69</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.24</v>
+        <v>1.7</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.06</v>
+        <v>1.76</v>
       </c>
       <c r="M38" t="n">
-        <v>3.2</v>
+        <v>3.53</v>
       </c>
       <c r="N38" t="n">
-        <v>3.69</v>
+        <v>3.73</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.15</v>
+        <v>1.6</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.7</v>
+        <v>2.24</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5612,10 +5612,10 @@
         <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF39" t="n">
         <v>0</v>
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,10 +5738,10 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.47</v>
+        <v>1.42</v>
       </c>
       <c r="M41" t="n">
-        <v>3.66</v>
+        <v>4.33</v>
       </c>
       <c r="N41" t="n">
-        <v>2.26</v>
+        <v>5.4</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5876,10 +5876,10 @@
         <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AF41" t="n">
         <v>0</v>
@@ -5918,22 +5918,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6050,22 +6050,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.42</v>
+        <v>1.8</v>
       </c>
       <c r="M43" t="n">
-        <v>4.33</v>
+        <v>3.39</v>
       </c>
       <c r="N43" t="n">
-        <v>5.4</v>
+        <v>3.71</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6134,16 +6134,16 @@
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
         <v>0</v>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Jeunesse Canach</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Jeunesse Canach</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6530,10 +6530,10 @@
         <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6710,22 +6710,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7058,10 +7058,10 @@
         <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD50" t="n">
         <v>0</v>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,13 +7142,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7190,10 +7190,10 @@
         <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD51" t="n">
         <v>0</v>
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7538,13 +7538,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7586,10 +7586,10 @@
         <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD54" t="n">
         <v>0</v>
@@ -7634,22 +7634,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7670,13 +7670,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7718,10 +7718,10 @@
         <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
         <v>0</v>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7802,13 +7802,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7850,10 +7850,10 @@
         <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
         <v>0</v>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8066,13 +8066,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8558,22 +8558,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Trenčín</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spartak Trnava</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8594,13 +8594,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.56</v>
+        <v>1.93</v>
       </c>
       <c r="M62" t="n">
-        <v>3.32</v>
+        <v>3.41</v>
       </c>
       <c r="N62" t="n">
-        <v>1.86</v>
+        <v>3.23</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8642,16 +8642,16 @@
         <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.78</v>
+        <v>1.45</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.92</v>
+        <v>2.55</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF62" t="n">
         <v>0</v>
@@ -8690,22 +8690,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Karpaty</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8774,10 +8774,10 @@
         <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD63" t="n">
         <v>0</v>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8858,13 +8858,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8906,10 +8906,10 @@
         <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD64" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,13 +8990,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9038,10 +9038,10 @@
         <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD65" t="n">
         <v>0</v>
@@ -9086,22 +9086,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,13 +9122,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9170,16 +9170,16 @@
         <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
         <v>0</v>
@@ -9218,22 +9218,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9254,13 +9254,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9302,10 +9302,10 @@
         <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AD67" t="n">
         <v>0</v>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9518,13 +9518,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9566,10 +9566,10 @@
         <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD69" t="n">
         <v>0</v>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9698,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9830,10 +9830,10 @@
         <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC71" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD71" t="n">
         <v>0</v>
@@ -9878,22 +9878,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.96</v>
+        <v>3.57</v>
       </c>
       <c r="M72" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="N72" t="n">
-        <v>3.08</v>
+        <v>1.8</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9962,10 +9962,10 @@
         <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="AC72" t="n">
-        <v>2.31</v>
+        <v>1.94</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,13 +10178,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10226,10 +10226,10 @@
         <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC75" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
@@ -10538,22 +10538,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,13 +10574,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC77" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD77" t="n">
         <v>0</v>
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Trenčín</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Spartak Trnava</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10754,10 +10754,10 @@
         <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC78" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD78" t="n">
         <v>0</v>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10838,13 +10838,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10886,10 +10886,10 @@
         <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC79" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD79" t="n">
         <v>0</v>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Karpaty</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD80" t="n">
         <v>0</v>
@@ -11198,22 +11198,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.63</v>
+        <v>3.56</v>
       </c>
       <c r="M84" t="n">
-        <v>2.96</v>
+        <v>3.31</v>
       </c>
       <c r="N84" t="n">
-        <v>2.49</v>
+        <v>1.86</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,10 +11546,10 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AC84" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.15</v>
+        <v>3.09</v>
       </c>
       <c r="M85" t="n">
-        <v>6.2</v>
+        <v>3.15</v>
       </c>
       <c r="N85" t="n">
-        <v>11</v>
+        <v>2.09</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11678,16 +11678,16 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="AC85" t="n">
-        <v>2.75</v>
+        <v>2.22</v>
       </c>
       <c r="AD85" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF85" t="n">
         <v>0</v>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.75</v>
+        <v>1.15</v>
       </c>
       <c r="M86" t="n">
-        <v>3.5</v>
+        <v>6.2</v>
       </c>
       <c r="N86" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,16 +11810,16 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AC86" t="n">
-        <v>1.95</v>
+        <v>2.75</v>
       </c>
       <c r="AD86" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF86" t="n">
         <v>0</v>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>3.09</v>
+        <v>1.75</v>
       </c>
       <c r="M87" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="N87" t="n">
-        <v>2.09</v>
+        <v>4</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11942,10 +11942,10 @@
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AC87" t="n">
-        <v>2.22</v>
+        <v>1.95</v>
       </c>
       <c r="AD87" t="n">
         <v>0</v>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12026,13 +12026,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>3.56</v>
+        <v>2.63</v>
       </c>
       <c r="M88" t="n">
-        <v>3.31</v>
+        <v>2.96</v>
       </c>
       <c r="N88" t="n">
-        <v>1.86</v>
+        <v>2.49</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12074,10 +12074,10 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AC88" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AD88" t="n">
         <v>0</v>
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,13 +12158,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12290,13 +12290,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12422,13 +12422,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.71</v>
+        <v>2.52</v>
       </c>
       <c r="M91" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="N91" t="n">
-        <v>4.6</v>
+        <v>3.03</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12470,10 +12470,10 @@
         <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD91" t="n">
         <v>0</v>
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12554,13 +12554,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.52</v>
+        <v>1.5</v>
       </c>
       <c r="M92" t="n">
-        <v>3</v>
+        <v>3.66</v>
       </c>
       <c r="N92" t="n">
-        <v>3.03</v>
+        <v>8.25</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12686,64 +12686,64 @@
         </is>
       </c>
       <c r="L93" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M93" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N93" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="n">
+        <v>0</v>
+      </c>
+      <c r="T93" t="n">
+        <v>0</v>
+      </c>
+      <c r="U93" t="n">
+        <v>0</v>
+      </c>
+      <c r="V93" t="n">
+        <v>0</v>
+      </c>
+      <c r="W93" t="n">
+        <v>0</v>
+      </c>
+      <c r="X93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB93" t="n">
         <v>1.5</v>
       </c>
-      <c r="M93" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="N93" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="O93" t="n">
-        <v>0</v>
-      </c>
-      <c r="P93" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
-      <c r="R93" t="n">
-        <v>0</v>
-      </c>
-      <c r="S93" t="n">
-        <v>0</v>
-      </c>
-      <c r="T93" t="n">
-        <v>0</v>
-      </c>
-      <c r="U93" t="n">
-        <v>0</v>
-      </c>
-      <c r="V93" t="n">
-        <v>0</v>
-      </c>
-      <c r="W93" t="n">
-        <v>0</v>
-      </c>
-      <c r="X93" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y93" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB93" t="n">
-        <v>0</v>
-      </c>
       <c r="AC93" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD93" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE93" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF93" t="n">
         <v>0</v>
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC94" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD94" t="n">
         <v>0</v>
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13082,13 +13082,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -13130,16 +13130,16 @@
         <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD96" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
         <v>0</v>
@@ -13310,22 +13310,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13346,13 +13346,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13394,16 +13394,16 @@
         <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC98" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD98" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AF98" t="n">
         <v>0</v>
@@ -13574,22 +13574,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13610,13 +13610,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13658,16 +13658,16 @@
         <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD100" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AE100" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AF100" t="n">
         <v>0</v>
@@ -13848,12 +13848,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13970,22 +13970,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14006,13 +14006,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -14112,12 +14112,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tatran Prešov</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14366,22 +14366,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Slutsk</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14498,22 +14498,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Slutsk</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14534,13 +14534,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14640,12 +14640,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Tatran Prešov</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14894,22 +14894,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15158,7 +15158,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -15242,10 +15242,10 @@
         <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC112" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD112" t="n">
         <v>0</v>
@@ -15422,7 +15422,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15458,13 +15458,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15506,10 +15506,10 @@
         <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD114" t="n">
         <v>0</v>
@@ -15554,22 +15554,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15686,22 +15686,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15722,13 +15722,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15770,10 +15770,10 @@
         <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC116" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD116" t="n">
         <v>0</v>
@@ -15818,7 +15818,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15950,22 +15950,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15986,13 +15986,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -16034,10 +16034,10 @@
         <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC118" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD118" t="n">
         <v>0</v>
@@ -16092,12 +16092,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16214,7 +16214,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -16224,12 +16224,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16346,22 +16346,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16488,12 +16488,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16610,7 +16610,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16620,12 +16620,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16646,10 +16646,10 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="M123" t="n">
-        <v>3.9</v>
+        <v>3.73</v>
       </c>
       <c r="N123" t="n">
         <v>5.6</v>
@@ -16694,10 +16694,10 @@
         <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AC123" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AD123" t="n">
         <v>0</v>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16778,10 +16778,10 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="M124" t="n">
-        <v>3.73</v>
+        <v>3.9</v>
       </c>
       <c r="N124" t="n">
         <v>5.6</v>
@@ -16826,10 +16826,10 @@
         <v>0</v>
       </c>
       <c r="AB124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC124" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AC124" t="n">
-        <v>1.9</v>
       </c>
       <c r="AD124" t="n">
         <v>0</v>
@@ -17006,22 +17006,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17042,13 +17042,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>1.68</v>
+        <v>2.13</v>
       </c>
       <c r="M126" t="n">
-        <v>3.75</v>
+        <v>2.99</v>
       </c>
       <c r="N126" t="n">
-        <v>4.8</v>
+        <v>3.17</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -17090,10 +17090,10 @@
         <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC126" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD126" t="n">
         <v>0</v>
@@ -17148,12 +17148,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17270,22 +17270,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17306,13 +17306,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -17354,10 +17354,10 @@
         <v>0</v>
       </c>
       <c r="AB128" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC128" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD128" t="n">
         <v>0</v>
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17666,7 +17666,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17676,12 +17676,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17702,13 +17702,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17744,16 +17744,16 @@
         <v>0</v>
       </c>
       <c r="Z131" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD131" t="n">
         <v>0</v>
@@ -18062,7 +18062,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -18072,12 +18072,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -18098,13 +18098,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -18140,16 +18140,16 @@
         <v>0</v>
       </c>
       <c r="Z134" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA134" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB134" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC134" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD134" t="n">
         <v>0</v>
@@ -18194,7 +18194,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -18204,12 +18204,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -18326,7 +18326,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -18336,12 +18336,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18362,13 +18362,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>2</v>
+        <v>2.37</v>
       </c>
       <c r="M136" t="n">
-        <v>2.94</v>
+        <v>2.72</v>
       </c>
       <c r="N136" t="n">
-        <v>3.57</v>
+        <v>3.03</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -18404,16 +18404,16 @@
         <v>0</v>
       </c>
       <c r="Z136" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="AA136" t="n">
-        <v>2.45</v>
+        <v>3.15</v>
       </c>
       <c r="AB136" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="AC136" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AD136" t="n">
         <v>0</v>
@@ -18996,12 +18996,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -19022,13 +19022,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>4.4</v>
+        <v>1.84</v>
       </c>
       <c r="M141" t="n">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="N141" t="n">
-        <v>1.77</v>
+        <v>3.8</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -19070,7 +19070,7 @@
         <v>0</v>
       </c>
       <c r="AB141" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC141" t="n">
         <v>1.57</v>
@@ -19128,12 +19128,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -19154,13 +19154,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>1.84</v>
+        <v>4.4</v>
       </c>
       <c r="M142" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="N142" t="n">
-        <v>3.8</v>
+        <v>1.77</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -19202,7 +19202,7 @@
         <v>0</v>
       </c>
       <c r="AB142" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC142" t="n">
         <v>1.57</v>

--- a/jogos_2025-08-03.xlsx
+++ b/jogos_2025-08-03.xlsx
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Slavia Praha II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Slavia Praha II</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Roasso Kumamoto</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Oleksandria</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.15</v>
+        <v>5.3</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>3.41</v>
       </c>
       <c r="N9" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1640,16 +1640,16 @@
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>Roasso Kumamoto</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oleksandria</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.3</v>
+        <v>3.15</v>
       </c>
       <c r="M10" t="n">
-        <v>3.41</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1772,16 +1772,16 @@
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Molodechno-DYuSSh 4</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Molodechno-DYuSSh 4</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.09</v>
+        <v>1.8</v>
       </c>
       <c r="M17" t="n">
-        <v>3.74</v>
+        <v>3.53</v>
       </c>
       <c r="N17" t="n">
-        <v>3.08</v>
+        <v>4.33</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,16 +2702,16 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.57</v>
+        <v>2.09</v>
       </c>
       <c r="M18" t="n">
-        <v>3.85</v>
+        <v>3.74</v>
       </c>
       <c r="N18" t="n">
-        <v>4.5</v>
+        <v>3.08</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,16 +2834,16 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD18" t="n">
         <v>2.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="M22" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="N22" t="n">
-        <v>3.51</v>
+        <v>4.5</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3365,13 +3365,13 @@
         <v>1.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.34</v>
+        <v>3.24</v>
       </c>
       <c r="M26" t="n">
-        <v>3.45</v>
+        <v>2.98</v>
       </c>
       <c r="N26" t="n">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,16 +3890,16 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -4070,22 +4070,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.41</v>
+        <v>3.34</v>
       </c>
       <c r="M28" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N28" t="n">
-        <v>2.46</v>
+        <v>1.89</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4154,16 +4154,16 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -4202,22 +4202,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4286,10 +4286,10 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4334,22 +4334,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.24</v>
+        <v>2.41</v>
       </c>
       <c r="M30" t="n">
-        <v>2.98</v>
+        <v>3.35</v>
       </c>
       <c r="N30" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4418,10 +4418,10 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -4598,22 +4598,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.89</v>
+        <v>1.24</v>
       </c>
       <c r="M32" t="n">
-        <v>3.53</v>
+        <v>5</v>
       </c>
       <c r="N32" t="n">
-        <v>3.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4682,10 +4682,10 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -4730,22 +4730,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>9.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="M33" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="N33" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,16 +4814,16 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AF33" t="n">
         <v>0</v>
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="M34" t="n">
         <v>6</v>
       </c>
-      <c r="M34" t="n">
-        <v>4.7</v>
-      </c>
       <c r="N34" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4946,16 +4946,16 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5078,10 +5078,10 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.47</v>
+        <v>1.42</v>
       </c>
       <c r="M39" t="n">
-        <v>3.66</v>
+        <v>4.33</v>
       </c>
       <c r="N39" t="n">
-        <v>2.26</v>
+        <v>5.4</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5612,10 +5612,10 @@
         <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AF39" t="n">
         <v>0</v>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.42</v>
+        <v>2.47</v>
       </c>
       <c r="M41" t="n">
-        <v>4.33</v>
+        <v>3.66</v>
       </c>
       <c r="N41" t="n">
-        <v>5.4</v>
+        <v>2.26</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5876,10 +5876,10 @@
         <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AF41" t="n">
         <v>0</v>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6002,10 +6002,10 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6134,10 +6134,10 @@
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
         <v>0</v>
@@ -6314,22 +6314,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Jeunesse Canach</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>Jeunesse Canach</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7058,10 +7058,10 @@
         <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
         <v>0</v>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,13 +7142,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7190,10 +7190,10 @@
         <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
         <v>0</v>
@@ -7238,22 +7238,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7274,13 +7274,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7538,13 +7538,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="M54" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="N54" t="n">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7586,10 +7586,10 @@
         <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AD54" t="n">
         <v>0</v>
@@ -7634,22 +7634,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7802,13 +7802,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7850,10 +7850,10 @@
         <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD56" t="n">
         <v>0</v>
@@ -7898,22 +7898,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7934,13 +7934,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.26</v>
+        <v>3.23</v>
       </c>
       <c r="M57" t="n">
-        <v>5</v>
+        <v>3.39</v>
       </c>
       <c r="N57" t="n">
-        <v>9.4</v>
+        <v>1.94</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7982,10 +7982,10 @@
         <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD57" t="n">
         <v>0</v>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8066,13 +8066,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Karpaty</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8774,10 +8774,10 @@
         <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD63" t="n">
         <v>0</v>
@@ -8822,22 +8822,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8858,13 +8858,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8906,10 +8906,10 @@
         <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD64" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,13 +8990,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9038,10 +9038,10 @@
         <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD65" t="n">
         <v>0</v>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Karpaty</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,13 +9122,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9170,10 +9170,10 @@
         <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD66" t="n">
         <v>0</v>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9350,22 +9350,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="M68" t="n">
-        <v>3.29</v>
+        <v>3.05</v>
       </c>
       <c r="N68" t="n">
-        <v>2.67</v>
+        <v>3.09</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9434,10 +9434,10 @@
         <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Trenčín</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Spartak Trnava</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9698,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9830,10 +9830,10 @@
         <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AD71" t="n">
         <v>0</v>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,13 +10046,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10094,10 +10094,10 @@
         <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC73" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD73" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10274,22 +10274,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Torpedo BelAZ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Gomel</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Torpedo BelAZ</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gomel</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10442,13 +10442,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10490,10 +10490,10 @@
         <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC76" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
@@ -10538,22 +10538,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,13 +10574,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AD77" t="n">
         <v>0</v>
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Trenčín</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spartak Trnava</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>3.56</v>
+        <v>1.44</v>
       </c>
       <c r="M78" t="n">
-        <v>3.32</v>
+        <v>4.2</v>
       </c>
       <c r="N78" t="n">
-        <v>1.86</v>
+        <v>5.4</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10754,10 +10754,10 @@
         <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AC78" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AD78" t="n">
         <v>0</v>
@@ -10802,22 +10802,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10838,13 +10838,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="M79" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="N79" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10886,10 +10886,10 @@
         <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AC79" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="AD79" t="n">
         <v>0</v>
@@ -10934,22 +10934,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11193,27 +11193,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11282,10 +11282,10 @@
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD82" t="n">
         <v>0</v>
@@ -11316,7 +11316,7 @@
         </is>
       </c>
       <c r="AL82" s="3" t="n">
-        <v>45872.5</v>
+        <v>45872.52083333334</v>
       </c>
     </row>
     <row r="83">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>3.56</v>
+        <v>1.76</v>
       </c>
       <c r="M84" t="n">
-        <v>3.31</v>
+        <v>3.6</v>
       </c>
       <c r="N84" t="n">
-        <v>1.86</v>
+        <v>4.2</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,10 +11546,10 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC84" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11678,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.15</v>
+        <v>3.56</v>
       </c>
       <c r="M86" t="n">
-        <v>6.2</v>
+        <v>3.31</v>
       </c>
       <c r="N86" t="n">
-        <v>11</v>
+        <v>1.86</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,16 +11810,16 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AC86" t="n">
-        <v>2.75</v>
+        <v>1.68</v>
       </c>
       <c r="AD86" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
         <v>0</v>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.75</v>
+        <v>3.09</v>
       </c>
       <c r="M87" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="N87" t="n">
-        <v>4</v>
+        <v>2.09</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11942,10 +11942,10 @@
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AC87" t="n">
-        <v>1.95</v>
+        <v>2.22</v>
       </c>
       <c r="AD87" t="n">
         <v>0</v>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12026,13 +12026,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.63</v>
+        <v>1.15</v>
       </c>
       <c r="M88" t="n">
-        <v>2.96</v>
+        <v>6.2</v>
       </c>
       <c r="N88" t="n">
-        <v>2.49</v>
+        <v>11</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12074,16 +12074,16 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="AC88" t="n">
-        <v>1.6</v>
+        <v>2.75</v>
       </c>
       <c r="AD88" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF88" t="n">
         <v>0</v>
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,13 +12158,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12290,13 +12290,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12386,22 +12386,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12422,13 +12422,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.52</v>
+        <v>6</v>
       </c>
       <c r="M91" t="n">
-        <v>3</v>
+        <v>3.89</v>
       </c>
       <c r="N91" t="n">
-        <v>3.03</v>
+        <v>1.44</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12476,10 +12476,10 @@
         <v>0</v>
       </c>
       <c r="AD91" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF91" t="n">
         <v>0</v>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12554,13 +12554,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="M92" t="n">
-        <v>3.66</v>
+        <v>3.35</v>
       </c>
       <c r="N92" t="n">
-        <v>8.25</v>
+        <v>4.6</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12602,10 +12602,10 @@
         <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC92" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD92" t="n">
         <v>0</v>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12686,13 +12686,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.45</v>
+        <v>2.52</v>
       </c>
       <c r="M93" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="N93" t="n">
-        <v>5.1</v>
+        <v>3.03</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12734,16 +12734,16 @@
         <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD93" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF93" t="n">
         <v>0</v>
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.71</v>
+        <v>1.45</v>
       </c>
       <c r="M94" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="N94" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12866,16 +12866,16 @@
         <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AC94" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="AD94" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE94" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF94" t="n">
         <v>0</v>
@@ -12914,22 +12914,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12950,13 +12950,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="M95" t="n">
-        <v>3.89</v>
+        <v>3.66</v>
       </c>
       <c r="N95" t="n">
-        <v>1.44</v>
+        <v>8.25</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -13004,10 +13004,10 @@
         <v>0</v>
       </c>
       <c r="AD95" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF95" t="n">
         <v>0</v>
@@ -13310,22 +13310,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13346,13 +13346,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13394,16 +13394,16 @@
         <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD98" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AF98" t="n">
         <v>0</v>
@@ -13574,22 +13574,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13610,13 +13610,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13658,16 +13658,16 @@
         <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC100" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD100" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AE100" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AF100" t="n">
         <v>0</v>
@@ -13706,22 +13706,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13742,13 +13742,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="M101" t="n">
-        <v>3.9</v>
+        <v>2.86</v>
       </c>
       <c r="N101" t="n">
-        <v>6</v>
+        <v>4.63</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13760,58 +13760,58 @@
         <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S101" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T101" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U101" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V101" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W101" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X101" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.95</v>
+        <v>2.9</v>
       </c>
       <c r="AC101" t="n">
-        <v>1.85</v>
+        <v>1.36</v>
       </c>
       <c r="AD101" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AE101" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF101" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG101" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH101" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AI101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
@@ -13833,12 +13833,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13874,13 +13874,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13922,10 +13922,10 @@
         <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC102" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD102" t="n">
         <v>0</v>
@@ -13956,7 +13956,7 @@
         </is>
       </c>
       <c r="AL102" s="3" t="n">
-        <v>45872.58333333334</v>
+        <v>45872.57291666666</v>
       </c>
     </row>
     <row r="103">
@@ -13970,22 +13970,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14366,22 +14366,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Slutsk</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14498,7 +14498,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14508,12 +14508,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Tatran Prešov</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14534,13 +14534,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14640,12 +14640,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tatran Prešov</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14798,13 +14798,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14894,22 +14894,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15021,27 +15021,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Slutsk</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15062,13 +15062,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -15110,10 +15110,10 @@
         <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD111" t="n">
         <v>0</v>
@@ -15144,7 +15144,7 @@
         </is>
       </c>
       <c r="AL111" s="3" t="n">
-        <v>45872.59375</v>
+        <v>45872.58333333334</v>
       </c>
     </row>
     <row r="112">
@@ -15153,12 +15153,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.39</v>
+        <v>1.93</v>
       </c>
       <c r="M112" t="n">
-        <v>2.99</v>
+        <v>3.41</v>
       </c>
       <c r="N112" t="n">
-        <v>2.73</v>
+        <v>3.25</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -15242,10 +15242,10 @@
         <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AC112" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AD112" t="n">
         <v>0</v>
@@ -15276,7 +15276,7 @@
         </is>
       </c>
       <c r="AL112" s="3" t="n">
-        <v>45872.60416666666</v>
+        <v>45872.59375</v>
       </c>
     </row>
     <row r="113">
@@ -15290,7 +15290,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -15300,12 +15300,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15326,13 +15326,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15368,10 +15368,10 @@
         <v>0</v>
       </c>
       <c r="Z113" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB113" t="n">
         <v>0</v>
@@ -15422,7 +15422,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15458,13 +15458,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15500,10 +15500,10 @@
         <v>0</v>
       </c>
       <c r="Z114" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA114" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB114" t="n">
         <v>0</v>
@@ -15549,12 +15549,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15590,13 +15590,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15638,10 +15638,10 @@
         <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC115" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD115" t="n">
         <v>0</v>
@@ -15672,7 +15672,7 @@
         </is>
       </c>
       <c r="AL115" s="3" t="n">
-        <v>45872.625</v>
+        <v>45872.60416666666</v>
       </c>
     </row>
     <row r="116">
@@ -15686,22 +15686,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15722,13 +15722,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15770,10 +15770,10 @@
         <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC116" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD116" t="n">
         <v>0</v>
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16214,22 +16214,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16250,13 +16250,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -16298,10 +16298,10 @@
         <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC120" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD120" t="n">
         <v>0</v>
@@ -16356,12 +16356,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16478,22 +16478,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16605,27 +16605,27 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16646,13 +16646,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16694,10 +16694,10 @@
         <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC123" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD123" t="n">
         <v>0</v>
@@ -16728,7 +16728,7 @@
         </is>
       </c>
       <c r="AL123" s="3" t="n">
-        <v>45872.63541666666</v>
+        <v>45872.625</v>
       </c>
     </row>
     <row r="124">
@@ -17001,12 +17001,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17042,13 +17042,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.13</v>
+        <v>1.48</v>
       </c>
       <c r="M126" t="n">
-        <v>2.99</v>
+        <v>3.73</v>
       </c>
       <c r="N126" t="n">
-        <v>3.17</v>
+        <v>5.6</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -17090,10 +17090,10 @@
         <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AC126" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AD126" t="n">
         <v>0</v>
@@ -17124,7 +17124,7 @@
         </is>
       </c>
       <c r="AL126" s="3" t="n">
-        <v>45872.64583333334</v>
+        <v>45872.63541666666</v>
       </c>
     </row>
     <row r="127">
@@ -17148,12 +17148,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17280,12 +17280,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17306,13 +17306,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -17402,22 +17402,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1.68</v>
+        <v>2.13</v>
       </c>
       <c r="M129" t="n">
-        <v>3.75</v>
+        <v>2.99</v>
       </c>
       <c r="N129" t="n">
-        <v>4.8</v>
+        <v>3.17</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17486,10 +17486,10 @@
         <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC129" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD129" t="n">
         <v>0</v>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17544,12 +17544,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17570,13 +17570,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.66</v>
+        <v>2.37</v>
       </c>
       <c r="M130" t="n">
-        <v>3.19</v>
+        <v>2.72</v>
       </c>
       <c r="N130" t="n">
-        <v>4.9</v>
+        <v>3.03</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17612,16 +17612,16 @@
         <v>0</v>
       </c>
       <c r="Z130" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AB130" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AC130" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AD130" t="n">
         <v>0</v>
@@ -17666,22 +17666,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17702,13 +17702,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17798,22 +17798,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17834,13 +17834,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17882,10 +17882,10 @@
         <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD132" t="n">
         <v>0</v>
@@ -17930,22 +17930,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17966,13 +17966,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -18062,7 +18062,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -18072,12 +18072,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -18098,13 +18098,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -18140,16 +18140,16 @@
         <v>0</v>
       </c>
       <c r="Z134" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC134" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD134" t="n">
         <v>0</v>
@@ -18194,7 +18194,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -18204,12 +18204,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -18230,13 +18230,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -18272,16 +18272,16 @@
         <v>0</v>
       </c>
       <c r="Z135" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA135" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC135" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD135" t="n">
         <v>0</v>
@@ -18326,22 +18326,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18362,13 +18362,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>2.37</v>
+        <v>1.65</v>
       </c>
       <c r="M136" t="n">
-        <v>2.72</v>
+        <v>3.88</v>
       </c>
       <c r="N136" t="n">
-        <v>3.03</v>
+        <v>5.06</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -18404,16 +18404,16 @@
         <v>0</v>
       </c>
       <c r="Z136" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AB136" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC136" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AD136" t="n">
         <v>0</v>
@@ -18458,7 +18458,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18468,12 +18468,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18494,13 +18494,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -18542,10 +18542,10 @@
         <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC137" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD137" t="n">
         <v>0</v>
@@ -18590,7 +18590,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18600,12 +18600,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18626,13 +18626,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -18722,7 +18722,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18732,12 +18732,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18758,13 +18758,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -18854,7 +18854,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18864,12 +18864,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18890,13 +18890,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>1.56</v>
+        <v>4.4</v>
       </c>
       <c r="M140" t="n">
-        <v>3.6</v>
+        <v>3.08</v>
       </c>
       <c r="N140" t="n">
-        <v>6.2</v>
+        <v>1.77</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -18941,7 +18941,7 @@
         <v>2.25</v>
       </c>
       <c r="AC140" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AD140" t="n">
         <v>0</v>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18996,12 +18996,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -19022,13 +19022,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M141" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -19070,10 +19070,10 @@
         <v>0</v>
       </c>
       <c r="AB141" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC141" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD141" t="n">
         <v>0</v>
@@ -19128,12 +19128,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -19154,13 +19154,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>4.4</v>
+        <v>1.84</v>
       </c>
       <c r="M142" t="n">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="N142" t="n">
-        <v>1.77</v>
+        <v>3.8</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -19202,7 +19202,7 @@
         <v>0</v>
       </c>
       <c r="AB142" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC142" t="n">
         <v>1.57</v>
@@ -19250,7 +19250,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -19260,12 +19260,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -19286,13 +19286,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M143" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -19334,10 +19334,10 @@
         <v>0</v>
       </c>
       <c r="AB143" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC143" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD143" t="n">
         <v>0</v>
@@ -19382,7 +19382,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -19392,12 +19392,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19418,13 +19418,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M144" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -19514,7 +19514,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19524,12 +19524,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19550,13 +19550,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M145" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>

--- a/jogos_2025-08-03.xlsx
+++ b/jogos_2025-08-03.xlsx
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Central Coast II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mt Druitt Town</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Central Coast II</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Mt Druitt Town</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Slavia Praha II</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Slavia Praha II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1562,22 +1562,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>Roasso Kumamoto</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Oleksandria</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>5.3</v>
+        <v>3.15</v>
       </c>
       <c r="M9" t="n">
-        <v>3.41</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1640,16 +1640,16 @@
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Roasso Kumamoto</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Oleksandria</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.15</v>
+        <v>5.3</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>3.41</v>
       </c>
       <c r="N10" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1772,16 +1772,16 @@
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Molodechno-DYuSSh 4</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Molodechno-DYuSSh 4</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.8</v>
+        <v>2.09</v>
       </c>
       <c r="M17" t="n">
-        <v>3.53</v>
+        <v>3.74</v>
       </c>
       <c r="N17" t="n">
-        <v>4.33</v>
+        <v>3.08</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,16 +2702,16 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.09</v>
+        <v>1.57</v>
       </c>
       <c r="M18" t="n">
-        <v>3.74</v>
+        <v>3.85</v>
       </c>
       <c r="N18" t="n">
-        <v>3.08</v>
+        <v>4.5</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,16 +2834,16 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AD18" t="n">
         <v>2.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="M22" t="n">
-        <v>3.85</v>
+        <v>3.53</v>
       </c>
       <c r="N22" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3365,13 +3365,13 @@
         <v>1.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.64</v>
+        <v>1.39</v>
       </c>
       <c r="M23" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="N23" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.39</v>
+        <v>1.64</v>
       </c>
       <c r="M24" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="N24" t="n">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3674,22 +3674,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.24</v>
+        <v>2.41</v>
       </c>
       <c r="M26" t="n">
-        <v>2.98</v>
+        <v>3.35</v>
       </c>
       <c r="N26" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -3938,22 +3938,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4334,22 +4334,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.41</v>
+        <v>1.89</v>
       </c>
       <c r="M30" t="n">
-        <v>3.35</v>
+        <v>3.53</v>
       </c>
       <c r="N30" t="n">
-        <v>2.46</v>
+        <v>3.25</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4466,22 +4466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.72</v>
+        <v>1.24</v>
       </c>
       <c r="M31" t="n">
-        <v>3.38</v>
+        <v>5</v>
       </c>
       <c r="N31" t="n">
-        <v>2.19</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -4598,22 +4598,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.24</v>
+        <v>2.72</v>
       </c>
       <c r="M32" t="n">
-        <v>5</v>
+        <v>3.38</v>
       </c>
       <c r="N32" t="n">
-        <v>8.800000000000001</v>
+        <v>2.19</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4682,10 +4682,10 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -4730,22 +4730,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,16 +4814,16 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
         <v>0</v>
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>9.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="M34" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="N34" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4946,16 +4946,16 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5078,10 +5078,10 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,16 +5210,16 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF36" t="n">
         <v>0</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.06</v>
+        <v>1.76</v>
       </c>
       <c r="M37" t="n">
-        <v>3.2</v>
+        <v>3.53</v>
       </c>
       <c r="N37" t="n">
-        <v>3.69</v>
+        <v>3.73</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.15</v>
+        <v>1.6</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.7</v>
+        <v>2.24</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.76</v>
+        <v>2.06</v>
       </c>
       <c r="M38" t="n">
-        <v>3.53</v>
+        <v>3.2</v>
       </c>
       <c r="N38" t="n">
-        <v>3.73</v>
+        <v>3.69</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.24</v>
+        <v>1.7</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.42</v>
+        <v>1.8</v>
       </c>
       <c r="M39" t="n">
-        <v>4.33</v>
+        <v>3.39</v>
       </c>
       <c r="N39" t="n">
-        <v>5.4</v>
+        <v>3.71</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5606,16 +5606,16 @@
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
         <v>0</v>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5744,10 +5744,10 @@
         <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5876,10 +5876,10 @@
         <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
         <v>0</v>
@@ -5918,22 +5918,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,64 +5954,64 @@
         </is>
       </c>
       <c r="L42" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M42" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="N42" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE42" t="n">
         <v>1.8</v>
-      </c>
-      <c r="M42" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="N42" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>0</v>
       </c>
       <c r="AF42" t="n">
         <v>0</v>
@@ -6314,22 +6314,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Jeunesse Canach</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6926,10 +6926,10 @@
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD49" t="n">
         <v>0</v>
@@ -6974,22 +6974,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7106,22 +7106,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7238,22 +7238,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Jeunesse Canach</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7274,13 +7274,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7406,13 +7406,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7454,10 +7454,10 @@
         <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD53" t="n">
         <v>0</v>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7538,13 +7538,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7586,10 +7586,10 @@
         <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
         <v>0</v>
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7802,13 +7802,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="M56" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="N56" t="n">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7850,10 +7850,10 @@
         <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AD56" t="n">
         <v>0</v>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7934,13 +7934,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7982,10 +7982,10 @@
         <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
         <v>0</v>
@@ -8030,22 +8030,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8066,13 +8066,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="M58" t="n">
-        <v>3.83</v>
+        <v>3.63</v>
       </c>
       <c r="N58" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -8114,10 +8114,10 @@
         <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD58" t="n">
         <v>0</v>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8330,13 +8330,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8378,10 +8378,10 @@
         <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
         <v>0</v>
@@ -8426,22 +8426,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8462,13 +8462,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.65</v>
+        <v>2.06</v>
       </c>
       <c r="M61" t="n">
-        <v>3.63</v>
+        <v>3.52</v>
       </c>
       <c r="N61" t="n">
-        <v>4.2</v>
+        <v>2.86</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8510,10 +8510,10 @@
         <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AC61" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AD61" t="n">
         <v>0</v>
@@ -8558,22 +8558,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8594,13 +8594,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8642,16 +8642,16 @@
         <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD62" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
         <v>0</v>
@@ -8690,22 +8690,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8822,22 +8822,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8858,13 +8858,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8906,10 +8906,10 @@
         <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AD64" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,13 +8990,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9038,10 +9038,10 @@
         <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD65" t="n">
         <v>0</v>
@@ -9086,22 +9086,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Karpaty</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,14 +9122,14 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.73</v>
+        <v>1.93</v>
       </c>
       <c r="M66" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="N66" t="n">
         <v>3.23</v>
       </c>
-      <c r="N66" t="n">
-        <v>2.54</v>
-      </c>
       <c r="O66" t="n">
         <v>0</v>
       </c>
@@ -9170,16 +9170,16 @@
         <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>2.2</v>
+        <v>1.45</v>
       </c>
       <c r="AC66" t="n">
-        <v>1.67</v>
+        <v>2.55</v>
       </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF66" t="n">
         <v>0</v>
@@ -9218,22 +9218,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9254,13 +9254,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9302,10 +9302,10 @@
         <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD67" t="n">
         <v>0</v>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9434,10 +9434,10 @@
         <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Karpaty</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9518,13 +9518,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9566,10 +9566,10 @@
         <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD69" t="n">
         <v>0</v>
@@ -9614,22 +9614,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Trenčín</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spartak Trnava</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>3.56</v>
+        <v>1.96</v>
       </c>
       <c r="M70" t="n">
-        <v>3.32</v>
+        <v>3.51</v>
       </c>
       <c r="N70" t="n">
-        <v>1.86</v>
+        <v>3.08</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9698,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AC70" t="n">
-        <v>1.92</v>
+        <v>2.31</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
@@ -9878,22 +9878,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.57</v>
+        <v>2.26</v>
       </c>
       <c r="M72" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="N72" t="n">
-        <v>1.8</v>
+        <v>2.67</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9962,10 +9962,10 @@
         <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="AC72" t="n">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,13 +10046,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10094,10 +10094,10 @@
         <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD73" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,13 +10178,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10226,10 +10226,10 @@
         <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
@@ -10274,22 +10274,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Torpedo BelAZ</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gomel</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC75" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Torpedo BelAZ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Gomel</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10442,13 +10442,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10490,10 +10490,10 @@
         <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,13 +10574,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC77" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD77" t="n">
         <v>0</v>
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10754,10 +10754,10 @@
         <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD78" t="n">
         <v>0</v>
@@ -10802,22 +10802,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10838,13 +10838,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10886,10 +10886,10 @@
         <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AD79" t="n">
         <v>0</v>
@@ -10934,22 +10934,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Trenčín</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Spartak Trnava</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD80" t="n">
         <v>0</v>
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11198,7 +11198,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11282,10 +11282,10 @@
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD82" t="n">
         <v>0</v>
@@ -11330,7 +11330,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD83" t="n">
         <v>0</v>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.76</v>
+        <v>3.56</v>
       </c>
       <c r="M84" t="n">
-        <v>3.6</v>
+        <v>3.31</v>
       </c>
       <c r="N84" t="n">
-        <v>4.2</v>
+        <v>1.86</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,10 +11546,10 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AC84" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11678,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,10 +11810,10 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>3.09</v>
+        <v>1.76</v>
       </c>
       <c r="M87" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="N87" t="n">
-        <v>2.09</v>
+        <v>4.2</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11942,10 +11942,10 @@
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AC87" t="n">
-        <v>2.22</v>
+        <v>1.95</v>
       </c>
       <c r="AD87" t="n">
         <v>0</v>
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,13 +12158,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12290,13 +12290,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12554,13 +12554,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.71</v>
+        <v>1.45</v>
       </c>
       <c r="M92" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="N92" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12602,16 +12602,16 @@
         <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AC92" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="AD92" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF92" t="n">
         <v>0</v>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12686,13 +12686,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.52</v>
+        <v>1.71</v>
       </c>
       <c r="M93" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="N93" t="n">
-        <v>3.03</v>
+        <v>4.6</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12734,10 +12734,10 @@
         <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC93" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD93" t="n">
         <v>0</v>
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12866,16 +12866,16 @@
         <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD94" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF94" t="n">
         <v>0</v>
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12950,13 +12950,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.5</v>
+        <v>2.52</v>
       </c>
       <c r="M95" t="n">
-        <v>3.66</v>
+        <v>3</v>
       </c>
       <c r="N95" t="n">
-        <v>8.25</v>
+        <v>3.03</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13082,13 +13082,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -13310,7 +13310,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13346,13 +13346,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13394,10 +13394,10 @@
         <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC98" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD98" t="n">
         <v>0</v>
@@ -13442,7 +13442,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13478,13 +13478,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13526,10 +13526,10 @@
         <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD99" t="n">
         <v>0</v>
@@ -13980,12 +13980,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14112,12 +14112,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14234,22 +14234,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14640,12 +14640,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14666,13 +14666,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14762,7 +14762,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14798,13 +14798,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14894,22 +14894,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15290,7 +15290,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -15300,12 +15300,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15326,13 +15326,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15368,10 +15368,10 @@
         <v>0</v>
       </c>
       <c r="Z113" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA113" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB113" t="n">
         <v>0</v>
@@ -15422,7 +15422,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15458,13 +15458,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.61</v>
+        <v>2.39</v>
       </c>
       <c r="M114" t="n">
-        <v>2.91</v>
+        <v>2.99</v>
       </c>
       <c r="N114" t="n">
-        <v>2.91</v>
+        <v>2.73</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15500,16 +15500,16 @@
         <v>0</v>
       </c>
       <c r="Z114" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC114" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD114" t="n">
         <v>0</v>
@@ -15554,7 +15554,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15590,13 +15590,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15638,10 +15638,10 @@
         <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD115" t="n">
         <v>0</v>
@@ -15686,7 +15686,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15950,22 +15950,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15986,13 +15986,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -16034,10 +16034,10 @@
         <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC118" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD118" t="n">
         <v>0</v>
@@ -16082,22 +16082,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16214,22 +16214,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16250,13 +16250,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -16298,10 +16298,10 @@
         <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC120" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD120" t="n">
         <v>0</v>
@@ -16356,12 +16356,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16478,22 +16478,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16610,7 +16610,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16620,12 +16620,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16778,13 +16778,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>1.5</v>
+        <v>2.11</v>
       </c>
       <c r="M124" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="N124" t="n">
-        <v>5.6</v>
+        <v>3.1</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16826,10 +16826,10 @@
         <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD124" t="n">
         <v>0</v>
@@ -16874,7 +16874,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16884,12 +16884,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16910,13 +16910,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.11</v>
+        <v>1.48</v>
       </c>
       <c r="M125" t="n">
-        <v>3.55</v>
+        <v>3.73</v>
       </c>
       <c r="N125" t="n">
-        <v>3.1</v>
+        <v>5.6</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16958,10 +16958,10 @@
         <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC125" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD125" t="n">
         <v>0</v>
@@ -17006,7 +17006,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17042,10 +17042,10 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="M126" t="n">
-        <v>3.73</v>
+        <v>3.9</v>
       </c>
       <c r="N126" t="n">
         <v>5.6</v>
@@ -17090,10 +17090,10 @@
         <v>0</v>
       </c>
       <c r="AB126" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC126" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AC126" t="n">
-        <v>1.9</v>
       </c>
       <c r="AD126" t="n">
         <v>0</v>
@@ -17138,22 +17138,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17174,13 +17174,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -17222,10 +17222,10 @@
         <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC127" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD127" t="n">
         <v>0</v>
@@ -17280,12 +17280,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17306,13 +17306,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -17402,22 +17402,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>2.13</v>
+        <v>1.68</v>
       </c>
       <c r="M129" t="n">
-        <v>2.99</v>
+        <v>3.75</v>
       </c>
       <c r="N129" t="n">
-        <v>3.17</v>
+        <v>4.8</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17486,10 +17486,10 @@
         <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC129" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD129" t="n">
         <v>0</v>
@@ -17666,22 +17666,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17702,13 +17702,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17808,12 +17808,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17834,13 +17834,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17876,16 +17876,16 @@
         <v>0</v>
       </c>
       <c r="Z132" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC132" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD132" t="n">
         <v>0</v>
@@ -17930,7 +17930,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17940,12 +17940,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17966,13 +17966,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -18014,10 +18014,10 @@
         <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC133" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD133" t="n">
         <v>0</v>
@@ -18062,22 +18062,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -18098,13 +18098,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -18194,22 +18194,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -18230,13 +18230,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="M135" t="n">
-        <v>2.94</v>
+        <v>3.88</v>
       </c>
       <c r="N135" t="n">
-        <v>3.57</v>
+        <v>5.06</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -18272,16 +18272,16 @@
         <v>0</v>
       </c>
       <c r="Z135" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="AC135" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AD135" t="n">
         <v>0</v>
@@ -18326,22 +18326,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18362,13 +18362,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -18410,10 +18410,10 @@
         <v>0</v>
       </c>
       <c r="AB136" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC136" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD136" t="n">
         <v>0</v>
@@ -18458,7 +18458,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18468,12 +18468,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18494,13 +18494,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -18542,10 +18542,10 @@
         <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC137" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD137" t="n">
         <v>0</v>
@@ -18864,12 +18864,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18890,13 +18890,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>4.4</v>
+        <v>1.84</v>
       </c>
       <c r="M140" t="n">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="N140" t="n">
-        <v>1.77</v>
+        <v>3.8</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -18938,7 +18938,7 @@
         <v>0</v>
       </c>
       <c r="AB140" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC140" t="n">
         <v>1.57</v>
@@ -19128,12 +19128,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -19154,13 +19154,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>1.84</v>
+        <v>4.4</v>
       </c>
       <c r="M142" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="N142" t="n">
-        <v>3.8</v>
+        <v>1.77</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -19202,7 +19202,7 @@
         <v>0</v>
       </c>
       <c r="AB142" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC142" t="n">
         <v>1.57</v>
@@ -19286,13 +19286,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="M143" t="n">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="N143" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -19724,10 +19724,10 @@
         <v>0</v>
       </c>
       <c r="Z146" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AA146" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB146" t="n">
         <v>2.37</v>

--- a/jogos_2025-08-03.xlsx
+++ b/jogos_2025-08-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL150"/>
+  <dimension ref="A1:AL157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -648,12 +648,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Central Coast II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Central Coast II</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Slavia Praha II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Slavia Praha II</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1557,27 +1557,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Roasso Kumamoto</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.15</v>
+        <v>2.63</v>
       </c>
       <c r="M9" t="n">
         <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>45872.29166666666</v>
+        <v>45872.22916666666</v>
       </c>
     </row>
     <row r="10">
@@ -1821,27 +1821,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Roasso Kumamoto</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.45</v>
+        <v>2.98</v>
       </c>
       <c r="M11" t="n">
-        <v>4.4</v>
+        <v>3.14</v>
       </c>
       <c r="N11" t="n">
-        <v>1.55</v>
+        <v>2.15</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,16 +1910,16 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="AL11" s="3" t="n">
-        <v>45872.3125</v>
+        <v>45872.29166666666</v>
       </c>
     </row>
     <row r="12">
@@ -1953,27 +1953,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2048,10 +2048,10 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="AL12" s="3" t="n">
-        <v>45872.33333333334</v>
+        <v>45872.3125</v>
       </c>
     </row>
     <row r="13">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Molodechno-DYuSSh 4</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Molodechno-DYuSSh 4</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="M16" t="n">
-        <v>3.8</v>
+        <v>3.52</v>
       </c>
       <c r="N16" t="n">
-        <v>3.51</v>
+        <v>4.2</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.15</v>
+        <v>1.89</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="AL16" s="3" t="n">
-        <v>45872.35416666666</v>
+        <v>45872.33333333334</v>
       </c>
     </row>
     <row r="17">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="M17" t="n">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="N17" t="n">
-        <v>3.08</v>
+        <v>3.51</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,16 +2702,16 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -2882,22 +2882,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,16 +2966,16 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3405,27 +3405,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.39</v>
+        <v>1.8</v>
       </c>
       <c r="M23" t="n">
-        <v>4.9</v>
+        <v>3.53</v>
       </c>
       <c r="N23" t="n">
-        <v>6.8</v>
+        <v>4.33</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="AL23" s="3" t="n">
-        <v>45872.35763888889</v>
+        <v>45872.35416666666</v>
       </c>
     </row>
     <row r="24">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.64</v>
+        <v>1.39</v>
       </c>
       <c r="M24" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="N24" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="AL25" s="3" t="n">
-        <v>45872.375</v>
+        <v>45872.35763888889</v>
       </c>
     </row>
     <row r="26">
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.41</v>
+        <v>3.24</v>
       </c>
       <c r="M26" t="n">
-        <v>3.35</v>
+        <v>2.98</v>
       </c>
       <c r="N26" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -3938,22 +3938,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4070,22 +4070,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.34</v>
+        <v>2.41</v>
       </c>
       <c r="M28" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N28" t="n">
-        <v>1.89</v>
+        <v>2.46</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4154,16 +4154,16 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.24</v>
+        <v>3.34</v>
       </c>
       <c r="M29" t="n">
-        <v>2.98</v>
+        <v>3.45</v>
       </c>
       <c r="N29" t="n">
-        <v>2.4</v>
+        <v>1.89</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4286,16 +4286,16 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.89</v>
+        <v>2.72</v>
       </c>
       <c r="M30" t="n">
-        <v>3.53</v>
+        <v>3.38</v>
       </c>
       <c r="N30" t="n">
-        <v>3.25</v>
+        <v>2.19</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4418,7 +4418,7 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC30" t="n">
         <v>2.05</v>
@@ -4466,22 +4466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.24</v>
+        <v>1.89</v>
       </c>
       <c r="M31" t="n">
-        <v>5</v>
+        <v>3.53</v>
       </c>
       <c r="N31" t="n">
-        <v>8.800000000000001</v>
+        <v>3.25</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -4598,22 +4598,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.72</v>
+        <v>1.24</v>
       </c>
       <c r="M32" t="n">
-        <v>3.38</v>
+        <v>5</v>
       </c>
       <c r="N32" t="n">
-        <v>2.19</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4682,10 +4682,10 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4848,7 +4848,7 @@
         </is>
       </c>
       <c r="AL33" s="3" t="n">
-        <v>45872.39583333334</v>
+        <v>45872.375</v>
       </c>
     </row>
     <row r="34">
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4946,16 +4946,16 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5078,16 +5078,16 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF35" t="n">
         <v>0</v>
@@ -5126,22 +5126,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>9.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="M36" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="N36" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,16 +5210,16 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AF36" t="n">
         <v>0</v>
@@ -5253,12 +5253,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.24</v>
+        <v>1.85</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="AL37" s="3" t="n">
-        <v>45872.40625</v>
+        <v>45872.39583333334</v>
       </c>
     </row>
     <row r="38">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.06</v>
+        <v>1.76</v>
       </c>
       <c r="M38" t="n">
-        <v>3.2</v>
+        <v>3.53</v>
       </c>
       <c r="N38" t="n">
-        <v>3.69</v>
+        <v>3.73</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.15</v>
+        <v>1.6</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.7</v>
+        <v>2.24</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="M39" t="n">
-        <v>3.39</v>
+        <v>3.2</v>
       </c>
       <c r="N39" t="n">
-        <v>3.71</v>
+        <v>3.69</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5606,10 +5606,10 @@
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -5640,7 +5640,7 @@
         </is>
       </c>
       <c r="AL39" s="3" t="n">
-        <v>45872.41666666666</v>
+        <v>45872.40625</v>
       </c>
     </row>
     <row r="40">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5744,10 +5744,10 @@
         <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
@@ -5786,22 +5786,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5918,22 +5918,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.42</v>
+        <v>1.8</v>
       </c>
       <c r="M42" t="n">
-        <v>4.33</v>
+        <v>3.39</v>
       </c>
       <c r="N42" t="n">
-        <v>5.4</v>
+        <v>3.71</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6002,16 +6002,16 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
         <v>0</v>
@@ -6050,22 +6050,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6140,10 +6140,10 @@
         <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF43" t="n">
         <v>0</v>
@@ -6177,12 +6177,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Suduroy</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6272,10 +6272,10 @@
         <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF44" t="n">
         <v>0</v>
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="AL44" s="3" t="n">
-        <v>45872.4375</v>
+        <v>45872.41666666666</v>
       </c>
     </row>
     <row r="45">
@@ -6309,27 +6309,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>Suduroy</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6432,7 +6432,7 @@
         </is>
       </c>
       <c r="AL45" s="3" t="n">
-        <v>45872.45833333334</v>
+        <v>45872.4375</v>
       </c>
     </row>
     <row r="46">
@@ -6710,22 +6710,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.64</v>
+        <v>3.23</v>
       </c>
       <c r="M49" t="n">
-        <v>3.25</v>
+        <v>3.39</v>
       </c>
       <c r="N49" t="n">
-        <v>2.31</v>
+        <v>1.94</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6926,10 +6926,10 @@
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AD49" t="n">
         <v>0</v>
@@ -6974,22 +6974,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7106,22 +7106,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Jeunesse Canach</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7370,22 +7370,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7406,13 +7406,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7454,10 +7454,10 @@
         <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
         <v>0</v>
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Jeunesse Canach</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7802,13 +7802,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7850,10 +7850,10 @@
         <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
         <v>0</v>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7934,13 +7934,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7982,10 +7982,10 @@
         <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD57" t="n">
         <v>0</v>
@@ -8025,27 +8025,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8066,13 +8066,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.65</v>
+        <v>2.65</v>
       </c>
       <c r="M58" t="n">
-        <v>3.63</v>
+        <v>3.34</v>
       </c>
       <c r="N58" t="n">
-        <v>4.2</v>
+        <v>2.26</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -8114,10 +8114,10 @@
         <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AC58" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AD58" t="n">
         <v>0</v>
@@ -8148,7 +8148,7 @@
         </is>
       </c>
       <c r="AL58" s="3" t="n">
-        <v>45872.47916666666</v>
+        <v>45872.45833333334</v>
       </c>
     </row>
     <row r="59">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8294,22 +8294,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8330,13 +8330,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8378,10 +8378,10 @@
         <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD60" t="n">
         <v>0</v>
@@ -8553,12 +8553,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8594,13 +8594,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8676,7 +8676,7 @@
         </is>
       </c>
       <c r="AL62" s="3" t="n">
-        <v>45872.5</v>
+        <v>45872.47916666666</v>
       </c>
     </row>
     <row r="63">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8858,13 +8858,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8906,10 +8906,10 @@
         <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD64" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Trenčín</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Spartak Trnava</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8990,13 +8990,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.14</v>
+        <v>3.56</v>
       </c>
       <c r="M65" t="n">
-        <v>3.05</v>
+        <v>3.32</v>
       </c>
       <c r="N65" t="n">
-        <v>3.09</v>
+        <v>1.86</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9038,10 +9038,10 @@
         <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AD65" t="n">
         <v>0</v>
@@ -9086,22 +9086,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9122,13 +9122,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9170,16 +9170,16 @@
         <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
         <v>0</v>
@@ -9218,22 +9218,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9254,13 +9254,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.47</v>
+        <v>3.57</v>
       </c>
       <c r="M67" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="N67" t="n">
-        <v>5.1</v>
+        <v>1.8</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9302,10 +9302,10 @@
         <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AC67" t="n">
-        <v>2.22</v>
+        <v>1.94</v>
       </c>
       <c r="AD67" t="n">
         <v>0</v>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Karpaty</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9434,10 +9434,10 @@
         <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -9482,22 +9482,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Karpaty</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9518,13 +9518,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.73</v>
+        <v>1.47</v>
       </c>
       <c r="M69" t="n">
-        <v>3.23</v>
+        <v>4.1</v>
       </c>
       <c r="N69" t="n">
-        <v>2.54</v>
+        <v>5.1</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9566,10 +9566,10 @@
         <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="AC69" t="n">
-        <v>1.67</v>
+        <v>2.22</v>
       </c>
       <c r="AD69" t="n">
         <v>0</v>
@@ -9614,22 +9614,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9650,13 +9650,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="M70" t="n">
-        <v>3.51</v>
+        <v>3.05</v>
       </c>
       <c r="N70" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9698,10 +9698,10 @@
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AC70" t="n">
-        <v>2.31</v>
+        <v>1.75</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9830,16 +9830,16 @@
         <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC71" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD71" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF71" t="n">
         <v>0</v>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Torpedo BelAZ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Gomel</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9962,10 +9962,10 @@
         <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
@@ -10010,22 +10010,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,13 +10046,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10094,10 +10094,10 @@
         <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC73" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD73" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,13 +10178,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10226,10 +10226,10 @@
         <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
@@ -10274,22 +10274,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.67</v>
+        <v>2.26</v>
       </c>
       <c r="M75" t="n">
-        <v>3.65</v>
+        <v>3.29</v>
       </c>
       <c r="N75" t="n">
-        <v>5</v>
+        <v>2.67</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="AC75" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Torpedo BelAZ</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gomel</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10442,13 +10442,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10490,10 +10490,10 @@
         <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC76" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,13 +10574,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD77" t="n">
         <v>0</v>
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Trenčín</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spartak Trnava</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD80" t="n">
         <v>0</v>
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11316,7 +11316,7 @@
         </is>
       </c>
       <c r="AL82" s="3" t="n">
-        <v>45872.52083333334</v>
+        <v>45872.5</v>
       </c>
     </row>
     <row r="83">
@@ -11325,12 +11325,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.63</v>
+        <v>1.67</v>
       </c>
       <c r="M83" t="n">
-        <v>2.96</v>
+        <v>3.65</v>
       </c>
       <c r="N83" t="n">
-        <v>2.49</v>
+        <v>5</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC83" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AD83" t="n">
         <v>0</v>
@@ -11448,7 +11448,7 @@
         </is>
       </c>
       <c r="AL83" s="3" t="n">
-        <v>45872.52083333334</v>
+        <v>45872.5</v>
       </c>
     </row>
     <row r="84">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>3.56</v>
+        <v>2.63</v>
       </c>
       <c r="M84" t="n">
-        <v>3.31</v>
+        <v>2.96</v>
       </c>
       <c r="N84" t="n">
-        <v>1.86</v>
+        <v>2.49</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11546,10 +11546,10 @@
         <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AC84" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11678,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.76</v>
+        <v>3.56</v>
       </c>
       <c r="M87" t="n">
-        <v>3.6</v>
+        <v>3.31</v>
       </c>
       <c r="N87" t="n">
-        <v>4.2</v>
+        <v>1.86</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11942,10 +11942,10 @@
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AC87" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AD87" t="n">
         <v>0</v>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12026,13 +12026,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.15</v>
+        <v>1.76</v>
       </c>
       <c r="M88" t="n">
-        <v>6.2</v>
+        <v>3.6</v>
       </c>
       <c r="N88" t="n">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12074,16 +12074,16 @@
         <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="AC88" t="n">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="AD88" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
         <v>0</v>
@@ -12117,12 +12117,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,13 +12158,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12206,10 +12206,10 @@
         <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC89" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD89" t="n">
         <v>0</v>
@@ -12240,7 +12240,7 @@
         </is>
       </c>
       <c r="AL89" s="3" t="n">
-        <v>45872.53125</v>
+        <v>45872.52083333334</v>
       </c>
     </row>
     <row r="90">
@@ -12249,12 +12249,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12290,13 +12290,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="M90" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="N90" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12338,16 +12338,16 @@
         <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC90" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD90" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF90" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
         </is>
       </c>
       <c r="AL90" s="3" t="n">
-        <v>45872.53125</v>
+        <v>45872.52083333334</v>
       </c>
     </row>
     <row r="91">
@@ -12381,27 +12381,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12422,13 +12422,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12476,10 +12476,10 @@
         <v>0</v>
       </c>
       <c r="AD91" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
         <v>0</v>
@@ -12504,7 +12504,7 @@
         </is>
       </c>
       <c r="AL91" s="3" t="n">
-        <v>45872.54166666666</v>
+        <v>45872.53125</v>
       </c>
     </row>
     <row r="92">
@@ -12513,12 +12513,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12554,13 +12554,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="M92" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="N92" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12602,16 +12602,16 @@
         <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD92" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF92" t="n">
         <v>0</v>
@@ -12636,7 +12636,7 @@
         </is>
       </c>
       <c r="AL92" s="3" t="n">
-        <v>45872.54166666666</v>
+        <v>45872.53125</v>
       </c>
     </row>
     <row r="93">
@@ -12650,7 +12650,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12686,13 +12686,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.71</v>
+        <v>2.52</v>
       </c>
       <c r="M93" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="N93" t="n">
-        <v>4.6</v>
+        <v>3.03</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12734,10 +12734,10 @@
         <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD93" t="n">
         <v>0</v>
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12866,16 +12866,16 @@
         <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC94" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD94" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE94" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF94" t="n">
         <v>0</v>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12950,13 +12950,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.52</v>
+        <v>1.71</v>
       </c>
       <c r="M95" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="N95" t="n">
-        <v>3.03</v>
+        <v>4.6</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12998,10 +12998,10 @@
         <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC95" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD95" t="n">
         <v>0</v>
@@ -13173,27 +13173,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13296,7 +13296,7 @@
         </is>
       </c>
       <c r="AL97" s="3" t="n">
-        <v>45872.55208333334</v>
+        <v>45872.54166666666</v>
       </c>
     </row>
     <row r="98">
@@ -13305,12 +13305,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13346,13 +13346,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.31</v>
+        <v>6</v>
       </c>
       <c r="M98" t="n">
-        <v>3.15</v>
+        <v>3.89</v>
       </c>
       <c r="N98" t="n">
-        <v>2.7</v>
+        <v>1.44</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13394,16 +13394,16 @@
         <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD98" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF98" t="n">
         <v>0</v>
@@ -13428,7 +13428,7 @@
         </is>
       </c>
       <c r="AL98" s="3" t="n">
-        <v>45872.5625</v>
+        <v>45872.54166666666</v>
       </c>
     </row>
     <row r="99">
@@ -13437,12 +13437,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13560,7 +13560,7 @@
         </is>
       </c>
       <c r="AL99" s="3" t="n">
-        <v>45872.5625</v>
+        <v>45872.55208333334</v>
       </c>
     </row>
     <row r="100">
@@ -13574,22 +13574,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13610,13 +13610,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.28</v>
+        <v>2.31</v>
       </c>
       <c r="M100" t="n">
-        <v>4.75</v>
+        <v>3.15</v>
       </c>
       <c r="N100" t="n">
-        <v>7.8</v>
+        <v>2.7</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13658,16 +13658,16 @@
         <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.61</v>
+        <v>1.84</v>
       </c>
       <c r="AC100" t="n">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="AD100" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AE100" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AF100" t="n">
         <v>0</v>
@@ -13701,12 +13701,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13742,13 +13742,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13760,58 +13760,58 @@
         <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T101" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U101" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V101" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W101" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X101" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="Z101" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD101" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF101" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG101" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH101" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AI101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         </is>
       </c>
       <c r="AL101" s="3" t="n">
-        <v>45872.57291666666</v>
+        <v>45872.5625</v>
       </c>
     </row>
     <row r="102">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13874,13 +13874,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="M102" t="n">
-        <v>3.9</v>
+        <v>4.75</v>
       </c>
       <c r="N102" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13922,16 +13922,16 @@
         <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AC102" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AD102" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AE102" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AF102" t="n">
         <v>0</v>
@@ -13956,7 +13956,7 @@
         </is>
       </c>
       <c r="AL102" s="3" t="n">
-        <v>45872.57291666666</v>
+        <v>45872.5625</v>
       </c>
     </row>
     <row r="103">
@@ -13965,27 +13965,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14006,13 +14006,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14024,58 +14024,58 @@
         <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S103" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T103" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U103" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V103" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W103" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X103" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y103" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Z103" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC103" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD103" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AE103" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF103" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG103" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH103" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AI103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         </is>
       </c>
       <c r="AL103" s="3" t="n">
-        <v>45872.58333333334</v>
+        <v>45872.57291666666</v>
       </c>
     </row>
     <row r="104">
@@ -14097,12 +14097,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -14112,12 +14112,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14138,13 +14138,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -14186,10 +14186,10 @@
         <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC104" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD104" t="n">
         <v>0</v>
@@ -14220,7 +14220,7 @@
         </is>
       </c>
       <c r="AL104" s="3" t="n">
-        <v>45872.58333333334</v>
+        <v>45872.57291666666</v>
       </c>
     </row>
     <row r="105">
@@ -14234,22 +14234,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14498,7 +14498,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14508,12 +14508,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tatran Prešov</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14534,13 +14534,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14640,12 +14640,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14666,13 +14666,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14772,12 +14772,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14894,7 +14894,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Tatran Prešov</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15026,22 +15026,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Slutsk</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15153,27 +15153,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Slutsk</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -15242,10 +15242,10 @@
         <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD112" t="n">
         <v>0</v>
@@ -15276,7 +15276,7 @@
         </is>
       </c>
       <c r="AL112" s="3" t="n">
-        <v>45872.59375</v>
+        <v>45872.58333333334</v>
       </c>
     </row>
     <row r="113">
@@ -15285,27 +15285,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15326,13 +15326,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15368,10 +15368,10 @@
         <v>0</v>
       </c>
       <c r="Z113" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB113" t="n">
         <v>0</v>
@@ -15408,7 +15408,7 @@
         </is>
       </c>
       <c r="AL113" s="3" t="n">
-        <v>45872.60416666666</v>
+        <v>45872.58333333334</v>
       </c>
     </row>
     <row r="114">
@@ -15417,12 +15417,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15458,13 +15458,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.39</v>
+        <v>1.93</v>
       </c>
       <c r="M114" t="n">
-        <v>2.99</v>
+        <v>3.41</v>
       </c>
       <c r="N114" t="n">
-        <v>2.73</v>
+        <v>3.25</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15506,10 +15506,10 @@
         <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AC114" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AD114" t="n">
         <v>0</v>
@@ -15540,7 +15540,7 @@
         </is>
       </c>
       <c r="AL114" s="3" t="n">
-        <v>45872.60416666666</v>
+        <v>45872.59375</v>
       </c>
     </row>
     <row r="115">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15590,13 +15590,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15632,10 +15632,10 @@
         <v>0</v>
       </c>
       <c r="Z115" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB115" t="n">
         <v>0</v>
@@ -15681,27 +15681,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15722,13 +15722,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15770,10 +15770,10 @@
         <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC116" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD116" t="n">
         <v>0</v>
@@ -15804,7 +15804,7 @@
         </is>
       </c>
       <c r="AL116" s="3" t="n">
-        <v>45872.625</v>
+        <v>45872.60416666666</v>
       </c>
     </row>
     <row r="117">
@@ -15813,27 +15813,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15936,7 +15936,7 @@
         </is>
       </c>
       <c r="AL117" s="3" t="n">
-        <v>45872.625</v>
+        <v>45872.60416666666</v>
       </c>
     </row>
     <row r="118">
@@ -15950,22 +15950,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15986,13 +15986,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.99</v>
+        <v>1.67</v>
       </c>
       <c r="M118" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="N118" t="n">
-        <v>3.25</v>
+        <v>6.14</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -16034,10 +16034,10 @@
         <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC118" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD118" t="n">
         <v>0</v>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16118,13 +16118,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -16166,10 +16166,10 @@
         <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC119" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD119" t="n">
         <v>0</v>
@@ -16224,12 +16224,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16250,13 +16250,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -16346,7 +16346,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16488,12 +16488,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16514,13 +16514,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16610,22 +16610,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16737,27 +16737,27 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16778,13 +16778,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="M124" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N124" t="n">
-        <v>3.1</v>
+        <v>4.37</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16860,7 +16860,7 @@
         </is>
       </c>
       <c r="AL124" s="3" t="n">
-        <v>45872.63541666666</v>
+        <v>45872.625</v>
       </c>
     </row>
     <row r="125">
@@ -16869,27 +16869,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16910,13 +16910,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>1.48</v>
+        <v>1.97</v>
       </c>
       <c r="M125" t="n">
-        <v>3.73</v>
+        <v>2.95</v>
       </c>
       <c r="N125" t="n">
-        <v>5.6</v>
+        <v>3.95</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16958,10 +16958,10 @@
         <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AC125" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AD125" t="n">
         <v>0</v>
@@ -16992,7 +16992,7 @@
         </is>
       </c>
       <c r="AL125" s="3" t="n">
-        <v>45872.63541666666</v>
+        <v>45872.625</v>
       </c>
     </row>
     <row r="126">
@@ -17006,7 +17006,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17042,10 +17042,10 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="M126" t="n">
-        <v>3.9</v>
+        <v>3.73</v>
       </c>
       <c r="N126" t="n">
         <v>5.6</v>
@@ -17090,10 +17090,10 @@
         <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AC126" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AD126" t="n">
         <v>0</v>
@@ -17133,12 +17133,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -17148,12 +17148,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17174,13 +17174,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.13</v>
+        <v>1.5</v>
       </c>
       <c r="M127" t="n">
-        <v>2.99</v>
+        <v>3.9</v>
       </c>
       <c r="N127" t="n">
-        <v>3.17</v>
+        <v>5.6</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -17222,10 +17222,10 @@
         <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AC127" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AD127" t="n">
         <v>0</v>
@@ -17256,7 +17256,7 @@
         </is>
       </c>
       <c r="AL127" s="3" t="n">
-        <v>45872.64583333334</v>
+        <v>45872.63541666666</v>
       </c>
     </row>
     <row r="128">
@@ -17265,27 +17265,27 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17306,13 +17306,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -17388,7 +17388,7 @@
         </is>
       </c>
       <c r="AL128" s="3" t="n">
-        <v>45872.64583333334</v>
+        <v>45872.63541666666</v>
       </c>
     </row>
     <row r="129">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1.68</v>
+        <v>2.19</v>
       </c>
       <c r="M129" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="N129" t="n">
-        <v>4.8</v>
+        <v>3.93</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17456,58 +17456,58 @@
         <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S129" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T129" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U129" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V129" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W129" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X129" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y129" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="Z129" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC129" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD129" t="n">
-        <v>0</v>
+        <v>6.97</v>
       </c>
       <c r="AE129" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF129" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG129" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH129" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AI129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
@@ -17529,27 +17529,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17570,13 +17570,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>2.37</v>
+        <v>2.13</v>
       </c>
       <c r="M130" t="n">
-        <v>2.72</v>
+        <v>2.99</v>
       </c>
       <c r="N130" t="n">
-        <v>3.03</v>
+        <v>3.17</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17612,16 +17612,16 @@
         <v>0</v>
       </c>
       <c r="Z130" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="AC130" t="n">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="AD130" t="n">
         <v>0</v>
@@ -17652,7 +17652,7 @@
         </is>
       </c>
       <c r="AL130" s="3" t="n">
-        <v>45872.66666666666</v>
+        <v>45872.64583333334</v>
       </c>
     </row>
     <row r="131">
@@ -17661,12 +17661,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17676,12 +17676,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17702,13 +17702,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17784,7 +17784,7 @@
         </is>
       </c>
       <c r="AL131" s="3" t="n">
-        <v>45872.66666666666</v>
+        <v>45872.64583333334</v>
       </c>
     </row>
     <row r="132">
@@ -17793,12 +17793,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17808,12 +17808,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17834,13 +17834,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="M132" t="n">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="N132" t="n">
-        <v>3.57</v>
+        <v>5</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17876,16 +17876,16 @@
         <v>0</v>
       </c>
       <c r="Z132" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AC132" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AD132" t="n">
         <v>0</v>
@@ -17916,7 +17916,7 @@
         </is>
       </c>
       <c r="AL132" s="3" t="n">
-        <v>45872.66666666666</v>
+        <v>45872.64583333334</v>
       </c>
     </row>
     <row r="133">
@@ -17930,7 +17930,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17940,12 +17940,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17966,13 +17966,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="M133" t="n">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="N133" t="n">
-        <v>4.9</v>
+        <v>6.81</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -18014,10 +18014,10 @@
         <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC133" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD133" t="n">
         <v>0</v>
@@ -18062,22 +18062,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -18098,13 +18098,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>1.51</v>
+        <v>2.37</v>
       </c>
       <c r="M134" t="n">
-        <v>3.78</v>
+        <v>2.72</v>
       </c>
       <c r="N134" t="n">
-        <v>4.91</v>
+        <v>3.03</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -18140,16 +18140,16 @@
         <v>0</v>
       </c>
       <c r="Z134" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AA134" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AB134" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC134" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD134" t="n">
         <v>0</v>
@@ -18326,7 +18326,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -18336,12 +18336,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18362,13 +18362,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -18404,16 +18404,16 @@
         <v>0</v>
       </c>
       <c r="Z136" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA136" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB136" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC136" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD136" t="n">
         <v>0</v>
@@ -18458,7 +18458,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18468,12 +18468,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18585,12 +18585,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18600,12 +18600,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18626,13 +18626,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="M138" t="n">
-        <v>4</v>
+        <v>3.19</v>
       </c>
       <c r="N138" t="n">
-        <v>4.97</v>
+        <v>4.9</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -18674,10 +18674,10 @@
         <v>0</v>
       </c>
       <c r="AB138" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC138" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD138" t="n">
         <v>0</v>
@@ -18708,7 +18708,7 @@
         </is>
       </c>
       <c r="AL138" s="3" t="n">
-        <v>45872.70833333334</v>
+        <v>45872.66666666666</v>
       </c>
     </row>
     <row r="139">
@@ -18717,27 +18717,27 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18758,13 +18758,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -18840,7 +18840,7 @@
         </is>
       </c>
       <c r="AL139" s="3" t="n">
-        <v>45872.70833333334</v>
+        <v>45872.66666666666</v>
       </c>
     </row>
     <row r="140">
@@ -18849,12 +18849,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18864,12 +18864,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18890,13 +18890,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N140" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -18938,10 +18938,10 @@
         <v>0</v>
       </c>
       <c r="AB140" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC140" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD140" t="n">
         <v>0</v>
@@ -18972,7 +18972,7 @@
         </is>
       </c>
       <c r="AL140" s="3" t="n">
-        <v>45872.77083333334</v>
+        <v>45872.6875</v>
       </c>
     </row>
     <row r="141">
@@ -18981,12 +18981,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18996,12 +18996,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -19104,7 +19104,7 @@
         </is>
       </c>
       <c r="AL141" s="3" t="n">
-        <v>45872.77083333334</v>
+        <v>45872.6875</v>
       </c>
     </row>
     <row r="142">
@@ -19113,12 +19113,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -19128,12 +19128,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -19154,13 +19154,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>4.4</v>
+        <v>2.42</v>
       </c>
       <c r="M142" t="n">
-        <v>3.08</v>
+        <v>2.7</v>
       </c>
       <c r="N142" t="n">
-        <v>1.77</v>
+        <v>3.43</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -19196,16 +19196,16 @@
         <v>0</v>
       </c>
       <c r="Z142" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AA142" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB142" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC142" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD142" t="n">
         <v>0</v>
@@ -19236,7 +19236,7 @@
         </is>
       </c>
       <c r="AL142" s="3" t="n">
-        <v>45872.77083333334</v>
+        <v>45872.70833333334</v>
       </c>
     </row>
     <row r="143">
@@ -19245,12 +19245,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -19260,12 +19260,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -19286,13 +19286,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="M143" t="n">
-        <v>3.52</v>
+        <v>4</v>
       </c>
       <c r="N143" t="n">
-        <v>5.6</v>
+        <v>4.97</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -19334,10 +19334,10 @@
         <v>0</v>
       </c>
       <c r="AB143" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC143" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD143" t="n">
         <v>0</v>
@@ -19368,7 +19368,7 @@
         </is>
       </c>
       <c r="AL143" s="3" t="n">
-        <v>45872.77083333334</v>
+        <v>45872.70833333334</v>
       </c>
     </row>
     <row r="144">
@@ -19377,12 +19377,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -19392,12 +19392,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19418,13 +19418,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M144" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -19436,58 +19436,58 @@
         <v>0</v>
       </c>
       <c r="R144" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S144" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T144" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U144" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V144" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W144" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X144" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y144" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Z144" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA144" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB144" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AC144" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD144" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AE144" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF144" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AG144" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH144" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI144" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         </is>
       </c>
       <c r="AL144" s="3" t="n">
-        <v>45872.79166666666</v>
+        <v>45872.76041666666</v>
       </c>
     </row>
     <row r="145">
@@ -19509,12 +19509,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19524,12 +19524,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19550,13 +19550,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>1.36</v>
+        <v>4.4</v>
       </c>
       <c r="M145" t="n">
-        <v>4.5</v>
+        <v>3.08</v>
       </c>
       <c r="N145" t="n">
-        <v>6.2</v>
+        <v>1.77</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -19598,10 +19598,10 @@
         <v>0</v>
       </c>
       <c r="AB145" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC145" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD145" t="n">
         <v>0</v>
@@ -19632,7 +19632,7 @@
         </is>
       </c>
       <c r="AL145" s="3" t="n">
-        <v>45872.79166666666</v>
+        <v>45872.77083333334</v>
       </c>
     </row>
     <row r="146">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -19656,12 +19656,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19682,13 +19682,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>4.6</v>
+        <v>1.84</v>
       </c>
       <c r="M146" t="n">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="N146" t="n">
-        <v>1.73</v>
+        <v>3.8</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -19724,16 +19724,16 @@
         <v>0</v>
       </c>
       <c r="Z146" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AB146" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AC146" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AD146" t="n">
         <v>0</v>
@@ -19764,7 +19764,7 @@
         </is>
       </c>
       <c r="AL146" s="3" t="n">
-        <v>45872.8125</v>
+        <v>45872.77083333334</v>
       </c>
     </row>
     <row r="147">
@@ -19773,12 +19773,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -19788,12 +19788,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19896,7 +19896,7 @@
         </is>
       </c>
       <c r="AL147" s="3" t="n">
-        <v>45872.83333333334</v>
+        <v>45872.77083333334</v>
       </c>
     </row>
     <row r="148">
@@ -19905,12 +19905,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19920,12 +19920,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19946,13 +19946,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>1.89</v>
+        <v>1.52</v>
       </c>
       <c r="M148" t="n">
-        <v>3.03</v>
+        <v>3.52</v>
       </c>
       <c r="N148" t="n">
-        <v>3.85</v>
+        <v>5.6</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -19994,7 +19994,7 @@
         <v>0</v>
       </c>
       <c r="AB148" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="AC148" t="n">
         <v>1.53</v>
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="AL148" s="3" t="n">
-        <v>45872.85416666666</v>
+        <v>45872.77083333334</v>
       </c>
     </row>
     <row r="149">
@@ -20037,12 +20037,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -20052,12 +20052,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -20160,7 +20160,7 @@
         </is>
       </c>
       <c r="AL149" s="3" t="n">
-        <v>45872.91666666666</v>
+        <v>45872.79166666666</v>
       </c>
     </row>
     <row r="150">
@@ -20169,129 +20169,1053 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Orlando Pride</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Utah Royals</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0</v>
+      </c>
+      <c r="I150" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L150" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M150" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N150" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O150" t="n">
+        <v>0</v>
+      </c>
+      <c r="P150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>0</v>
+      </c>
+      <c r="R150" t="n">
+        <v>0</v>
+      </c>
+      <c r="S150" t="n">
+        <v>0</v>
+      </c>
+      <c r="T150" t="n">
+        <v>0</v>
+      </c>
+      <c r="U150" t="n">
+        <v>0</v>
+      </c>
+      <c r="V150" t="n">
+        <v>0</v>
+      </c>
+      <c r="W150" t="n">
+        <v>0</v>
+      </c>
+      <c r="X150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL150" s="3" t="n">
+        <v>45872.79166666666</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>45872</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Philadelphia Union II</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>FC Cincinnati II</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L151" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" t="n">
+        <v>0</v>
+      </c>
+      <c r="N151" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" t="n">
+        <v>0</v>
+      </c>
+      <c r="P151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>0</v>
+      </c>
+      <c r="R151" t="n">
+        <v>0</v>
+      </c>
+      <c r="S151" t="n">
+        <v>0</v>
+      </c>
+      <c r="T151" t="n">
+        <v>0</v>
+      </c>
+      <c r="U151" t="n">
+        <v>0</v>
+      </c>
+      <c r="V151" t="n">
+        <v>0</v>
+      </c>
+      <c r="W151" t="n">
+        <v>0</v>
+      </c>
+      <c r="X151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL151" s="3" t="n">
+        <v>45872.79166666666</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>45872</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Ypiranga Erechim</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Caxias</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0</v>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L152" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" t="n">
+        <v>0</v>
+      </c>
+      <c r="N152" t="n">
+        <v>0</v>
+      </c>
+      <c r="O152" t="n">
+        <v>0</v>
+      </c>
+      <c r="P152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>0</v>
+      </c>
+      <c r="R152" t="n">
+        <v>0</v>
+      </c>
+      <c r="S152" t="n">
+        <v>0</v>
+      </c>
+      <c r="T152" t="n">
+        <v>0</v>
+      </c>
+      <c r="U152" t="n">
+        <v>0</v>
+      </c>
+      <c r="V152" t="n">
+        <v>0</v>
+      </c>
+      <c r="W152" t="n">
+        <v>0</v>
+      </c>
+      <c r="X152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL152" s="3" t="n">
+        <v>45872.79166666666</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>45872</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L153" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M153" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="N153" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0</v>
+      </c>
+      <c r="P153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>0</v>
+      </c>
+      <c r="R153" t="n">
+        <v>0</v>
+      </c>
+      <c r="S153" t="n">
+        <v>0</v>
+      </c>
+      <c r="T153" t="n">
+        <v>0</v>
+      </c>
+      <c r="U153" t="n">
+        <v>0</v>
+      </c>
+      <c r="V153" t="n">
+        <v>0</v>
+      </c>
+      <c r="W153" t="n">
+        <v>0</v>
+      </c>
+      <c r="X153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z153" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AA153" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB153" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AC153" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL153" s="3" t="n">
+        <v>45872.8125</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>45872</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Orlando City II</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>New York City II</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0</v>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L154" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" t="n">
+        <v>0</v>
+      </c>
+      <c r="N154" t="n">
+        <v>0</v>
+      </c>
+      <c r="O154" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>0</v>
+      </c>
+      <c r="R154" t="n">
+        <v>0</v>
+      </c>
+      <c r="S154" t="n">
+        <v>0</v>
+      </c>
+      <c r="T154" t="n">
+        <v>0</v>
+      </c>
+      <c r="U154" t="n">
+        <v>0</v>
+      </c>
+      <c r="V154" t="n">
+        <v>0</v>
+      </c>
+      <c r="W154" t="n">
+        <v>0</v>
+      </c>
+      <c r="X154" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ154" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK154" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL154" s="3" t="n">
+        <v>45872.83333333334</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>45872</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0</v>
+      </c>
+      <c r="I155" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0</v>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L155" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="M155" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="N155" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O155" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>0</v>
+      </c>
+      <c r="R155" t="n">
+        <v>0</v>
+      </c>
+      <c r="S155" t="n">
+        <v>0</v>
+      </c>
+      <c r="T155" t="n">
+        <v>0</v>
+      </c>
+      <c r="U155" t="n">
+        <v>0</v>
+      </c>
+      <c r="V155" t="n">
+        <v>0</v>
+      </c>
+      <c r="W155" t="n">
+        <v>0</v>
+      </c>
+      <c r="X155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB155" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AC155" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL155" s="3" t="n">
+        <v>45872.85416666666</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>45872</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Portland Timbers II</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Real Monarchs</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0</v>
+      </c>
+      <c r="I156" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L156" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" t="n">
+        <v>0</v>
+      </c>
+      <c r="N156" t="n">
+        <v>0</v>
+      </c>
+      <c r="O156" t="n">
+        <v>0</v>
+      </c>
+      <c r="P156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>0</v>
+      </c>
+      <c r="R156" t="n">
+        <v>0</v>
+      </c>
+      <c r="S156" t="n">
+        <v>0</v>
+      </c>
+      <c r="T156" t="n">
+        <v>0</v>
+      </c>
+      <c r="U156" t="n">
+        <v>0</v>
+      </c>
+      <c r="V156" t="n">
+        <v>0</v>
+      </c>
+      <c r="W156" t="n">
+        <v>0</v>
+      </c>
+      <c r="X156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL156" s="3" t="n">
+        <v>45872.91666666666</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>45872</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
+      <c r="C157" t="inlineStr">
         <is>
           <t>USA MLS Next Pro</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
+      <c r="D157" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
+      <c r="E157" t="inlineStr">
         <is>
           <t>Los Angeles II</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr">
+      <c r="F157" t="inlineStr">
         <is>
           <t>San Jose Earthquakes II</t>
         </is>
       </c>
-      <c r="G150" t="n">
-        <v>0</v>
-      </c>
-      <c r="H150" t="n">
-        <v>0</v>
-      </c>
-      <c r="I150" t="n">
-        <v>0</v>
-      </c>
-      <c r="J150" t="n">
-        <v>0</v>
-      </c>
-      <c r="K150" t="inlineStr">
+      <c r="G157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0</v>
+      </c>
+      <c r="I157" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L150" t="n">
-        <v>0</v>
-      </c>
-      <c r="M150" t="n">
-        <v>0</v>
-      </c>
-      <c r="N150" t="n">
-        <v>0</v>
-      </c>
-      <c r="O150" t="n">
-        <v>0</v>
-      </c>
-      <c r="P150" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
-      <c r="R150" t="n">
-        <v>0</v>
-      </c>
-      <c r="S150" t="n">
-        <v>0</v>
-      </c>
-      <c r="T150" t="n">
-        <v>0</v>
-      </c>
-      <c r="U150" t="n">
-        <v>0</v>
-      </c>
-      <c r="V150" t="n">
-        <v>0</v>
-      </c>
-      <c r="W150" t="n">
-        <v>0</v>
-      </c>
-      <c r="X150" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y150" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ150" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK150" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL150" s="3" t="n">
+      <c r="L157" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" t="n">
+        <v>0</v>
+      </c>
+      <c r="N157" t="n">
+        <v>0</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+      <c r="P157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>0</v>
+      </c>
+      <c r="R157" t="n">
+        <v>0</v>
+      </c>
+      <c r="S157" t="n">
+        <v>0</v>
+      </c>
+      <c r="T157" t="n">
+        <v>0</v>
+      </c>
+      <c r="U157" t="n">
+        <v>0</v>
+      </c>
+      <c r="V157" t="n">
+        <v>0</v>
+      </c>
+      <c r="W157" t="n">
+        <v>0</v>
+      </c>
+      <c r="X157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL157" s="3" t="n">
         <v>45872.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-03.xlsx
+++ b/jogos_2025-08-03.xlsx
@@ -13706,7 +13706,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13716,25 +13716,25 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -13742,85 +13742,85 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="M101" t="n">
         <v>3.1</v>
       </c>
       <c r="N101" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O101" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="Q101" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="R101" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="S101" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="T101" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="U101" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="V101" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="W101" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X101" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Y101" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA101" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC101" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD101" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH101" t="n">
         <v>9</v>
       </c>
-      <c r="Z101" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA101" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB101" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC101" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD101" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE101" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AF101" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG101" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH101" t="n">
-        <v>6</v>
-      </c>
       <c r="AI101" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>['51', '65']</t>
+          <t>['47']</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>['32', '89']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AL101" s="3" t="n">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13848,111 +13848,111 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G102" t="n">
+        <v>2</v>
+      </c>
+      <c r="H102" t="n">
+        <v>2</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
         <v>1</v>
       </c>
-      <c r="H102" t="n">
-        <v>1</v>
-      </c>
-      <c r="I102" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" t="n">
-        <v>0</v>
-      </c>
       <c r="K102" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.45</v>
+        <v>2.25</v>
       </c>
       <c r="M102" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="N102" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="O102" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="P102" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="R102" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="S102" t="n">
-        <v>4.33</v>
+        <v>2.62</v>
       </c>
       <c r="T102" t="n">
-        <v>2.22</v>
+        <v>2.9</v>
       </c>
       <c r="U102" t="n">
-        <v>1.58</v>
+        <v>1.35</v>
       </c>
       <c r="V102" t="n">
-        <v>4.75</v>
+        <v>7.8</v>
       </c>
       <c r="W102" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="X102" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y102" t="n">
-        <v>14.9</v>
+        <v>9</v>
       </c>
       <c r="Z102" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AA102" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
       <c r="AC102" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="AD102" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="AE102" t="n">
-        <v>1.63</v>
+        <v>1.24</v>
       </c>
       <c r="AF102" t="n">
-        <v>1.47</v>
+        <v>1.75</v>
       </c>
       <c r="AG102" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="AH102" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="AI102" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>['51', '65']</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>['32', '89']</t>
         </is>
       </c>
       <c r="AL102" s="3" t="n">
@@ -13970,35 +13970,35 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -14006,85 +14006,85 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.28</v>
+        <v>2.7</v>
       </c>
       <c r="M103" t="n">
-        <v>4.75</v>
+        <v>3.3</v>
       </c>
       <c r="N103" t="n">
-        <v>7.8</v>
+        <v>2.33</v>
       </c>
       <c r="O103" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P103" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R103" t="n">
         <v>1.36</v>
       </c>
-      <c r="P103" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q103" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R103" t="n">
-        <v>1.3</v>
-      </c>
       <c r="S103" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="T103" t="n">
-        <v>2.38</v>
+        <v>2.71</v>
       </c>
       <c r="U103" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="V103" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W103" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X103" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y103" t="n">
         <v>10</v>
       </c>
       <c r="Z103" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AA103" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AC103" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AD103" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="AE103" t="n">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AF103" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AG103" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AH103" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AI103" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>['1', '4', '48', '59', '71']</t>
+          <t>['17', '90+2']</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+3']</t>
         </is>
       </c>
       <c r="AL103" s="3" t="n">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -14112,19 +14112,19 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G104" t="n">
         <v>1</v>
       </c>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I104" t="n">
         <v>0</v>
@@ -14138,85 +14138,85 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="M104" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="N104" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O104" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="P104" t="n">
-        <v>6.75</v>
+        <v>19</v>
       </c>
       <c r="Q104" t="n">
         <v>2.63</v>
       </c>
       <c r="R104" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="S104" t="n">
-        <v>2.5</v>
+        <v>4.33</v>
       </c>
       <c r="T104" t="n">
-        <v>3.5</v>
+        <v>2.22</v>
       </c>
       <c r="U104" t="n">
-        <v>1.29</v>
+        <v>1.58</v>
       </c>
       <c r="V104" t="n">
-        <v>10</v>
+        <v>4.75</v>
       </c>
       <c r="W104" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="X104" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Y104" t="n">
-        <v>7.44</v>
+        <v>14.9</v>
       </c>
       <c r="Z104" t="n">
-        <v>1.48</v>
+        <v>1.13</v>
       </c>
       <c r="AA104" t="n">
-        <v>2.74</v>
+        <v>4.6</v>
       </c>
       <c r="AB104" t="n">
-        <v>2.3</v>
+        <v>1.47</v>
       </c>
       <c r="AC104" t="n">
-        <v>1.55</v>
+        <v>2.35</v>
       </c>
       <c r="AD104" t="n">
-        <v>4.76</v>
+        <v>2.4</v>
       </c>
       <c r="AE104" t="n">
-        <v>1.2</v>
+        <v>1.63</v>
       </c>
       <c r="AF104" t="n">
-        <v>2.2</v>
+        <v>1.47</v>
       </c>
       <c r="AG104" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="AH104" t="n">
-        <v>9</v>
+        <v>3.1</v>
       </c>
       <c r="AI104" t="n">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>['47']</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AL104" s="3" t="n">
@@ -14234,35 +14234,35 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G105" t="n">
+        <v>5</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
         <v>2</v>
       </c>
-      <c r="H105" t="n">
-        <v>1</v>
-      </c>
-      <c r="I105" t="n">
-        <v>1</v>
-      </c>
       <c r="J105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -14270,85 +14270,85 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.7</v>
+        <v>1.28</v>
       </c>
       <c r="M105" t="n">
-        <v>3.3</v>
+        <v>4.75</v>
       </c>
       <c r="N105" t="n">
-        <v>2.33</v>
+        <v>7.8</v>
       </c>
       <c r="O105" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="P105" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="Q105" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="R105" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S105" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="T105" t="n">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="U105" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="V105" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W105" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X105" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y105" t="n">
         <v>10</v>
       </c>
       <c r="Z105" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AA105" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AC105" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AD105" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="AE105" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="AF105" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AG105" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AH105" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="AI105" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>['17', '90+2']</t>
+          <t>['1', '4', '48', '59', '71']</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>['45+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AL105" s="3" t="n">
@@ -14366,121 +14366,121 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G106" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" t="n">
+        <v>3</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
         <v>2</v>
       </c>
-      <c r="H106" t="n">
-        <v>0</v>
-      </c>
-      <c r="I106" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" t="n">
-        <v>0</v>
-      </c>
       <c r="K106" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L106" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="M106" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="N106" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O106" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P106" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R106" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S106" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T106" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="U106" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V106" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W106" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X106" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB106" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AC106" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD106" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF106" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AG106" t="n">
         <v>1.5</v>
       </c>
-      <c r="M106" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N106" t="n">
-        <v>7</v>
-      </c>
-      <c r="O106" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="P106" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q106" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R106" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S106" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T106" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U106" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V106" t="n">
-        <v>7</v>
-      </c>
-      <c r="W106" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X106" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y106" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z106" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AA106" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB106" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AC106" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD106" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AE106" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF106" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG106" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AH106" t="n">
-        <v>6.6</v>
+        <v>13.5</v>
       </c>
       <c r="AI106" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>['90+3', '90+6']</t>
+          <t>['72']</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5', '13', '90+6']</t>
         </is>
       </c>
       <c r="AL106" s="3" t="n">
@@ -14498,35 +14498,35 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H107" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I107" t="n">
         <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
@@ -14534,85 +14534,85 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.37</v>
+        <v>1.5</v>
       </c>
       <c r="M107" t="n">
-        <v>2.63</v>
+        <v>3.9</v>
       </c>
       <c r="N107" t="n">
-        <v>3.3</v>
+        <v>7</v>
       </c>
       <c r="O107" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P107" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R107" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S107" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T107" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U107" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V107" t="n">
+        <v>7</v>
+      </c>
+      <c r="W107" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X107" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB107" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AC107" t="n">
         <v>1.8</v>
       </c>
-      <c r="P107" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q107" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R107" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="S107" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="T107" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="U107" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V107" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W107" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X107" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Y107" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z107" t="n">
+      <c r="AD107" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF107" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG107" t="n">
         <v>1.7</v>
       </c>
-      <c r="AA107" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB107" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AC107" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD107" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AE107" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF107" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AG107" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AH107" t="n">
-        <v>13.5</v>
+        <v>6.6</v>
       </c>
       <c r="AI107" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>['72']</t>
+          <t>['90+3', '90+6']</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>['5', '13', '90+6']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AL107" s="3" t="n">
@@ -14762,35 +14762,35 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G109" t="n">
+        <v>1</v>
+      </c>
+      <c r="H109" t="n">
         <v>3</v>
       </c>
-      <c r="H109" t="n">
-        <v>0</v>
-      </c>
       <c r="I109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
@@ -14798,85 +14798,85 @@
         </is>
       </c>
       <c r="L109" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="M109" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N109" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="O109" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P109" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R109" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S109" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T109" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U109" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V109" t="n">
+        <v>5</v>
+      </c>
+      <c r="W109" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X109" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA109" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB109" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC109" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD109" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE109" t="n">
         <v>1.45</v>
       </c>
-      <c r="M109" t="n">
-        <v>4</v>
-      </c>
-      <c r="N109" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O109" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="P109" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="Q109" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R109" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S109" t="n">
-        <v>3</v>
-      </c>
-      <c r="T109" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U109" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V109" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W109" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X109" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y109" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="Z109" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA109" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB109" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC109" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD109" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE109" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AF109" t="n">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="AG109" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AH109" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="AI109" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>['16', '28', '42']</t>
+          <t>['8']</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9', '31', '72']</t>
         </is>
       </c>
       <c r="AL109" s="3" t="n">
@@ -14894,7 +14894,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14919,7 +14919,7 @@
         <v>1</v>
       </c>
       <c r="I110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -14930,52 +14930,52 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>3</v>
+        <v>1.83</v>
       </c>
       <c r="M110" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="N110" t="n">
-        <v>2.27</v>
+        <v>3.85</v>
       </c>
       <c r="O110" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="P110" t="n">
-        <v>12.25</v>
+        <v>8.5</v>
       </c>
       <c r="Q110" t="n">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="R110" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S110" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T110" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U110" t="n">
         <v>1.36</v>
       </c>
-      <c r="S110" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T110" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U110" t="n">
-        <v>1.39</v>
-      </c>
       <c r="V110" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W110" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X110" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y110" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Z110" t="n">
         <v>1.25</v>
       </c>
       <c r="AA110" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AB110" t="n">
         <v>1.95</v>
@@ -14987,28 +14987,28 @@
         <v>3.2</v>
       </c>
       <c r="AE110" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AF110" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AG110" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH110" t="n">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="AI110" t="n">
         <v>1.1</v>
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>['76']</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
         <is>
-          <t>['83']</t>
+          <t>['90+5']</t>
         </is>
       </c>
       <c r="AL110" s="3" t="n">
@@ -15026,7 +15026,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -15036,19 +15036,19 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tatran Prešov</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G111" t="n">
         <v>1</v>
       </c>
       <c r="H111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I111" t="n">
         <v>1</v>
@@ -15062,85 +15062,85 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.44</v>
+        <v>3</v>
       </c>
       <c r="M111" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="N111" t="n">
-        <v>6</v>
+        <v>2.25</v>
       </c>
       <c r="O111" t="n">
-        <v>1.44</v>
+        <v>2.2</v>
       </c>
       <c r="P111" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Q111" t="n">
-        <v>3</v>
+        <v>1.73</v>
       </c>
       <c r="R111" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S111" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="T111" t="n">
-        <v>2.38</v>
+        <v>2.9</v>
       </c>
       <c r="U111" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="V111" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="W111" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X111" t="n">
         <v>1.03</v>
       </c>
       <c r="Y111" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="Z111" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AA111" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="AC111" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD111" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE111" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF111" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG111" t="n">
         <v>2.1</v>
       </c>
-      <c r="AD111" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AE111" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF111" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG111" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AH111" t="n">
-        <v>4.8</v>
+        <v>6.25</v>
       </c>
       <c r="AI111" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>['45']</t>
+          <t>['4']</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['56']</t>
         </is>
       </c>
       <c r="AL111" s="3" t="n">
@@ -15168,25 +15168,25 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G112" t="n">
+        <v>2</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" t="n">
         <v>1</v>
       </c>
-      <c r="H112" t="n">
-        <v>1</v>
-      </c>
-      <c r="I112" t="n">
-        <v>0</v>
-      </c>
       <c r="J112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
@@ -15194,40 +15194,40 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>3.55</v>
+        <v>2.75</v>
       </c>
       <c r="M112" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N112" t="n">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="O112" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="P112" t="n">
         <v>13.25</v>
       </c>
       <c r="Q112" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="R112" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S112" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="T112" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="U112" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V112" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W112" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X112" t="n">
         <v>1</v>
@@ -15239,40 +15239,40 @@
         <v>1.28</v>
       </c>
       <c r="AA112" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AC112" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AD112" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AE112" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AF112" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG112" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH112" t="n">
-        <v>7.3</v>
+        <v>5.75</v>
       </c>
       <c r="AI112" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>['84']</t>
+          <t>['17', '79']</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
         <is>
-          <t>['33']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AL112" s="3" t="n">
@@ -15300,12 +15300,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15315,96 +15315,96 @@
         <v>1</v>
       </c>
       <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
         <v>1</v>
       </c>
-      <c r="J113" t="n">
-        <v>0</v>
-      </c>
       <c r="K113" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="M113" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N113" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="O113" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="P113" t="n">
-        <v>15</v>
+        <v>13.25</v>
       </c>
       <c r="Q113" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="R113" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S113" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="T113" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="U113" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V113" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W113" t="n">
         <v>1.07</v>
       </c>
       <c r="X113" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y113" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="Z113" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AA113" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AB113" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AC113" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AD113" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AE113" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AF113" t="n">
         <v>1.8</v>
       </c>
       <c r="AG113" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH113" t="n">
-        <v>6.25</v>
+        <v>7.3</v>
       </c>
       <c r="AI113" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>['4']</t>
+          <t>['84']</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
         <is>
-          <t>['56']</t>
+          <t>['33']</t>
         </is>
       </c>
       <c r="AL113" s="3" t="n">
@@ -15422,35 +15422,35 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I114" t="n">
         <v>1</v>
       </c>
       <c r="J114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
@@ -15458,85 +15458,85 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.83</v>
+        <v>3.05</v>
       </c>
       <c r="M114" t="n">
-        <v>3.38</v>
+        <v>3.8</v>
       </c>
       <c r="N114" t="n">
-        <v>3.85</v>
+        <v>1.97</v>
       </c>
       <c r="O114" t="n">
-        <v>1.53</v>
+        <v>2.15</v>
       </c>
       <c r="P114" t="n">
-        <v>8.5</v>
+        <v>13.5</v>
       </c>
       <c r="Q114" t="n">
-        <v>2.63</v>
+        <v>1.75</v>
       </c>
       <c r="R114" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S114" t="n">
-        <v>2.76</v>
+        <v>3.55</v>
       </c>
       <c r="T114" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="U114" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="V114" t="n">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="W114" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X114" t="n">
         <v>1.03</v>
       </c>
       <c r="Y114" t="n">
-        <v>8.5</v>
+        <v>12</v>
       </c>
       <c r="Z114" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AA114" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="AB114" t="n">
-        <v>1.95</v>
+        <v>1.54</v>
       </c>
       <c r="AC114" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AD114" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="AE114" t="n">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="AF114" t="n">
-        <v>1.8</v>
+        <v>1.49</v>
       </c>
       <c r="AG114" t="n">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="AH114" t="n">
-        <v>5.75</v>
+        <v>4.4</v>
       </c>
       <c r="AI114" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>['39']</t>
+          <t>['16', '69']</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
         <is>
-          <t>['90+5']</t>
+          <t>['18', '71']</t>
         </is>
       </c>
       <c r="AL114" s="3" t="n">
@@ -15554,35 +15554,35 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Tatran Prešov</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I115" t="n">
         <v>1</v>
       </c>
       <c r="J115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -15590,85 +15590,85 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>3.05</v>
+        <v>1.44</v>
       </c>
       <c r="M115" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="N115" t="n">
-        <v>1.97</v>
+        <v>6</v>
       </c>
       <c r="O115" t="n">
-        <v>2.15</v>
+        <v>1.44</v>
       </c>
       <c r="P115" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="Q115" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="R115" t="n">
         <v>1.3</v>
       </c>
       <c r="S115" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="T115" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="U115" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="V115" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="W115" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X115" t="n">
         <v>1.03</v>
       </c>
       <c r="Y115" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z115" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AA115" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="AB115" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AC115" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD115" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AE115" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="AF115" t="n">
-        <v>1.49</v>
+        <v>1.83</v>
       </c>
       <c r="AG115" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="AH115" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AI115" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>['16', '69']</t>
+          <t>['45']</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
         <is>
-          <t>['18', '71']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AL115" s="3" t="n">
@@ -15686,121 +15686,121 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Slutsk</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G116" t="n">
         <v>1</v>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L116" t="n">
+        <v>3</v>
+      </c>
+      <c r="M116" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N116" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="O116" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P116" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R116" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S116" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T116" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U116" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V116" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W116" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X116" t="n">
         <v>1</v>
       </c>
-      <c r="J116" t="n">
-        <v>0</v>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L116" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="M116" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N116" t="n">
-        <v>11</v>
-      </c>
-      <c r="O116" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P116" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Q116" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R116" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S116" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T116" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U116" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V116" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W116" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X116" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y116" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="Z116" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AA116" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AC116" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AD116" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="AE116" t="n">
-        <v>1.49</v>
+        <v>1.26</v>
       </c>
       <c r="AF116" t="n">
-        <v>2.85</v>
+        <v>1.71</v>
       </c>
       <c r="AG116" t="n">
-        <v>1.37</v>
+        <v>2</v>
       </c>
       <c r="AH116" t="n">
-        <v>4.1</v>
+        <v>6.25</v>
       </c>
       <c r="AI116" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>['15']</t>
+          <t>['76']</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['83']</t>
         </is>
       </c>
       <c r="AL116" s="3" t="n">
@@ -15818,7 +15818,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15828,25 +15828,25 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Slutsk</t>
         </is>
       </c>
       <c r="G117" t="n">
         <v>1</v>
       </c>
       <c r="H117" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I117" t="n">
         <v>1</v>
       </c>
       <c r="J117" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
@@ -15854,85 +15854,85 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>2.85</v>
+        <v>1.21</v>
       </c>
       <c r="M117" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="N117" t="n">
-        <v>2.17</v>
+        <v>11</v>
       </c>
       <c r="O117" t="n">
-        <v>2.3</v>
+        <v>1.15</v>
       </c>
       <c r="P117" t="n">
         <v>12.5</v>
       </c>
       <c r="Q117" t="n">
-        <v>1.67</v>
+        <v>6.5</v>
       </c>
       <c r="R117" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S117" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T117" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="U117" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="V117" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="W117" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X117" t="n">
         <v>1.02</v>
       </c>
       <c r="Y117" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="Z117" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AI117" t="n">
         <v>1.2</v>
       </c>
-      <c r="AA117" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB117" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC117" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD117" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE117" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF117" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG117" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH117" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AI117" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>['8']</t>
+          <t>['15']</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>['9', '31', '72']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AL117" s="3" t="n">
@@ -15960,22 +15960,22 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -15986,80 +15986,80 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.75</v>
+        <v>1.45</v>
       </c>
       <c r="M118" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="N118" t="n">
-        <v>2.31</v>
+        <v>6.5</v>
       </c>
       <c r="O118" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="P118" t="n">
-        <v>13.25</v>
+        <v>11.25</v>
       </c>
       <c r="Q118" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="R118" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="S118" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="T118" t="n">
-        <v>2.95</v>
+        <v>2.65</v>
       </c>
       <c r="U118" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="V118" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W118" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X118" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y118" t="n">
-        <v>9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Z118" t="n">
         <v>1.28</v>
       </c>
       <c r="AA118" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AC118" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AD118" t="n">
-        <v>3.28</v>
+        <v>2.9</v>
       </c>
       <c r="AE118" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AF118" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AG118" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AH118" t="n">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="AI118" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>['17', '79']</t>
+          <t>['16', '28', '42']</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -16214,7 +16214,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -16224,111 +16224,111 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G120" t="n">
+        <v>2</v>
+      </c>
+      <c r="H120" t="n">
+        <v>2</v>
+      </c>
+      <c r="I120" t="n">
+        <v>2</v>
+      </c>
+      <c r="J120" t="n">
         <v>1</v>
       </c>
-      <c r="H120" t="n">
-        <v>0</v>
-      </c>
-      <c r="I120" t="n">
-        <v>1</v>
-      </c>
-      <c r="J120" t="n">
-        <v>0</v>
-      </c>
       <c r="K120" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="M120" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="N120" t="n">
-        <v>2.91</v>
+        <v>2.6</v>
       </c>
       <c r="O120" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="P120" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="Q120" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="R120" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="S120" t="n">
-        <v>2.53</v>
+        <v>2.84</v>
       </c>
       <c r="T120" t="n">
-        <v>3.24</v>
+        <v>2.8</v>
       </c>
       <c r="U120" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="V120" t="n">
-        <v>8.199999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="W120" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X120" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y120" t="n">
-        <v>7.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Z120" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AA120" t="n">
-        <v>2.44</v>
+        <v>3.2</v>
       </c>
       <c r="AB120" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AC120" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AD120" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="AE120" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AF120" t="n">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="AG120" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AH120" t="n">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="AI120" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>['1']</t>
+          <t>['15', '21']</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11', '80']</t>
         </is>
       </c>
       <c r="AL120" s="3" t="n">
@@ -16346,7 +16346,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -16356,25 +16356,25 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H121" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
@@ -16382,85 +16382,85 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="M121" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="N121" t="n">
-        <v>2.6</v>
+        <v>2.91</v>
       </c>
       <c r="O121" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="P121" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="Q121" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="R121" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="S121" t="n">
-        <v>2.84</v>
+        <v>2.53</v>
       </c>
       <c r="T121" t="n">
-        <v>2.8</v>
+        <v>3.24</v>
       </c>
       <c r="U121" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="V121" t="n">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W121" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X121" t="n">
         <v>1.06</v>
       </c>
-      <c r="X121" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y121" t="n">
-        <v>8.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="Z121" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AA121" t="n">
-        <v>3.2</v>
+        <v>2.44</v>
       </c>
       <c r="AB121" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AC121" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AD121" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="AE121" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AF121" t="n">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="AG121" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AH121" t="n">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="AI121" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>['15', '21']</t>
+          <t>['1']</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>['11', '80']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AL121" s="3" t="n">
@@ -16610,35 +16610,35 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H123" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I123" t="n">
         <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -16646,85 +16646,85 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1.84</v>
+        <v>7.88</v>
       </c>
       <c r="M123" t="n">
-        <v>3.23</v>
+        <v>4.92</v>
       </c>
       <c r="N123" t="n">
-        <v>3.93</v>
+        <v>1.35</v>
       </c>
       <c r="O123" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P123" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R123" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S123" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T123" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U123" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V123" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W123" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X123" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AB123" t="n">
         <v>1.67</v>
       </c>
-      <c r="P123" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Q123" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R123" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S123" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T123" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U123" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V123" t="n">
-        <v>9</v>
-      </c>
-      <c r="W123" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X123" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y123" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z123" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AA123" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AB123" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AC123" t="n">
-        <v>1.58</v>
+        <v>2.15</v>
       </c>
       <c r="AD123" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="AE123" t="n">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="AF123" t="n">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="AG123" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AH123" t="n">
-        <v>8.5</v>
+        <v>4.6</v>
       </c>
       <c r="AI123" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>['47', '65']</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+2', '57', '71']</t>
         </is>
       </c>
       <c r="AL123" s="3" t="n">
@@ -16742,35 +16742,35 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H124" t="n">
         <v>1</v>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
@@ -16778,85 +16778,85 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.37</v>
+        <v>1.6</v>
       </c>
       <c r="M124" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="N124" t="n">
-        <v>2.85</v>
+        <v>4</v>
       </c>
       <c r="O124" t="n">
-        <v>1.72</v>
+        <v>1.44</v>
       </c>
       <c r="P124" t="n">
-        <v>17.25</v>
+        <v>20</v>
       </c>
       <c r="Q124" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="R124" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="S124" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T124" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U124" t="n">
+        <v>2</v>
+      </c>
+      <c r="V124" t="n">
         <v>3.2</v>
       </c>
-      <c r="T124" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="U124" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V124" t="n">
-        <v>5.5</v>
-      </c>
       <c r="W124" t="n">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="X124" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z124" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="AA124" t="n">
-        <v>4.3</v>
+        <v>8.5</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.65</v>
+        <v>1.22</v>
       </c>
       <c r="AC124" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="AD124" t="n">
-        <v>2.55</v>
+        <v>1.62</v>
       </c>
       <c r="AE124" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="AF124" t="n">
-        <v>1.54</v>
+        <v>1.3</v>
       </c>
       <c r="AG124" t="n">
-        <v>2.38</v>
+        <v>3.2</v>
       </c>
       <c r="AH124" t="n">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="AI124" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>['90+4']</t>
+          <t>['2', '42', '49', '51', '56', '67']</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
         <is>
-          <t>['89']</t>
+          <t>['15']</t>
         </is>
       </c>
       <c r="AL124" s="3" t="n">
@@ -16874,7 +16874,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16884,25 +16884,25 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -16910,85 +16910,85 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>1.6</v>
+        <v>1.84</v>
       </c>
       <c r="M125" t="n">
-        <v>4.6</v>
+        <v>3.23</v>
       </c>
       <c r="N125" t="n">
-        <v>4</v>
+        <v>3.93</v>
       </c>
       <c r="O125" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="P125" t="n">
-        <v>20</v>
+        <v>6.5</v>
       </c>
       <c r="Q125" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R125" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S125" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T125" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U125" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V125" t="n">
+        <v>9</v>
+      </c>
+      <c r="W125" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X125" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AA125" t="n">
         <v>2.63</v>
       </c>
-      <c r="R125" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S125" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T125" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U125" t="n">
-        <v>2</v>
-      </c>
-      <c r="V125" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="W125" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X125" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y125" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z125" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AA125" t="n">
+      <c r="AB125" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH125" t="n">
         <v>8.5</v>
       </c>
-      <c r="AB125" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC125" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD125" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE125" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF125" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AG125" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH125" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AI125" t="n">
-        <v>1.5</v>
+        <v>1.03</v>
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>['2', '42', '49', '51', '56', '67']</t>
+          <t>['47', '65']</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
         <is>
-          <t>['15']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AL125" s="3" t="n">
@@ -17016,111 +17016,111 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G126" t="n">
+        <v>2</v>
+      </c>
+      <c r="H126" t="n">
+        <v>2</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
         <v>1</v>
       </c>
-      <c r="H126" t="n">
-        <v>0</v>
-      </c>
-      <c r="I126" t="n">
-        <v>0</v>
-      </c>
-      <c r="J126" t="n">
-        <v>0</v>
-      </c>
       <c r="K126" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="M126" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N126" t="n">
+        <v>4</v>
+      </c>
+      <c r="O126" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P126" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="Q126" t="n">
         <v>3.25</v>
       </c>
-      <c r="N126" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O126" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="P126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q126" t="n">
-        <v>3.4</v>
-      </c>
       <c r="R126" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="S126" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="T126" t="n">
-        <v>4.25</v>
+        <v>3.75</v>
       </c>
       <c r="U126" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="V126" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W126" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X126" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Y126" t="n">
         <v>6</v>
       </c>
       <c r="Z126" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AA126" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AB126" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AC126" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AD126" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AE126" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF126" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="AG126" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="AH126" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AI126" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>['76']</t>
+          <t>['53', '83']</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['10', '58']</t>
         </is>
       </c>
       <c r="AL126" s="3" t="n">
@@ -17138,121 +17138,121 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G127" t="n">
+        <v>2</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>2</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L127" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M127" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N127" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O127" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P127" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R127" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="S127" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="T127" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U127" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V127" t="n">
+        <v>11</v>
+      </c>
+      <c r="W127" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X127" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI127" t="n">
         <v>1</v>
       </c>
-      <c r="H127" t="n">
-        <v>3</v>
-      </c>
-      <c r="I127" t="n">
-        <v>0</v>
-      </c>
-      <c r="J127" t="n">
-        <v>1</v>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L127" t="n">
-        <v>7.88</v>
-      </c>
-      <c r="M127" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="N127" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="O127" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P127" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Q127" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="R127" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S127" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T127" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U127" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V127" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W127" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X127" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y127" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z127" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AA127" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AB127" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC127" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD127" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE127" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF127" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG127" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH127" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AI127" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>['77']</t>
+          <t>['7', '17']</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
         <is>
-          <t>['45+2', '57', '71']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AL127" s="3" t="n">
@@ -17280,22 +17280,22 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -17306,80 +17306,80 @@
         </is>
       </c>
       <c r="L128" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M128" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N128" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O128" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P128" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="R128" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S128" t="n">
         <v>2.2</v>
       </c>
-      <c r="M128" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N128" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O128" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="P128" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q128" t="n">
+      <c r="T128" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="U128" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V128" t="n">
+        <v>10</v>
+      </c>
+      <c r="W128" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X128" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF128" t="n">
         <v>2.3</v>
       </c>
-      <c r="R128" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="S128" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="T128" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U128" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V128" t="n">
-        <v>11</v>
-      </c>
-      <c r="W128" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X128" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Y128" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Z128" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA128" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB128" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC128" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD128" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AE128" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AF128" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AG128" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AH128" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AI128" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>['7', '17']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -17402,29 +17402,29 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I129" t="n">
         <v>0</v>
@@ -17438,85 +17438,85 @@
         </is>
       </c>
       <c r="L129" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="M129" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N129" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O129" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="P129" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R129" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S129" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T129" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="U129" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V129" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W129" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X129" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC129" t="n">
         <v>2.15</v>
       </c>
-      <c r="M129" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N129" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O129" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="P129" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Q129" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="R129" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S129" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T129" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="U129" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V129" t="n">
-        <v>10</v>
-      </c>
-      <c r="W129" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X129" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Y129" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="Z129" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA129" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB129" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC129" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AD129" t="n">
-        <v>5.5</v>
+        <v>2.55</v>
       </c>
       <c r="AE129" t="n">
-        <v>1.13</v>
+        <v>1.65</v>
       </c>
       <c r="AF129" t="n">
-        <v>2.3</v>
+        <v>1.54</v>
       </c>
       <c r="AG129" t="n">
-        <v>1.57</v>
+        <v>2.38</v>
       </c>
       <c r="AH129" t="n">
-        <v>10</v>
+        <v>4.6</v>
       </c>
       <c r="AI129" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['89']</t>
         </is>
       </c>
       <c r="AL129" s="3" t="n">
@@ -17544,25 +17544,25 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I130" t="n">
         <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
@@ -17570,85 +17570,85 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="M130" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="N130" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="O130" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="P130" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R130" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="S130" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="T130" t="n">
-        <v>3.75</v>
+        <v>4.25</v>
       </c>
       <c r="U130" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="V130" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="W130" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X130" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Y130" t="n">
         <v>6</v>
       </c>
       <c r="Z130" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AA130" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AB130" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AC130" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AD130" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AE130" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF130" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="AG130" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="AH130" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AI130" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>['53', '83']</t>
+          <t>['76']</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
         <is>
-          <t>['10', '58']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AL130" s="3" t="n">
@@ -17798,7 +17798,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17808,111 +17808,111 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>5</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="n">
         <v>2</v>
       </c>
-      <c r="H132" t="n">
-        <v>0</v>
-      </c>
-      <c r="I132" t="n">
-        <v>0</v>
-      </c>
-      <c r="J132" t="n">
-        <v>0</v>
-      </c>
       <c r="K132" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.4</v>
+        <v>1.96</v>
       </c>
       <c r="M132" t="n">
-        <v>4.23</v>
+        <v>3.53</v>
       </c>
       <c r="N132" t="n">
-        <v>7.6</v>
+        <v>3.06</v>
       </c>
       <c r="O132" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="P132" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Q132" t="n">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="R132" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="S132" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="T132" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="U132" t="n">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="V132" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W132" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X132" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y132" t="n">
-        <v>9.300000000000001</v>
+        <v>13</v>
       </c>
       <c r="Z132" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AA132" t="n">
-        <v>2.55</v>
+        <v>4.25</v>
       </c>
       <c r="AB132" t="n">
-        <v>2.45</v>
+        <v>1.57</v>
       </c>
       <c r="AC132" t="n">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="AD132" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="AE132" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="AF132" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AG132" t="n">
-        <v>1.42</v>
+        <v>2.38</v>
       </c>
       <c r="AH132" t="n">
-        <v>6.5</v>
+        <v>3.9</v>
       </c>
       <c r="AI132" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>['70', '84']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['23', '45', '54', '64', '71']</t>
         </is>
       </c>
       <c r="AL132" s="3" t="n">
@@ -17930,7 +17930,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17940,25 +17940,25 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H133" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I133" t="n">
         <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
@@ -17966,85 +17966,85 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>1.96</v>
+        <v>1.4</v>
       </c>
       <c r="M133" t="n">
-        <v>3.53</v>
+        <v>4.23</v>
       </c>
       <c r="N133" t="n">
-        <v>3.06</v>
+        <v>7.6</v>
       </c>
       <c r="O133" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="P133" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Q133" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="R133" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S133" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T133" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U133" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V133" t="n">
+        <v>7</v>
+      </c>
+      <c r="W133" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X133" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Z133" t="n">
         <v>1.29</v>
       </c>
-      <c r="S133" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T133" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U133" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V133" t="n">
-        <v>5</v>
-      </c>
-      <c r="W133" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X133" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y133" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z133" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AA133" t="n">
-        <v>4.25</v>
+        <v>2.55</v>
       </c>
       <c r="AB133" t="n">
-        <v>1.57</v>
+        <v>2.45</v>
       </c>
       <c r="AC133" t="n">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="AD133" t="n">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="AE133" t="n">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="AF133" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AG133" t="n">
-        <v>2.38</v>
+        <v>1.42</v>
       </c>
       <c r="AH133" t="n">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="AI133" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
+          <t>['70', '84']</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
           <t>[]</t>
-        </is>
-      </c>
-      <c r="AK133" t="inlineStr">
-        <is>
-          <t>['23', '45', '54', '64', '71']</t>
         </is>
       </c>
       <c r="AL133" s="3" t="n">
@@ -18084,17 +18084,17 @@
         <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I134" t="n">
         <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L134" t="n">
@@ -18176,7 +18176,7 @@
       </c>
       <c r="AK134" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['27', '61', '90+4']</t>
         </is>
       </c>
       <c r="AL134" s="3" t="n">
@@ -18590,7 +18590,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18600,12 +18600,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18622,80 +18622,80 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>2.04</v>
+        <v>1.72</v>
       </c>
       <c r="M138" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="N138" t="n">
-        <v>4.04</v>
+        <v>4.4</v>
       </c>
       <c r="O138" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="P138" t="n">
-        <v>6.75</v>
+        <v>8.5</v>
       </c>
       <c r="Q138" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="R138" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="S138" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="T138" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="U138" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="V138" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W138" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X138" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y138" t="n">
-        <v>6.55</v>
+        <v>8.5</v>
       </c>
       <c r="Z138" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AA138" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="AB138" t="n">
-        <v>2.48</v>
+        <v>2.07</v>
       </c>
       <c r="AC138" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AD138" t="n">
-        <v>4.75</v>
+        <v>3.72</v>
       </c>
       <c r="AE138" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AF138" t="n">
-        <v>2.16</v>
+        <v>1.93</v>
       </c>
       <c r="AG138" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH138" t="n">
-        <v>11</v>
+        <v>7.7</v>
       </c>
       <c r="AI138" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
@@ -18722,35 +18722,35 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
         <v>2</v>
       </c>
-      <c r="H139" t="n">
-        <v>1</v>
-      </c>
       <c r="I139" t="n">
         <v>0</v>
       </c>
       <c r="J139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
@@ -18758,85 +18758,85 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="M139" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N139" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="O139" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="P139" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="Q139" t="n">
         <v>2.4</v>
       </c>
       <c r="R139" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="S139" t="n">
-        <v>3.3</v>
+        <v>2.38</v>
       </c>
       <c r="T139" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U139" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V139" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="W139" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X139" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB139" t="n">
         <v>2.25</v>
       </c>
-      <c r="U139" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V139" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="W139" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X139" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y139" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="Z139" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AA139" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB139" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AC139" t="n">
-        <v>2.25</v>
+        <v>1.53</v>
       </c>
       <c r="AD139" t="n">
-        <v>2.45</v>
+        <v>4.7</v>
       </c>
       <c r="AE139" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="AF139" t="n">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="AG139" t="n">
-        <v>2.23</v>
+        <v>1.7</v>
       </c>
       <c r="AH139" t="n">
-        <v>3.58</v>
+        <v>9.1</v>
       </c>
       <c r="AI139" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>['53', '90+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
         <is>
-          <t>['45+3']</t>
+          <t>['23', '41']</t>
         </is>
       </c>
       <c r="AL139" s="3" t="n">
@@ -18854,121 +18854,121 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I140" t="n">
         <v>0</v>
       </c>
       <c r="J140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>3.06</v>
+        <v>2.04</v>
       </c>
       <c r="M140" t="n">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="N140" t="n">
-        <v>2.3</v>
+        <v>4.04</v>
       </c>
       <c r="O140" t="n">
-        <v>2.22</v>
+        <v>1.63</v>
       </c>
       <c r="P140" t="n">
-        <v>7.8</v>
+        <v>6.75</v>
       </c>
       <c r="Q140" t="n">
-        <v>1.86</v>
+        <v>2.8</v>
       </c>
       <c r="R140" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S140" t="n">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="T140" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="U140" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="V140" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="W140" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X140" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y140" t="n">
-        <v>8</v>
+        <v>6.55</v>
       </c>
       <c r="Z140" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AA140" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="AB140" t="n">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="AC140" t="n">
         <v>1.55</v>
       </c>
       <c r="AD140" t="n">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
       <c r="AE140" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF140" t="n">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="AG140" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH140" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI140" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['6']</t>
         </is>
       </c>
       <c r="AL140" s="3" t="n">
@@ -18986,7 +18986,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18996,111 +18996,111 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H141" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I141" t="n">
         <v>0</v>
       </c>
       <c r="J141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>2.14</v>
+        <v>1.44</v>
       </c>
       <c r="M141" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N141" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="O141" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P141" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="Q141" t="n">
         <v>3</v>
       </c>
-      <c r="N141" t="n">
-        <v>4</v>
-      </c>
-      <c r="O141" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="P141" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q141" t="n">
-        <v>2.75</v>
-      </c>
       <c r="R141" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="S141" t="n">
-        <v>2.21</v>
+        <v>3.25</v>
       </c>
       <c r="T141" t="n">
-        <v>3.6</v>
+        <v>2.63</v>
       </c>
       <c r="U141" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="V141" t="n">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="W141" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="X141" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y141" t="n">
-        <v>6.75</v>
+        <v>9.25</v>
       </c>
       <c r="Z141" t="n">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="AA141" t="n">
-        <v>2.45</v>
+        <v>3.55</v>
       </c>
       <c r="AB141" t="n">
-        <v>2.63</v>
+        <v>1.75</v>
       </c>
       <c r="AC141" t="n">
-        <v>1.45</v>
+        <v>1.95</v>
       </c>
       <c r="AD141" t="n">
-        <v>5.56</v>
+        <v>3.44</v>
       </c>
       <c r="AE141" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="AF141" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AG141" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AH141" t="n">
-        <v>11</v>
+        <v>6.95</v>
       </c>
       <c r="AI141" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['52', '79']</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['32', '68']</t>
         </is>
       </c>
       <c r="AL141" s="3" t="n">
@@ -19137,20 +19137,20 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H142" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I142" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L142" t="n">
@@ -19227,12 +19227,12 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['6', '27', '37']</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['67', '73']</t>
         </is>
       </c>
       <c r="AL142" s="3" t="n">
@@ -19250,29 +19250,29 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I143" t="n">
         <v>0</v>
@@ -19282,89 +19282,89 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>1.44</v>
+        <v>3.16</v>
       </c>
       <c r="M143" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="N143" t="n">
-        <v>5.75</v>
+        <v>2.01</v>
       </c>
       <c r="O143" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="P143" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="Q143" t="n">
-        <v>3</v>
+        <v>1.73</v>
       </c>
       <c r="R143" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="S143" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="T143" t="n">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="U143" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="V143" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="W143" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X143" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y143" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z143" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AA143" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB143" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AC143" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="AD143" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AE143" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF143" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AG143" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AH143" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI143" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AL143" s="3" t="n">
@@ -19382,29 +19382,29 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G144" t="n">
         <v>0</v>
       </c>
       <c r="H144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I144" t="n">
         <v>0</v>
@@ -19414,77 +19414,77 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>2.1</v>
+        <v>3.06</v>
       </c>
       <c r="M144" t="n">
-        <v>3.25</v>
+        <v>2.97</v>
       </c>
       <c r="N144" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="O144" t="n">
-        <v>1.8</v>
+        <v>2.22</v>
       </c>
       <c r="P144" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="Q144" t="n">
-        <v>2.4</v>
+        <v>1.86</v>
       </c>
       <c r="R144" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="S144" t="n">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="T144" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="U144" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V144" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W144" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X144" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y144" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z144" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AA144" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="AB144" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC144" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AD144" t="n">
-        <v>4.7</v>
+        <v>4.25</v>
       </c>
       <c r="AE144" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF144" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AG144" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH144" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="AI144" t="n">
         <v>1.05</v>
@@ -19496,7 +19496,7 @@
       </c>
       <c r="AK144" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AL144" s="3" t="n">
@@ -19514,121 +19514,121 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>3.16</v>
+        <v>2.14</v>
       </c>
       <c r="M145" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="N145" t="n">
-        <v>2.01</v>
+        <v>4</v>
       </c>
       <c r="O145" t="n">
-        <v>2.4</v>
+        <v>1.73</v>
       </c>
       <c r="P145" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="Q145" t="n">
-        <v>1.73</v>
+        <v>2.75</v>
       </c>
       <c r="R145" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="S145" t="n">
-        <v>2.5</v>
+        <v>2.21</v>
       </c>
       <c r="T145" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U145" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="V145" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W145" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X145" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y145" t="n">
-        <v>8.5</v>
+        <v>6.75</v>
       </c>
       <c r="Z145" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AA145" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="AB145" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC145" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AD145" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="AE145" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF145" t="n">
         <v>2.2</v>
       </c>
-      <c r="AC145" t="n">
+      <c r="AG145" t="n">
         <v>1.55</v>
       </c>
-      <c r="AD145" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AE145" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF145" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG145" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AH145" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI145" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['26']</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['32']</t>
         </is>
       </c>
       <c r="AL145" s="3" t="n">
@@ -19665,20 +19665,20 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L146" t="n">
@@ -19755,7 +19755,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2', '77']</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
@@ -19778,121 +19778,121 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I147" t="n">
         <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="M147" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="N147" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="O147" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P147" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R147" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S147" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T147" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U147" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V147" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W147" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X147" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB147" t="n">
         <v>1.5</v>
       </c>
-      <c r="P147" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q147" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R147" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S147" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T147" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U147" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V147" t="n">
-        <v>8</v>
-      </c>
-      <c r="W147" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X147" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y147" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z147" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA147" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB147" t="n">
-        <v>2.07</v>
-      </c>
       <c r="AC147" t="n">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="AD147" t="n">
-        <v>3.72</v>
+        <v>2.45</v>
       </c>
       <c r="AE147" t="n">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="AF147" t="n">
-        <v>1.93</v>
+        <v>1.64</v>
       </c>
       <c r="AG147" t="n">
-        <v>1.73</v>
+        <v>2.23</v>
       </c>
       <c r="AH147" t="n">
-        <v>7.7</v>
+        <v>3.58</v>
       </c>
       <c r="AI147" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['53', '90+3']</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+3']</t>
         </is>
       </c>
       <c r="AL147" s="3" t="n">
@@ -19920,16 +19920,16 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -19942,84 +19942,84 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L148" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M148" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N148" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="O148" t="n">
         <v>1.5</v>
       </c>
-      <c r="M148" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N148" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="O148" t="n">
-        <v>1.55</v>
-      </c>
       <c r="P148" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="Q148" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="R148" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="S148" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="T148" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="U148" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="V148" t="n">
-        <v>8.9</v>
+        <v>10</v>
       </c>
       <c r="W148" t="n">
         <v>1.03</v>
       </c>
       <c r="X148" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y148" t="n">
-        <v>7</v>
+        <v>6.15</v>
       </c>
       <c r="Z148" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AA148" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="AB148" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="AC148" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AD148" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="AE148" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AF148" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AG148" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="AH148" t="n">
-        <v>8.5</v>
+        <v>12</v>
       </c>
       <c r="AI148" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['56', '79']</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -20052,111 +20052,111 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I149" t="n">
         <v>0</v>
       </c>
       <c r="J149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="M149" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N149" t="n">
-        <v>6.78</v>
+        <v>5.75</v>
       </c>
       <c r="O149" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="P149" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="Q149" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="R149" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="S149" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="T149" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="U149" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="V149" t="n">
-        <v>10</v>
+        <v>8.9</v>
       </c>
       <c r="W149" t="n">
         <v>1.03</v>
       </c>
       <c r="X149" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y149" t="n">
-        <v>6.15</v>
+        <v>7</v>
       </c>
       <c r="Z149" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AA149" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB149" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC149" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD149" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE149" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF149" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG149" t="n">
         <v>1.55</v>
       </c>
-      <c r="AA149" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB149" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC149" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD149" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AE149" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF149" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AG149" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AH149" t="n">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="AI149" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['74']</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['16']</t>
         </is>
       </c>
       <c r="AL149" s="3" t="n">
@@ -20193,20 +20193,20 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L150" t="n">
@@ -20283,12 +20283,12 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+4', '85']</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['48']</t>
         </is>
       </c>
       <c r="AL150" s="3" t="n">
@@ -20306,7 +20306,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -20316,12 +20316,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -20338,80 +20338,80 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="M151" t="n">
-        <v>2.79</v>
+        <v>3.6</v>
       </c>
       <c r="N151" t="n">
-        <v>2.69</v>
+        <v>4.2</v>
       </c>
       <c r="O151" t="n">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="P151" t="n">
-        <v>5</v>
+        <v>9.75</v>
       </c>
       <c r="Q151" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="R151" t="n">
-        <v>1.7</v>
+        <v>1.34</v>
       </c>
       <c r="S151" t="n">
-        <v>2.05</v>
+        <v>2.95</v>
       </c>
       <c r="T151" t="n">
-        <v>4</v>
+        <v>2.48</v>
       </c>
       <c r="U151" t="n">
-        <v>1.14</v>
+        <v>1.45</v>
       </c>
       <c r="V151" t="n">
-        <v>11</v>
+        <v>6.25</v>
       </c>
       <c r="W151" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="X151" t="n">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="Y151" t="n">
-        <v>5.45</v>
+        <v>12</v>
       </c>
       <c r="Z151" t="n">
-        <v>1.7</v>
+        <v>1.22</v>
       </c>
       <c r="AA151" t="n">
-        <v>2.1</v>
+        <v>3.88</v>
       </c>
       <c r="AB151" t="n">
-        <v>3.05</v>
+        <v>1.75</v>
       </c>
       <c r="AC151" t="n">
-        <v>1.33</v>
+        <v>2.03</v>
       </c>
       <c r="AD151" t="n">
-        <v>7.3</v>
+        <v>2.9</v>
       </c>
       <c r="AE151" t="n">
-        <v>1.03</v>
+        <v>1.42</v>
       </c>
       <c r="AF151" t="n">
-        <v>2.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG151" t="n">
-        <v>1.48</v>
+        <v>2.2</v>
       </c>
       <c r="AH151" t="n">
-        <v>13</v>
+        <v>4.75</v>
       </c>
       <c r="AI151" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
@@ -20438,7 +20438,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -20448,103 +20448,103 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G152" t="n">
         <v>0</v>
       </c>
       <c r="H152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I152" t="n">
         <v>0</v>
       </c>
       <c r="J152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="M152" t="n">
-        <v>3.6</v>
+        <v>2.79</v>
       </c>
       <c r="N152" t="n">
-        <v>4.2</v>
+        <v>2.69</v>
       </c>
       <c r="O152" t="n">
-        <v>1.5</v>
+        <v>2.15</v>
       </c>
       <c r="P152" t="n">
-        <v>9.75</v>
+        <v>5</v>
       </c>
       <c r="Q152" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="R152" t="n">
-        <v>1.34</v>
+        <v>1.7</v>
       </c>
       <c r="S152" t="n">
-        <v>2.95</v>
+        <v>2.05</v>
       </c>
       <c r="T152" t="n">
-        <v>2.48</v>
+        <v>4</v>
       </c>
       <c r="U152" t="n">
-        <v>1.45</v>
+        <v>1.14</v>
       </c>
       <c r="V152" t="n">
-        <v>6.25</v>
+        <v>11</v>
       </c>
       <c r="W152" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="X152" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="Z152" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA152" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB152" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AC152" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD152" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AE152" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF152" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AG152" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AH152" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI152" t="n">
         <v>1.02</v>
       </c>
-      <c r="Y152" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z152" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA152" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AB152" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC152" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AD152" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE152" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF152" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG152" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH152" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AI152" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AJ152" t="inlineStr">
         <is>
           <t>[]</t>
@@ -20552,7 +20552,7 @@
       </c>
       <c r="AK152" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['26']</t>
         </is>
       </c>
       <c r="AL152" s="3" t="n">
@@ -20627,7 +20627,7 @@
         <v>1.65</v>
       </c>
       <c r="S153" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="T153" t="n">
         <v>4</v>
@@ -20651,22 +20651,22 @@
         <v>1.63</v>
       </c>
       <c r="AA153" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AB153" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="AC153" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AD153" t="n">
-        <v>6.06</v>
+        <v>6.1</v>
       </c>
       <c r="AE153" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF153" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="AG153" t="n">
         <v>1.38</v>
@@ -20675,7 +20675,7 @@
         <v>11.5</v>
       </c>
       <c r="AI153" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
@@ -20702,7 +20702,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20712,12 +20712,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20738,76 +20738,76 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>4.75</v>
+        <v>1.5</v>
       </c>
       <c r="M154" t="n">
-        <v>3.24</v>
+        <v>3.75</v>
       </c>
       <c r="N154" t="n">
-        <v>1.85</v>
+        <v>7.2</v>
       </c>
       <c r="O154" t="n">
-        <v>2.63</v>
+        <v>1.5</v>
       </c>
       <c r="P154" t="n">
-        <v>6.5</v>
+        <v>7.25</v>
       </c>
       <c r="Q154" t="n">
-        <v>1.67</v>
+        <v>3.1</v>
       </c>
       <c r="R154" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="S154" t="n">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="T154" t="n">
-        <v>3.42</v>
+        <v>3</v>
       </c>
       <c r="U154" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="V154" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W154" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X154" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y154" t="n">
         <v>8</v>
       </c>
-      <c r="W154" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X154" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y154" t="n">
-        <v>6.85</v>
-      </c>
       <c r="Z154" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AA154" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AB154" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="AC154" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AD154" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="AE154" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF154" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AG154" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AH154" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="AI154" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20844,12 +20844,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20870,76 +20870,76 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="M155" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N155" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="O155" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="P155" t="n">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="Q155" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="R155" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S155" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="T155" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U155" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V155" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W155" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X155" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y155" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="Z155" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AA155" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AB155" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AC155" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AD155" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AE155" t="n">
         <v>1.25</v>
       </c>
       <c r="AF155" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AG155" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AH155" t="n">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="AI155" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
@@ -20966,7 +20966,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -20976,12 +20976,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -21002,76 +21002,76 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="M156" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="N156" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="O156" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="P156" t="n">
-        <v>7.25</v>
+        <v>7</v>
       </c>
       <c r="Q156" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R156" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S156" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T156" t="n">
         <v>3.1</v>
       </c>
-      <c r="R156" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S156" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T156" t="n">
-        <v>3</v>
-      </c>
       <c r="U156" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="V156" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="W156" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X156" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y156" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="Z156" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AA156" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AB156" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC156" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AD156" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AE156" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AF156" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AG156" t="n">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="AH156" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="AI156" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
@@ -21098,7 +21098,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -21108,12 +21108,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -21134,76 +21134,76 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="M157" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="N157" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="O157" t="n">
-        <v>1.8</v>
+        <v>2.63</v>
       </c>
       <c r="P157" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q157" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="R157" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="S157" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="T157" t="n">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="U157" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="V157" t="n">
-        <v>8</v>
+        <v>9.1</v>
       </c>
       <c r="W157" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="X157" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y157" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="Z157" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA157" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB157" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AC157" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AD157" t="n">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="AE157" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF157" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AG157" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AH157" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AI157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
@@ -21240,12 +21240,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -21266,76 +21266,76 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>1.74</v>
+        <v>2.3</v>
       </c>
       <c r="M158" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="N158" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="O158" t="n">
-        <v>1.48</v>
+        <v>1.83</v>
       </c>
       <c r="P158" t="n">
-        <v>6.2</v>
+        <v>6.45</v>
       </c>
       <c r="Q158" t="n">
-        <v>3.58</v>
+        <v>2.38</v>
       </c>
       <c r="R158" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="S158" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="T158" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="U158" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V158" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W158" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X158" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Y158" t="n">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
       <c r="Z158" t="n">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="AA158" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AB158" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="AC158" t="n">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="AD158" t="n">
-        <v>6.35</v>
+        <v>4.33</v>
       </c>
       <c r="AE158" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF158" t="n">
-        <v>2.5</v>
+        <v>2.02</v>
       </c>
       <c r="AG158" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AH158" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AI158" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
@@ -21401,10 +21401,10 @@
         <v>1.33</v>
       </c>
       <c r="M159" t="n">
-        <v>5</v>
+        <v>5.37</v>
       </c>
       <c r="N159" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O159" t="n">
         <v>1.4</v>
@@ -21416,58 +21416,58 @@
         <v>3.2</v>
       </c>
       <c r="R159" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="S159" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T159" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="U159" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="V159" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="W159" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X159" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y159" t="n">
-        <v>11</v>
+        <v>12.9</v>
       </c>
       <c r="Z159" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AA159" t="n">
         <v>3.7</v>
       </c>
       <c r="AB159" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AC159" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AD159" t="n">
-        <v>2.52</v>
+        <v>2.35</v>
       </c>
       <c r="AE159" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AF159" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AG159" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH159" t="n">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="AI159" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
@@ -21530,13 +21530,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="M160" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="N160" t="n">
-        <v>6.58</v>
+        <v>6.8</v>
       </c>
       <c r="O160" t="n">
         <v>1.44</v>
@@ -21548,58 +21548,58 @@
         <v>2.75</v>
       </c>
       <c r="R160" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="S160" t="n">
-        <v>3.28</v>
+        <v>2.93</v>
       </c>
       <c r="T160" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="U160" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="V160" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="W160" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X160" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y160" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z160" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AA160" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AB160" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AC160" t="n">
-        <v>2.23</v>
+        <v>2.08</v>
       </c>
       <c r="AD160" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="AE160" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AF160" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AG160" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AH160" t="n">
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
       <c r="AI160" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
@@ -21636,12 +21636,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21662,76 +21662,76 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>2.36</v>
+        <v>1.68</v>
       </c>
       <c r="M161" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="N161" t="n">
-        <v>3.15</v>
+        <v>5.5</v>
       </c>
       <c r="O161" t="n">
-        <v>1.83</v>
+        <v>1.48</v>
       </c>
       <c r="P161" t="n">
-        <v>6.45</v>
+        <v>6.2</v>
       </c>
       <c r="Q161" t="n">
-        <v>2.38</v>
+        <v>3.58</v>
       </c>
       <c r="R161" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S161" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="T161" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U161" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="V161" t="n">
-        <v>8.5</v>
+        <v>12</v>
       </c>
       <c r="W161" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X161" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y161" t="n">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
       <c r="Z161" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AA161" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB161" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD161" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AE161" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF161" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AG161" t="n">
         <v>1.46</v>
       </c>
-      <c r="AA161" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB161" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC161" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD161" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AE161" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF161" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG161" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AH161" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AI161" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>4.4</v>
       </c>
       <c r="M162" t="n">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="N162" t="n">
         <v>1.98</v>
@@ -21824,40 +21824,40 @@
         <v>1.28</v>
       </c>
       <c r="V162" t="n">
-        <v>8.5</v>
+        <v>9.4</v>
       </c>
       <c r="W162" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X162" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y162" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="Z162" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AA162" t="n">
         <v>2.6</v>
       </c>
       <c r="AB162" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AC162" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AD162" t="n">
-        <v>4.75</v>
+        <v>4.88</v>
       </c>
       <c r="AE162" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF162" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG162" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AH162" t="n">
         <v>9.300000000000001</v>
@@ -21926,13 +21926,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="M163" t="n">
-        <v>3.9</v>
+        <v>4.41</v>
       </c>
       <c r="N163" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="O163" t="n">
         <v>1.73</v>
@@ -21950,16 +21950,16 @@
         <v>3.6</v>
       </c>
       <c r="T163" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="U163" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="V163" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="W163" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="X163" t="n">
         <v>0</v>
@@ -21977,16 +21977,16 @@
         <v>1.28</v>
       </c>
       <c r="AC163" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AD163" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AE163" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AF163" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AG163" t="n">
         <v>3.25</v>
@@ -21995,7 +21995,7 @@
         <v>2.45</v>
       </c>
       <c r="AI163" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
@@ -22058,13 +22058,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="M164" t="n">
-        <v>2.85</v>
+        <v>2.94</v>
       </c>
       <c r="N164" t="n">
-        <v>4.14</v>
+        <v>3.52</v>
       </c>
       <c r="O164" t="n">
         <v>1.83</v>
@@ -22082,7 +22082,7 @@
         <v>2.05</v>
       </c>
       <c r="T164" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="U164" t="n">
         <v>1.18</v>
@@ -22091,28 +22091,28 @@
         <v>11</v>
       </c>
       <c r="W164" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X164" t="n">
         <v>1.15</v>
       </c>
       <c r="Y164" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="Z164" t="n">
         <v>1.7</v>
       </c>
       <c r="AA164" t="n">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="AB164" t="n">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="AC164" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AD164" t="n">
-        <v>7.4</v>
+        <v>6.25</v>
       </c>
       <c r="AE164" t="n">
         <v>1.1</v>
@@ -22190,13 +22190,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="M165" t="n">
-        <v>3.18</v>
+        <v>3.03</v>
       </c>
       <c r="N165" t="n">
-        <v>3.92</v>
+        <v>3.85</v>
       </c>
       <c r="O165" t="n">
         <v>1.67</v>
@@ -22208,7 +22208,7 @@
         <v>2.75</v>
       </c>
       <c r="R165" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="S165" t="n">
         <v>2.35</v>
@@ -22223,7 +22223,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="W165" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X165" t="n">
         <v>1.11</v>
@@ -22232,28 +22232,28 @@
         <v>6.25</v>
       </c>
       <c r="Z165" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AA165" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AB165" t="n">
-        <v>2.66</v>
+        <v>2.38</v>
       </c>
       <c r="AC165" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AD165" t="n">
         <v>4.75</v>
       </c>
       <c r="AE165" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF165" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AG165" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AH165" t="n">
         <v>13</v>
@@ -22322,13 +22322,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="M166" t="n">
-        <v>3.55</v>
+        <v>3.17</v>
       </c>
       <c r="N166" t="n">
-        <v>3.45</v>
+        <v>3.03</v>
       </c>
       <c r="O166" t="n">
         <v>1.8</v>
@@ -22355,13 +22355,13 @@
         <v>5.5</v>
       </c>
       <c r="W166" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X166" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y166" t="n">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="Z166" t="n">
         <v>1.25</v>
@@ -22370,28 +22370,28 @@
         <v>3.7</v>
       </c>
       <c r="AB166" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC166" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AD166" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AE166" t="n">
         <v>1.4</v>
       </c>
       <c r="AF166" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG166" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH166" t="n">
-        <v>4.33</v>
+        <v>4.7</v>
       </c>
       <c r="AI166" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
@@ -22457,10 +22457,10 @@
         <v>2.6</v>
       </c>
       <c r="M167" t="n">
-        <v>3.68</v>
+        <v>3.85</v>
       </c>
       <c r="N167" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="O167" t="n">
         <v>1.83</v>
@@ -22478,13 +22478,13 @@
         <v>3.3</v>
       </c>
       <c r="T167" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="U167" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="V167" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="W167" t="n">
         <v>1.15</v>
@@ -22505,7 +22505,7 @@
         <v>1.55</v>
       </c>
       <c r="AC167" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD167" t="n">
         <v>2.35</v>
@@ -22514,7 +22514,7 @@
         <v>1.55</v>
       </c>
       <c r="AF167" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AG167" t="n">
         <v>2.5</v>
@@ -22523,7 +22523,7 @@
         <v>3.8</v>
       </c>
       <c r="AI167" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
@@ -22634,16 +22634,16 @@
         <v>4.8</v>
       </c>
       <c r="AB168" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AC168" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AD168" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AE168" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AF168" t="n">
         <v>1.4</v>
@@ -22652,7 +22652,7 @@
         <v>2.6</v>
       </c>
       <c r="AH168" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AI168" t="n">
         <v>1.25</v>
